--- a/artfynd/S 152-2026 artfynd.xlsx
+++ b/artfynd/S 152-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ194"/>
+  <dimension ref="A1:AZ195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15952,32 +15952,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>136346607</v>
+        <v>136631248</v>
       </c>
       <c r="B140" t="n">
-        <v>58162</v>
+        <v>58167</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15995,10 +15995,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>686529</v>
+        <v>686469</v>
       </c>
       <c r="R140" t="n">
-        <v>6563051</v>
+        <v>6563013</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16025,12 +16025,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16056,13 +16056,13 @@
       <c r="AY140" t="inlineStr"/>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136346607</t>
+          <t>https://artportalen.se/Sighting/136631248</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>136346721</v>
+        <v>136346607</v>
       </c>
       <c r="B141" t="n">
         <v>58162</v>
@@ -16105,10 +16105,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>686678</v>
+        <v>686529</v>
       </c>
       <c r="R141" t="n">
-        <v>6563074</v>
+        <v>6563051</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16166,13 +16166,13 @@
       <c r="AY141" t="inlineStr"/>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136346721</t>
+          <t>https://artportalen.se/Sighting/136346607</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>136422024</v>
+        <v>136346721</v>
       </c>
       <c r="B142" t="n">
         <v>58162</v>
@@ -16215,10 +16215,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>686531</v>
+        <v>686678</v>
       </c>
       <c r="R142" t="n">
-        <v>6563059</v>
+        <v>6563074</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16245,12 +16245,12 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16276,13 +16276,13 @@
       <c r="AY142" t="inlineStr"/>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136422024</t>
+          <t>https://artportalen.se/Sighting/136346721</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>136557077</v>
+        <v>136422024</v>
       </c>
       <c r="B143" t="n">
         <v>58162</v>
@@ -16325,10 +16325,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>686733</v>
+        <v>686531</v>
       </c>
       <c r="R143" t="n">
-        <v>6563216</v>
+        <v>6563059</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16355,12 +16355,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16386,16 +16386,16 @@
       <c r="AY143" t="inlineStr"/>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136557077</t>
+          <t>https://artportalen.se/Sighting/136422024</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>136259916</v>
+        <v>136557077</v>
       </c>
       <c r="B144" t="n">
-        <v>8463</v>
+        <v>58162</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16403,30 +16403,29 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>106545</v>
+        <v>103023</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr"/>
       <c r="M144" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N144" t="inlineStr"/>
@@ -16436,10 +16435,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>686457</v>
+        <v>686733</v>
       </c>
       <c r="R144" t="n">
-        <v>6563062</v>
+        <v>6563216</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16466,12 +16465,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16480,7 +16479,6 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
-      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
@@ -16498,13 +16496,13 @@
       <c r="AY144" t="inlineStr"/>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136259916</t>
+          <t>https://artportalen.se/Sighting/136557077</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>136330063</v>
+        <v>136259916</v>
       </c>
       <c r="B145" t="n">
         <v>8463</v>
@@ -16548,10 +16546,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>686661</v>
+        <v>686457</v>
       </c>
       <c r="R145" t="n">
-        <v>6563103</v>
+        <v>6563062</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16578,12 +16576,12 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16610,55 +16608,60 @@
       <c r="AY145" t="inlineStr"/>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136330063</t>
+          <t>https://artportalen.se/Sighting/136259916</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>109890506</v>
+        <v>136330063</v>
       </c>
       <c r="B146" t="n">
-        <v>99118</v>
+        <v>8463</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Ö Norrby Mosse, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>686831</v>
+        <v>686661</v>
       </c>
       <c r="R146" t="n">
-        <v>6563216</v>
+        <v>6563103</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16685,12 +16688,12 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16717,13 +16720,13 @@
       <c r="AY146" t="inlineStr"/>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109890506</t>
+          <t>https://artportalen.se/Sighting/136330063</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>122781008</v>
+        <v>109890506</v>
       </c>
       <c r="B147" t="n">
         <v>99118</v>
@@ -16758,14 +16761,14 @@
       <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Knärot, Srm</t>
+          <t>Ö Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>686833</v>
+        <v>686831</v>
       </c>
       <c r="R147" t="n">
-        <v>6563215</v>
+        <v>6563216</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16792,17 +16795,12 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC147" t="inlineStr">
-        <is>
-          <t>Knärot</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16818,24 +16816,24 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122781008</t>
+          <t>https://artportalen.se/Sighting/109890506</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126418709</v>
+        <v>122781008</v>
       </c>
       <c r="B148" t="n">
         <v>99118</v>
@@ -16863,29 +16861,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr"/>
       <c r="L148" t="inlineStr"/>
       <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Knärot, Srm</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>686771</v>
+        <v>686833</v>
       </c>
       <c r="R148" t="n">
-        <v>6563297</v>
+        <v>6563215</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16912,17 +16902,17 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>Två av dem i knopp, ca 3 m väster om de andra.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16938,24 +16928,24 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126418709</t>
+          <t>https://artportalen.se/Sighting/122781008</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126418756</v>
+        <v>126418709</v>
       </c>
       <c r="B149" t="n">
         <v>99118</v>
@@ -16985,7 +16975,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -17002,10 +16992,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>686781</v>
+        <v>686771</v>
       </c>
       <c r="R149" t="n">
-        <v>6563292</v>
+        <v>6563297</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17042,7 +17032,7 @@
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>En av dem i knopp.</t>
+          <t>Två av dem i knopp, ca 3 m väster om de andra.</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17069,13 +17059,13 @@
       <c r="AY149" t="inlineStr"/>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126418756</t>
+          <t>https://artportalen.se/Sighting/126418709</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129564285</v>
+        <v>126418756</v>
       </c>
       <c r="B150" t="n">
         <v>99118</v>
@@ -17103,8 +17093,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr"/>
       <c r="N150" t="inlineStr"/>
@@ -17114,10 +17112,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>686625</v>
+        <v>686781</v>
       </c>
       <c r="R150" t="n">
-        <v>6563000</v>
+        <v>6563292</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17144,12 +17142,17 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>En av dem i knopp.</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17176,63 +17179,55 @@
       <c r="AY150" t="inlineStr"/>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129564285</t>
+          <t>https://artportalen.se/Sighting/126418756</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126234373</v>
+        <v>129564285</v>
       </c>
       <c r="B151" t="n">
-        <v>106244</v>
+        <v>99118</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr"/>
       <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Norrby mosse SO, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>686756</v>
+        <v>686625</v>
       </c>
       <c r="R151" t="n">
-        <v>6563092</v>
+        <v>6563000</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17259,12 +17254,12 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17280,27 +17275,27 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126234373</t>
+          <t>https://artportalen.se/Sighting/129564285</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>122929342</v>
+        <v>126234373</v>
       </c>
       <c r="B152" t="n">
-        <v>97986</v>
+        <v>106244</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17308,41 +17303,49 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>221946</v>
+        <v>221144</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr"/>
       <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>Norrby mosse SO, Srm</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>686569</v>
+        <v>686756</v>
       </c>
       <c r="R152" t="n">
-        <v>6562949</v>
+        <v>6563092</v>
       </c>
       <c r="S152" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -17366,22 +17369,12 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="Z152" t="inlineStr">
-        <is>
-          <t>10:52</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="AB152" t="inlineStr">
-        <is>
-          <t>10:52</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17390,33 +17383,34 @@
       <c r="AE152" t="b">
         <v>0</v>
       </c>
+      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122929342</t>
+          <t>https://artportalen.se/Sighting/126234373</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>134487656</v>
+        <v>122929342</v>
       </c>
       <c r="B153" t="n">
-        <v>99217</v>
+        <v>97986</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17424,45 +17418,41 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>221952</v>
+        <v>221946</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr"/>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr"/>
       <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>686835</v>
+        <v>686569</v>
       </c>
       <c r="R153" t="n">
-        <v>6563212</v>
+        <v>6562949</v>
       </c>
       <c r="S153" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -17486,17 +17476,22 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>2 i blom samt några plantor med endast blad.</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17505,72 +17500,76 @@
       <c r="AE153" t="b">
         <v>0</v>
       </c>
-      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
       </c>
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134487656</t>
+          <t>https://artportalen.se/Sighting/122929342</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>118843519</v>
+        <v>134487656</v>
       </c>
       <c r="B154" t="n">
-        <v>91431</v>
+        <v>99217</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6039941</v>
+        <v>221952</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Gelatinfingersvamp</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Ramaria primulina</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr"/>
       <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Norrby Mosse, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>686668</v>
+        <v>686835</v>
       </c>
       <c r="R154" t="n">
-        <v>6563218</v>
+        <v>6563212</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17597,17 +17596,17 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>Kollekt BR55. Dublett av tidigare fynd för att rapportera resultat av sekvensering. Ursprungligt fynd rapporterat av Bodil Ravn och finns här https://www.artportalen.se/Sighting/112337794</t>
+          <t>2 i blom samt några plantor med endast blad.</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17623,78 +17622,65 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY154" t="inlineStr">
-        <is>
-          <t>Fynd med DNA-sekvens - extern</t>
-        </is>
-      </c>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr"/>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118843519</t>
+          <t>https://artportalen.se/Sighting/134487656</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>122203249</v>
+        <v>118843519</v>
       </c>
       <c r="B155" t="n">
-        <v>96554</v>
+        <v>91431</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>210</v>
+        <v>6039941</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Gelatinfingersvamp</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Ramaria primulina</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr"/>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
-      <c r="L155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
       <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Ö Norrbytorp, Srm</t>
+          <t>Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>687968</v>
+        <v>686668</v>
       </c>
       <c r="R155" t="n">
-        <v>6562733</v>
+        <v>6563218</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17721,17 +17707,17 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>På murken granlåga i äldre skog.</t>
+          <t>Kollekt BR55. Dublett av tidigare fynd för att rapportera resultat av sekvensering. Ursprungligt fynd rapporterat av Bodil Ravn och finns här https://www.artportalen.se/Sighting/112337794</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17747,24 +17733,28 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
-        </is>
-      </c>
-      <c r="AY155" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr">
+        <is>
+          <t>Fynd med DNA-sekvens - extern</t>
+        </is>
+      </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122203249</t>
+          <t>https://artportalen.se/Sighting/118843519</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>122780924</v>
+        <v>122203249</v>
       </c>
       <c r="B156" t="n">
         <v>96554</v>
@@ -17792,21 +17782,29 @@
           <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
-      <c r="I156" t="inlineStr"/>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
       <c r="J156" t="inlineStr"/>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr"/>
       <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Grön sköldmossa, Srm</t>
+          <t>Ö Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>687970</v>
+        <v>687968</v>
       </c>
       <c r="R156" t="n">
-        <v>6562732</v>
+        <v>6562733</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17833,17 +17831,17 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>Grön sköldmossa på rutten stam</t>
+          <t>På murken granlåga i äldre skog.</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17859,65 +17857,66 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122780924</t>
+          <t>https://artportalen.se/Sighting/122203249</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129624531</v>
+        <v>122780924</v>
       </c>
       <c r="B157" t="n">
-        <v>90946</v>
+        <v>96554</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>889</v>
+        <v>210</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vintertagging</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Plicatura pendula</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Grön sköldmossa, Srm</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>687931</v>
+        <v>687970</v>
       </c>
       <c r="R157" t="n">
-        <v>6562811</v>
+        <v>6562732</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17944,12 +17943,17 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa på rutten stam</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17965,24 +17969,24 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129624531</t>
+          <t>https://artportalen.se/Sighting/122780924</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129624696</v>
+        <v>129624531</v>
       </c>
       <c r="B158" t="n">
         <v>90946</v>
@@ -18020,10 +18024,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>687973</v>
+        <v>687931</v>
       </c>
       <c r="R158" t="n">
-        <v>6562815</v>
+        <v>6562811</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18058,11 +18062,6 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>På död tall.</t>
-        </is>
-      </c>
       <c r="AD158" t="b">
         <v>0</v>
       </c>
@@ -18087,16 +18086,16 @@
       <c r="AY158" t="inlineStr"/>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129624696</t>
+          <t>https://artportalen.se/Sighting/129624531</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>122203275</v>
+        <v>129624696</v>
       </c>
       <c r="B159" t="n">
-        <v>91909</v>
+        <v>90946</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18104,21 +18103,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1202</v>
+        <v>889</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Plicatura pendula</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -18127,14 +18126,14 @@
       <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Ö Norrbytorp, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>687981</v>
+        <v>687973</v>
       </c>
       <c r="R159" t="n">
-        <v>6562724</v>
+        <v>6562815</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18161,12 +18160,17 @@
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>På död tall.</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -18193,58 +18197,54 @@
       <c r="AY159" t="inlineStr"/>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122203275</t>
+          <t>https://artportalen.se/Sighting/129624696</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>135358856</v>
+        <v>122203275</v>
       </c>
       <c r="B160" t="n">
-        <v>91573</v>
+        <v>91909</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>2051</v>
+        <v>1202</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr"/>
       <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Ö Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>688004</v>
+        <v>687981</v>
       </c>
       <c r="R160" t="n">
-        <v>6562799</v>
+        <v>6562724</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18271,12 +18271,12 @@
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -18303,58 +18303,61 @@
       <c r="AY160" t="inlineStr"/>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358856</t>
+          <t>https://artportalen.se/Sighting/122203275</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>136241603</v>
+        <v>135358856</v>
       </c>
       <c r="B161" t="n">
-        <v>96927</v>
+        <v>91573</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>2180</v>
+        <v>2051</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr"/>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr"/>
-      <c r="L161" t="inlineStr"/>
       <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Norrbytorp, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>688059</v>
+        <v>688004</v>
       </c>
       <c r="R161" t="n">
-        <v>6562773</v>
+        <v>6562799</v>
       </c>
       <c r="S161" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -18378,22 +18381,12 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="Z161" t="inlineStr">
-        <is>
-          <t>13:09</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="AB161" t="inlineStr">
-        <is>
-          <t>13:09</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18409,27 +18402,27 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Björn Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Björn Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136241603</t>
+          <t>https://artportalen.se/Sighting/135358856</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>136231090</v>
+        <v>136241603</v>
       </c>
       <c r="B162" t="n">
-        <v>96645</v>
+        <v>96927</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18437,37 +18430,41 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>2671</v>
+        <v>2180</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Norrby torp, Norrby torp, Srm</t>
+          <t>Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>688046</v>
+        <v>688059</v>
       </c>
       <c r="R162" t="n">
-        <v>6562700</v>
+        <v>6562773</v>
       </c>
       <c r="S162" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -18494,44 +18491,55 @@
           <t>2026-08-30</t>
         </is>
       </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
       <c r="AD162" t="b">
         <v>0</v>
       </c>
       <c r="AE162" t="b">
         <v>0</v>
       </c>
+      <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="b">
         <v>0</v>
       </c>
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Björn Persson</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Björn Persson</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136231090</t>
+          <t>https://artportalen.se/Sighting/136241603</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128314411</v>
+        <v>136231090</v>
       </c>
       <c r="B163" t="n">
-        <v>92348</v>
+        <v>96645</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18539,45 +18547,34 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>5420</v>
+        <v>2671</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K163" t="inlineStr"/>
-      <c r="N163" t="inlineStr"/>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrby torp, Norrby torp, Srm</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>688088</v>
+        <v>688046</v>
       </c>
       <c r="R163" t="n">
-        <v>6562722</v>
+        <v>6562700</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18604,12 +18601,12 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18618,34 +18615,33 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
-      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128314411</t>
+          <t>https://artportalen.se/Sighting/136231090</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>136394237</v>
+        <v>128314411</v>
       </c>
       <c r="B164" t="n">
-        <v>92513</v>
+        <v>92348</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18670,20 +18666,31 @@
           <t>(Fr.) Pat.</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr"/>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Norrbytorp, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>688093</v>
+        <v>688088</v>
       </c>
       <c r="R164" t="n">
-        <v>6562720</v>
+        <v>6562722</v>
       </c>
       <c r="S164" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -18707,22 +18714,12 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="Z164" t="inlineStr">
-        <is>
-          <t>12:05</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="AB164" t="inlineStr">
-        <is>
-          <t>12:05</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -18731,33 +18728,34 @@
       <c r="AE164" t="b">
         <v>0</v>
       </c>
+      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
       </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136394237</t>
+          <t>https://artportalen.se/Sighting/128314411</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>136268106</v>
+        <v>136394237</v>
       </c>
       <c r="B165" t="n">
-        <v>92065</v>
+        <v>92513</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18765,40 +18763,37 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>5447</v>
+        <v>5420</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>687910</v>
+        <v>688093</v>
       </c>
       <c r="R165" t="n">
-        <v>6562787</v>
+        <v>6562720</v>
       </c>
       <c r="S165" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -18825,14 +18820,19 @@
           <t>2026-08-30</t>
         </is>
       </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="AC165" t="inlineStr">
-        <is>
-          <t>På rätt klen, senvuxen?, lutande granlåga i ett kärr.</t>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18841,56 +18841,55 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
-      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136268106</t>
+          <t>https://artportalen.se/Sighting/136394237</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128314833</v>
+        <v>136268106</v>
       </c>
       <c r="B166" t="n">
-        <v>93235</v>
+        <v>92065</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -18903,10 +18902,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>688073</v>
+        <v>687910</v>
       </c>
       <c r="R166" t="n">
-        <v>6562768</v>
+        <v>6562787</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18933,12 +18932,17 @@
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>På rätt klen, senvuxen?, lutande granlåga i ett kärr.</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18965,13 +18969,13 @@
       <c r="AY166" t="inlineStr"/>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128314833</t>
+          <t>https://artportalen.se/Sighting/136268106</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128317789</v>
+        <v>128314833</v>
       </c>
       <c r="B167" t="n">
         <v>93235</v>
@@ -19009,10 +19013,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>688094</v>
+        <v>688073</v>
       </c>
       <c r="R167" t="n">
-        <v>6562777</v>
+        <v>6562768</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19071,13 +19075,13 @@
       <c r="AY167" t="inlineStr"/>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128317789</t>
+          <t>https://artportalen.se/Sighting/128314833</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128526064</v>
+        <v>128317789</v>
       </c>
       <c r="B168" t="n">
         <v>93235</v>
@@ -19115,10 +19119,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>687952</v>
+        <v>688094</v>
       </c>
       <c r="R168" t="n">
-        <v>6562790</v>
+        <v>6562777</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19145,12 +19149,12 @@
       </c>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -19177,13 +19181,13 @@
       <c r="AY168" t="inlineStr"/>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128526064</t>
+          <t>https://artportalen.se/Sighting/128317789</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128646583</v>
+        <v>128526064</v>
       </c>
       <c r="B169" t="n">
         <v>93235</v>
@@ -19221,10 +19225,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>688067</v>
+        <v>687952</v>
       </c>
       <c r="R169" t="n">
-        <v>6562731</v>
+        <v>6562790</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19251,12 +19255,12 @@
       </c>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -19283,16 +19287,16 @@
       <c r="AY169" t="inlineStr"/>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128646583</t>
+          <t>https://artportalen.se/Sighting/128526064</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>136241765</v>
+        <v>128646583</v>
       </c>
       <c r="B170" t="n">
-        <v>80093</v>
+        <v>93235</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19300,44 +19304,40 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K170" t="inlineStr"/>
       <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Norrbytorp, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>688014</v>
+        <v>688067</v>
       </c>
       <c r="R170" t="n">
-        <v>6562734</v>
+        <v>6562731</v>
       </c>
       <c r="S170" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -19361,22 +19361,12 @@
       </c>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="Z170" t="inlineStr">
-        <is>
-          <t>12:38</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="AB170" t="inlineStr">
-        <is>
-          <t>12:38</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19392,27 +19382,27 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Björn Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Björn Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136241765</t>
+          <t>https://artportalen.se/Sighting/128646583</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>17285491</v>
+        <v>136241765</v>
       </c>
       <c r="B171" t="n">
-        <v>80432</v>
+        <v>80093</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19420,39 +19410,44 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr"/>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Norrby torp, 480 m Ö, Srm</t>
+          <t>Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>688111</v>
+        <v>688014</v>
       </c>
       <c r="R171" t="n">
-        <v>6562706</v>
+        <v>6562734</v>
       </c>
       <c r="S171" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -19476,17 +19471,22 @@
       </c>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>2015-04-02</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>2015-04-02</t>
-        </is>
-      </c>
-      <c r="AC171" t="inlineStr">
-        <is>
-          <t>På ek i bergskanten, ca 220 cm omkrets. Sparsamt vid 20 resp. 70 cm höjd.</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19495,35 +19495,31 @@
       <c r="AE171" t="b">
         <v>0</v>
       </c>
+      <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="b">
         <v>0</v>
-      </c>
-      <c r="AI171" t="inlineStr">
-        <is>
-          <t>Yngre gallrad blandskog</t>
-        </is>
       </c>
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Björn Persson</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Björn Persson</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/17285491</t>
+          <t>https://artportalen.se/Sighting/136241765</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>79273786</v>
+        <v>17285491</v>
       </c>
       <c r="B172" t="n">
         <v>80432</v>
@@ -19552,16 +19548,18 @@
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Åvadal, Srm</t>
+          <t>Norrby torp, 480 m Ö, Srm</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>688109</v>
+        <v>688111</v>
       </c>
       <c r="R172" t="n">
-        <v>6562704</v>
+        <v>6562706</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19588,12 +19586,17 @@
       </c>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>2019-08-01</t>
+          <t>2015-04-02</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>2019-08-01</t>
+          <t>2015-04-02</t>
+        </is>
+      </c>
+      <c r="AC172" t="inlineStr">
+        <is>
+          <t>På ek i bergskanten, ca 220 cm omkrets. Sparsamt vid 20 resp. 70 cm höjd.</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -19605,42 +19608,32 @@
       <c r="AG172" t="b">
         <v>0</v>
       </c>
-      <c r="AJ172" t="inlineStr">
-        <is>
-          <t>skogsek</t>
-        </is>
-      </c>
-      <c r="AK172" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
-      </c>
-      <c r="AO172" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
+      <c r="AI172" t="inlineStr">
+        <is>
+          <t>Yngre gallrad blandskog</t>
         </is>
       </c>
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Gustav Wikström</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Gustav Wikström</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/79273786</t>
+          <t>https://artportalen.se/Sighting/17285491</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>89840770</v>
+        <v>79273786</v>
       </c>
       <c r="B173" t="n">
         <v>80432</v>
@@ -19669,19 +19662,16 @@
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
-      <c r="J173" t="inlineStr"/>
-      <c r="K173" t="inlineStr"/>
-      <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Ö Norrby Torp, Srm</t>
+          <t>Åvadal, Srm</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>688146</v>
+        <v>688109</v>
       </c>
       <c r="R173" t="n">
-        <v>6562738</v>
+        <v>6562704</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19708,17 +19698,12 @@
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>2020-12-30</t>
+          <t>2019-08-01</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>2020-12-30</t>
-        </is>
-      </c>
-      <c r="AC173" t="inlineStr">
-        <is>
-          <t>Tre bålar på en ek som inte längre ser ut att vara så livskraftig. Finns en annan noterad ek med lavar en bit ifrån.</t>
+          <t>2019-08-01</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19727,31 +19712,45 @@
       <c r="AE173" t="b">
         <v>0</v>
       </c>
-      <c r="AF173" t="inlineStr"/>
       <c r="AG173" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ173" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK173" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO173" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
       </c>
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Gustav Wikström</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Gustav Wikström</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89840770</t>
+          <t>https://artportalen.se/Sighting/79273786</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>112384453</v>
+        <v>89840770</v>
       </c>
       <c r="B174" t="n">
         <v>80432</v>
@@ -19785,14 +19784,14 @@
       <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Norrby torp Ö om, Srm</t>
+          <t>Ö Norrby Torp, Srm</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>688145</v>
+        <v>688146</v>
       </c>
       <c r="R174" t="n">
-        <v>6562737</v>
+        <v>6562738</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19819,17 +19818,17 @@
       </c>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2020-12-30</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2020-12-30</t>
         </is>
       </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>Återfynd. På halvdöd ek med blottad ved men några levande grenar i toppen, ca 120 cm omkrets. Två mindre blaffor i dåligt skick, hänger något löst, ca 40 resp. 130 cm höjd.</t>
+          <t>Tre bålar på en ek som inte längre ser ut att vara så livskraftig. Finns en annan noterad ek med lavar en bit ifrån.</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19845,24 +19844,24 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112384453</t>
+          <t>https://artportalen.se/Sighting/89840770</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>122779297</v>
+        <v>112384453</v>
       </c>
       <c r="B175" t="n">
         <v>80432</v>
@@ -19896,14 +19895,14 @@
       <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Lunglav, Srm</t>
+          <t>Norrby torp Ö om, Srm</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>688116</v>
+        <v>688145</v>
       </c>
       <c r="R175" t="n">
-        <v>6562703</v>
+        <v>6562737</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19930,17 +19929,17 @@
       </c>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>Lunglav på gammal ek</t>
+          <t>Återfynd. På halvdöd ek med blottad ved men några levande grenar i toppen, ca 120 cm omkrets. Två mindre blaffor i dåligt skick, hänger något löst, ca 40 resp. 130 cm höjd.</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19956,81 +19955,68 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122779297</t>
+          <t>https://artportalen.se/Sighting/112384453</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>125923864</v>
+        <v>122779297</v>
       </c>
       <c r="B176" t="n">
-        <v>57754</v>
+        <v>80432</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>102118</v>
+        <v>6458</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr"/>
-      <c r="L176" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
       <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Lunglav, Srm</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>687916</v>
+        <v>688116</v>
       </c>
       <c r="R176" t="n">
-        <v>6562815</v>
+        <v>6562703</v>
       </c>
       <c r="S176" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -20054,17 +20040,17 @@
       </c>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>Stöttes och stannade nära, det fanns ett ägg. Än så länge?</t>
+          <t>Lunglav på gammal ek</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -20073,63 +20059,72 @@
       <c r="AE176" t="b">
         <v>0</v>
       </c>
+      <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="b">
         <v>0</v>
       </c>
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125923864</t>
+          <t>https://artportalen.se/Sighting/122779297</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128317861</v>
+        <v>125923864</v>
       </c>
       <c r="B177" t="n">
-        <v>58114</v>
+        <v>57754</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>103021</v>
+        <v>102118</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K177" t="inlineStr"/>
-      <c r="L177" t="inlineStr"/>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>bo, ägg/ungar</t>
         </is>
       </c>
       <c r="N177" t="inlineStr"/>
@@ -20139,10 +20134,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>688058</v>
+        <v>687916</v>
       </c>
       <c r="R177" t="n">
-        <v>6562805</v>
+        <v>6562815</v>
       </c>
       <c r="S177" t="n">
         <v>25</v>
@@ -20169,12 +20164,17 @@
       </c>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>Stöttes och stannade nära, det fanns ett ägg. Än så länge?</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20200,16 +20200,16 @@
       <c r="AY177" t="inlineStr"/>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128317861</t>
+          <t>https://artportalen.se/Sighting/125923864</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>136138855</v>
+        <v>128317861</v>
       </c>
       <c r="B178" t="n">
-        <v>58167</v>
+        <v>58114</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20249,13 +20249,13 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>687836</v>
+        <v>688058</v>
       </c>
       <c r="R178" t="n">
-        <v>6562786</v>
+        <v>6562805</v>
       </c>
       <c r="S178" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -20279,12 +20279,12 @@
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -20310,13 +20310,13 @@
       <c r="AY178" t="inlineStr"/>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136138855</t>
+          <t>https://artportalen.se/Sighting/128317861</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>136138971</v>
+        <v>136138855</v>
       </c>
       <c r="B179" t="n">
         <v>58167</v>
@@ -20359,13 +20359,13 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>687977</v>
+        <v>687836</v>
       </c>
       <c r="R179" t="n">
-        <v>6562735</v>
+        <v>6562786</v>
       </c>
       <c r="S179" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -20420,71 +20420,62 @@
       <c r="AY179" t="inlineStr"/>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136138971</t>
+          <t>https://artportalen.se/Sighting/136138855</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>122692266</v>
+        <v>136138971</v>
       </c>
       <c r="B180" t="n">
-        <v>58826</v>
+        <v>58167</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>208242</v>
+        <v>103021</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J180" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr"/>
       <c r="K180" t="inlineStr"/>
       <c r="L180" t="inlineStr"/>
       <c r="M180" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N180" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>687868</v>
+        <v>687977</v>
       </c>
       <c r="R180" t="n">
-        <v>6562755</v>
+        <v>6562735</v>
       </c>
       <c r="S180" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -20508,17 +20499,12 @@
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AC180" t="inlineStr">
-        <is>
-          <t>Mindre vattensalamander</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -20527,34 +20513,33 @@
       <c r="AE180" t="b">
         <v>0</v>
       </c>
-      <c r="AF180" t="inlineStr"/>
       <c r="AG180" t="b">
         <v>0</v>
       </c>
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122692266</t>
+          <t>https://artportalen.se/Sighting/136138971</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>136241491</v>
+        <v>122692266</v>
       </c>
       <c r="B181" t="n">
-        <v>58843</v>
+        <v>58826</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20562,16 +20547,16 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>208245</v>
+        <v>208242</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -20579,19 +20564,31 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I181" t="inlineStr"/>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr"/>
       <c r="L181" t="inlineStr"/>
-      <c r="M181" t="inlineStr"/>
-      <c r="N181" t="inlineStr"/>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Mindre vattensalamander, Srm</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>687873</v>
+        <v>687868</v>
       </c>
       <c r="R181" t="n">
         <v>6562755</v>
@@ -20621,17 +20618,17 @@
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AC181" t="inlineStr">
         <is>
-          <t>Troligen årsunge.</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -20647,27 +20644,27 @@
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136241491</t>
+          <t>https://artportalen.se/Sighting/122692266</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>101544040</v>
+        <v>136241491</v>
       </c>
       <c r="B182" t="n">
-        <v>99035</v>
+        <v>58843</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20675,41 +20672,42 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>219790</v>
+        <v>208245</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr"/>
       <c r="L182" t="inlineStr"/>
+      <c r="M182" t="inlineStr"/>
       <c r="N182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>NO Norrby Torp, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>687896</v>
+        <v>687873</v>
       </c>
       <c r="R182" t="n">
-        <v>6562764</v>
+        <v>6562755</v>
       </c>
       <c r="S182" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -20733,12 +20731,17 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2022-06-09</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2022-06-09</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>Troligen årsunge.</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -20765,16 +20768,16 @@
       <c r="AY182" t="inlineStr"/>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101544040</t>
+          <t>https://artportalen.se/Sighting/136241491</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>136394236</v>
+        <v>101544040</v>
       </c>
       <c r="B183" t="n">
-        <v>98204</v>
+        <v>99035</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20782,37 +20785,41 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr"/>
+      <c r="N183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Norrbytorp, Srm</t>
+          <t>NO Norrby Torp, Srm</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>687882</v>
+        <v>687896</v>
       </c>
       <c r="R183" t="n">
-        <v>6562761</v>
+        <v>6562764</v>
       </c>
       <c r="S183" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -20836,22 +20843,12 @@
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="Z183" t="inlineStr">
-        <is>
-          <t>11:26</t>
+          <t>2022-06-09</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="AB183" t="inlineStr">
-        <is>
-          <t>11:26</t>
+          <t>2022-06-09</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -20860,33 +20857,34 @@
       <c r="AE183" t="b">
         <v>0</v>
       </c>
+      <c r="AF183" t="inlineStr"/>
       <c r="AG183" t="b">
         <v>0</v>
       </c>
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136394236</t>
+          <t>https://artportalen.se/Sighting/101544040</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>122930166</v>
+        <v>136394236</v>
       </c>
       <c r="B184" t="n">
-        <v>96554</v>
+        <v>98204</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20894,41 +20892,37 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>210</v>
+        <v>221945</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
-      <c r="J184" t="inlineStr"/>
-      <c r="K184" t="inlineStr"/>
-      <c r="L184" t="inlineStr"/>
-      <c r="N184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>686762</v>
+        <v>687882</v>
       </c>
       <c r="R184" t="n">
-        <v>6562715</v>
+        <v>6562761</v>
       </c>
       <c r="S184" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -20952,22 +20946,22 @@
       </c>
       <c r="Y184" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -20982,68 +20976,69 @@
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122930166</t>
+          <t>https://artportalen.se/Sighting/136394236</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>119061006</v>
+        <v>122930166</v>
       </c>
       <c r="B185" t="n">
-        <v>91533</v>
+        <v>96554</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>2051</v>
+        <v>210</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
       <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>S Norrby mosse, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>686477</v>
+        <v>686762</v>
       </c>
       <c r="R185" t="n">
-        <v>6562857</v>
+        <v>6562715</v>
       </c>
       <c r="S185" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -21067,17 +21062,22 @@
       </c>
       <c r="Y185" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="Z185" t="inlineStr">
+        <is>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC185" t="inlineStr">
-        <is>
-          <t>Brukad skog nära kant mot gammal.</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AB185" t="inlineStr">
+        <is>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -21086,81 +21086,74 @@
       <c r="AE185" t="b">
         <v>0</v>
       </c>
-      <c r="AF185" t="inlineStr"/>
       <c r="AG185" t="b">
         <v>0</v>
       </c>
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119061006</t>
+          <t>https://artportalen.se/Sighting/122930166</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>122929535</v>
+        <v>119061006</v>
       </c>
       <c r="B186" t="n">
-        <v>8455</v>
+        <v>91533</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>106545</v>
+        <v>2051</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr"/>
-      <c r="L186" t="inlineStr"/>
-      <c r="M186" t="inlineStr"/>
       <c r="N186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>S Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>686612</v>
+        <v>686477</v>
       </c>
       <c r="R186" t="n">
-        <v>6562882</v>
+        <v>6562857</v>
       </c>
       <c r="S186" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -21184,22 +21177,17 @@
       </c>
       <c r="Y186" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="Z186" t="inlineStr">
-        <is>
-          <t>11:01</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="AB186" t="inlineStr">
-        <is>
-          <t>11:01</t>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>Brukad skog nära kant mot gammal.</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -21208,33 +21196,34 @@
       <c r="AE186" t="b">
         <v>0</v>
       </c>
+      <c r="AF186" t="inlineStr"/>
       <c r="AG186" t="b">
         <v>0</v>
       </c>
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122929535</t>
+          <t>https://artportalen.se/Sighting/119061006</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>122928987</v>
+        <v>122929535</v>
       </c>
       <c r="B187" t="n">
-        <v>97983</v>
+        <v>8455</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21242,27 +21231,32 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr"/>
       <c r="L187" t="inlineStr"/>
+      <c r="M187" t="inlineStr"/>
       <c r="N187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
@@ -21270,13 +21264,13 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>686389</v>
+        <v>686612</v>
       </c>
       <c r="R187" t="n">
-        <v>6562967</v>
+        <v>6562882</v>
       </c>
       <c r="S187" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -21305,7 +21299,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -21315,7 +21309,7 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -21341,51 +21335,55 @@
       <c r="AY187" t="inlineStr"/>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122928987</t>
+          <t>https://artportalen.se/Sighting/122929535</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>126061106</v>
+        <v>122928987</v>
       </c>
       <c r="B188" t="n">
-        <v>91333</v>
+        <v>97983</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>2008</v>
+        <v>221945</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Pers., nom.sanct.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr"/>
+      <c r="N188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>686883</v>
+        <v>686389</v>
       </c>
       <c r="R188" t="n">
-        <v>6562742</v>
+        <v>6562967</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21412,22 +21410,22 @@
       </c>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -21442,49 +21440,49 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061106</t>
+          <t>https://artportalen.se/Sighting/122928987</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>126061107</v>
+        <v>126061106</v>
       </c>
       <c r="B189" t="n">
-        <v>96458</v>
+        <v>91333</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>2818</v>
+        <v>2008</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Pers., nom.sanct.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -21494,10 +21492,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>686880</v>
+        <v>686883</v>
       </c>
       <c r="R189" t="n">
-        <v>6562745</v>
+        <v>6562742</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21529,7 +21527,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -21539,7 +21537,7 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -21565,16 +21563,16 @@
       <c r="AY189" t="inlineStr"/>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061107</t>
+          <t>https://artportalen.se/Sighting/126061106</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129215187</v>
+        <v>126061107</v>
       </c>
       <c r="B190" t="n">
-        <v>91872</v>
+        <v>96458</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -21582,37 +21580,34 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>5447</v>
+        <v>2818</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
-      <c r="J190" t="inlineStr"/>
-      <c r="K190" t="inlineStr"/>
-      <c r="N190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>686977</v>
+        <v>686880</v>
       </c>
       <c r="R190" t="n">
-        <v>6562706</v>
+        <v>6562745</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21639,12 +21634,22 @@
       </c>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z190" t="inlineStr">
+        <is>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB190" t="inlineStr">
+        <is>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -21653,34 +21658,33 @@
       <c r="AE190" t="b">
         <v>0</v>
       </c>
-      <c r="AF190" t="inlineStr"/>
       <c r="AG190" t="b">
         <v>0</v>
       </c>
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215187</t>
+          <t>https://artportalen.se/Sighting/126061107</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>126061104</v>
+        <v>129215187</v>
       </c>
       <c r="B191" t="n">
-        <v>4775</v>
+        <v>91872</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21688,34 +21692,37 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>100299</v>
+        <v>5447</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr"/>
+      <c r="N191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>686868</v>
+        <v>686977</v>
       </c>
       <c r="R191" t="n">
-        <v>6562739</v>
+        <v>6562706</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21742,22 +21749,12 @@
       </c>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z191" t="inlineStr">
-        <is>
-          <t>13:41</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB191" t="inlineStr">
-        <is>
-          <t>13:41</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -21766,53 +21763,34 @@
       <c r="AE191" t="b">
         <v>0</v>
       </c>
+      <c r="AF191" t="inlineStr"/>
       <c r="AG191" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ191" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK191" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL191" t="inlineStr">
-        <is>
-          <t>Stående död gran.</t>
-        </is>
-      </c>
-      <c r="AO191" t="inlineStr">
-        <is>
-          <t>Picea abies # Stående död gran.</t>
-        </is>
       </c>
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061104</t>
+          <t>https://artportalen.se/Sighting/129215187</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>126061116</v>
+        <v>126061104</v>
       </c>
       <c r="B192" t="n">
-        <v>44177</v>
+        <v>4775</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21820,21 +21798,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>101735</v>
+        <v>100299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -21844,10 +21822,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>686928</v>
+        <v>686868</v>
       </c>
       <c r="R192" t="n">
-        <v>6562716</v>
+        <v>6562739</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21879,7 +21857,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -21889,7 +21867,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -21903,22 +21881,22 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>fnöskticka</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK192" t="inlineStr">
         <is>
-          <t>Fomes fomentarius</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL192" t="inlineStr">
         <is>
-          <t>Fnöskticka på björk.</t>
+          <t>Stående död gran.</t>
         </is>
       </c>
       <c r="AO192" t="inlineStr">
         <is>
-          <t>Fomes fomentarius # Fnöskticka på björk.</t>
+          <t>Picea abies # Stående död gran.</t>
         </is>
       </c>
       <c r="AT192" t="inlineStr"/>
@@ -21935,16 +21913,16 @@
       <c r="AY192" t="inlineStr"/>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061116</t>
+          <t>https://artportalen.se/Sighting/126061104</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>125974903</v>
+        <v>126061116</v>
       </c>
       <c r="B193" t="n">
-        <v>8444</v>
+        <v>44177</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21952,50 +21930,37 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>106554</v>
+        <v>101735</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I193" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J193" t="inlineStr"/>
-      <c r="K193" t="inlineStr"/>
-      <c r="L193" t="inlineStr"/>
-      <c r="M193" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N193" t="inlineStr"/>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>söder om Tyresta, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>686838</v>
+        <v>686928</v>
       </c>
       <c r="R193" t="n">
-        <v>6562733</v>
+        <v>6562716</v>
       </c>
       <c r="S193" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -22022,14 +21987,19 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA193" t="inlineStr">
         <is>
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC193" t="inlineStr">
-        <is>
-          <t>gammal björklåga med spår längs hela stammen</t>
+      <c r="AB193" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -22038,51 +22008,50 @@
       <c r="AE193" t="b">
         <v>0</v>
       </c>
-      <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="b">
         <v>0</v>
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>vårtbjörk</t>
+          <t>fnöskticka</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
         <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
-      <c r="AM193" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
+          <t>Fomes fomentarius</t>
+        </is>
+      </c>
+      <c r="AL193" t="inlineStr">
+        <is>
+          <t>Fnöskticka på björk.</t>
         </is>
       </c>
       <c r="AO193" t="inlineStr">
         <is>
-          <t>Wood surface of dead wood # Betula pendula</t>
+          <t>Fomes fomentarius # Fnöskticka på björk.</t>
         </is>
       </c>
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Nette Bygren</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Nette Bygren</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125974903</t>
+          <t>https://artportalen.se/Sighting/126061116</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>126061105</v>
+        <v>125974903</v>
       </c>
       <c r="B194" t="n">
         <v>8444</v>
@@ -22110,20 +22079,33 @@
           <t>Janson, 1856</t>
         </is>
       </c>
-      <c r="I194" t="inlineStr"/>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>söder om Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>686860</v>
+        <v>686838</v>
       </c>
       <c r="R194" t="n">
-        <v>6562743</v>
+        <v>6562733</v>
       </c>
       <c r="S194" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -22150,19 +22132,14 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z194" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA194" t="inlineStr">
         <is>
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AB194" t="inlineStr">
-        <is>
-          <t>13:36</t>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>gammal björklåga med spår längs hela stammen</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -22171,37 +22148,170 @@
       <c r="AE194" t="b">
         <v>0</v>
       </c>
+      <c r="AF194" t="inlineStr"/>
       <c r="AG194" t="b">
         <v>0</v>
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>vårtbjörk</t>
         </is>
       </c>
       <c r="AK194" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AM194" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO194" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Wood surface of dead wood # Betula pendula</t>
         </is>
       </c>
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Nette Bygren</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Nette Bygren</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
       <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125974903</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>126061105</v>
+      </c>
+      <c r="B195" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr"/>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>Ö Tyresta by, Srm</t>
+        </is>
+      </c>
+      <c r="Q195" t="n">
+        <v>686860</v>
+      </c>
+      <c r="R195" t="n">
+        <v>6562743</v>
+      </c>
+      <c r="S195" t="n">
+        <v>10</v>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W195" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y195" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z195" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB195" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AD195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ195" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK195" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO195" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AT195" t="inlineStr"/>
+      <c r="AW195" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX195" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/126061105</t>
         </is>
@@ -22402,6 +22512,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 152-2026 artfynd.xlsx
+++ b/artfynd/S 152-2026 artfynd.xlsx
@@ -2433,7 +2433,7 @@
         <v>136261113</v>
       </c>
       <c r="B18" t="n">
-        <v>96930</v>
+        <v>96931</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>136394246</v>
       </c>
       <c r="B19" t="n">
-        <v>96930</v>
+        <v>96931</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         <v>136557239</v>
       </c>
       <c r="B21" t="n">
-        <v>91881</v>
+        <v>91882</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>136697244</v>
       </c>
       <c r="B24" t="n">
-        <v>93395</v>
+        <v>93396</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>136497924</v>
       </c>
       <c r="B27" t="n">
-        <v>93397</v>
+        <v>93398</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>136138429</v>
       </c>
       <c r="B31" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>136159959</v>
       </c>
       <c r="B32" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>136193282</v>
       </c>
       <c r="B33" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>136193424</v>
       </c>
       <c r="B34" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
         <v>136232449</v>
       </c>
       <c r="B35" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>136394238</v>
       </c>
       <c r="B36" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         <v>136422890</v>
       </c>
       <c r="B37" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>136697333</v>
       </c>
       <c r="B38" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         <v>136697388</v>
       </c>
       <c r="B39" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         <v>136697399</v>
       </c>
       <c r="B40" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5341,7 +5341,7 @@
         <v>136394243</v>
       </c>
       <c r="B45" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -9924,7 +9924,7 @@
         <v>136234180</v>
       </c>
       <c r="B86" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>136394241</v>
       </c>
       <c r="B87" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10138,7 +10138,7 @@
         <v>136394242</v>
       </c>
       <c r="B88" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         <v>136394244</v>
       </c>
       <c r="B89" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>136394245</v>
       </c>
       <c r="B90" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>136234148</v>
       </c>
       <c r="B92" t="n">
-        <v>98210</v>
+        <v>98211</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         <v>136329952</v>
       </c>
       <c r="B108" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12469,7 +12469,7 @@
         <v>136330044</v>
       </c>
       <c r="B109" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13250,7 +13250,7 @@
         <v>136330155</v>
       </c>
       <c r="B116" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13356,7 +13356,7 @@
         <v>136330904</v>
       </c>
       <c r="B117" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -19079,7 +19079,7 @@
         <v>136241603</v>
       </c>
       <c r="B168" t="n">
-        <v>96930</v>
+        <v>96931</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19196,7 +19196,7 @@
         <v>136231090</v>
       </c>
       <c r="B169" t="n">
-        <v>96648</v>
+        <v>96649</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19298,7 +19298,7 @@
         <v>136697134</v>
       </c>
       <c r="B170" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19518,7 +19518,7 @@
         <v>136394237</v>
       </c>
       <c r="B172" t="n">
-        <v>92516</v>
+        <v>92517</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19630,7 +19630,7 @@
         <v>136268106</v>
       </c>
       <c r="B173" t="n">
-        <v>92068</v>
+        <v>92069</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19741,7 +19741,7 @@
         <v>136697126</v>
       </c>
       <c r="B174" t="n">
-        <v>92068</v>
+        <v>92069</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -21753,7 +21753,7 @@
         <v>136394236</v>
       </c>
       <c r="B192" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>

--- a/artfynd/S 152-2026 artfynd.xlsx
+++ b/artfynd/S 152-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ203"/>
+  <dimension ref="A1:AZ206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14426,48 +14426,45 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128646813</v>
+        <v>136737384</v>
       </c>
       <c r="B127" t="n">
-        <v>92567</v>
+        <v>93442</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6031</v>
+        <v>5966</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrbytorp_inventering_2026-08-30, Srm</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>686827</v>
+        <v>686751</v>
       </c>
       <c r="R127" t="n">
-        <v>6563224</v>
+        <v>6563152</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14494,12 +14491,27 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>8 fruktkroppar</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14508,79 +14520,71 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Björn Persson</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Björn Persson</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128646813</t>
+          <t>https://artportalen.se/Sighting/136737384</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>112337759</v>
+        <v>136737387</v>
       </c>
       <c r="B128" t="n">
-        <v>90691</v>
+        <v>93442</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6276</v>
+        <v>5966</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Norrby Mosse, Srm</t>
+          <t>Norrbytorp_inventering_2026-08-30, Srm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>686738</v>
+        <v>686626</v>
       </c>
       <c r="R128" t="n">
-        <v>6563118</v>
+        <v>6563112</v>
       </c>
       <c r="S128" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -14604,12 +14608,22 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14618,56 +14632,55 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Björn Persson</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Björn Persson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112337759</t>
+          <t>https://artportalen.se/Sighting/136737387</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129591415</v>
+        <v>128646813</v>
       </c>
       <c r="B129" t="n">
-        <v>79327</v>
+        <v>92567</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>6031</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14680,10 +14693,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>686678</v>
+        <v>686827</v>
       </c>
       <c r="R129" t="n">
-        <v>6563229</v>
+        <v>6563224</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14710,17 +14723,12 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>På tallstam samt några delar av bålen som lossnat och hamnat på en liten gran.</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14747,54 +14755,58 @@
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129591415</t>
+          <t>https://artportalen.se/Sighting/128646813</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>96643356</v>
+        <v>112337759</v>
       </c>
       <c r="B130" t="n">
-        <v>79351</v>
+        <v>90691</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6434</v>
+        <v>6276</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr"/>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr"/>
       <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Norrby mosse S om, Srm</t>
+          <t>Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>686692</v>
+        <v>686738</v>
       </c>
       <c r="R130" t="n">
-        <v>6563028</v>
+        <v>6563118</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14821,12 +14833,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14842,49 +14854,49 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96643356</t>
+          <t>https://artportalen.se/Sighting/112337759</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>97239536</v>
+        <v>129591415</v>
       </c>
       <c r="B131" t="n">
-        <v>79351</v>
+        <v>79327</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14893,17 +14905,17 @@
       <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>S Norrby mosse, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>686697</v>
+        <v>686678</v>
       </c>
       <c r="R131" t="n">
-        <v>6563033</v>
+        <v>6563229</v>
       </c>
       <c r="S131" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14927,27 +14939,17 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2021-11-20</t>
-        </is>
-      </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>11:14</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2021-11-20</t>
-        </is>
-      </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>11:14</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>Förevisade av Bodil och Ulf</t>
+          <t>På tallstam samt några delar av bålen som lossnat och hamnat på en liten gran.</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14963,24 +14965,24 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Thomas Strid</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Thomas Strid, Bodil Ravn, Ulf Johansson, Tiina Laantee</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97239536</t>
+          <t>https://artportalen.se/Sighting/129591415</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>106813853</v>
+        <v>96643356</v>
       </c>
       <c r="B132" t="n">
         <v>79351</v>
@@ -15014,14 +15016,14 @@
       <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Österhaninge, Srm</t>
+          <t>Norrby mosse S om, Srm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>686702</v>
+        <v>686692</v>
       </c>
       <c r="R132" t="n">
-        <v>6563040</v>
+        <v>6563028</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15048,12 +15050,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2021-11-20</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2021-11-20</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15066,42 +15068,27 @@
       <c r="AG132" t="b">
         <v>0</v>
       </c>
-      <c r="AI132" t="inlineStr">
-        <is>
-          <t>tallhällmark, på bark av Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AP132" t="inlineStr">
-        <is>
-          <t>Stockholm-Naturhistoriska riksmuseet</t>
-        </is>
-      </c>
-      <c r="AR132" t="inlineStr">
-        <is>
-          <t>21-1065</t>
-        </is>
-      </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Thomas Strid</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Thomas Strid, Göran Odelvik, Tiina Laantee, Ulf Johansson, Bodil Ravn</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106813853</t>
+          <t>https://artportalen.se/Sighting/96643356</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121859628</v>
+        <v>97239536</v>
       </c>
       <c r="B133" t="n">
         <v>79351</v>
@@ -15130,19 +15117,22 @@
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Öster om Tyresta by, Tyresta, Srm</t>
+          <t>S Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q133" t="n">
         <v>686697</v>
       </c>
       <c r="R133" t="n">
-        <v>6563030</v>
+        <v>6563033</v>
       </c>
       <c r="S133" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -15166,22 +15156,27 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2021-11-20</t>
         </is>
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2021-11-20</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Förevisade av Bodil och Ulf</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15190,53 +15185,34 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ133" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK133" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL133" t="inlineStr">
-        <is>
-          <t>Levande äldre tall.</t>
-        </is>
-      </c>
-      <c r="AO133" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Levande äldre tall.</t>
-        </is>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Thomas Strid, Bodil Ravn, Ulf Johansson, Tiina Laantee</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859628</t>
+          <t>https://artportalen.se/Sighting/97239536</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121859622</v>
+        <v>106813853</v>
       </c>
       <c r="B134" t="n">
-        <v>57950</v>
+        <v>79351</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15244,42 +15220,37 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Öster om Tyresta by, Tyresta, Srm</t>
+          <t>Österhaninge, Srm</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>686574</v>
+        <v>686702</v>
       </c>
       <c r="R134" t="n">
-        <v>6562988</v>
+        <v>6563040</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15306,27 +15277,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>17:37</t>
+          <t>2021-11-20</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>Födosökshack långt ner på stående död tall.</t>
+          <t>2021-11-20</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15335,33 +15291,49 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
+      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
+      </c>
+      <c r="AI134" t="inlineStr">
+        <is>
+          <t>tallhällmark, på bark av Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AP134" t="inlineStr">
+        <is>
+          <t>Stockholm-Naturhistoriska riksmuseet</t>
+        </is>
+      </c>
+      <c r="AR134" t="inlineStr">
+        <is>
+          <t>21-1065</t>
+        </is>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Thomas Strid, Göran Odelvik, Tiina Laantee, Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859622</t>
+          <t>https://artportalen.se/Sighting/106813853</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>122929399</v>
+        <v>121859628</v>
       </c>
       <c r="B135" t="n">
-        <v>57950</v>
+        <v>79351</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15369,45 +15341,37 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>686567</v>
+        <v>686697</v>
       </c>
       <c r="R135" t="n">
-        <v>6562954</v>
+        <v>6563030</v>
       </c>
       <c r="S135" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15431,22 +15395,22 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15457,78 +15421,89 @@
       </c>
       <c r="AG135" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ135" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK135" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL135" t="inlineStr">
+        <is>
+          <t>Levande äldre tall.</t>
+        </is>
+      </c>
+      <c r="AO135" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Levande äldre tall.</t>
+        </is>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122929399</t>
+          <t>https://artportalen.se/Sighting/121859628</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126418797</v>
+        <v>136737383</v>
       </c>
       <c r="B136" t="n">
-        <v>56895</v>
+        <v>80093</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100088</v>
+        <v>6453</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrbytorp_inventering_2026-08-30, Srm</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>686803</v>
+        <v>686713</v>
       </c>
       <c r="R136" t="n">
-        <v>6563297</v>
+        <v>6563218</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15552,12 +15527,22 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15566,34 +15551,33 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
-      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Björn Persson</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Björn Persson</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126418797</t>
+          <t>https://artportalen.se/Sighting/136737383</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>134100841</v>
+        <v>121859622</v>
       </c>
       <c r="B137" t="n">
-        <v>56915</v>
+        <v>57950</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15601,16 +15585,16 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>100088</v>
+        <v>100049</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -15618,26 +15602,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
       <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>686486</v>
+        <v>686574</v>
       </c>
       <c r="R137" t="n">
-        <v>6563086</v>
+        <v>6562988</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15664,12 +15647,27 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>Födosökshack långt ner på stående död tall.</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15678,34 +15676,33 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
-      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134100841</t>
+          <t>https://artportalen.se/Sighting/121859622</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121859623</v>
+        <v>122929399</v>
       </c>
       <c r="B138" t="n">
-        <v>5179</v>
+        <v>57950</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15713,42 +15710,45 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Öster om Tyresta by, Tyresta, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>686581</v>
+        <v>686567</v>
       </c>
       <c r="R138" t="n">
-        <v>6562989</v>
+        <v>6562954</v>
       </c>
       <c r="S138" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15772,22 +15772,22 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15798,83 +15798,64 @@
       </c>
       <c r="AG138" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ138" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK138" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL138" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO138" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
       </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859623</t>
+          <t>https://artportalen.se/Sighting/122929399</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128510434</v>
+        <v>126418797</v>
       </c>
       <c r="B139" t="n">
-        <v>58114</v>
+        <v>56895</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>103021</v>
+        <v>100088</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M139" t="inlineStr"/>
       <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
@@ -15882,10 +15863,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>686650</v>
+        <v>686803</v>
       </c>
       <c r="R139" t="n">
-        <v>6563214</v>
+        <v>6563297</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15912,12 +15893,12 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15926,6 +15907,7 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -15943,48 +15925,49 @@
       <c r="AY139" t="inlineStr"/>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128510434</t>
+          <t>https://artportalen.se/Sighting/126418797</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128886960</v>
+        <v>134100841</v>
       </c>
       <c r="B140" t="n">
-        <v>58114</v>
+        <v>56915</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>103021</v>
+        <v>100088</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M140" t="inlineStr"/>
       <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
@@ -15992,13 +15975,13 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>686792</v>
+        <v>686486</v>
       </c>
       <c r="R140" t="n">
-        <v>6563221</v>
+        <v>6563086</v>
       </c>
       <c r="S140" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -16022,12 +16005,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16036,6 +16019,7 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -16053,62 +16037,59 @@
       <c r="AY140" t="inlineStr"/>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128886960</t>
+          <t>https://artportalen.se/Sighting/134100841</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129230389</v>
+        <v>121859623</v>
       </c>
       <c r="B141" t="n">
-        <v>58114</v>
+        <v>5179</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
       <c r="M141" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N141" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>686793</v>
+        <v>686581</v>
       </c>
       <c r="R141" t="n">
-        <v>6563302</v>
+        <v>6562989</v>
       </c>
       <c r="S141" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -16132,12 +16113,22 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16148,28 +16139,48 @@
       </c>
       <c r="AG141" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ141" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK141" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL141" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO141" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
       </c>
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129230389</t>
+          <t>https://artportalen.se/Sighting/121859623</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129591579</v>
+        <v>128510434</v>
       </c>
       <c r="B142" t="n">
         <v>58114</v>
@@ -16212,13 +16223,13 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>686618</v>
+        <v>686650</v>
       </c>
       <c r="R142" t="n">
-        <v>6563047</v>
+        <v>6563214</v>
       </c>
       <c r="S142" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -16242,12 +16253,12 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16273,16 +16284,16 @@
       <c r="AY142" t="inlineStr"/>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129591579</t>
+          <t>https://artportalen.se/Sighting/128510434</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>133115563</v>
+        <v>128886960</v>
       </c>
       <c r="B143" t="n">
-        <v>58136</v>
+        <v>58114</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16312,7 +16323,7 @@
       <c r="L143" t="inlineStr"/>
       <c r="M143" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N143" t="inlineStr"/>
@@ -16322,13 +16333,13 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>686651</v>
+        <v>686792</v>
       </c>
       <c r="R143" t="n">
-        <v>6563184</v>
+        <v>6563221</v>
       </c>
       <c r="S143" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -16352,12 +16363,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16383,16 +16394,16 @@
       <c r="AY143" t="inlineStr"/>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133115563</t>
+          <t>https://artportalen.se/Sighting/128886960</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>136330004</v>
+        <v>129230389</v>
       </c>
       <c r="B144" t="n">
-        <v>58167</v>
+        <v>58114</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16432,13 +16443,13 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>686477</v>
+        <v>686793</v>
       </c>
       <c r="R144" t="n">
-        <v>6563053</v>
+        <v>6563302</v>
       </c>
       <c r="S144" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -16462,12 +16473,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16493,16 +16504,16 @@
       <c r="AY144" t="inlineStr"/>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136330004</t>
+          <t>https://artportalen.se/Sighting/129230389</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>136422006</v>
+        <v>129591579</v>
       </c>
       <c r="B145" t="n">
-        <v>58167</v>
+        <v>58114</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16542,13 +16553,13 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>686531</v>
+        <v>686618</v>
       </c>
       <c r="R145" t="n">
-        <v>6563059</v>
+        <v>6563047</v>
       </c>
       <c r="S145" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -16572,12 +16583,12 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16603,16 +16614,16 @@
       <c r="AY145" t="inlineStr"/>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136422006</t>
+          <t>https://artportalen.se/Sighting/129591579</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>136631248</v>
+        <v>133115563</v>
       </c>
       <c r="B146" t="n">
-        <v>58167</v>
+        <v>58136</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16642,7 +16653,7 @@
       <c r="L146" t="inlineStr"/>
       <c r="M146" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N146" t="inlineStr"/>
@@ -16652,10 +16663,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>686469</v>
+        <v>686651</v>
       </c>
       <c r="R146" t="n">
-        <v>6563013</v>
+        <v>6563184</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16682,12 +16693,12 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16713,38 +16724,38 @@
       <c r="AY146" t="inlineStr"/>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136631248</t>
+          <t>https://artportalen.se/Sighting/133115563</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>136346607</v>
+        <v>136330004</v>
       </c>
       <c r="B147" t="n">
-        <v>58162</v>
+        <v>58167</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16762,10 +16773,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>686529</v>
+        <v>686477</v>
       </c>
       <c r="R147" t="n">
-        <v>6563051</v>
+        <v>6563053</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16792,12 +16803,12 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16823,38 +16834,38 @@
       <c r="AY147" t="inlineStr"/>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136346607</t>
+          <t>https://artportalen.se/Sighting/136330004</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>136346721</v>
+        <v>136422006</v>
       </c>
       <c r="B148" t="n">
-        <v>58162</v>
+        <v>58167</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16872,10 +16883,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>686678</v>
+        <v>686531</v>
       </c>
       <c r="R148" t="n">
-        <v>6563074</v>
+        <v>6563059</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16902,12 +16913,12 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16933,38 +16944,38 @@
       <c r="AY148" t="inlineStr"/>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136346721</t>
+          <t>https://artportalen.se/Sighting/136422006</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>136422024</v>
+        <v>136631248</v>
       </c>
       <c r="B149" t="n">
-        <v>58162</v>
+        <v>58167</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16982,10 +16993,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>686531</v>
+        <v>686469</v>
       </c>
       <c r="R149" t="n">
-        <v>6563059</v>
+        <v>6563013</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17012,12 +17023,12 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17043,13 +17054,13 @@
       <c r="AY149" t="inlineStr"/>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136422024</t>
+          <t>https://artportalen.se/Sighting/136631248</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>136557077</v>
+        <v>136346607</v>
       </c>
       <c r="B150" t="n">
         <v>58162</v>
@@ -17092,10 +17103,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>686733</v>
+        <v>686529</v>
       </c>
       <c r="R150" t="n">
-        <v>6563216</v>
+        <v>6563051</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17122,12 +17133,12 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17153,16 +17164,16 @@
       <c r="AY150" t="inlineStr"/>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136557077</t>
+          <t>https://artportalen.se/Sighting/136346607</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>136259916</v>
+        <v>136346721</v>
       </c>
       <c r="B151" t="n">
-        <v>8463</v>
+        <v>58162</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17170,30 +17181,29 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>106545</v>
+        <v>103023</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr"/>
       <c r="M151" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N151" t="inlineStr"/>
@@ -17203,10 +17213,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>686457</v>
+        <v>686678</v>
       </c>
       <c r="R151" t="n">
-        <v>6563062</v>
+        <v>6563074</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17233,12 +17243,12 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17247,7 +17257,6 @@
       <c r="AE151" t="b">
         <v>0</v>
       </c>
-      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>
@@ -17265,16 +17274,16 @@
       <c r="AY151" t="inlineStr"/>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136259916</t>
+          <t>https://artportalen.se/Sighting/136346721</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>136330063</v>
+        <v>136422024</v>
       </c>
       <c r="B152" t="n">
-        <v>8463</v>
+        <v>58162</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17282,30 +17291,29 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>106545</v>
+        <v>103023</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr"/>
       <c r="M152" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N152" t="inlineStr"/>
@@ -17315,10 +17323,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>686661</v>
+        <v>686531</v>
       </c>
       <c r="R152" t="n">
-        <v>6563103</v>
+        <v>6563059</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17345,12 +17353,12 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17359,7 +17367,6 @@
       <c r="AE152" t="b">
         <v>0</v>
       </c>
-      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
@@ -17377,52 +17384,56 @@
       <c r="AY152" t="inlineStr"/>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136330063</t>
+          <t>https://artportalen.se/Sighting/136422024</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>109890506</v>
+        <v>136557077</v>
       </c>
       <c r="B153" t="n">
-        <v>99118</v>
+        <v>58162</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>220787</v>
+        <v>103023</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
-      <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Ö Norrby Mosse, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>686831</v>
+        <v>686733</v>
       </c>
       <c r="R153" t="n">
         <v>6563216</v>
@@ -17452,12 +17463,12 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17466,7 +17477,6 @@
       <c r="AE153" t="b">
         <v>0</v>
       </c>
-      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
       </c>
@@ -17484,55 +17494,60 @@
       <c r="AY153" t="inlineStr"/>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109890506</t>
+          <t>https://artportalen.se/Sighting/136557077</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>122781008</v>
+        <v>136259916</v>
       </c>
       <c r="B154" t="n">
-        <v>99118</v>
+        <v>8463</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Knärot, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>686833</v>
+        <v>686457</v>
       </c>
       <c r="R154" t="n">
-        <v>6563215</v>
+        <v>6563062</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17559,17 +17574,12 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>Knärot</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17585,63 +17595,60 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122781008</t>
+          <t>https://artportalen.se/Sighting/136259916</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126418709</v>
+        <v>136330063</v>
       </c>
       <c r="B155" t="n">
-        <v>99118</v>
+        <v>8463</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
@@ -17649,10 +17656,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>686771</v>
+        <v>686661</v>
       </c>
       <c r="R155" t="n">
-        <v>6563297</v>
+        <v>6563103</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17679,17 +17686,12 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>Två av dem i knopp, ca 3 m väster om de andra.</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17716,13 +17718,13 @@
       <c r="AY155" t="inlineStr"/>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126418709</t>
+          <t>https://artportalen.se/Sighting/136330063</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>126418756</v>
+        <v>109890506</v>
       </c>
       <c r="B156" t="n">
         <v>99118</v>
@@ -17750,29 +17752,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr"/>
       <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Ö Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>686781</v>
+        <v>686831</v>
       </c>
       <c r="R156" t="n">
-        <v>6563292</v>
+        <v>6563216</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17799,17 +17793,12 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>En av dem i knopp.</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17836,13 +17825,13 @@
       <c r="AY156" t="inlineStr"/>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126418756</t>
+          <t>https://artportalen.se/Sighting/109890506</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129564285</v>
+        <v>122781008</v>
       </c>
       <c r="B157" t="n">
         <v>99118</v>
@@ -17877,14 +17866,14 @@
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Knärot, Srm</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>686625</v>
+        <v>686833</v>
       </c>
       <c r="R157" t="n">
-        <v>6563000</v>
+        <v>6563215</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17911,12 +17900,17 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17932,59 +17926,59 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129564285</t>
+          <t>https://artportalen.se/Sighting/122781008</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>126234373</v>
+        <v>126418709</v>
       </c>
       <c r="B158" t="n">
-        <v>106244</v>
+        <v>99118</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
@@ -17992,14 +17986,14 @@
       <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Norrby mosse SO, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>686756</v>
+        <v>686771</v>
       </c>
       <c r="R158" t="n">
-        <v>6563092</v>
+        <v>6563297</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18026,12 +18020,17 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>Två av dem i knopp, ca 3 m väster om de andra.</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -18047,69 +18046,77 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126234373</t>
+          <t>https://artportalen.se/Sighting/126418709</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>122929342</v>
+        <v>126418756</v>
       </c>
       <c r="B159" t="n">
-        <v>97986</v>
+        <v>99118</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>221946</v>
+        <v>220787</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr"/>
       <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>686569</v>
+        <v>686781</v>
       </c>
       <c r="R159" t="n">
-        <v>6562949</v>
+        <v>6563292</v>
       </c>
       <c r="S159" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -18133,22 +18140,17 @@
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>10:52</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>10:52</t>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>En av dem i knopp.</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -18157,64 +18159,61 @@
       <c r="AE159" t="b">
         <v>0</v>
       </c>
+      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122929342</t>
+          <t>https://artportalen.se/Sighting/126418756</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>134487656</v>
+        <v>129564285</v>
       </c>
       <c r="B160" t="n">
-        <v>99217</v>
+        <v>99118</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr"/>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr"/>
       <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
@@ -18223,10 +18222,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>686835</v>
+        <v>686625</v>
       </c>
       <c r="R160" t="n">
-        <v>6563212</v>
+        <v>6563000</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18253,17 +18252,12 @@
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>2 i blom samt några plantor med endast blad.</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -18290,54 +18284,63 @@
       <c r="AY160" t="inlineStr"/>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134487656</t>
+          <t>https://artportalen.se/Sighting/129564285</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>118843519</v>
+        <v>126234373</v>
       </c>
       <c r="B161" t="n">
-        <v>91431</v>
+        <v>106244</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6039941</v>
+        <v>221144</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Gelatinfingersvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Ramaria primulina</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
       <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Norrby Mosse, Srm</t>
+          <t>Norrby mosse SO, Srm</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>686668</v>
+        <v>686756</v>
       </c>
       <c r="R161" t="n">
-        <v>6563218</v>
+        <v>6563092</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18364,17 +18367,12 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
-        </is>
-      </c>
-      <c r="AC161" t="inlineStr">
-        <is>
-          <t>Kollekt BR55. Dublett av tidigare fynd för att rapportera resultat av sekvensering. Ursprungligt fynd rapporterat av Bodil Ravn och finns här https://www.artportalen.se/Sighting/112337794</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18390,31 +18388,27 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY161" t="inlineStr">
-        <is>
-          <t>Fynd med DNA-sekvens - extern</t>
-        </is>
-      </c>
+          <t>Ulf Johansson, Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr"/>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118843519</t>
+          <t>https://artportalen.se/Sighting/126234373</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>122203249</v>
+        <v>122929342</v>
       </c>
       <c r="B162" t="n">
-        <v>96554</v>
+        <v>97986</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18422,49 +18416,41 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>210</v>
+        <v>221946</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr"/>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+      <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr"/>
       <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Ö Norrbytorp, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>687968</v>
+        <v>686569</v>
       </c>
       <c r="R162" t="n">
-        <v>6562733</v>
+        <v>6562949</v>
       </c>
       <c r="S162" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -18488,17 +18474,22 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
-        </is>
-      </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>På murken granlåga i äldre skog.</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18507,34 +18498,33 @@
       <c r="AE162" t="b">
         <v>0</v>
       </c>
-      <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="b">
         <v>0</v>
       </c>
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122203249</t>
+          <t>https://artportalen.se/Sighting/122929342</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>122780924</v>
+        <v>134487656</v>
       </c>
       <c r="B163" t="n">
-        <v>96554</v>
+        <v>99217</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18542,38 +18532,42 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>210</v>
+        <v>221952</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr"/>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr"/>
       <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Grön sköldmossa, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>687970</v>
+        <v>686835</v>
       </c>
       <c r="R163" t="n">
-        <v>6562732</v>
+        <v>6563212</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18600,17 +18594,17 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>Grön sköldmossa på rutten stam</t>
+          <t>2 i blom samt några plantor med endast blad.</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18626,27 +18620,27 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122780924</t>
+          <t>https://artportalen.se/Sighting/134487656</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129624531</v>
+        <v>118843519</v>
       </c>
       <c r="B164" t="n">
-        <v>90946</v>
+        <v>91431</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18654,21 +18648,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>889</v>
+        <v>6039941</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Vintertagging</t>
+          <t>Gelatinfingersvamp</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Plicatura pendula</t>
+          <t>Ramaria primulina</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -18677,14 +18671,14 @@
       <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>687931</v>
+        <v>686668</v>
       </c>
       <c r="R164" t="n">
-        <v>6562811</v>
+        <v>6563218</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18711,12 +18705,17 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>Kollekt BR55. Dublett av tidigare fynd för att rapportera resultat av sekvensering. Ursprungligt fynd rapporterat av Bodil Ravn och finns här https://www.artportalen.se/Sighting/112337794</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -18732,65 +18731,78 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
-        </is>
-      </c>
-      <c r="AY164" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr">
+        <is>
+          <t>Fynd med DNA-sekvens - extern</t>
+        </is>
+      </c>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129624531</t>
+          <t>https://artportalen.se/Sighting/118843519</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129624696</v>
+        <v>122203249</v>
       </c>
       <c r="B165" t="n">
-        <v>90946</v>
+        <v>96554</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>889</v>
+        <v>210</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vintertagging</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Plicatura pendula</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
       <c r="J165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr"/>
       <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Ö Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>687973</v>
+        <v>687968</v>
       </c>
       <c r="R165" t="n">
-        <v>6562815</v>
+        <v>6562733</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18817,17 +18829,17 @@
       </c>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="AC165" t="inlineStr">
         <is>
-          <t>På död tall.</t>
+          <t>På murken granlåga i äldre skog.</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18854,54 +18866,55 @@
       <c r="AY165" t="inlineStr"/>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129624696</t>
+          <t>https://artportalen.se/Sighting/122203249</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>122203275</v>
+        <v>122780924</v>
       </c>
       <c r="B166" t="n">
-        <v>91909</v>
+        <v>96554</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>1202</v>
+        <v>210</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
       <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Ö Norrbytorp, Srm</t>
+          <t>Grön sköldmossa, Srm</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>687981</v>
+        <v>687970</v>
       </c>
       <c r="R166" t="n">
-        <v>6562724</v>
+        <v>6562732</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18928,12 +18941,17 @@
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa på rutten stam</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18949,56 +18967,52 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122203275</t>
+          <t>https://artportalen.se/Sighting/122780924</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>135358856</v>
+        <v>129624531</v>
       </c>
       <c r="B167" t="n">
-        <v>91573</v>
+        <v>90946</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>2051</v>
+        <v>889</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Plicatura pendula</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
       <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr"/>
       <c r="N167" t="inlineStr"/>
@@ -19008,10 +19022,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>688004</v>
+        <v>687931</v>
       </c>
       <c r="R167" t="n">
-        <v>6562799</v>
+        <v>6562811</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19038,12 +19052,12 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -19070,58 +19084,57 @@
       <c r="AY167" t="inlineStr"/>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358856</t>
+          <t>https://artportalen.se/Sighting/129624531</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>136241603</v>
+        <v>129624696</v>
       </c>
       <c r="B168" t="n">
-        <v>96931</v>
+        <v>90946</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>2180</v>
+        <v>889</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Plicatura pendula</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr"/>
-      <c r="L168" t="inlineStr"/>
       <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Norrbytorp, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>688059</v>
+        <v>687973</v>
       </c>
       <c r="R168" t="n">
-        <v>6562773</v>
+        <v>6562815</v>
       </c>
       <c r="S168" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -19145,22 +19158,17 @@
       </c>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="Z168" t="inlineStr">
-        <is>
-          <t>13:09</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="AB168" t="inlineStr">
-        <is>
-          <t>13:09</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC168" t="inlineStr">
+        <is>
+          <t>På död tall.</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -19176,62 +19184,65 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Björn Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Björn Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136241603</t>
+          <t>https://artportalen.se/Sighting/129624696</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>136231090</v>
+        <v>122203275</v>
       </c>
       <c r="B169" t="n">
-        <v>96649</v>
+        <v>91909</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>2671</v>
+        <v>1202</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Norrby torp, Norrby torp, Srm</t>
+          <t>Ö Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>688046</v>
+        <v>687981</v>
       </c>
       <c r="R169" t="n">
-        <v>6562700</v>
+        <v>6562724</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19258,12 +19269,12 @@
       </c>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -19272,58 +19283,63 @@
       <c r="AE169" t="b">
         <v>0</v>
       </c>
+      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
       </c>
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136231090</t>
+          <t>https://artportalen.se/Sighting/122203275</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>136697134</v>
+        <v>135358856</v>
       </c>
       <c r="B170" t="n">
-        <v>93404</v>
+        <v>91573</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>4364</v>
+        <v>2051</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr"/>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr"/>
       <c r="N170" t="inlineStr"/>
@@ -19333,10 +19349,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>688040</v>
+        <v>688004</v>
       </c>
       <c r="R170" t="n">
-        <v>6562791</v>
+        <v>6562799</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19363,12 +19379,12 @@
       </c>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19395,16 +19411,16 @@
       <c r="AY170" t="inlineStr"/>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136697134</t>
+          <t>https://artportalen.se/Sighting/135358856</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128314411</v>
+        <v>136241603</v>
       </c>
       <c r="B171" t="n">
-        <v>92348</v>
+        <v>96931</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19412,48 +19428,41 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>5420</v>
+        <v>2180</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J171" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
       <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>688088</v>
+        <v>688059</v>
       </c>
       <c r="R171" t="n">
-        <v>6562722</v>
+        <v>6562773</v>
       </c>
       <c r="S171" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -19477,12 +19486,22 @@
       </c>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19498,27 +19517,27 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Björn Persson</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Björn Persson</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128314411</t>
+          <t>https://artportalen.se/Sighting/136241603</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>136394237</v>
+        <v>136231090</v>
       </c>
       <c r="B172" t="n">
-        <v>92517</v>
+        <v>96649</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19526,37 +19545,37 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>5420</v>
+        <v>2671</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Norrbytorp, Srm</t>
+          <t>Norrby torp, Norrby torp, Srm</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>688093</v>
+        <v>688046</v>
       </c>
       <c r="R172" t="n">
-        <v>6562720</v>
+        <v>6562700</v>
       </c>
       <c r="S172" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -19583,19 +19602,9 @@
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="Z172" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="AB172" t="inlineStr">
-        <is>
-          <t>12:05</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -19610,49 +19619,49 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136394237</t>
+          <t>https://artportalen.se/Sighting/136231090</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>136268106</v>
+        <v>136697134</v>
       </c>
       <c r="B173" t="n">
-        <v>92069</v>
+        <v>93404</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -19665,10 +19674,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>687910</v>
+        <v>688040</v>
       </c>
       <c r="R173" t="n">
-        <v>6562787</v>
+        <v>6562791</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19695,17 +19704,12 @@
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="AC173" t="inlineStr">
-        <is>
-          <t>På rätt klen, senvuxen?, lutande granlåga i ett kärr.</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19732,16 +19736,16 @@
       <c r="AY173" t="inlineStr"/>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136268106</t>
+          <t>https://artportalen.se/Sighting/136697134</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>136697126</v>
+        <v>128314411</v>
       </c>
       <c r="B174" t="n">
-        <v>92069</v>
+        <v>92348</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19749,25 +19753,33 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>5447</v>
+        <v>5420</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr"/>
-      <c r="J174" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K174" t="inlineStr"/>
       <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
@@ -19776,10 +19788,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>687998</v>
+        <v>688088</v>
       </c>
       <c r="R174" t="n">
-        <v>6562803</v>
+        <v>6562722</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19806,12 +19818,12 @@
       </c>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19838,57 +19850,54 @@
       <c r="AY174" t="inlineStr"/>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136697126</t>
+          <t>https://artportalen.se/Sighting/128314411</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>128314833</v>
+        <v>136394237</v>
       </c>
       <c r="B175" t="n">
-        <v>93235</v>
+        <v>92517</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>5966</v>
+        <v>5420</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
-      <c r="J175" t="inlineStr"/>
-      <c r="K175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>688073</v>
+        <v>688093</v>
       </c>
       <c r="R175" t="n">
-        <v>6562768</v>
+        <v>6562720</v>
       </c>
       <c r="S175" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -19912,12 +19921,22 @@
       </c>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="Z175" t="inlineStr">
+        <is>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AB175" t="inlineStr">
+        <is>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19926,56 +19945,55 @@
       <c r="AE175" t="b">
         <v>0</v>
       </c>
-      <c r="AF175" t="inlineStr"/>
       <c r="AG175" t="b">
         <v>0</v>
       </c>
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128314833</t>
+          <t>https://artportalen.se/Sighting/136394237</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128317789</v>
+        <v>136268106</v>
       </c>
       <c r="B176" t="n">
-        <v>93235</v>
+        <v>92069</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -19988,10 +20006,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>688094</v>
+        <v>687910</v>
       </c>
       <c r="R176" t="n">
-        <v>6562777</v>
+        <v>6562787</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -20018,12 +20036,17 @@
       </c>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>På rätt klen, senvuxen?, lutande granlåga i ett kärr.</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -20050,38 +20073,38 @@
       <c r="AY176" t="inlineStr"/>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128317789</t>
+          <t>https://artportalen.se/Sighting/136268106</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128526064</v>
+        <v>136697126</v>
       </c>
       <c r="B177" t="n">
-        <v>93235</v>
+        <v>92069</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -20094,10 +20117,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>687952</v>
+        <v>687998</v>
       </c>
       <c r="R177" t="n">
-        <v>6562790</v>
+        <v>6562803</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -20124,12 +20147,12 @@
       </c>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20156,13 +20179,13 @@
       <c r="AY177" t="inlineStr"/>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128526064</t>
+          <t>https://artportalen.se/Sighting/136697126</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128646583</v>
+        <v>128314833</v>
       </c>
       <c r="B178" t="n">
         <v>93235</v>
@@ -20200,10 +20223,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>688067</v>
+        <v>688073</v>
       </c>
       <c r="R178" t="n">
-        <v>6562731</v>
+        <v>6562768</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20230,12 +20253,12 @@
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -20262,16 +20285,16 @@
       <c r="AY178" t="inlineStr"/>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128646583</t>
+          <t>https://artportalen.se/Sighting/128314833</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>136241765</v>
+        <v>128317789</v>
       </c>
       <c r="B179" t="n">
-        <v>80093</v>
+        <v>93235</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20279,44 +20302,40 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr"/>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K179" t="inlineStr"/>
       <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Norrbytorp, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>688014</v>
+        <v>688094</v>
       </c>
       <c r="R179" t="n">
-        <v>6562734</v>
+        <v>6562777</v>
       </c>
       <c r="S179" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -20340,22 +20359,12 @@
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="Z179" t="inlineStr">
-        <is>
-          <t>12:38</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="AB179" t="inlineStr">
-        <is>
-          <t>12:38</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -20371,27 +20380,27 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Björn Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Björn Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136241765</t>
+          <t>https://artportalen.se/Sighting/128317789</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>17285491</v>
+        <v>128526064</v>
       </c>
       <c r="B180" t="n">
-        <v>80432</v>
+        <v>93235</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20399,36 +20408,37 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6458</v>
+        <v>5966</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr"/>
+      <c r="N180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Norrby torp, 480 m Ö, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>688111</v>
+        <v>687952</v>
       </c>
       <c r="R180" t="n">
-        <v>6562706</v>
+        <v>6562790</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20455,17 +20465,12 @@
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>2015-04-02</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>2015-04-02</t>
-        </is>
-      </c>
-      <c r="AC180" t="inlineStr">
-        <is>
-          <t>På ek i bergskanten, ca 220 cm omkrets. Sparsamt vid 20 resp. 70 cm höjd.</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -20474,38 +20479,34 @@
       <c r="AE180" t="b">
         <v>0</v>
       </c>
+      <c r="AF180" t="inlineStr"/>
       <c r="AG180" t="b">
         <v>0</v>
-      </c>
-      <c r="AI180" t="inlineStr">
-        <is>
-          <t>Yngre gallrad blandskog</t>
-        </is>
       </c>
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/17285491</t>
+          <t>https://artportalen.se/Sighting/128526064</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>79273786</v>
+        <v>128646583</v>
       </c>
       <c r="B181" t="n">
-        <v>80432</v>
+        <v>93235</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20513,34 +20514,37 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6458</v>
+        <v>5966</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr"/>
+      <c r="N181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Åvadal, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>688109</v>
+        <v>688067</v>
       </c>
       <c r="R181" t="n">
-        <v>6562704</v>
+        <v>6562731</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20567,12 +20571,12 @@
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2019-08-01</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2019-08-01</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -20581,48 +20585,34 @@
       <c r="AE181" t="b">
         <v>0</v>
       </c>
+      <c r="AF181" t="inlineStr"/>
       <c r="AG181" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ181" t="inlineStr">
-        <is>
-          <t>skogsek</t>
-        </is>
-      </c>
-      <c r="AK181" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
-      </c>
-      <c r="AO181" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
       </c>
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Gustav Wikström</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Gustav Wikström</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/79273786</t>
+          <t>https://artportalen.se/Sighting/128646583</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>89840770</v>
+        <v>136241765</v>
       </c>
       <c r="B182" t="n">
-        <v>80432</v>
+        <v>80093</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20630,40 +20620,44 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="J182" t="inlineStr"/>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Ö Norrby Torp, Srm</t>
+          <t>Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>688146</v>
+        <v>688014</v>
       </c>
       <c r="R182" t="n">
-        <v>6562738</v>
+        <v>6562734</v>
       </c>
       <c r="S182" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -20687,17 +20681,22 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2020-12-30</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="Z182" t="inlineStr">
+        <is>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2020-12-30</t>
-        </is>
-      </c>
-      <c r="AC182" t="inlineStr">
-        <is>
-          <t>Tre bålar på en ek som inte längre ser ut att vara så livskraftig. Finns en annan noterad ek med lavar en bit ifrån.</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AB182" t="inlineStr">
+        <is>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -20713,24 +20712,24 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Björn Persson</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Björn Persson</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89840770</t>
+          <t>https://artportalen.se/Sighting/136241765</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>112384453</v>
+        <v>17285491</v>
       </c>
       <c r="B183" t="n">
         <v>80432</v>
@@ -20761,17 +20760,16 @@
       <c r="I183" t="inlineStr"/>
       <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr"/>
-      <c r="N183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Norrby torp Ö om, Srm</t>
+          <t>Norrby torp, 480 m Ö, Srm</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>688145</v>
+        <v>688111</v>
       </c>
       <c r="R183" t="n">
-        <v>6562737</v>
+        <v>6562706</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20798,17 +20796,17 @@
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2015-04-02</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2015-04-02</t>
         </is>
       </c>
       <c r="AC183" t="inlineStr">
         <is>
-          <t>Återfynd. På halvdöd ek med blottad ved men några levande grenar i toppen, ca 120 cm omkrets. Två mindre blaffor i dåligt skick, hänger något löst, ca 40 resp. 130 cm höjd.</t>
+          <t>På ek i bergskanten, ca 220 cm omkrets. Sparsamt vid 20 resp. 70 cm höjd.</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -20817,9 +20815,13 @@
       <c r="AE183" t="b">
         <v>0</v>
       </c>
-      <c r="AF183" t="inlineStr"/>
       <c r="AG183" t="b">
         <v>0</v>
+      </c>
+      <c r="AI183" t="inlineStr">
+        <is>
+          <t>Yngre gallrad blandskog</t>
+        </is>
       </c>
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
@@ -20829,19 +20831,19 @@
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112384453</t>
+          <t>https://artportalen.se/Sighting/17285491</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>122779297</v>
+        <v>79273786</v>
       </c>
       <c r="B184" t="n">
         <v>80432</v>
@@ -20870,19 +20872,16 @@
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
-      <c r="J184" t="inlineStr"/>
-      <c r="K184" t="inlineStr"/>
-      <c r="N184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Lunglav, Srm</t>
+          <t>Åvadal, Srm</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>688116</v>
+        <v>688109</v>
       </c>
       <c r="R184" t="n">
-        <v>6562703</v>
+        <v>6562704</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20909,17 +20908,12 @@
       </c>
       <c r="Y184" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2019-08-01</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC184" t="inlineStr">
-        <is>
-          <t>Lunglav på gammal ek</t>
+          <t>2019-08-01</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -20928,88 +20922,89 @@
       <c r="AE184" t="b">
         <v>0</v>
       </c>
-      <c r="AF184" t="inlineStr"/>
       <c r="AG184" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ184" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK184" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO184" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
       </c>
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Gustav Wikström</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Gustav Wikström</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122779297</t>
+          <t>https://artportalen.se/Sighting/79273786</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>125923864</v>
+        <v>89840770</v>
       </c>
       <c r="B185" t="n">
-        <v>57754</v>
+        <v>80432</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>102118</v>
+        <v>6458</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr"/>
-      <c r="L185" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M185" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
       <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Ö Norrby Torp, Srm</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>687916</v>
+        <v>688146</v>
       </c>
       <c r="R185" t="n">
-        <v>6562815</v>
+        <v>6562738</v>
       </c>
       <c r="S185" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -21033,17 +21028,17 @@
       </c>
       <c r="Y185" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2020-12-30</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2020-12-30</t>
         </is>
       </c>
       <c r="AC185" t="inlineStr">
         <is>
-          <t>Stöttes och stannade nära, det fanns ett ägg. Än så länge?</t>
+          <t>Tre bålar på en ek som inte längre ser ut att vara så livskraftig. Finns en annan noterad ek med lavar en bit ifrån.</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -21052,6 +21047,7 @@
       <c r="AE185" t="b">
         <v>0</v>
       </c>
+      <c r="AF185" t="inlineStr"/>
       <c r="AG185" t="b">
         <v>0</v>
       </c>
@@ -21069,16 +21065,16 @@
       <c r="AY185" t="inlineStr"/>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125923864</t>
+          <t>https://artportalen.se/Sighting/89840770</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>128317861</v>
+        <v>112384453</v>
       </c>
       <c r="B186" t="n">
-        <v>58114</v>
+        <v>80432</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21086,45 +21082,40 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr"/>
-      <c r="L186" t="inlineStr"/>
-      <c r="M186" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrby torp Ö om, Srm</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>688058</v>
+        <v>688145</v>
       </c>
       <c r="R186" t="n">
-        <v>6562805</v>
+        <v>6562737</v>
       </c>
       <c r="S186" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -21148,12 +21139,17 @@
       </c>
       <c r="Y186" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>Återfynd. På halvdöd ek med blottad ved men några levande grenar i toppen, ca 120 cm omkrets. Två mindre blaffor i dåligt skick, hänger något löst, ca 40 resp. 130 cm höjd.</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -21162,33 +21158,34 @@
       <c r="AE186" t="b">
         <v>0</v>
       </c>
+      <c r="AF186" t="inlineStr"/>
       <c r="AG186" t="b">
         <v>0</v>
       </c>
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128317861</t>
+          <t>https://artportalen.se/Sighting/112384453</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>136138855</v>
+        <v>122779297</v>
       </c>
       <c r="B187" t="n">
-        <v>58167</v>
+        <v>80432</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21196,42 +21193,37 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr"/>
-      <c r="L187" t="inlineStr"/>
-      <c r="M187" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Lunglav, Srm</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>687836</v>
+        <v>688116</v>
       </c>
       <c r="R187" t="n">
-        <v>6562786</v>
+        <v>6562703</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21258,12 +21250,17 @@
       </c>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC187" t="inlineStr">
+        <is>
+          <t>Lunglav på gammal ek</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -21272,63 +21269,72 @@
       <c r="AE187" t="b">
         <v>0</v>
       </c>
+      <c r="AF187" t="inlineStr"/>
       <c r="AG187" t="b">
         <v>0</v>
       </c>
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136138855</t>
+          <t>https://artportalen.se/Sighting/122779297</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>136138971</v>
+        <v>125923864</v>
       </c>
       <c r="B188" t="n">
-        <v>58167</v>
+        <v>57754</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>103021</v>
+        <v>102118</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K188" t="inlineStr"/>
-      <c r="L188" t="inlineStr"/>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>bo, ägg/ungar</t>
         </is>
       </c>
       <c r="N188" t="inlineStr"/>
@@ -21338,10 +21344,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>687977</v>
+        <v>687916</v>
       </c>
       <c r="R188" t="n">
-        <v>6562735</v>
+        <v>6562815</v>
       </c>
       <c r="S188" t="n">
         <v>25</v>
@@ -21368,12 +21374,17 @@
       </c>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AC188" t="inlineStr">
+        <is>
+          <t>Stöttes och stannade nära, det fanns ett ägg. Än så länge?</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -21399,71 +21410,62 @@
       <c r="AY188" t="inlineStr"/>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136138971</t>
+          <t>https://artportalen.se/Sighting/125923864</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>122692266</v>
+        <v>128317861</v>
       </c>
       <c r="B189" t="n">
-        <v>58826</v>
+        <v>58114</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>208242</v>
+        <v>103021</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J189" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr"/>
       <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr"/>
       <c r="M189" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N189" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>687868</v>
+        <v>688058</v>
       </c>
       <c r="R189" t="n">
-        <v>6562755</v>
+        <v>6562805</v>
       </c>
       <c r="S189" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -21487,17 +21489,12 @@
       </c>
       <c r="Y189" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AC189" t="inlineStr">
-        <is>
-          <t>Mindre vattensalamander</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -21506,63 +21503,65 @@
       <c r="AE189" t="b">
         <v>0</v>
       </c>
-      <c r="AF189" t="inlineStr"/>
       <c r="AG189" t="b">
         <v>0</v>
       </c>
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122692266</t>
+          <t>https://artportalen.se/Sighting/128317861</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>136241491</v>
+        <v>136138855</v>
       </c>
       <c r="B190" t="n">
-        <v>58843</v>
+        <v>58167</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>208245</v>
+        <v>103021</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
-      <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr"/>
       <c r="L190" t="inlineStr"/>
-      <c r="M190" t="inlineStr"/>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
@@ -21570,10 +21569,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>687873</v>
+        <v>687836</v>
       </c>
       <c r="R190" t="n">
-        <v>6562755</v>
+        <v>6562786</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21600,17 +21599,12 @@
       </c>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="AC190" t="inlineStr">
-        <is>
-          <t>Troligen årsunge.</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -21619,7 +21613,6 @@
       <c r="AE190" t="b">
         <v>0</v>
       </c>
-      <c r="AF190" t="inlineStr"/>
       <c r="AG190" t="b">
         <v>0</v>
       </c>
@@ -21637,55 +21630,59 @@
       <c r="AY190" t="inlineStr"/>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136241491</t>
+          <t>https://artportalen.se/Sighting/136138855</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>101544040</v>
+        <v>136138971</v>
       </c>
       <c r="B191" t="n">
-        <v>99035</v>
+        <v>58167</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
-      <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr"/>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>NO Norrby Torp, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>687896</v>
+        <v>687977</v>
       </c>
       <c r="R191" t="n">
-        <v>6562764</v>
+        <v>6562735</v>
       </c>
       <c r="S191" t="n">
         <v>25</v>
@@ -21712,12 +21709,12 @@
       </c>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>2022-06-09</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>2022-06-09</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -21726,7 +21723,6 @@
       <c r="AE191" t="b">
         <v>0</v>
       </c>
-      <c r="AF191" t="inlineStr"/>
       <c r="AG191" t="b">
         <v>0</v>
       </c>
@@ -21744,16 +21740,16 @@
       <c r="AY191" t="inlineStr"/>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101544040</t>
+          <t>https://artportalen.se/Sighting/136138971</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>136394236</v>
+        <v>122692266</v>
       </c>
       <c r="B192" t="n">
-        <v>98208</v>
+        <v>58826</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21761,37 +21757,54 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>221945</v>
+        <v>208242</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Norrbytorp, Srm</t>
+          <t>Mindre vattensalamander, Srm</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>687882</v>
+        <v>687868</v>
       </c>
       <c r="R192" t="n">
-        <v>6562761</v>
+        <v>6562755</v>
       </c>
       <c r="S192" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -21815,22 +21828,17 @@
       </c>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="Z192" t="inlineStr">
-        <is>
-          <t>11:26</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="AB192" t="inlineStr">
-        <is>
-          <t>11:26</t>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AC192" t="inlineStr">
+        <is>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -21839,33 +21847,34 @@
       <c r="AE192" t="b">
         <v>0</v>
       </c>
+      <c r="AF192" t="inlineStr"/>
       <c r="AG192" t="b">
         <v>0</v>
       </c>
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136394236</t>
+          <t>https://artportalen.se/Sighting/122692266</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>122930166</v>
+        <v>136241491</v>
       </c>
       <c r="B193" t="n">
-        <v>96554</v>
+        <v>58843</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21873,41 +21882,42 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>210</v>
+        <v>208245</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr"/>
       <c r="L193" t="inlineStr"/>
+      <c r="M193" t="inlineStr"/>
       <c r="N193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>686762</v>
+        <v>687873</v>
       </c>
       <c r="R193" t="n">
-        <v>6562715</v>
+        <v>6562755</v>
       </c>
       <c r="S193" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -21931,22 +21941,17 @@
       </c>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="Z193" t="inlineStr">
-        <is>
-          <t>11:21</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="AB193" t="inlineStr">
-        <is>
-          <t>11:21</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>Troligen årsunge.</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -21955,74 +21960,76 @@
       <c r="AE193" t="b">
         <v>0</v>
       </c>
+      <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="b">
         <v>0</v>
       </c>
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122930166</t>
+          <t>https://artportalen.se/Sighting/136241491</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>119061006</v>
+        <v>101544040</v>
       </c>
       <c r="B194" t="n">
-        <v>91533</v>
+        <v>99035</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>2051</v>
+        <v>219790</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
       <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr"/>
       <c r="N194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>S Norrby mosse, Srm</t>
+          <t>NO Norrby Torp, Srm</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>686477</v>
+        <v>687896</v>
       </c>
       <c r="R194" t="n">
-        <v>6562857</v>
+        <v>6562764</v>
       </c>
       <c r="S194" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -22046,17 +22053,12 @@
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2022-06-09</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC194" t="inlineStr">
-        <is>
-          <t>Brukad skog nära kant mot gammal.</t>
+          <t>2022-06-09</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -22083,16 +22085,16 @@
       <c r="AY194" t="inlineStr"/>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119061006</t>
+          <t>https://artportalen.se/Sighting/101544040</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>122929535</v>
+        <v>136394236</v>
       </c>
       <c r="B195" t="n">
-        <v>8455</v>
+        <v>98208</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -22100,46 +22102,37 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>106545</v>
+        <v>221945</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J195" t="inlineStr"/>
-      <c r="K195" t="inlineStr"/>
-      <c r="L195" t="inlineStr"/>
-      <c r="M195" t="inlineStr"/>
-      <c r="N195" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>686612</v>
+        <v>687882</v>
       </c>
       <c r="R195" t="n">
-        <v>6562882</v>
+        <v>6562761</v>
       </c>
       <c r="S195" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -22163,22 +22156,22 @@
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -22193,27 +22186,27 @@
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122929535</t>
+          <t>https://artportalen.se/Sighting/136394236</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>122928987</v>
+        <v>122930166</v>
       </c>
       <c r="B196" t="n">
-        <v>97983</v>
+        <v>96554</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22221,21 +22214,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>221945</v>
+        <v>210</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -22249,13 +22242,13 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>686389</v>
+        <v>686762</v>
       </c>
       <c r="R196" t="n">
-        <v>6562967</v>
+        <v>6562715</v>
       </c>
       <c r="S196" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
@@ -22284,7 +22277,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -22294,7 +22287,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -22320,51 +22313,54 @@
       <c r="AY196" t="inlineStr"/>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122928987</t>
+          <t>https://artportalen.se/Sighting/122930166</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>126061106</v>
+        <v>119061006</v>
       </c>
       <c r="B197" t="n">
-        <v>91333</v>
+        <v>91533</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>2008</v>
+        <v>2051</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Pers., nom.sanct.</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr"/>
+      <c r="N197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>S Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>686883</v>
+        <v>686477</v>
       </c>
       <c r="R197" t="n">
-        <v>6562742</v>
+        <v>6562857</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -22391,22 +22387,17 @@
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z197" t="inlineStr">
-        <is>
-          <t>13:23</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB197" t="inlineStr">
-        <is>
-          <t>13:23</t>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC197" t="inlineStr">
+        <is>
+          <t>Brukad skog nära kant mot gammal.</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -22415,33 +22406,34 @@
       <c r="AE197" t="b">
         <v>0</v>
       </c>
+      <c r="AF197" t="inlineStr"/>
       <c r="AG197" t="b">
         <v>0</v>
       </c>
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061106</t>
+          <t>https://artportalen.se/Sighting/119061006</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>126061107</v>
+        <v>122929535</v>
       </c>
       <c r="B198" t="n">
-        <v>96458</v>
+        <v>8455</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -22449,37 +22441,46 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>2818</v>
+        <v>106545</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr"/>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr"/>
+      <c r="M198" t="inlineStr"/>
+      <c r="N198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>686880</v>
+        <v>686612</v>
       </c>
       <c r="R198" t="n">
-        <v>6562745</v>
+        <v>6562882</v>
       </c>
       <c r="S198" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -22503,22 +22504,22 @@
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -22533,27 +22534,27 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061107</t>
+          <t>https://artportalen.se/Sighting/122929535</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129215187</v>
+        <v>122928987</v>
       </c>
       <c r="B199" t="n">
-        <v>91872</v>
+        <v>97983</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22561,37 +22562,38 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
       <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr"/>
       <c r="N199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>686977</v>
+        <v>686389</v>
       </c>
       <c r="R199" t="n">
-        <v>6562706</v>
+        <v>6562967</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22618,12 +22620,22 @@
       </c>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AB199" t="inlineStr">
+        <is>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -22632,56 +22644,55 @@
       <c r="AE199" t="b">
         <v>0</v>
       </c>
-      <c r="AF199" t="inlineStr"/>
       <c r="AG199" t="b">
         <v>0</v>
       </c>
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215187</t>
+          <t>https://artportalen.se/Sighting/122928987</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>126061104</v>
+        <v>126061106</v>
       </c>
       <c r="B200" t="n">
-        <v>4775</v>
+        <v>91333</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>100299</v>
+        <v>2008</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Pers., nom.sanct.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -22691,10 +22702,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>686868</v>
+        <v>686883</v>
       </c>
       <c r="R200" t="n">
-        <v>6562739</v>
+        <v>6562742</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22726,7 +22737,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -22736,7 +22747,7 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -22747,26 +22758,6 @@
       </c>
       <c r="AG200" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ200" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK200" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL200" t="inlineStr">
-        <is>
-          <t>Stående död gran.</t>
-        </is>
-      </c>
-      <c r="AO200" t="inlineStr">
-        <is>
-          <t>Picea abies # Stående död gran.</t>
-        </is>
       </c>
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
@@ -22782,16 +22773,16 @@
       <c r="AY200" t="inlineStr"/>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061104</t>
+          <t>https://artportalen.se/Sighting/126061106</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>126061116</v>
+        <v>126061107</v>
       </c>
       <c r="B201" t="n">
-        <v>44177</v>
+        <v>96458</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -22799,21 +22790,21 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>101735</v>
+        <v>2818</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -22823,10 +22814,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>686928</v>
+        <v>686880</v>
       </c>
       <c r="R201" t="n">
-        <v>6562716</v>
+        <v>6562745</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22858,7 +22849,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -22868,7 +22859,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -22879,26 +22870,6 @@
       </c>
       <c r="AG201" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ201" t="inlineStr">
-        <is>
-          <t>fnöskticka</t>
-        </is>
-      </c>
-      <c r="AK201" t="inlineStr">
-        <is>
-          <t>Fomes fomentarius</t>
-        </is>
-      </c>
-      <c r="AL201" t="inlineStr">
-        <is>
-          <t>Fnöskticka på björk.</t>
-        </is>
-      </c>
-      <c r="AO201" t="inlineStr">
-        <is>
-          <t>Fomes fomentarius # Fnöskticka på björk.</t>
-        </is>
       </c>
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
@@ -22914,16 +22885,16 @@
       <c r="AY201" t="inlineStr"/>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061116</t>
+          <t>https://artportalen.se/Sighting/126061107</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>125974903</v>
+        <v>129215187</v>
       </c>
       <c r="B202" t="n">
-        <v>8444</v>
+        <v>91872</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -22931,50 +22902,40 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>106554</v>
+        <v>5447</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr"/>
       <c r="J202" t="inlineStr"/>
       <c r="K202" t="inlineStr"/>
-      <c r="L202" t="inlineStr"/>
-      <c r="M202" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>söder om Tyresta, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>686838</v>
+        <v>686977</v>
       </c>
       <c r="R202" t="n">
-        <v>6562733</v>
+        <v>6562706</v>
       </c>
       <c r="S202" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -22998,17 +22959,12 @@
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC202" t="inlineStr">
-        <is>
-          <t>gammal björklåga med spår längs hela stammen</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -23021,50 +22977,30 @@
       <c r="AG202" t="b">
         <v>0</v>
       </c>
-      <c r="AJ202" t="inlineStr">
-        <is>
-          <t>vårtbjörk</t>
-        </is>
-      </c>
-      <c r="AK202" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
-      <c r="AM202" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO202" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Betula pendula</t>
-        </is>
-      </c>
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Nette Bygren</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Nette Bygren</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125974903</t>
+          <t>https://artportalen.se/Sighting/129215187</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>126061105</v>
+        <v>126061104</v>
       </c>
       <c r="B203" t="n">
-        <v>8444</v>
+        <v>4775</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -23072,21 +23008,21 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>106554</v>
+        <v>100299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -23096,10 +23032,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>686860</v>
+        <v>686868</v>
       </c>
       <c r="R203" t="n">
-        <v>6562743</v>
+        <v>6562739</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -23131,7 +23067,7 @@
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
@@ -23141,7 +23077,7 @@
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -23155,17 +23091,22 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL203" t="inlineStr">
+        <is>
+          <t>Stående död gran.</t>
         </is>
       </c>
       <c r="AO203" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies # Stående död gran.</t>
         </is>
       </c>
       <c r="AT203" t="inlineStr"/>
@@ -23181,6 +23122,406 @@
       </c>
       <c r="AY203" t="inlineStr"/>
       <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061104</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>126061116</v>
+      </c>
+      <c r="B204" t="n">
+        <v>44177</v>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr"/>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>Ö Tyresta by, Srm</t>
+        </is>
+      </c>
+      <c r="Q204" t="n">
+        <v>686928</v>
+      </c>
+      <c r="R204" t="n">
+        <v>6562716</v>
+      </c>
+      <c r="S204" t="n">
+        <v>10</v>
+      </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W204" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y204" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z204" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB204" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AD204" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE204" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG204" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ204" t="inlineStr">
+        <is>
+          <t>fnöskticka</t>
+        </is>
+      </c>
+      <c r="AK204" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
+      </c>
+      <c r="AL204" t="inlineStr">
+        <is>
+          <t>Fnöskticka på björk.</t>
+        </is>
+      </c>
+      <c r="AO204" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius # Fnöskticka på björk.</t>
+        </is>
+      </c>
+      <c r="AT204" t="inlineStr"/>
+      <c r="AW204" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX204" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061116</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>125974903</v>
+      </c>
+      <c r="B205" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr"/>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr"/>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr"/>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>söder om Tyresta, Srm</t>
+        </is>
+      </c>
+      <c r="Q205" t="n">
+        <v>686838</v>
+      </c>
+      <c r="R205" t="n">
+        <v>6562733</v>
+      </c>
+      <c r="S205" t="n">
+        <v>5</v>
+      </c>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y205" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t>gammal björklåga med spår längs hela stammen</t>
+        </is>
+      </c>
+      <c r="AD205" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE205" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF205" t="inlineStr"/>
+      <c r="AG205" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ205" t="inlineStr">
+        <is>
+          <t>vårtbjörk</t>
+        </is>
+      </c>
+      <c r="AK205" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AM205" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO205" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Betula pendula</t>
+        </is>
+      </c>
+      <c r="AT205" t="inlineStr"/>
+      <c r="AW205" t="inlineStr">
+        <is>
+          <t>Nette Bygren</t>
+        </is>
+      </c>
+      <c r="AX205" t="inlineStr">
+        <is>
+          <t>Nette Bygren</t>
+        </is>
+      </c>
+      <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125974903</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>126061105</v>
+      </c>
+      <c r="B206" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr"/>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>Ö Tyresta by, Srm</t>
+        </is>
+      </c>
+      <c r="Q206" t="n">
+        <v>686860</v>
+      </c>
+      <c r="R206" t="n">
+        <v>6562743</v>
+      </c>
+      <c r="S206" t="n">
+        <v>10</v>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W206" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y206" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z206" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB206" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AD206" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE206" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG206" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ206" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK206" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO206" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AT206" t="inlineStr"/>
+      <c r="AW206" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX206" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/126061105</t>
         </is>
@@ -23390,6 +23731,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 152-2026 artfynd.xlsx
+++ b/artfynd/S 152-2026 artfynd.xlsx
@@ -1870,7 +1870,7 @@
         <v>136422855</v>
       </c>
       <c r="B13" t="n">
-        <v>90842</v>
+        <v>90844</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>136497917</v>
       </c>
       <c r="B14" t="n">
-        <v>90842</v>
+        <v>90844</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>136697240</v>
       </c>
       <c r="B15" t="n">
-        <v>90842</v>
+        <v>90844</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>136778801</v>
       </c>
       <c r="B16" t="n">
-        <v>90842</v>
+        <v>90844</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>136697189</v>
       </c>
       <c r="B18" t="n">
-        <v>90857</v>
+        <v>90859</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>136261113</v>
       </c>
       <c r="B19" t="n">
-        <v>96936</v>
+        <v>96938</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>136394246</v>
       </c>
       <c r="B20" t="n">
-        <v>96936</v>
+        <v>96938</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>136777570</v>
       </c>
       <c r="B21" t="n">
-        <v>96936</v>
+        <v>96938</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>136557239</v>
       </c>
       <c r="B23" t="n">
-        <v>91887</v>
+        <v>91889</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>136697244</v>
       </c>
       <c r="B26" t="n">
-        <v>93401</v>
+        <v>93403</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>136497924</v>
       </c>
       <c r="B29" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>136777559</v>
       </c>
       <c r="B30" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>136193282</v>
       </c>
       <c r="B36" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>136193424</v>
       </c>
       <c r="B37" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>136232449</v>
       </c>
       <c r="B38" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         <v>136394238</v>
       </c>
       <c r="B39" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>136422890</v>
       </c>
       <c r="B40" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>136697333</v>
       </c>
       <c r="B41" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>136697388</v>
       </c>
       <c r="B42" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
         <v>136697399</v>
       </c>
       <c r="B43" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         <v>136777560</v>
       </c>
       <c r="B44" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>136777566</v>
       </c>
       <c r="B45" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>136778803</v>
       </c>
       <c r="B46" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5588,7 +5588,7 @@
         <v>136778804</v>
       </c>
       <c r="B47" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         <v>136778808</v>
       </c>
       <c r="B48" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         <v>136778810</v>
       </c>
       <c r="B49" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
         <v>136801360</v>
       </c>
       <c r="B50" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>136801292</v>
       </c>
       <c r="B54" t="n">
-        <v>93421</v>
+        <v>93423</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6927,7 +6927,7 @@
         <v>136394243</v>
       </c>
       <c r="B59" t="n">
-        <v>92132</v>
+        <v>92134</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         <v>136801166</v>
       </c>
       <c r="B69" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>136801323</v>
       </c>
       <c r="B70" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>136801440</v>
       </c>
       <c r="B71" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8339,7 +8339,7 @@
         <v>136824502</v>
       </c>
       <c r="B72" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8445,7 +8445,7 @@
         <v>136824536</v>
       </c>
       <c r="B73" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         <v>136824638</v>
       </c>
       <c r="B74" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         <v>136801417</v>
       </c>
       <c r="B76" t="n">
-        <v>92789</v>
+        <v>92791</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -12744,7 +12744,7 @@
         <v>136777571</v>
       </c>
       <c r="B111" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13862,7 +13862,7 @@
         <v>136234180</v>
       </c>
       <c r="B121" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13964,7 +13964,7 @@
         <v>136394241</v>
       </c>
       <c r="B122" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14076,7 +14076,7 @@
         <v>136394242</v>
       </c>
       <c r="B123" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14188,7 +14188,7 @@
         <v>136394244</v>
       </c>
       <c r="B124" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14300,7 +14300,7 @@
         <v>136394245</v>
       </c>
       <c r="B125" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14412,7 +14412,7 @@
         <v>136778812</v>
       </c>
       <c r="B126" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14640,7 +14640,7 @@
         <v>136234148</v>
       </c>
       <c r="B128" t="n">
-        <v>98216</v>
+        <v>98218</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -16405,7 +16405,7 @@
         <v>136329952</v>
       </c>
       <c r="B144" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16519,7 +16519,7 @@
         <v>136330044</v>
       </c>
       <c r="B145" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17300,7 +17300,7 @@
         <v>136330155</v>
       </c>
       <c r="B152" t="n">
-        <v>92132</v>
+        <v>92134</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17406,7 +17406,7 @@
         <v>136330904</v>
       </c>
       <c r="B153" t="n">
-        <v>92132</v>
+        <v>92134</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17843,7 +17843,7 @@
         <v>136778218</v>
       </c>
       <c r="B157" t="n">
-        <v>93435</v>
+        <v>93437</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18585,7 +18585,7 @@
         <v>136737384</v>
       </c>
       <c r="B164" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18702,7 +18702,7 @@
         <v>136737387</v>
       </c>
       <c r="B165" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18814,7 +18814,7 @@
         <v>136778023</v>
       </c>
       <c r="B166" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18920,7 +18920,7 @@
         <v>136778100</v>
       </c>
       <c r="B167" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19026,7 +19026,7 @@
         <v>136778150</v>
       </c>
       <c r="B168" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19132,7 +19132,7 @@
         <v>136778261</v>
       </c>
       <c r="B169" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19238,7 +19238,7 @@
         <v>136778691</v>
       </c>
       <c r="B170" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19344,7 +19344,7 @@
         <v>136778703</v>
       </c>
       <c r="B171" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19450,7 +19450,7 @@
         <v>136778721</v>
       </c>
       <c r="B172" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         <v>136778733</v>
       </c>
       <c r="B173" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19662,7 +19662,7 @@
         <v>136778740</v>
       </c>
       <c r="B174" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -24997,7 +24997,7 @@
         <v>136777554</v>
       </c>
       <c r="B221" t="n">
-        <v>96782</v>
+        <v>96784</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -25447,7 +25447,7 @@
         <v>136778798</v>
       </c>
       <c r="B225" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -25684,7 +25684,7 @@
         <v>136777555</v>
       </c>
       <c r="B227" t="n">
-        <v>96829</v>
+        <v>96831</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -25811,7 +25811,7 @@
         <v>136241603</v>
       </c>
       <c r="B228" t="n">
-        <v>96936</v>
+        <v>96938</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -25928,7 +25928,7 @@
         <v>136777551</v>
       </c>
       <c r="B229" t="n">
-        <v>96259</v>
+        <v>96261</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -26051,7 +26051,7 @@
         <v>136231090</v>
       </c>
       <c r="B230" t="n">
-        <v>96654</v>
+        <v>96656</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -26153,7 +26153,7 @@
         <v>136777556</v>
       </c>
       <c r="B231" t="n">
-        <v>96686</v>
+        <v>96688</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -26280,7 +26280,7 @@
         <v>136697134</v>
       </c>
       <c r="B232" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -26386,7 +26386,7 @@
         <v>136778799</v>
       </c>
       <c r="B233" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -26616,7 +26616,7 @@
         <v>136394237</v>
       </c>
       <c r="B235" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -26728,7 +26728,7 @@
         <v>136268106</v>
       </c>
       <c r="B236" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -26839,7 +26839,7 @@
         <v>136697126</v>
       </c>
       <c r="B237" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -27369,7 +27369,7 @@
         <v>136801045</v>
       </c>
       <c r="B242" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -27475,7 +27475,7 @@
         <v>136801064</v>
       </c>
       <c r="B243" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -29659,7 +29659,7 @@
         <v>136394236</v>
       </c>
       <c r="B262" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>

--- a/artfynd/S 152-2026 artfynd.xlsx
+++ b/artfynd/S 152-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ276"/>
+  <dimension ref="A1:AZ278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22839,32 +22839,32 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>136346607</v>
+        <v>136947615</v>
       </c>
       <c r="B202" t="n">
-        <v>58164</v>
+        <v>58169</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -22882,10 +22882,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>686529</v>
+        <v>686485</v>
       </c>
       <c r="R202" t="n">
-        <v>6563051</v>
+        <v>6562997</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22912,12 +22912,12 @@
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -22943,13 +22943,13 @@
       <c r="AY202" t="inlineStr"/>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136346607</t>
+          <t>https://artportalen.se/Sighting/136947615</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>136346721</v>
+        <v>136346607</v>
       </c>
       <c r="B203" t="n">
         <v>58164</v>
@@ -22992,10 +22992,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>686678</v>
+        <v>686529</v>
       </c>
       <c r="R203" t="n">
-        <v>6563074</v>
+        <v>6563051</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -23053,13 +23053,13 @@
       <c r="AY203" t="inlineStr"/>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136346721</t>
+          <t>https://artportalen.se/Sighting/136346607</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>136422024</v>
+        <v>136346721</v>
       </c>
       <c r="B204" t="n">
         <v>58164</v>
@@ -23102,10 +23102,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>686531</v>
+        <v>686678</v>
       </c>
       <c r="R204" t="n">
-        <v>6563059</v>
+        <v>6563074</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -23132,12 +23132,12 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -23163,13 +23163,13 @@
       <c r="AY204" t="inlineStr"/>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136422024</t>
+          <t>https://artportalen.se/Sighting/136346721</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>136557077</v>
+        <v>136422024</v>
       </c>
       <c r="B205" t="n">
         <v>58164</v>
@@ -23212,10 +23212,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>686733</v>
+        <v>686531</v>
       </c>
       <c r="R205" t="n">
-        <v>6563216</v>
+        <v>6563059</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -23242,12 +23242,12 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -23273,16 +23273,16 @@
       <c r="AY205" t="inlineStr"/>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136557077</t>
+          <t>https://artportalen.se/Sighting/136422024</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>136259916</v>
+        <v>136557077</v>
       </c>
       <c r="B206" t="n">
-        <v>8463</v>
+        <v>58164</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -23290,30 +23290,29 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>106545</v>
+        <v>103023</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
-      <c r="J206" t="inlineStr"/>
       <c r="K206" t="inlineStr"/>
       <c r="L206" t="inlineStr"/>
       <c r="M206" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N206" t="inlineStr"/>
@@ -23323,10 +23322,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>686457</v>
+        <v>686733</v>
       </c>
       <c r="R206" t="n">
-        <v>6563062</v>
+        <v>6563216</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -23353,12 +23352,12 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -23367,7 +23366,6 @@
       <c r="AE206" t="b">
         <v>0</v>
       </c>
-      <c r="AF206" t="inlineStr"/>
       <c r="AG206" t="b">
         <v>0</v>
       </c>
@@ -23385,13 +23383,13 @@
       <c r="AY206" t="inlineStr"/>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136259916</t>
+          <t>https://artportalen.se/Sighting/136557077</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>136330063</v>
+        <v>136259916</v>
       </c>
       <c r="B207" t="n">
         <v>8463</v>
@@ -23435,10 +23433,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>686661</v>
+        <v>686457</v>
       </c>
       <c r="R207" t="n">
-        <v>6563103</v>
+        <v>6563062</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -23465,12 +23463,12 @@
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -23497,16 +23495,16 @@
       <c r="AY207" t="inlineStr"/>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136330063</t>
+          <t>https://artportalen.se/Sighting/136259916</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>136767139</v>
+        <v>136330063</v>
       </c>
       <c r="B208" t="n">
-        <v>56875</v>
+        <v>8463</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -23514,37 +23512,46 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>205992</v>
+        <v>106545</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
+      <c r="J208" t="inlineStr"/>
+      <c r="K208" t="inlineStr"/>
+      <c r="L208" t="inlineStr"/>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Norrby torp, Tyresta, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>686742</v>
+        <v>686661</v>
       </c>
       <c r="R208" t="n">
-        <v>6563155</v>
+        <v>6563103</v>
       </c>
       <c r="S208" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -23568,22 +23575,12 @@
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="Z208" t="inlineStr">
-        <is>
-          <t>23:28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="AB208" t="inlineStr">
-        <is>
-          <t>23:28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -23592,33 +23589,34 @@
       <c r="AE208" t="b">
         <v>0</v>
       </c>
+      <c r="AF208" t="inlineStr"/>
       <c r="AG208" t="b">
         <v>0</v>
       </c>
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136767139</t>
+          <t>https://artportalen.se/Sighting/136330063</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>136767130</v>
+        <v>136767139</v>
       </c>
       <c r="B209" t="n">
-        <v>56887</v>
+        <v>56875</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -23626,21 +23624,21 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -23650,10 +23648,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>686656</v>
+        <v>686742</v>
       </c>
       <c r="R209" t="n">
-        <v>6563100</v>
+        <v>6563155</v>
       </c>
       <c r="S209" t="n">
         <v>25</v>
@@ -23680,22 +23678,22 @@
       </c>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z209" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AB209" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -23721,13 +23719,13 @@
       <c r="AY209" t="inlineStr"/>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136767130</t>
+          <t>https://artportalen.se/Sighting/136767139</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>136767147</v>
+        <v>136767130</v>
       </c>
       <c r="B210" t="n">
         <v>56887</v>
@@ -23762,10 +23760,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>686742</v>
+        <v>686656</v>
       </c>
       <c r="R210" t="n">
-        <v>6563155</v>
+        <v>6563100</v>
       </c>
       <c r="S210" t="n">
         <v>25</v>
@@ -23792,22 +23790,22 @@
       </c>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>04:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="AB210" t="inlineStr">
         <is>
-          <t>04:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -23833,52 +23831,51 @@
       <c r="AY210" t="inlineStr"/>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136767147</t>
+          <t>https://artportalen.se/Sighting/136767130</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>136767125</v>
+        <v>136767147</v>
       </c>
       <c r="B211" t="n">
-        <v>56866</v>
+        <v>56887</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Cnephaeus nilssonii</t>
-        </is>
-      </c>
-      <c r="H211" t="inlineStr"/>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
       <c r="I211" t="inlineStr"/>
-      <c r="J211" t="inlineStr"/>
-      <c r="K211" t="inlineStr"/>
-      <c r="L211" t="inlineStr"/>
-      <c r="M211" t="inlineStr"/>
-      <c r="N211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
           <t>Norrby torp, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>686656</v>
+        <v>686742</v>
       </c>
       <c r="R211" t="n">
-        <v>6563100</v>
+        <v>6563155</v>
       </c>
       <c r="S211" t="n">
         <v>25</v>
@@ -23905,22 +23902,22 @@
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>04:21</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AB211" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>04:21</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -23946,13 +23943,13 @@
       <c r="AY211" t="inlineStr"/>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136767125</t>
+          <t>https://artportalen.se/Sighting/136767147</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>136767144</v>
+        <v>136767125</v>
       </c>
       <c r="B212" t="n">
         <v>56866</v>
@@ -23977,16 +23974,21 @@
       </c>
       <c r="H212" t="inlineStr"/>
       <c r="I212" t="inlineStr"/>
+      <c r="J212" t="inlineStr"/>
+      <c r="K212" t="inlineStr"/>
+      <c r="L212" t="inlineStr"/>
+      <c r="M212" t="inlineStr"/>
+      <c r="N212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
           <t>Norrby torp, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>686742</v>
+        <v>686656</v>
       </c>
       <c r="R212" t="n">
-        <v>6563155</v>
+        <v>6563100</v>
       </c>
       <c r="S212" t="n">
         <v>25</v>
@@ -24013,22 +24015,22 @@
       </c>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -24054,58 +24056,50 @@
       <c r="AY212" t="inlineStr"/>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136767144</t>
+          <t>https://artportalen.se/Sighting/136767125</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>109890506</v>
+        <v>136767144</v>
       </c>
       <c r="B213" t="n">
-        <v>99118</v>
+        <v>56866</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>220787</v>
+        <v>205998</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr"/>
       <c r="I213" t="inlineStr"/>
-      <c r="J213" t="inlineStr"/>
-      <c r="K213" t="inlineStr"/>
-      <c r="L213" t="inlineStr"/>
-      <c r="N213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
-          <t>Ö Norrby Mosse, Srm</t>
+          <t>Norrby torp, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>686831</v>
+        <v>686742</v>
       </c>
       <c r="R213" t="n">
-        <v>6563216</v>
+        <v>6563155</v>
       </c>
       <c r="S213" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T213" t="inlineStr">
         <is>
@@ -24129,12 +24123,22 @@
       </c>
       <c r="Y213" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="Z213" t="inlineStr">
+        <is>
+          <t>23:10</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AB213" t="inlineStr">
+        <is>
+          <t>23:10</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -24143,31 +24147,30 @@
       <c r="AE213" t="b">
         <v>0</v>
       </c>
-      <c r="AF213" t="inlineStr"/>
       <c r="AG213" t="b">
         <v>0</v>
       </c>
       <c r="AT213" t="inlineStr"/>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109890506</t>
+          <t>https://artportalen.se/Sighting/136767144</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>122781008</v>
+        <v>109890506</v>
       </c>
       <c r="B214" t="n">
         <v>99118</v>
@@ -24202,14 +24205,14 @@
       <c r="N214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Knärot, Srm</t>
+          <t>Ö Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>686833</v>
+        <v>686831</v>
       </c>
       <c r="R214" t="n">
-        <v>6563215</v>
+        <v>6563216</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -24236,17 +24239,12 @@
       </c>
       <c r="Y214" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC214" t="inlineStr">
-        <is>
-          <t>Knärot</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -24262,24 +24260,24 @@
       <c r="AT214" t="inlineStr"/>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
       <c r="AZ214" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122781008</t>
+          <t>https://artportalen.se/Sighting/109890506</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>126418709</v>
+        <v>122781008</v>
       </c>
       <c r="B215" t="n">
         <v>99118</v>
@@ -24307,29 +24305,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I215" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J215" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I215" t="inlineStr"/>
+      <c r="J215" t="inlineStr"/>
       <c r="K215" t="inlineStr"/>
       <c r="L215" t="inlineStr"/>
       <c r="N215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Knärot, Srm</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>686771</v>
+        <v>686833</v>
       </c>
       <c r="R215" t="n">
-        <v>6563297</v>
+        <v>6563215</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -24356,17 +24346,17 @@
       </c>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AC215" t="inlineStr">
         <is>
-          <t>Två av dem i knopp, ca 3 m väster om de andra.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -24382,24 +24372,24 @@
       <c r="AT215" t="inlineStr"/>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126418709</t>
+          <t>https://artportalen.se/Sighting/122781008</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>126418756</v>
+        <v>126418709</v>
       </c>
       <c r="B216" t="n">
         <v>99118</v>
@@ -24429,7 +24419,7 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
@@ -24446,10 +24436,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>686781</v>
+        <v>686771</v>
       </c>
       <c r="R216" t="n">
-        <v>6563292</v>
+        <v>6563297</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -24486,7 +24476,7 @@
       </c>
       <c r="AC216" t="inlineStr">
         <is>
-          <t>En av dem i knopp.</t>
+          <t>Två av dem i knopp, ca 3 m väster om de andra.</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -24513,13 +24503,13 @@
       <c r="AY216" t="inlineStr"/>
       <c r="AZ216" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126418756</t>
+          <t>https://artportalen.se/Sighting/126418709</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>129564285</v>
+        <v>126418756</v>
       </c>
       <c r="B217" t="n">
         <v>99118</v>
@@ -24547,8 +24537,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I217" t="inlineStr"/>
-      <c r="J217" t="inlineStr"/>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K217" t="inlineStr"/>
       <c r="L217" t="inlineStr"/>
       <c r="N217" t="inlineStr"/>
@@ -24558,10 +24556,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>686625</v>
+        <v>686781</v>
       </c>
       <c r="R217" t="n">
-        <v>6563000</v>
+        <v>6563292</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -24588,12 +24586,17 @@
       </c>
       <c r="Y217" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC217" t="inlineStr">
+        <is>
+          <t>En av dem i knopp.</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -24620,63 +24623,55 @@
       <c r="AY217" t="inlineStr"/>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129564285</t>
+          <t>https://artportalen.se/Sighting/126418756</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>126234373</v>
+        <v>129564285</v>
       </c>
       <c r="B218" t="n">
-        <v>106244</v>
+        <v>99118</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I218" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J218" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr"/>
+      <c r="J218" t="inlineStr"/>
       <c r="K218" t="inlineStr"/>
       <c r="L218" t="inlineStr"/>
       <c r="N218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Norrby mosse SO, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>686756</v>
+        <v>686625</v>
       </c>
       <c r="R218" t="n">
-        <v>6563092</v>
+        <v>6563000</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -24703,12 +24698,12 @@
       </c>
       <c r="Y218" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -24724,27 +24719,27 @@
       <c r="AT218" t="inlineStr"/>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126234373</t>
+          <t>https://artportalen.se/Sighting/129564285</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>122929342</v>
+        <v>126234373</v>
       </c>
       <c r="B219" t="n">
-        <v>97986</v>
+        <v>106244</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -24752,41 +24747,49 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>221946</v>
+        <v>221144</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I219" t="inlineStr"/>
-      <c r="J219" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K219" t="inlineStr"/>
       <c r="L219" t="inlineStr"/>
       <c r="N219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>Norrby mosse SO, Srm</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>686569</v>
+        <v>686756</v>
       </c>
       <c r="R219" t="n">
-        <v>6562949</v>
+        <v>6563092</v>
       </c>
       <c r="S219" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -24810,22 +24813,12 @@
       </c>
       <c r="Y219" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="Z219" t="inlineStr">
-        <is>
-          <t>10:52</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="AB219" t="inlineStr">
-        <is>
-          <t>10:52</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -24834,33 +24827,34 @@
       <c r="AE219" t="b">
         <v>0</v>
       </c>
+      <c r="AF219" t="inlineStr"/>
       <c r="AG219" t="b">
         <v>0</v>
       </c>
       <c r="AT219" t="inlineStr"/>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122929342</t>
+          <t>https://artportalen.se/Sighting/126234373</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>134487656</v>
+        <v>122929342</v>
       </c>
       <c r="B220" t="n">
-        <v>99217</v>
+        <v>97986</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -24868,45 +24862,41 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>221952</v>
+        <v>221946</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
       <c r="J220" t="inlineStr"/>
-      <c r="K220" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K220" t="inlineStr"/>
       <c r="L220" t="inlineStr"/>
       <c r="N220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>686835</v>
+        <v>686569</v>
       </c>
       <c r="R220" t="n">
-        <v>6563212</v>
+        <v>6562949</v>
       </c>
       <c r="S220" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T220" t="inlineStr">
         <is>
@@ -24930,17 +24920,22 @@
       </c>
       <c r="Y220" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="Z220" t="inlineStr">
+        <is>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="AC220" t="inlineStr">
-        <is>
-          <t>2 i blom samt några plantor med endast blad.</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AB220" t="inlineStr">
+        <is>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -24949,72 +24944,76 @@
       <c r="AE220" t="b">
         <v>0</v>
       </c>
-      <c r="AF220" t="inlineStr"/>
       <c r="AG220" t="b">
         <v>0</v>
       </c>
       <c r="AT220" t="inlineStr"/>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134487656</t>
+          <t>https://artportalen.se/Sighting/122929342</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>118843519</v>
+        <v>134487656</v>
       </c>
       <c r="B221" t="n">
-        <v>91431</v>
+        <v>99217</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6039941</v>
+        <v>221952</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Gelatinfingersvamp</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Ramaria primulina</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
       <c r="J221" t="inlineStr"/>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr"/>
       <c r="N221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Norrby Mosse, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>686668</v>
+        <v>686835</v>
       </c>
       <c r="R221" t="n">
-        <v>6563218</v>
+        <v>6563212</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -25041,17 +25040,17 @@
       </c>
       <c r="Y221" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AC221" t="inlineStr">
         <is>
-          <t>Kollekt BR55. Dublett av tidigare fynd för att rapportera resultat av sekvensering. Ursprungligt fynd rapporterat av Bodil Ravn och finns här https://www.artportalen.se/Sighting/112337794</t>
+          <t>2 i blom samt några plantor med endast blad.</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -25067,78 +25066,65 @@
       <c r="AT221" t="inlineStr"/>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY221" t="inlineStr">
-        <is>
-          <t>Fynd med DNA-sekvens - extern</t>
-        </is>
-      </c>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY221" t="inlineStr"/>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118843519</t>
+          <t>https://artportalen.se/Sighting/134487656</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>122203249</v>
+        <v>118843519</v>
       </c>
       <c r="B222" t="n">
-        <v>96554</v>
+        <v>91431</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>210</v>
+        <v>6039941</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Gelatinfingersvamp</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Ramaria primulina</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I222" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr"/>
       <c r="J222" t="inlineStr"/>
-      <c r="K222" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
-      <c r="L222" t="inlineStr"/>
+      <c r="K222" t="inlineStr"/>
       <c r="N222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Ö Norrbytorp, Srm</t>
+          <t>Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>687968</v>
+        <v>686668</v>
       </c>
       <c r="R222" t="n">
-        <v>6562733</v>
+        <v>6563218</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -25165,17 +25151,17 @@
       </c>
       <c r="Y222" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AC222" t="inlineStr">
         <is>
-          <t>På murken granlåga i äldre skog.</t>
+          <t>Kollekt BR55. Dublett av tidigare fynd för att rapportera resultat av sekvensering. Ursprungligt fynd rapporterat av Bodil Ravn och finns här https://www.artportalen.se/Sighting/112337794</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -25191,24 +25177,28 @@
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
-        </is>
-      </c>
-      <c r="AY222" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY222" t="inlineStr">
+        <is>
+          <t>Fynd med DNA-sekvens - extern</t>
+        </is>
+      </c>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122203249</t>
+          <t>https://artportalen.se/Sighting/118843519</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>122780924</v>
+        <v>122203249</v>
       </c>
       <c r="B223" t="n">
         <v>96554</v>
@@ -25236,21 +25226,29 @@
           <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
-      <c r="I223" t="inlineStr"/>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
       <c r="J223" t="inlineStr"/>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr"/>
       <c r="N223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Grön sköldmossa, Srm</t>
+          <t>Ö Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>687970</v>
+        <v>687968</v>
       </c>
       <c r="R223" t="n">
-        <v>6562732</v>
+        <v>6562733</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -25277,17 +25275,17 @@
       </c>
       <c r="Y223" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="AC223" t="inlineStr">
         <is>
-          <t>Grön sköldmossa på rutten stam</t>
+          <t>På murken granlåga i äldre skog.</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -25303,27 +25301,27 @@
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122780924</t>
+          <t>https://artportalen.se/Sighting/122203249</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>136777554</v>
+        <v>122780924</v>
       </c>
       <c r="B224" t="n">
-        <v>96784</v>
+        <v>96554</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -25349,19 +25347,23 @@
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
+      <c r="J224" t="inlineStr"/>
+      <c r="K224" t="inlineStr"/>
+      <c r="L224" t="inlineStr"/>
+      <c r="N224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
-          <t>Norrby torp, Tyresta, Srm</t>
+          <t>Grön sköldmossa, Srm</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>687973</v>
+        <v>687970</v>
       </c>
       <c r="R224" t="n">
-        <v>6562731</v>
+        <v>6562732</v>
       </c>
       <c r="S224" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T224" t="inlineStr">
         <is>
@@ -25385,22 +25387,17 @@
       </c>
       <c r="Y224" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="Z224" t="inlineStr">
-        <is>
-          <t>12:19</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="AB224" t="inlineStr">
-        <is>
-          <t>12:19</t>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC224" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa på rutten stam</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -25409,89 +25406,72 @@
       <c r="AE224" t="b">
         <v>0</v>
       </c>
+      <c r="AF224" t="inlineStr"/>
       <c r="AG224" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ224" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK224" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO224" t="inlineStr">
-        <is>
-          <t>Kraftigt nedbruten granlåga # Picea abies</t>
-        </is>
       </c>
       <c r="AT224" t="inlineStr"/>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136777554</t>
+          <t>https://artportalen.se/Sighting/122780924</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129624531</v>
+        <v>136777554</v>
       </c>
       <c r="B225" t="n">
-        <v>90946</v>
+        <v>96784</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>889</v>
+        <v>210</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Vintertagging</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Plicatura pendula</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
-      <c r="J225" t="inlineStr"/>
-      <c r="K225" t="inlineStr"/>
-      <c r="N225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrby torp, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>687931</v>
+        <v>687973</v>
       </c>
       <c r="R225" t="n">
-        <v>6562811</v>
+        <v>6562731</v>
       </c>
       <c r="S225" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T225" t="inlineStr">
         <is>
@@ -25515,12 +25495,22 @@
       </c>
       <c r="Y225" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="Z225" t="inlineStr">
+        <is>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AB225" t="inlineStr">
+        <is>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -25529,31 +25519,45 @@
       <c r="AE225" t="b">
         <v>0</v>
       </c>
-      <c r="AF225" t="inlineStr"/>
       <c r="AG225" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ225" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK225" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO225" t="inlineStr">
+        <is>
+          <t>Kraftigt nedbruten granlåga # Picea abies</t>
+        </is>
       </c>
       <c r="AT225" t="inlineStr"/>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129624531</t>
+          <t>https://artportalen.se/Sighting/136777554</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>129624696</v>
+        <v>129624531</v>
       </c>
       <c r="B226" t="n">
         <v>90946</v>
@@ -25591,10 +25595,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>687973</v>
+        <v>687931</v>
       </c>
       <c r="R226" t="n">
-        <v>6562815</v>
+        <v>6562811</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -25629,11 +25633,6 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC226" t="inlineStr">
-        <is>
-          <t>På död tall.</t>
-        </is>
-      </c>
       <c r="AD226" t="b">
         <v>0</v>
       </c>
@@ -25658,16 +25657,16 @@
       <c r="AY226" t="inlineStr"/>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129624696</t>
+          <t>https://artportalen.se/Sighting/129624531</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>122203275</v>
+        <v>129624696</v>
       </c>
       <c r="B227" t="n">
-        <v>91909</v>
+        <v>90946</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -25675,21 +25674,21 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>1202</v>
+        <v>889</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Plicatura pendula</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -25698,14 +25697,14 @@
       <c r="N227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
-          <t>Ö Norrbytorp, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>687981</v>
+        <v>687973</v>
       </c>
       <c r="R227" t="n">
-        <v>6562724</v>
+        <v>6562815</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25732,12 +25731,17 @@
       </c>
       <c r="Y227" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC227" t="inlineStr">
+        <is>
+          <t>På död tall.</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -25764,16 +25768,16 @@
       <c r="AY227" t="inlineStr"/>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122203275</t>
+          <t>https://artportalen.se/Sighting/129624696</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>136778798</v>
+        <v>122203275</v>
       </c>
       <c r="B228" t="n">
-        <v>92113</v>
+        <v>91909</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -25799,19 +25803,22 @@
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
+      <c r="J228" t="inlineStr"/>
+      <c r="K228" t="inlineStr"/>
+      <c r="N228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
-          <t>Norrbytorp_inventering_2026-08-30, Srm</t>
+          <t>Ö Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>687985</v>
+        <v>687981</v>
       </c>
       <c r="R228" t="n">
-        <v>6562721</v>
+        <v>6562724</v>
       </c>
       <c r="S228" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T228" t="inlineStr">
         <is>
@@ -25835,22 +25842,12 @@
       </c>
       <c r="Y228" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="Z228" t="inlineStr">
-        <is>
-          <t>12:11</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="AB228" t="inlineStr">
-        <is>
-          <t>12:11</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -25859,93 +25856,72 @@
       <c r="AE228" t="b">
         <v>0</v>
       </c>
+      <c r="AF228" t="inlineStr"/>
       <c r="AG228" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ228" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK228" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO228" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT228" t="inlineStr"/>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136778798</t>
+          <t>https://artportalen.se/Sighting/122203275</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>135358856</v>
+        <v>136778798</v>
       </c>
       <c r="B229" t="n">
-        <v>91573</v>
+        <v>92113</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>2051</v>
+        <v>1202</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I229" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J229" t="inlineStr"/>
-      <c r="K229" t="inlineStr"/>
-      <c r="N229" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrbytorp_inventering_2026-08-30, Srm</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>688004</v>
+        <v>687985</v>
       </c>
       <c r="R229" t="n">
-        <v>6562799</v>
+        <v>6562721</v>
       </c>
       <c r="S229" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T229" t="inlineStr">
         <is>
@@ -25969,12 +25945,22 @@
       </c>
       <c r="Y229" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="Z229" t="inlineStr">
+        <is>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AB229" t="inlineStr">
+        <is>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -25983,72 +25969,93 @@
       <c r="AE229" t="b">
         <v>0</v>
       </c>
-      <c r="AF229" t="inlineStr"/>
       <c r="AG229" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ229" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK229" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO229" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT229" t="inlineStr"/>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358856</t>
+          <t>https://artportalen.se/Sighting/136778798</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>136777555</v>
+        <v>135358856</v>
       </c>
       <c r="B230" t="n">
-        <v>96831</v>
+        <v>91573</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>2170</v>
+        <v>2051</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I230" t="inlineStr"/>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr"/>
+      <c r="K230" t="inlineStr"/>
+      <c r="N230" t="inlineStr"/>
       <c r="P230" t="inlineStr">
         <is>
-          <t>Norrby torp, Tyresta, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>687973</v>
+        <v>688004</v>
       </c>
       <c r="R230" t="n">
-        <v>6562731</v>
+        <v>6562799</v>
       </c>
       <c r="S230" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T230" t="inlineStr">
         <is>
@@ -26072,22 +26079,12 @@
       </c>
       <c r="Y230" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="Z230" t="inlineStr">
-        <is>
-          <t>12:19</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="AB230" t="inlineStr">
-        <is>
-          <t>12:19</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -26096,48 +26093,34 @@
       <c r="AE230" t="b">
         <v>0</v>
       </c>
+      <c r="AF230" t="inlineStr"/>
       <c r="AG230" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ230" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK230" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO230" t="inlineStr">
-        <is>
-          <t>Kraftigt nedbruten granlåga # Picea abies</t>
-        </is>
       </c>
       <c r="AT230" t="inlineStr"/>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136777555</t>
+          <t>https://artportalen.se/Sighting/135358856</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>136241603</v>
+        <v>136777555</v>
       </c>
       <c r="B231" t="n">
-        <v>96938</v>
+        <v>96831</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -26145,38 +26128,34 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>2180</v>
+        <v>2170</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
-      <c r="J231" t="inlineStr"/>
-      <c r="K231" t="inlineStr"/>
-      <c r="L231" t="inlineStr"/>
-      <c r="N231" t="inlineStr"/>
       <c r="P231" t="inlineStr">
         <is>
-          <t>Norrbytorp, Srm</t>
+          <t>Norrby torp, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>688059</v>
+        <v>687973</v>
       </c>
       <c r="R231" t="n">
-        <v>6562773</v>
+        <v>6562731</v>
       </c>
       <c r="S231" t="n">
         <v>5</v>
@@ -26208,7 +26187,7 @@
       </c>
       <c r="Z231" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
@@ -26218,7 +26197,7 @@
       </c>
       <c r="AB231" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -26227,34 +26206,48 @@
       <c r="AE231" t="b">
         <v>0</v>
       </c>
-      <c r="AF231" t="inlineStr"/>
       <c r="AG231" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ231" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK231" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO231" t="inlineStr">
+        <is>
+          <t>Kraftigt nedbruten granlåga # Picea abies</t>
+        </is>
       </c>
       <c r="AT231" t="inlineStr"/>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>Björn Persson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>Björn Persson</t>
+          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136241603</t>
+          <t>https://artportalen.se/Sighting/136777555</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>136777551</v>
+        <v>136241603</v>
       </c>
       <c r="B232" t="n">
-        <v>96261</v>
+        <v>96938</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -26262,33 +26255,41 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>2558</v>
+        <v>2180</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Krushättemossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Ulota crispa s.lat.</t>
-        </is>
-      </c>
-      <c r="H232" t="inlineStr"/>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
       <c r="I232" t="inlineStr"/>
+      <c r="J232" t="inlineStr"/>
+      <c r="K232" t="inlineStr"/>
+      <c r="L232" t="inlineStr"/>
+      <c r="N232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
-          <t>Norrby torp, Tyresta, Srm</t>
+          <t>Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>687848</v>
+        <v>688059</v>
       </c>
       <c r="R232" t="n">
-        <v>6562771</v>
+        <v>6562773</v>
       </c>
       <c r="S232" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T232" t="inlineStr">
         <is>
@@ -26317,7 +26318,7 @@
       </c>
       <c r="Z232" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
@@ -26327,7 +26328,7 @@
       </c>
       <c r="AB232" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -26336,48 +26337,34 @@
       <c r="AE232" t="b">
         <v>0</v>
       </c>
+      <c r="AF232" t="inlineStr"/>
       <c r="AG232" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ232" t="inlineStr">
-        <is>
-          <t>hassel</t>
-        </is>
-      </c>
-      <c r="AK232" t="inlineStr">
-        <is>
-          <t>Corylus avellana</t>
-        </is>
-      </c>
-      <c r="AO232" t="inlineStr">
-        <is>
-          <t>Levande hasselgren # Corylus avellana</t>
-        </is>
       </c>
       <c r="AT232" t="inlineStr"/>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Björn Persson</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
+          <t>Björn Persson</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136777551</t>
+          <t>https://artportalen.se/Sighting/136241603</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>136231090</v>
+        <v>136777551</v>
       </c>
       <c r="B233" t="n">
-        <v>96656</v>
+        <v>96261</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -26385,37 +26372,33 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>2671</v>
+        <v>2558</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Krushättemossa</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
-        </is>
-      </c>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
+          <t>Ulota crispa s.lat.</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr"/>
       <c r="I233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
-          <t>Norrby torp, Norrby torp, Srm</t>
+          <t>Norrby torp, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>688046</v>
+        <v>687848</v>
       </c>
       <c r="R233" t="n">
-        <v>6562700</v>
+        <v>6562771</v>
       </c>
       <c r="S233" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T233" t="inlineStr">
         <is>
@@ -26442,11 +26425,21 @@
           <t>2026-08-30</t>
         </is>
       </c>
+      <c r="Z233" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA233" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
+      <c r="AB233" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AD233" t="b">
         <v>0</v>
       </c>
@@ -26455,31 +26448,46 @@
       </c>
       <c r="AG233" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ233" t="inlineStr">
+        <is>
+          <t>hassel</t>
+        </is>
+      </c>
+      <c r="AK233" t="inlineStr">
+        <is>
+          <t>Corylus avellana</t>
+        </is>
+      </c>
+      <c r="AO233" t="inlineStr">
+        <is>
+          <t>Levande hasselgren # Corylus avellana</t>
+        </is>
       </c>
       <c r="AT233" t="inlineStr"/>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136231090</t>
+          <t>https://artportalen.se/Sighting/136777551</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>136777556</v>
+        <v>136231090</v>
       </c>
       <c r="B234" t="n">
-        <v>96688</v>
+        <v>96656</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -26487,37 +26495,37 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>2818</v>
+        <v>2671</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
       <c r="P234" t="inlineStr">
         <is>
-          <t>Norrby torp, Tyresta, Srm</t>
+          <t>Norrby torp, Norrby torp, Srm</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>687973</v>
+        <v>688046</v>
       </c>
       <c r="R234" t="n">
-        <v>6562731</v>
+        <v>6562700</v>
       </c>
       <c r="S234" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T234" t="inlineStr">
         <is>
@@ -26544,21 +26552,11 @@
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="Z234" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
       <c r="AA234" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="AB234" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
       <c r="AD234" t="b">
         <v>0</v>
       </c>
@@ -26567,87 +26565,69 @@
       </c>
       <c r="AG234" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ234" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK234" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO234" t="inlineStr">
-        <is>
-          <t>Kraftigt nedbruten granlåga # Picea abies</t>
-        </is>
       </c>
       <c r="AT234" t="inlineStr"/>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136777556</t>
+          <t>https://artportalen.se/Sighting/136231090</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>136697134</v>
+        <v>136777556</v>
       </c>
       <c r="B235" t="n">
-        <v>93411</v>
+        <v>96688</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>4364</v>
+        <v>2818</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
-      <c r="J235" t="inlineStr"/>
-      <c r="K235" t="inlineStr"/>
-      <c r="N235" t="inlineStr"/>
       <c r="P235" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrby torp, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>688040</v>
+        <v>687973</v>
       </c>
       <c r="R235" t="n">
-        <v>6562791</v>
+        <v>6562731</v>
       </c>
       <c r="S235" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T235" t="inlineStr">
         <is>
@@ -26671,12 +26651,22 @@
       </c>
       <c r="Y235" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="Z235" t="inlineStr">
+        <is>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA235" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AB235" t="inlineStr">
+        <is>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -26685,31 +26675,45 @@
       <c r="AE235" t="b">
         <v>0</v>
       </c>
-      <c r="AF235" t="inlineStr"/>
       <c r="AG235" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ235" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK235" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO235" t="inlineStr">
+        <is>
+          <t>Kraftigt nedbruten granlåga # Picea abies</t>
+        </is>
       </c>
       <c r="AT235" t="inlineStr"/>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136697134</t>
+          <t>https://artportalen.se/Sighting/136777556</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>136778799</v>
+        <v>136697134</v>
       </c>
       <c r="B236" t="n">
         <v>93411</v>
@@ -26737,24 +26741,23 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I236" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I236" t="inlineStr"/>
+      <c r="J236" t="inlineStr"/>
+      <c r="K236" t="inlineStr"/>
+      <c r="N236" t="inlineStr"/>
       <c r="P236" t="inlineStr">
         <is>
-          <t>Norrbytorp_inventering_2026-08-30, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>688075</v>
+        <v>688040</v>
       </c>
       <c r="R236" t="n">
-        <v>6562783</v>
+        <v>6562791</v>
       </c>
       <c r="S236" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T236" t="inlineStr">
         <is>
@@ -26778,22 +26781,12 @@
       </c>
       <c r="Y236" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="Z236" t="inlineStr">
-        <is>
-          <t>13:26</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="AB236" t="inlineStr">
-        <is>
-          <t>13:26</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -26802,82 +26795,76 @@
       <c r="AE236" t="b">
         <v>0</v>
       </c>
+      <c r="AF236" t="inlineStr"/>
       <c r="AG236" t="b">
         <v>0</v>
       </c>
       <c r="AT236" t="inlineStr"/>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136778799</t>
+          <t>https://artportalen.se/Sighting/136697134</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>128314411</v>
+        <v>136778799</v>
       </c>
       <c r="B237" t="n">
-        <v>92348</v>
+        <v>93411</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>5420</v>
+        <v>4364</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J237" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K237" t="inlineStr"/>
-      <c r="N237" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P237" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrbytorp_inventering_2026-08-30, Srm</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>688088</v>
+        <v>688075</v>
       </c>
       <c r="R237" t="n">
-        <v>6562722</v>
+        <v>6562783</v>
       </c>
       <c r="S237" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T237" t="inlineStr">
         <is>
@@ -26901,12 +26888,22 @@
       </c>
       <c r="Y237" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="Z237" t="inlineStr">
+        <is>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AB237" t="inlineStr">
+        <is>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -26915,34 +26912,33 @@
       <c r="AE237" t="b">
         <v>0</v>
       </c>
-      <c r="AF237" t="inlineStr"/>
       <c r="AG237" t="b">
         <v>0</v>
       </c>
       <c r="AT237" t="inlineStr"/>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128314411</t>
+          <t>https://artportalen.se/Sighting/136778799</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>136394237</v>
+        <v>128314411</v>
       </c>
       <c r="B238" t="n">
-        <v>92524</v>
+        <v>92348</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -26967,20 +26963,31 @@
           <t>(Fr.) Pat.</t>
         </is>
       </c>
-      <c r="I238" t="inlineStr"/>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr"/>
+      <c r="N238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
-          <t>Norrbytorp, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>688093</v>
+        <v>688088</v>
       </c>
       <c r="R238" t="n">
-        <v>6562720</v>
+        <v>6562722</v>
       </c>
       <c r="S238" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T238" t="inlineStr">
         <is>
@@ -27004,22 +27011,12 @@
       </c>
       <c r="Y238" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="Z238" t="inlineStr">
-        <is>
-          <t>12:05</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="AB238" t="inlineStr">
-        <is>
-          <t>12:05</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -27028,33 +27025,34 @@
       <c r="AE238" t="b">
         <v>0</v>
       </c>
+      <c r="AF238" t="inlineStr"/>
       <c r="AG238" t="b">
         <v>0</v>
       </c>
       <c r="AT238" t="inlineStr"/>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136394237</t>
+          <t>https://artportalen.se/Sighting/128314411</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>136268106</v>
+        <v>136394237</v>
       </c>
       <c r="B239" t="n">
-        <v>92076</v>
+        <v>92524</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -27062,40 +27060,37 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>5447</v>
+        <v>5420</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
-      <c r="J239" t="inlineStr"/>
-      <c r="K239" t="inlineStr"/>
-      <c r="N239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>687910</v>
+        <v>688093</v>
       </c>
       <c r="R239" t="n">
-        <v>6562787</v>
+        <v>6562720</v>
       </c>
       <c r="S239" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T239" t="inlineStr">
         <is>
@@ -27122,14 +27117,19 @@
           <t>2026-08-30</t>
         </is>
       </c>
+      <c r="Z239" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
       <c r="AA239" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="AC239" t="inlineStr">
-        <is>
-          <t>På rätt klen, senvuxen?, lutande granlåga i ett kärr.</t>
+      <c r="AB239" t="inlineStr">
+        <is>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -27138,31 +27138,30 @@
       <c r="AE239" t="b">
         <v>0</v>
       </c>
-      <c r="AF239" t="inlineStr"/>
       <c r="AG239" t="b">
         <v>0</v>
       </c>
       <c r="AT239" t="inlineStr"/>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136268106</t>
+          <t>https://artportalen.se/Sighting/136394237</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>136697126</v>
+        <v>136268106</v>
       </c>
       <c r="B240" t="n">
         <v>92076</v>
@@ -27200,10 +27199,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>687998</v>
+        <v>687910</v>
       </c>
       <c r="R240" t="n">
-        <v>6562803</v>
+        <v>6562787</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -27230,12 +27229,17 @@
       </c>
       <c r="Y240" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AC240" t="inlineStr">
+        <is>
+          <t>På rätt klen, senvuxen?, lutande granlåga i ett kärr.</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -27262,38 +27266,38 @@
       <c r="AY240" t="inlineStr"/>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136697126</t>
+          <t>https://artportalen.se/Sighting/136268106</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>128314833</v>
+        <v>136697126</v>
       </c>
       <c r="B241" t="n">
-        <v>93235</v>
+        <v>92076</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -27306,10 +27310,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>688073</v>
+        <v>687998</v>
       </c>
       <c r="R241" t="n">
-        <v>6562768</v>
+        <v>6562803</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -27336,12 +27340,12 @@
       </c>
       <c r="Y241" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AA241" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AD241" t="b">
@@ -27368,13 +27372,13 @@
       <c r="AY241" t="inlineStr"/>
       <c r="AZ241" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128314833</t>
+          <t>https://artportalen.se/Sighting/136697126</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>128317789</v>
+        <v>128314833</v>
       </c>
       <c r="B242" t="n">
         <v>93235</v>
@@ -27412,10 +27416,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>688094</v>
+        <v>688073</v>
       </c>
       <c r="R242" t="n">
-        <v>6562777</v>
+        <v>6562768</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -27474,13 +27478,13 @@
       <c r="AY242" t="inlineStr"/>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128317789</t>
+          <t>https://artportalen.se/Sighting/128314833</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>128526064</v>
+        <v>128317789</v>
       </c>
       <c r="B243" t="n">
         <v>93235</v>
@@ -27518,10 +27522,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>687952</v>
+        <v>688094</v>
       </c>
       <c r="R243" t="n">
-        <v>6562790</v>
+        <v>6562777</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -27548,12 +27552,12 @@
       </c>
       <c r="Y243" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -27580,13 +27584,13 @@
       <c r="AY243" t="inlineStr"/>
       <c r="AZ243" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128526064</t>
+          <t>https://artportalen.se/Sighting/128317789</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>128646583</v>
+        <v>128526064</v>
       </c>
       <c r="B244" t="n">
         <v>93235</v>
@@ -27624,10 +27628,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>688067</v>
+        <v>687952</v>
       </c>
       <c r="R244" t="n">
-        <v>6562731</v>
+        <v>6562790</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -27654,12 +27658,12 @@
       </c>
       <c r="Y244" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -27686,16 +27690,16 @@
       <c r="AY244" t="inlineStr"/>
       <c r="AZ244" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128646583</t>
+          <t>https://artportalen.se/Sighting/128526064</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>136801045</v>
+        <v>128646583</v>
       </c>
       <c r="B245" t="n">
-        <v>93449</v>
+        <v>93235</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -27730,10 +27734,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>687990</v>
+        <v>688067</v>
       </c>
       <c r="R245" t="n">
-        <v>6562795</v>
+        <v>6562731</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -27760,12 +27764,12 @@
       </c>
       <c r="Y245" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -27792,13 +27796,13 @@
       <c r="AY245" t="inlineStr"/>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136801045</t>
+          <t>https://artportalen.se/Sighting/128646583</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>136801064</v>
+        <v>136801045</v>
       </c>
       <c r="B246" t="n">
         <v>93449</v>
@@ -27836,10 +27840,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>687946</v>
+        <v>687990</v>
       </c>
       <c r="R246" t="n">
-        <v>6562790</v>
+        <v>6562795</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -27898,16 +27902,16 @@
       <c r="AY246" t="inlineStr"/>
       <c r="AZ246" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136801064</t>
+          <t>https://artportalen.se/Sighting/136801045</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>136241765</v>
+        <v>136801064</v>
       </c>
       <c r="B247" t="n">
-        <v>80095</v>
+        <v>93449</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -27915,44 +27919,40 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
       <c r="J247" t="inlineStr"/>
-      <c r="K247" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K247" t="inlineStr"/>
       <c r="N247" t="inlineStr"/>
       <c r="P247" t="inlineStr">
         <is>
-          <t>Norrbytorp, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>688014</v>
+        <v>687946</v>
       </c>
       <c r="R247" t="n">
-        <v>6562734</v>
+        <v>6562790</v>
       </c>
       <c r="S247" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T247" t="inlineStr">
         <is>
@@ -27976,22 +27976,12 @@
       </c>
       <c r="Y247" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="Z247" t="inlineStr">
-        <is>
-          <t>12:38</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA247" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="AB247" t="inlineStr">
-        <is>
-          <t>12:38</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -28007,27 +27997,27 @@
       <c r="AT247" t="inlineStr"/>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>Björn Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>Björn Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136241765</t>
+          <t>https://artportalen.se/Sighting/136801064</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>17285491</v>
+        <v>136241765</v>
       </c>
       <c r="B248" t="n">
-        <v>80432</v>
+        <v>80095</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -28035,39 +28025,44 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
       <c r="J248" t="inlineStr"/>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N248" t="inlineStr"/>
       <c r="P248" t="inlineStr">
         <is>
-          <t>Norrby torp, 480 m Ö, Srm</t>
+          <t>Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>688111</v>
+        <v>688014</v>
       </c>
       <c r="R248" t="n">
-        <v>6562706</v>
+        <v>6562734</v>
       </c>
       <c r="S248" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T248" t="inlineStr">
         <is>
@@ -28091,17 +28086,22 @@
       </c>
       <c r="Y248" t="inlineStr">
         <is>
-          <t>2015-04-02</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="Z248" t="inlineStr">
+        <is>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
         <is>
-          <t>2015-04-02</t>
-        </is>
-      </c>
-      <c r="AC248" t="inlineStr">
-        <is>
-          <t>På ek i bergskanten, ca 220 cm omkrets. Sparsamt vid 20 resp. 70 cm höjd.</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AB248" t="inlineStr">
+        <is>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -28110,35 +28110,31 @@
       <c r="AE248" t="b">
         <v>0</v>
       </c>
+      <c r="AF248" t="inlineStr"/>
       <c r="AG248" t="b">
         <v>0</v>
-      </c>
-      <c r="AI248" t="inlineStr">
-        <is>
-          <t>Yngre gallrad blandskog</t>
-        </is>
       </c>
       <c r="AT248" t="inlineStr"/>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Björn Persson</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Björn Persson</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/17285491</t>
+          <t>https://artportalen.se/Sighting/136241765</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>79273786</v>
+        <v>17285491</v>
       </c>
       <c r="B249" t="n">
         <v>80432</v>
@@ -28167,16 +28163,18 @@
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
+      <c r="J249" t="inlineStr"/>
+      <c r="K249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
-          <t>Åvadal, Srm</t>
+          <t>Norrby torp, 480 m Ö, Srm</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>688109</v>
+        <v>688111</v>
       </c>
       <c r="R249" t="n">
-        <v>6562704</v>
+        <v>6562706</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -28203,12 +28201,17 @@
       </c>
       <c r="Y249" t="inlineStr">
         <is>
-          <t>2019-08-01</t>
+          <t>2015-04-02</t>
         </is>
       </c>
       <c r="AA249" t="inlineStr">
         <is>
-          <t>2019-08-01</t>
+          <t>2015-04-02</t>
+        </is>
+      </c>
+      <c r="AC249" t="inlineStr">
+        <is>
+          <t>På ek i bergskanten, ca 220 cm omkrets. Sparsamt vid 20 resp. 70 cm höjd.</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -28220,42 +28223,32 @@
       <c r="AG249" t="b">
         <v>0</v>
       </c>
-      <c r="AJ249" t="inlineStr">
-        <is>
-          <t>skogsek</t>
-        </is>
-      </c>
-      <c r="AK249" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
-      </c>
-      <c r="AO249" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
+      <c r="AI249" t="inlineStr">
+        <is>
+          <t>Yngre gallrad blandskog</t>
         </is>
       </c>
       <c r="AT249" t="inlineStr"/>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>Gustav Wikström</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>Gustav Wikström</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/79273786</t>
+          <t>https://artportalen.se/Sighting/17285491</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>89840770</v>
+        <v>79273786</v>
       </c>
       <c r="B250" t="n">
         <v>80432</v>
@@ -28284,19 +28277,16 @@
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
-      <c r="J250" t="inlineStr"/>
-      <c r="K250" t="inlineStr"/>
-      <c r="N250" t="inlineStr"/>
       <c r="P250" t="inlineStr">
         <is>
-          <t>Ö Norrby Torp, Srm</t>
+          <t>Åvadal, Srm</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>688146</v>
+        <v>688109</v>
       </c>
       <c r="R250" t="n">
-        <v>6562738</v>
+        <v>6562704</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -28323,17 +28313,12 @@
       </c>
       <c r="Y250" t="inlineStr">
         <is>
-          <t>2020-12-30</t>
+          <t>2019-08-01</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
         <is>
-          <t>2020-12-30</t>
-        </is>
-      </c>
-      <c r="AC250" t="inlineStr">
-        <is>
-          <t>Tre bålar på en ek som inte längre ser ut att vara så livskraftig. Finns en annan noterad ek med lavar en bit ifrån.</t>
+          <t>2019-08-01</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -28342,31 +28327,45 @@
       <c r="AE250" t="b">
         <v>0</v>
       </c>
-      <c r="AF250" t="inlineStr"/>
       <c r="AG250" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ250" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK250" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO250" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
       </c>
       <c r="AT250" t="inlineStr"/>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Gustav Wikström</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Gustav Wikström</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89840770</t>
+          <t>https://artportalen.se/Sighting/79273786</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>112384453</v>
+        <v>89840770</v>
       </c>
       <c r="B251" t="n">
         <v>80432</v>
@@ -28400,14 +28399,14 @@
       <c r="N251" t="inlineStr"/>
       <c r="P251" t="inlineStr">
         <is>
-          <t>Norrby torp Ö om, Srm</t>
+          <t>Ö Norrby Torp, Srm</t>
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>688145</v>
+        <v>688146</v>
       </c>
       <c r="R251" t="n">
-        <v>6562737</v>
+        <v>6562738</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -28434,17 +28433,17 @@
       </c>
       <c r="Y251" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2020-12-30</t>
         </is>
       </c>
       <c r="AA251" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2020-12-30</t>
         </is>
       </c>
       <c r="AC251" t="inlineStr">
         <is>
-          <t>Återfynd. På halvdöd ek med blottad ved men några levande grenar i toppen, ca 120 cm omkrets. Två mindre blaffor i dåligt skick, hänger något löst, ca 40 resp. 130 cm höjd.</t>
+          <t>Tre bålar på en ek som inte längre ser ut att vara så livskraftig. Finns en annan noterad ek med lavar en bit ifrån.</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -28460,24 +28459,24 @@
       <c r="AT251" t="inlineStr"/>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112384453</t>
+          <t>https://artportalen.se/Sighting/89840770</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>122779297</v>
+        <v>112384453</v>
       </c>
       <c r="B252" t="n">
         <v>80432</v>
@@ -28511,14 +28510,14 @@
       <c r="N252" t="inlineStr"/>
       <c r="P252" t="inlineStr">
         <is>
-          <t>Lunglav, Srm</t>
+          <t>Norrby torp Ö om, Srm</t>
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>688116</v>
+        <v>688145</v>
       </c>
       <c r="R252" t="n">
-        <v>6562703</v>
+        <v>6562737</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -28545,17 +28544,17 @@
       </c>
       <c r="Y252" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA252" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AC252" t="inlineStr">
         <is>
-          <t>Lunglav på gammal ek</t>
+          <t>Återfynd. På halvdöd ek med blottad ved men några levande grenar i toppen, ca 120 cm omkrets. Två mindre blaffor i dåligt skick, hänger något löst, ca 40 resp. 130 cm höjd.</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -28571,81 +28570,68 @@
       <c r="AT252" t="inlineStr"/>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122779297</t>
+          <t>https://artportalen.se/Sighting/112384453</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>125923864</v>
+        <v>122779297</v>
       </c>
       <c r="B253" t="n">
-        <v>57754</v>
+        <v>80432</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>102118</v>
+        <v>6458</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I253" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr"/>
+      <c r="J253" t="inlineStr"/>
       <c r="K253" t="inlineStr"/>
-      <c r="L253" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M253" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
       <c r="N253" t="inlineStr"/>
       <c r="P253" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Lunglav, Srm</t>
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>687916</v>
+        <v>688116</v>
       </c>
       <c r="R253" t="n">
-        <v>6562815</v>
+        <v>6562703</v>
       </c>
       <c r="S253" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T253" t="inlineStr">
         <is>
@@ -28669,17 +28655,17 @@
       </c>
       <c r="Y253" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA253" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AC253" t="inlineStr">
         <is>
-          <t>Stöttes och stannade nära, det fanns ett ägg. Än så länge?</t>
+          <t>Lunglav på gammal ek</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -28688,63 +28674,72 @@
       <c r="AE253" t="b">
         <v>0</v>
       </c>
+      <c r="AF253" t="inlineStr"/>
       <c r="AG253" t="b">
         <v>0</v>
       </c>
       <c r="AT253" t="inlineStr"/>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125923864</t>
+          <t>https://artportalen.se/Sighting/122779297</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>128317861</v>
+        <v>125923864</v>
       </c>
       <c r="B254" t="n">
-        <v>58114</v>
+        <v>57754</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>103021</v>
+        <v>102118</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I254" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K254" t="inlineStr"/>
-      <c r="L254" t="inlineStr"/>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>bo, ägg/ungar</t>
         </is>
       </c>
       <c r="N254" t="inlineStr"/>
@@ -28754,10 +28749,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>688058</v>
+        <v>687916</v>
       </c>
       <c r="R254" t="n">
-        <v>6562805</v>
+        <v>6562815</v>
       </c>
       <c r="S254" t="n">
         <v>25</v>
@@ -28784,12 +28779,17 @@
       </c>
       <c r="Y254" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AC254" t="inlineStr">
+        <is>
+          <t>Stöttes och stannade nära, det fanns ett ägg. Än så länge?</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -28815,16 +28815,16 @@
       <c r="AY254" t="inlineStr"/>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128317861</t>
+          <t>https://artportalen.se/Sighting/125923864</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>136138855</v>
+        <v>128317861</v>
       </c>
       <c r="B255" t="n">
-        <v>58169</v>
+        <v>58114</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -28864,13 +28864,13 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>687836</v>
+        <v>688058</v>
       </c>
       <c r="R255" t="n">
-        <v>6562786</v>
+        <v>6562805</v>
       </c>
       <c r="S255" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T255" t="inlineStr">
         <is>
@@ -28894,12 +28894,12 @@
       </c>
       <c r="Y255" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA255" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD255" t="b">
@@ -28925,13 +28925,13 @@
       <c r="AY255" t="inlineStr"/>
       <c r="AZ255" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136138855</t>
+          <t>https://artportalen.se/Sighting/128317861</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>136138971</v>
+        <v>136138855</v>
       </c>
       <c r="B256" t="n">
         <v>58169</v>
@@ -28974,13 +28974,13 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>687977</v>
+        <v>687836</v>
       </c>
       <c r="R256" t="n">
-        <v>6562735</v>
+        <v>6562786</v>
       </c>
       <c r="S256" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T256" t="inlineStr">
         <is>
@@ -29035,13 +29035,13 @@
       <c r="AY256" t="inlineStr"/>
       <c r="AZ256" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136138971</t>
+          <t>https://artportalen.se/Sighting/136138855</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>136823037</v>
+        <v>136138971</v>
       </c>
       <c r="B257" t="n">
         <v>58169</v>
@@ -29084,10 +29084,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>688141</v>
+        <v>687977</v>
       </c>
       <c r="R257" t="n">
-        <v>6562748</v>
+        <v>6562735</v>
       </c>
       <c r="S257" t="n">
         <v>25</v>
@@ -29114,12 +29114,12 @@
       </c>
       <c r="Y257" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AA257" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AD257" t="b">
@@ -29145,13 +29145,13 @@
       <c r="AY257" t="inlineStr"/>
       <c r="AZ257" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136823037</t>
+          <t>https://artportalen.se/Sighting/136138971</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>136823087</v>
+        <v>136823037</v>
       </c>
       <c r="B258" t="n">
         <v>58169</v>
@@ -29194,13 +29194,13 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>687936</v>
+        <v>688141</v>
       </c>
       <c r="R258" t="n">
-        <v>6562770</v>
+        <v>6562748</v>
       </c>
       <c r="S258" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T258" t="inlineStr">
         <is>
@@ -29255,59 +29255,62 @@
       <c r="AY258" t="inlineStr"/>
       <c r="AZ258" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136823087</t>
+          <t>https://artportalen.se/Sighting/136823037</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>136777552</v>
+        <v>136823087</v>
       </c>
       <c r="B259" t="n">
-        <v>5202</v>
+        <v>58169</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
+      <c r="K259" t="inlineStr"/>
+      <c r="L259" t="inlineStr"/>
       <c r="M259" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N259" t="inlineStr"/>
       <c r="P259" t="inlineStr">
         <is>
-          <t>Norrby torp, Tyresta, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>687944</v>
+        <v>687936</v>
       </c>
       <c r="R259" t="n">
-        <v>6562783</v>
+        <v>6562770</v>
       </c>
       <c r="S259" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T259" t="inlineStr">
         <is>
@@ -29331,22 +29334,12 @@
       </c>
       <c r="Y259" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="Z259" t="inlineStr">
-        <is>
-          <t>11:54</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA259" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="AB259" t="inlineStr">
-        <is>
-          <t>11:54</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD259" t="b">
@@ -29357,46 +29350,31 @@
       </c>
       <c r="AG259" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ259" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK259" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO259" t="inlineStr">
-        <is>
-          <t>Klen barklös granlåga # Picea abies</t>
-        </is>
       </c>
       <c r="AT259" t="inlineStr"/>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
       <c r="AZ259" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136777552</t>
+          <t>https://artportalen.se/Sighting/136823087</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>136823074</v>
+        <v>136777552</v>
       </c>
       <c r="B260" t="n">
-        <v>8463</v>
+        <v>5202</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -29404,46 +29382,42 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
-      <c r="J260" t="inlineStr"/>
-      <c r="K260" t="inlineStr"/>
-      <c r="L260" t="inlineStr"/>
       <c r="M260" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N260" t="inlineStr"/>
       <c r="P260" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrby torp, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>687940</v>
+        <v>687944</v>
       </c>
       <c r="R260" t="n">
-        <v>6562785</v>
+        <v>6562783</v>
       </c>
       <c r="S260" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T260" t="inlineStr">
         <is>
@@ -29467,12 +29441,22 @@
       </c>
       <c r="Y260" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="Z260" t="inlineStr">
+        <is>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA260" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AB260" t="inlineStr">
+        <is>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD260" t="b">
@@ -29481,34 +29465,48 @@
       <c r="AE260" t="b">
         <v>0</v>
       </c>
-      <c r="AF260" t="inlineStr"/>
       <c r="AG260" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ260" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK260" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO260" t="inlineStr">
+        <is>
+          <t>Klen barklös granlåga # Picea abies</t>
+        </is>
       </c>
       <c r="AT260" t="inlineStr"/>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
       <c r="AZ260" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136823074</t>
+          <t>https://artportalen.se/Sighting/136777552</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>136777549</v>
+        <v>136823074</v>
       </c>
       <c r="B261" t="n">
-        <v>8452</v>
+        <v>8463</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -29516,42 +29514,46 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
+      <c r="J261" t="inlineStr"/>
+      <c r="K261" t="inlineStr"/>
+      <c r="L261" t="inlineStr"/>
       <c r="M261" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
+      <c r="N261" t="inlineStr"/>
       <c r="P261" t="inlineStr">
         <is>
-          <t>Norrby torp, Tyresta, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>687859</v>
+        <v>687940</v>
       </c>
       <c r="R261" t="n">
-        <v>6562767</v>
+        <v>6562785</v>
       </c>
       <c r="S261" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T261" t="inlineStr">
         <is>
@@ -29575,22 +29577,12 @@
       </c>
       <c r="Y261" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="Z261" t="inlineStr">
-        <is>
-          <t>11:28</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA261" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="AB261" t="inlineStr">
-        <is>
-          <t>11:28</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD261" t="b">
@@ -29599,48 +29591,34 @@
       <c r="AE261" t="b">
         <v>0</v>
       </c>
+      <c r="AF261" t="inlineStr"/>
       <c r="AG261" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ261" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK261" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO261" t="inlineStr">
-        <is>
-          <t>Död stående björk # Betula</t>
-        </is>
       </c>
       <c r="AT261" t="inlineStr"/>
       <c r="AW261" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
       <c r="AZ261" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136777549</t>
+          <t>https://artportalen.se/Sighting/136823074</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>122692266</v>
+        <v>136777549</v>
       </c>
       <c r="B262" t="n">
-        <v>58826</v>
+        <v>8452</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -29648,54 +29626,42 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>208242</v>
+        <v>106554</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I262" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J262" t="inlineStr"/>
-      <c r="K262" t="inlineStr"/>
-      <c r="L262" t="inlineStr"/>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr"/>
       <c r="M262" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N262" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P262" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander, Srm</t>
+          <t>Norrby torp, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>687868</v>
+        <v>687859</v>
       </c>
       <c r="R262" t="n">
-        <v>6562755</v>
+        <v>6562767</v>
       </c>
       <c r="S262" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T262" t="inlineStr">
         <is>
@@ -29719,17 +29685,22 @@
       </c>
       <c r="Y262" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="Z262" t="inlineStr">
+        <is>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA262" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AC262" t="inlineStr">
-        <is>
-          <t>Mindre vattensalamander</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AB262" t="inlineStr">
+        <is>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD262" t="b">
@@ -29738,34 +29709,48 @@
       <c r="AE262" t="b">
         <v>0</v>
       </c>
-      <c r="AF262" t="inlineStr"/>
       <c r="AG262" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ262" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK262" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO262" t="inlineStr">
+        <is>
+          <t>Död stående björk # Betula</t>
+        </is>
       </c>
       <c r="AT262" t="inlineStr"/>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
       <c r="AZ262" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122692266</t>
+          <t>https://artportalen.se/Sighting/136777549</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>136241491</v>
+        <v>122692266</v>
       </c>
       <c r="B263" t="n">
-        <v>58845</v>
+        <v>58826</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -29773,16 +29758,16 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>208245</v>
+        <v>208242</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -29790,19 +29775,31 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I263" t="inlineStr"/>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J263" t="inlineStr"/>
       <c r="K263" t="inlineStr"/>
       <c r="L263" t="inlineStr"/>
-      <c r="M263" t="inlineStr"/>
-      <c r="N263" t="inlineStr"/>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P263" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Mindre vattensalamander, Srm</t>
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>687873</v>
+        <v>687868</v>
       </c>
       <c r="R263" t="n">
         <v>6562755</v>
@@ -29832,17 +29829,17 @@
       </c>
       <c r="Y263" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA263" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AC263" t="inlineStr">
         <is>
-          <t>Troligen årsunge.</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="AD263" t="b">
@@ -29858,27 +29855,27 @@
       <c r="AT263" t="inlineStr"/>
       <c r="AW263" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
       <c r="AZ263" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136241491</t>
+          <t>https://artportalen.se/Sighting/122692266</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>101544040</v>
+        <v>136241491</v>
       </c>
       <c r="B264" t="n">
-        <v>99035</v>
+        <v>58845</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -29886,41 +29883,42 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>219790</v>
+        <v>208245</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
       <c r="J264" t="inlineStr"/>
       <c r="K264" t="inlineStr"/>
       <c r="L264" t="inlineStr"/>
+      <c r="M264" t="inlineStr"/>
       <c r="N264" t="inlineStr"/>
       <c r="P264" t="inlineStr">
         <is>
-          <t>NO Norrby Torp, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>687896</v>
+        <v>687873</v>
       </c>
       <c r="R264" t="n">
-        <v>6562764</v>
+        <v>6562755</v>
       </c>
       <c r="S264" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T264" t="inlineStr">
         <is>
@@ -29944,12 +29942,17 @@
       </c>
       <c r="Y264" t="inlineStr">
         <is>
-          <t>2022-06-09</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="AA264" t="inlineStr">
         <is>
-          <t>2022-06-09</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AC264" t="inlineStr">
+        <is>
+          <t>Troligen årsunge.</t>
         </is>
       </c>
       <c r="AD264" t="b">
@@ -29976,16 +29979,16 @@
       <c r="AY264" t="inlineStr"/>
       <c r="AZ264" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101544040</t>
+          <t>https://artportalen.se/Sighting/136241491</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>136394236</v>
+        <v>101544040</v>
       </c>
       <c r="B265" t="n">
-        <v>98215</v>
+        <v>99035</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -29993,37 +29996,41 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
+      <c r="J265" t="inlineStr"/>
+      <c r="K265" t="inlineStr"/>
+      <c r="L265" t="inlineStr"/>
+      <c r="N265" t="inlineStr"/>
       <c r="P265" t="inlineStr">
         <is>
-          <t>Norrbytorp, Srm</t>
+          <t>NO Norrby Torp, Srm</t>
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>687882</v>
+        <v>687896</v>
       </c>
       <c r="R265" t="n">
-        <v>6562761</v>
+        <v>6562764</v>
       </c>
       <c r="S265" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="T265" t="inlineStr">
         <is>
@@ -30047,22 +30054,12 @@
       </c>
       <c r="Y265" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="Z265" t="inlineStr">
-        <is>
-          <t>11:26</t>
+          <t>2022-06-09</t>
         </is>
       </c>
       <c r="AA265" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="AB265" t="inlineStr">
-        <is>
-          <t>11:26</t>
+          <t>2022-06-09</t>
         </is>
       </c>
       <c r="AD265" t="b">
@@ -30071,33 +30068,34 @@
       <c r="AE265" t="b">
         <v>0</v>
       </c>
+      <c r="AF265" t="inlineStr"/>
       <c r="AG265" t="b">
         <v>0</v>
       </c>
       <c r="AT265" t="inlineStr"/>
       <c r="AW265" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
       <c r="AZ265" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136394236</t>
+          <t>https://artportalen.se/Sighting/101544040</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>122930166</v>
+        <v>136394236</v>
       </c>
       <c r="B266" t="n">
-        <v>96554</v>
+        <v>98215</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -30105,41 +30103,37 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>210</v>
+        <v>221945</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
-      <c r="J266" t="inlineStr"/>
-      <c r="K266" t="inlineStr"/>
-      <c r="L266" t="inlineStr"/>
-      <c r="N266" t="inlineStr"/>
       <c r="P266" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>686762</v>
+        <v>687882</v>
       </c>
       <c r="R266" t="n">
-        <v>6562715</v>
+        <v>6562761</v>
       </c>
       <c r="S266" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="T266" t="inlineStr">
         <is>
@@ -30163,22 +30157,22 @@
       </c>
       <c r="Y266" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="Z266" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA266" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="AB266" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD266" t="b">
@@ -30193,68 +30187,69 @@
       <c r="AT266" t="inlineStr"/>
       <c r="AW266" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX266" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
       <c r="AZ266" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122930166</t>
+          <t>https://artportalen.se/Sighting/136394236</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>119061006</v>
+        <v>122930166</v>
       </c>
       <c r="B267" t="n">
-        <v>91533</v>
+        <v>96554</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>2051</v>
+        <v>210</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
       <c r="J267" t="inlineStr"/>
       <c r="K267" t="inlineStr"/>
+      <c r="L267" t="inlineStr"/>
       <c r="N267" t="inlineStr"/>
       <c r="P267" t="inlineStr">
         <is>
-          <t>S Norrby mosse, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>686477</v>
+        <v>686762</v>
       </c>
       <c r="R267" t="n">
-        <v>6562857</v>
+        <v>6562715</v>
       </c>
       <c r="S267" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="T267" t="inlineStr">
         <is>
@@ -30278,17 +30273,22 @@
       </c>
       <c r="Y267" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="Z267" t="inlineStr">
+        <is>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA267" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC267" t="inlineStr">
-        <is>
-          <t>Brukad skog nära kant mot gammal.</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AB267" t="inlineStr">
+        <is>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD267" t="b">
@@ -30297,81 +30297,74 @@
       <c r="AE267" t="b">
         <v>0</v>
       </c>
-      <c r="AF267" t="inlineStr"/>
       <c r="AG267" t="b">
         <v>0</v>
       </c>
       <c r="AT267" t="inlineStr"/>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
       <c r="AZ267" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119061006</t>
+          <t>https://artportalen.se/Sighting/122930166</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>122929535</v>
+        <v>119061006</v>
       </c>
       <c r="B268" t="n">
-        <v>8455</v>
+        <v>91533</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>106545</v>
+        <v>2051</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I268" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr"/>
       <c r="J268" t="inlineStr"/>
       <c r="K268" t="inlineStr"/>
-      <c r="L268" t="inlineStr"/>
-      <c r="M268" t="inlineStr"/>
       <c r="N268" t="inlineStr"/>
       <c r="P268" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>S Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>686612</v>
+        <v>686477</v>
       </c>
       <c r="R268" t="n">
-        <v>6562882</v>
+        <v>6562857</v>
       </c>
       <c r="S268" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T268" t="inlineStr">
         <is>
@@ -30395,22 +30388,17 @@
       </c>
       <c r="Y268" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="Z268" t="inlineStr">
-        <is>
-          <t>11:01</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA268" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="AB268" t="inlineStr">
-        <is>
-          <t>11:01</t>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC268" t="inlineStr">
+        <is>
+          <t>Brukad skog nära kant mot gammal.</t>
         </is>
       </c>
       <c r="AD268" t="b">
@@ -30419,33 +30407,34 @@
       <c r="AE268" t="b">
         <v>0</v>
       </c>
+      <c r="AF268" t="inlineStr"/>
       <c r="AG268" t="b">
         <v>0</v>
       </c>
       <c r="AT268" t="inlineStr"/>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
       <c r="AZ268" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122929535</t>
+          <t>https://artportalen.se/Sighting/119061006</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>122928987</v>
+        <v>136947774</v>
       </c>
       <c r="B269" t="n">
-        <v>97983</v>
+        <v>57195</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -30453,38 +30442,50 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I269" t="inlineStr"/>
-      <c r="J269" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K269" t="inlineStr"/>
-      <c r="L269" t="inlineStr"/>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N269" t="inlineStr"/>
       <c r="P269" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>686389</v>
+        <v>686354</v>
       </c>
       <c r="R269" t="n">
-        <v>6562967</v>
+        <v>6562881</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -30511,22 +30512,17 @@
       </c>
       <c r="Y269" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="Z269" t="inlineStr">
-        <is>
-          <t>10:36</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AA269" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="AB269" t="inlineStr">
-        <is>
-          <t>10:36</t>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AC269" t="inlineStr">
+        <is>
+          <t>Ruggad stjärtpenna, 33.5 cm.</t>
         </is>
       </c>
       <c r="AD269" t="b">
@@ -30541,65 +30537,74 @@
       <c r="AT269" t="inlineStr"/>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
       <c r="AZ269" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122928987</t>
+          <t>https://artportalen.se/Sighting/136947774</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>126061106</v>
+        <v>122929535</v>
       </c>
       <c r="B270" t="n">
-        <v>91333</v>
+        <v>8455</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>2008</v>
+        <v>106545</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>Pers., nom.sanct.</t>
-        </is>
-      </c>
-      <c r="I270" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr"/>
+      <c r="K270" t="inlineStr"/>
+      <c r="L270" t="inlineStr"/>
+      <c r="M270" t="inlineStr"/>
+      <c r="N270" t="inlineStr"/>
       <c r="P270" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>686883</v>
+        <v>686612</v>
       </c>
       <c r="R270" t="n">
-        <v>6562742</v>
+        <v>6562882</v>
       </c>
       <c r="S270" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T270" t="inlineStr">
         <is>
@@ -30623,22 +30628,22 @@
       </c>
       <c r="Y270" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="Z270" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA270" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="AB270" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD270" t="b">
@@ -30653,27 +30658,27 @@
       <c r="AT270" t="inlineStr"/>
       <c r="AW270" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
       <c r="AZ270" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061106</t>
+          <t>https://artportalen.se/Sighting/122929535</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>126061107</v>
+        <v>122928987</v>
       </c>
       <c r="B271" t="n">
-        <v>96458</v>
+        <v>97983</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -30681,34 +30686,38 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>2818</v>
+        <v>221945</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
+      <c r="J271" t="inlineStr"/>
+      <c r="K271" t="inlineStr"/>
+      <c r="L271" t="inlineStr"/>
+      <c r="N271" t="inlineStr"/>
       <c r="P271" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>686880</v>
+        <v>686389</v>
       </c>
       <c r="R271" t="n">
-        <v>6562745</v>
+        <v>6562967</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -30735,22 +30744,22 @@
       </c>
       <c r="Y271" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="Z271" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA271" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="AB271" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD271" t="b">
@@ -30765,65 +30774,62 @@
       <c r="AT271" t="inlineStr"/>
       <c r="AW271" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX271" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY271" t="inlineStr"/>
       <c r="AZ271" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061107</t>
+          <t>https://artportalen.se/Sighting/122928987</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>129215187</v>
+        <v>126061106</v>
       </c>
       <c r="B272" t="n">
-        <v>91872</v>
+        <v>91333</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>5447</v>
+        <v>2008</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Pers., nom.sanct.</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
-      <c r="J272" t="inlineStr"/>
-      <c r="K272" t="inlineStr"/>
-      <c r="N272" t="inlineStr"/>
       <c r="P272" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>686977</v>
+        <v>686883</v>
       </c>
       <c r="R272" t="n">
-        <v>6562706</v>
+        <v>6562742</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -30850,12 +30856,22 @@
       </c>
       <c r="Y272" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z272" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA272" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB272" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD272" t="b">
@@ -30864,34 +30880,33 @@
       <c r="AE272" t="b">
         <v>0</v>
       </c>
-      <c r="AF272" t="inlineStr"/>
       <c r="AG272" t="b">
         <v>0</v>
       </c>
       <c r="AT272" t="inlineStr"/>
       <c r="AW272" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX272" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY272" t="inlineStr"/>
       <c r="AZ272" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215187</t>
+          <t>https://artportalen.se/Sighting/126061106</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>126061104</v>
+        <v>126061107</v>
       </c>
       <c r="B273" t="n">
-        <v>4775</v>
+        <v>96458</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -30899,21 +30914,21 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>100299</v>
+        <v>2818</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
@@ -30923,10 +30938,10 @@
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>686868</v>
+        <v>686880</v>
       </c>
       <c r="R273" t="n">
-        <v>6562739</v>
+        <v>6562745</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -30958,7 +30973,7 @@
       </c>
       <c r="Z273" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA273" t="inlineStr">
@@ -30968,7 +30983,7 @@
       </c>
       <c r="AB273" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD273" t="b">
@@ -30979,26 +30994,6 @@
       </c>
       <c r="AG273" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ273" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK273" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL273" t="inlineStr">
-        <is>
-          <t>Stående död gran.</t>
-        </is>
-      </c>
-      <c r="AO273" t="inlineStr">
-        <is>
-          <t>Picea abies # Stående död gran.</t>
-        </is>
       </c>
       <c r="AT273" t="inlineStr"/>
       <c r="AW273" t="inlineStr">
@@ -31014,16 +31009,16 @@
       <c r="AY273" t="inlineStr"/>
       <c r="AZ273" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061104</t>
+          <t>https://artportalen.se/Sighting/126061107</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>126061116</v>
+        <v>129215187</v>
       </c>
       <c r="B274" t="n">
-        <v>44177</v>
+        <v>91872</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -31031,34 +31026,37 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>101735</v>
+        <v>5447</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
+      <c r="J274" t="inlineStr"/>
+      <c r="K274" t="inlineStr"/>
+      <c r="N274" t="inlineStr"/>
       <c r="P274" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>686928</v>
+        <v>686977</v>
       </c>
       <c r="R274" t="n">
-        <v>6562716</v>
+        <v>6562706</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -31085,22 +31083,12 @@
       </c>
       <c r="Y274" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z274" t="inlineStr">
-        <is>
-          <t>11:58</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AA274" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB274" t="inlineStr">
-        <is>
-          <t>11:58</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AD274" t="b">
@@ -31109,53 +31097,34 @@
       <c r="AE274" t="b">
         <v>0</v>
       </c>
+      <c r="AF274" t="inlineStr"/>
       <c r="AG274" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ274" t="inlineStr">
-        <is>
-          <t>fnöskticka</t>
-        </is>
-      </c>
-      <c r="AK274" t="inlineStr">
-        <is>
-          <t>Fomes fomentarius</t>
-        </is>
-      </c>
-      <c r="AL274" t="inlineStr">
-        <is>
-          <t>Fnöskticka på björk.</t>
-        </is>
-      </c>
-      <c r="AO274" t="inlineStr">
-        <is>
-          <t>Fomes fomentarius # Fnöskticka på björk.</t>
-        </is>
       </c>
       <c r="AT274" t="inlineStr"/>
       <c r="AW274" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX274" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY274" t="inlineStr"/>
       <c r="AZ274" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061116</t>
+          <t>https://artportalen.se/Sighting/129215187</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>125974903</v>
+        <v>126061104</v>
       </c>
       <c r="B275" t="n">
-        <v>8444</v>
+        <v>4775</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -31163,50 +31132,37 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>106554</v>
+        <v>100299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I275" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J275" t="inlineStr"/>
-      <c r="K275" t="inlineStr"/>
-      <c r="L275" t="inlineStr"/>
-      <c r="M275" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N275" t="inlineStr"/>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr"/>
       <c r="P275" t="inlineStr">
         <is>
-          <t>söder om Tyresta, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>686838</v>
+        <v>686868</v>
       </c>
       <c r="R275" t="n">
-        <v>6562733</v>
+        <v>6562739</v>
       </c>
       <c r="S275" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T275" t="inlineStr">
         <is>
@@ -31233,14 +31189,19 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="Z275" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
       <c r="AA275" t="inlineStr">
         <is>
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC275" t="inlineStr">
-        <is>
-          <t>gammal björklåga med spår längs hela stammen</t>
+      <c r="AB275" t="inlineStr">
+        <is>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD275" t="b">
@@ -31249,54 +31210,53 @@
       <c r="AE275" t="b">
         <v>0</v>
       </c>
-      <c r="AF275" t="inlineStr"/>
       <c r="AG275" t="b">
         <v>0</v>
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>vårtbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
         <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
-      <c r="AM275" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL275" t="inlineStr">
+        <is>
+          <t>Stående död gran.</t>
         </is>
       </c>
       <c r="AO275" t="inlineStr">
         <is>
-          <t>Wood surface of dead wood # Betula pendula</t>
+          <t>Picea abies # Stående död gran.</t>
         </is>
       </c>
       <c r="AT275" t="inlineStr"/>
       <c r="AW275" t="inlineStr">
         <is>
-          <t>Nette Bygren</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX275" t="inlineStr">
         <is>
-          <t>Nette Bygren</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY275" t="inlineStr"/>
       <c r="AZ275" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125974903</t>
+          <t>https://artportalen.se/Sighting/126061104</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>126061105</v>
+        <v>126061116</v>
       </c>
       <c r="B276" t="n">
-        <v>8444</v>
+        <v>44177</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -31304,21 +31264,21 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>106554</v>
+        <v>101735</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
@@ -31328,10 +31288,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>686860</v>
+        <v>686928</v>
       </c>
       <c r="R276" t="n">
-        <v>6562743</v>
+        <v>6562716</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -31363,7 +31323,7 @@
       </c>
       <c r="Z276" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA276" t="inlineStr">
@@ -31373,7 +31333,7 @@
       </c>
       <c r="AB276" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD276" t="b">
@@ -31387,17 +31347,22 @@
       </c>
       <c r="AJ276" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>fnöskticka</t>
         </is>
       </c>
       <c r="AK276" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Fomes fomentarius</t>
+        </is>
+      </c>
+      <c r="AL276" t="inlineStr">
+        <is>
+          <t>Fnöskticka på björk.</t>
         </is>
       </c>
       <c r="AO276" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Fomes fomentarius # Fnöskticka på björk.</t>
         </is>
       </c>
       <c r="AT276" t="inlineStr"/>
@@ -31413,6 +31378,274 @@
       </c>
       <c r="AY276" t="inlineStr"/>
       <c r="AZ276" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061116</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>125974903</v>
+      </c>
+      <c r="B277" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E277" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr"/>
+      <c r="K277" t="inlineStr"/>
+      <c r="L277" t="inlineStr"/>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N277" t="inlineStr"/>
+      <c r="P277" t="inlineStr">
+        <is>
+          <t>söder om Tyresta, Srm</t>
+        </is>
+      </c>
+      <c r="Q277" t="n">
+        <v>686838</v>
+      </c>
+      <c r="R277" t="n">
+        <v>6562733</v>
+      </c>
+      <c r="S277" t="n">
+        <v>5</v>
+      </c>
+      <c r="T277" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U277" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V277" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W277" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y277" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA277" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC277" t="inlineStr">
+        <is>
+          <t>gammal björklåga med spår längs hela stammen</t>
+        </is>
+      </c>
+      <c r="AD277" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE277" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF277" t="inlineStr"/>
+      <c r="AG277" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ277" t="inlineStr">
+        <is>
+          <t>vårtbjörk</t>
+        </is>
+      </c>
+      <c r="AK277" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AM277" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO277" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Betula pendula</t>
+        </is>
+      </c>
+      <c r="AT277" t="inlineStr"/>
+      <c r="AW277" t="inlineStr">
+        <is>
+          <t>Nette Bygren</t>
+        </is>
+      </c>
+      <c r="AX277" t="inlineStr">
+        <is>
+          <t>Nette Bygren</t>
+        </is>
+      </c>
+      <c r="AY277" t="inlineStr"/>
+      <c r="AZ277" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125974903</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>126061105</v>
+      </c>
+      <c r="B278" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E278" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr"/>
+      <c r="P278" t="inlineStr">
+        <is>
+          <t>Ö Tyresta by, Srm</t>
+        </is>
+      </c>
+      <c r="Q278" t="n">
+        <v>686860</v>
+      </c>
+      <c r="R278" t="n">
+        <v>6562743</v>
+      </c>
+      <c r="S278" t="n">
+        <v>10</v>
+      </c>
+      <c r="T278" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U278" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V278" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W278" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y278" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z278" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA278" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB278" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AD278" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE278" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG278" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ278" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK278" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO278" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AT278" t="inlineStr"/>
+      <c r="AW278" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX278" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AY278" t="inlineStr"/>
+      <c r="AZ278" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/126061105</t>
         </is>
@@ -31695,6 +31928,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ274" r:id="rId273"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ275" r:id="rId274"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ278" r:id="rId277"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 152-2026 artfynd.xlsx
+++ b/artfynd/S 152-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ278"/>
+  <dimension ref="A1:AZ279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21822,10 +21822,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>121859623</v>
+        <v>136972809</v>
       </c>
       <c r="B193" t="n">
-        <v>5179</v>
+        <v>57195</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21833,39 +21833,50 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I193" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Öster om Tyresta by, Tyresta, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>686581</v>
+        <v>686701</v>
       </c>
       <c r="R193" t="n">
-        <v>6562989</v>
+        <v>6563078</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21892,22 +21903,17 @@
       </c>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="Z193" t="inlineStr">
-        <is>
-          <t>17:36</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="AB193" t="inlineStr">
-        <is>
-          <t>17:36</t>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>Tuppfjädrar i nybalad grop.</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -21918,94 +21924,71 @@
       </c>
       <c r="AG193" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ193" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK193" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL193" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO193" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
       </c>
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859623</t>
+          <t>https://artportalen.se/Sighting/136972809</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>128510434</v>
+        <v>121859623</v>
       </c>
       <c r="B194" t="n">
-        <v>58114</v>
+        <v>5179</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
-      <c r="K194" t="inlineStr"/>
-      <c r="L194" t="inlineStr"/>
       <c r="M194" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N194" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>686650</v>
+        <v>686581</v>
       </c>
       <c r="R194" t="n">
-        <v>6563214</v>
+        <v>6562989</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -22032,12 +22015,22 @@
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="Z194" t="inlineStr">
+        <is>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="AB194" t="inlineStr">
+        <is>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -22048,28 +22041,48 @@
       </c>
       <c r="AG194" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ194" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK194" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL194" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO194" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
       </c>
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128510434</t>
+          <t>https://artportalen.se/Sighting/121859623</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>128886960</v>
+        <v>128510434</v>
       </c>
       <c r="B195" t="n">
         <v>58114</v>
@@ -22112,13 +22125,13 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>686792</v>
+        <v>686650</v>
       </c>
       <c r="R195" t="n">
-        <v>6563221</v>
+        <v>6563214</v>
       </c>
       <c r="S195" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -22142,12 +22155,12 @@
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -22173,13 +22186,13 @@
       <c r="AY195" t="inlineStr"/>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128886960</t>
+          <t>https://artportalen.se/Sighting/128510434</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129230389</v>
+        <v>128886960</v>
       </c>
       <c r="B196" t="n">
         <v>58114</v>
@@ -22222,10 +22235,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>686793</v>
+        <v>686792</v>
       </c>
       <c r="R196" t="n">
-        <v>6563302</v>
+        <v>6563221</v>
       </c>
       <c r="S196" t="n">
         <v>25</v>
@@ -22252,12 +22265,12 @@
       </c>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -22283,13 +22296,13 @@
       <c r="AY196" t="inlineStr"/>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129230389</t>
+          <t>https://artportalen.se/Sighting/128886960</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129591579</v>
+        <v>129230389</v>
       </c>
       <c r="B197" t="n">
         <v>58114</v>
@@ -22332,10 +22345,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>686618</v>
+        <v>686793</v>
       </c>
       <c r="R197" t="n">
-        <v>6563047</v>
+        <v>6563302</v>
       </c>
       <c r="S197" t="n">
         <v>25</v>
@@ -22362,12 +22375,12 @@
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -22393,16 +22406,16 @@
       <c r="AY197" t="inlineStr"/>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129591579</t>
+          <t>https://artportalen.se/Sighting/129230389</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>133115563</v>
+        <v>129591579</v>
       </c>
       <c r="B198" t="n">
-        <v>58136</v>
+        <v>58114</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -22432,7 +22445,7 @@
       <c r="L198" t="inlineStr"/>
       <c r="M198" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N198" t="inlineStr"/>
@@ -22442,13 +22455,13 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>686651</v>
+        <v>686618</v>
       </c>
       <c r="R198" t="n">
-        <v>6563184</v>
+        <v>6563047</v>
       </c>
       <c r="S198" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -22472,12 +22485,12 @@
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -22503,16 +22516,16 @@
       <c r="AY198" t="inlineStr"/>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133115563</t>
+          <t>https://artportalen.se/Sighting/129591579</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>136330004</v>
+        <v>133115563</v>
       </c>
       <c r="B199" t="n">
-        <v>58169</v>
+        <v>58136</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22542,7 +22555,7 @@
       <c r="L199" t="inlineStr"/>
       <c r="M199" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N199" t="inlineStr"/>
@@ -22552,10 +22565,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>686477</v>
+        <v>686651</v>
       </c>
       <c r="R199" t="n">
-        <v>6563053</v>
+        <v>6563184</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22582,12 +22595,12 @@
       </c>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -22613,13 +22626,13 @@
       <c r="AY199" t="inlineStr"/>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136330004</t>
+          <t>https://artportalen.se/Sighting/133115563</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>136422006</v>
+        <v>136330004</v>
       </c>
       <c r="B200" t="n">
         <v>58169</v>
@@ -22662,10 +22675,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>686531</v>
+        <v>686477</v>
       </c>
       <c r="R200" t="n">
-        <v>6563059</v>
+        <v>6563053</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22692,12 +22705,12 @@
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -22723,13 +22736,13 @@
       <c r="AY200" t="inlineStr"/>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136422006</t>
+          <t>https://artportalen.se/Sighting/136330004</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>136631248</v>
+        <v>136422006</v>
       </c>
       <c r="B201" t="n">
         <v>58169</v>
@@ -22772,10 +22785,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>686469</v>
+        <v>686531</v>
       </c>
       <c r="R201" t="n">
-        <v>6563013</v>
+        <v>6563059</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22802,12 +22815,12 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -22833,13 +22846,13 @@
       <c r="AY201" t="inlineStr"/>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136631248</t>
+          <t>https://artportalen.se/Sighting/136422006</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>136947615</v>
+        <v>136631248</v>
       </c>
       <c r="B202" t="n">
         <v>58169</v>
@@ -22882,10 +22895,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>686485</v>
+        <v>686469</v>
       </c>
       <c r="R202" t="n">
-        <v>6562997</v>
+        <v>6563013</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22912,12 +22925,12 @@
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -22943,38 +22956,38 @@
       <c r="AY202" t="inlineStr"/>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136947615</t>
+          <t>https://artportalen.se/Sighting/136631248</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>136346607</v>
+        <v>136947615</v>
       </c>
       <c r="B203" t="n">
-        <v>58164</v>
+        <v>58169</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -22992,10 +23005,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>686529</v>
+        <v>686485</v>
       </c>
       <c r="R203" t="n">
-        <v>6563051</v>
+        <v>6562997</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -23022,12 +23035,12 @@
       </c>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -23053,13 +23066,13 @@
       <c r="AY203" t="inlineStr"/>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136346607</t>
+          <t>https://artportalen.se/Sighting/136947615</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>136346721</v>
+        <v>136346607</v>
       </c>
       <c r="B204" t="n">
         <v>58164</v>
@@ -23102,10 +23115,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>686678</v>
+        <v>686529</v>
       </c>
       <c r="R204" t="n">
-        <v>6563074</v>
+        <v>6563051</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -23163,13 +23176,13 @@
       <c r="AY204" t="inlineStr"/>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136346721</t>
+          <t>https://artportalen.se/Sighting/136346607</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>136422024</v>
+        <v>136346721</v>
       </c>
       <c r="B205" t="n">
         <v>58164</v>
@@ -23212,10 +23225,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>686531</v>
+        <v>686678</v>
       </c>
       <c r="R205" t="n">
-        <v>6563059</v>
+        <v>6563074</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -23242,12 +23255,12 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -23273,13 +23286,13 @@
       <c r="AY205" t="inlineStr"/>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136422024</t>
+          <t>https://artportalen.se/Sighting/136346721</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>136557077</v>
+        <v>136422024</v>
       </c>
       <c r="B206" t="n">
         <v>58164</v>
@@ -23322,10 +23335,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>686733</v>
+        <v>686531</v>
       </c>
       <c r="R206" t="n">
-        <v>6563216</v>
+        <v>6563059</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -23352,12 +23365,12 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -23383,16 +23396,16 @@
       <c r="AY206" t="inlineStr"/>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136557077</t>
+          <t>https://artportalen.se/Sighting/136422024</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>136259916</v>
+        <v>136557077</v>
       </c>
       <c r="B207" t="n">
-        <v>8463</v>
+        <v>58164</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -23400,30 +23413,29 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>106545</v>
+        <v>103023</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
-      <c r="J207" t="inlineStr"/>
       <c r="K207" t="inlineStr"/>
       <c r="L207" t="inlineStr"/>
       <c r="M207" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N207" t="inlineStr"/>
@@ -23433,10 +23445,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>686457</v>
+        <v>686733</v>
       </c>
       <c r="R207" t="n">
-        <v>6563062</v>
+        <v>6563216</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -23463,12 +23475,12 @@
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -23477,7 +23489,6 @@
       <c r="AE207" t="b">
         <v>0</v>
       </c>
-      <c r="AF207" t="inlineStr"/>
       <c r="AG207" t="b">
         <v>0</v>
       </c>
@@ -23495,13 +23506,13 @@
       <c r="AY207" t="inlineStr"/>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136259916</t>
+          <t>https://artportalen.se/Sighting/136557077</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>136330063</v>
+        <v>136259916</v>
       </c>
       <c r="B208" t="n">
         <v>8463</v>
@@ -23545,10 +23556,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>686661</v>
+        <v>686457</v>
       </c>
       <c r="R208" t="n">
-        <v>6563103</v>
+        <v>6563062</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23575,12 +23586,12 @@
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -23607,16 +23618,16 @@
       <c r="AY208" t="inlineStr"/>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136330063</t>
+          <t>https://artportalen.se/Sighting/136259916</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>136767139</v>
+        <v>136330063</v>
       </c>
       <c r="B209" t="n">
-        <v>56875</v>
+        <v>8463</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -23624,37 +23635,46 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>205992</v>
+        <v>106545</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
+      <c r="J209" t="inlineStr"/>
+      <c r="K209" t="inlineStr"/>
+      <c r="L209" t="inlineStr"/>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Norrby torp, Tyresta, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>686742</v>
+        <v>686661</v>
       </c>
       <c r="R209" t="n">
-        <v>6563155</v>
+        <v>6563103</v>
       </c>
       <c r="S209" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T209" t="inlineStr">
         <is>
@@ -23678,22 +23698,12 @@
       </c>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="Z209" t="inlineStr">
-        <is>
-          <t>23:28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="AB209" t="inlineStr">
-        <is>
-          <t>23:28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -23702,33 +23712,34 @@
       <c r="AE209" t="b">
         <v>0</v>
       </c>
+      <c r="AF209" t="inlineStr"/>
       <c r="AG209" t="b">
         <v>0</v>
       </c>
       <c r="AT209" t="inlineStr"/>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136767139</t>
+          <t>https://artportalen.se/Sighting/136330063</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>136767130</v>
+        <v>136767139</v>
       </c>
       <c r="B210" t="n">
-        <v>56887</v>
+        <v>56875</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -23736,21 +23747,21 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -23760,10 +23771,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>686656</v>
+        <v>686742</v>
       </c>
       <c r="R210" t="n">
-        <v>6563100</v>
+        <v>6563155</v>
       </c>
       <c r="S210" t="n">
         <v>25</v>
@@ -23790,22 +23801,22 @@
       </c>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AB210" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -23831,13 +23842,13 @@
       <c r="AY210" t="inlineStr"/>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136767130</t>
+          <t>https://artportalen.se/Sighting/136767139</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>136767147</v>
+        <v>136767130</v>
       </c>
       <c r="B211" t="n">
         <v>56887</v>
@@ -23872,10 +23883,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>686742</v>
+        <v>686656</v>
       </c>
       <c r="R211" t="n">
-        <v>6563155</v>
+        <v>6563100</v>
       </c>
       <c r="S211" t="n">
         <v>25</v>
@@ -23902,22 +23913,22 @@
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>04:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="AB211" t="inlineStr">
         <is>
-          <t>04:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -23943,52 +23954,51 @@
       <c r="AY211" t="inlineStr"/>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136767147</t>
+          <t>https://artportalen.se/Sighting/136767130</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>136767125</v>
+        <v>136767147</v>
       </c>
       <c r="B212" t="n">
-        <v>56866</v>
+        <v>56887</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Cnephaeus nilssonii</t>
-        </is>
-      </c>
-      <c r="H212" t="inlineStr"/>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
       <c r="I212" t="inlineStr"/>
-      <c r="J212" t="inlineStr"/>
-      <c r="K212" t="inlineStr"/>
-      <c r="L212" t="inlineStr"/>
-      <c r="M212" t="inlineStr"/>
-      <c r="N212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
           <t>Norrby torp, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>686656</v>
+        <v>686742</v>
       </c>
       <c r="R212" t="n">
-        <v>6563100</v>
+        <v>6563155</v>
       </c>
       <c r="S212" t="n">
         <v>25</v>
@@ -24015,22 +24025,22 @@
       </c>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>04:21</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>04:21</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -24056,13 +24066,13 @@
       <c r="AY212" t="inlineStr"/>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136767125</t>
+          <t>https://artportalen.se/Sighting/136767147</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>136767144</v>
+        <v>136767125</v>
       </c>
       <c r="B213" t="n">
         <v>56866</v>
@@ -24087,16 +24097,21 @@
       </c>
       <c r="H213" t="inlineStr"/>
       <c r="I213" t="inlineStr"/>
+      <c r="J213" t="inlineStr"/>
+      <c r="K213" t="inlineStr"/>
+      <c r="L213" t="inlineStr"/>
+      <c r="M213" t="inlineStr"/>
+      <c r="N213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
           <t>Norrby torp, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>686742</v>
+        <v>686656</v>
       </c>
       <c r="R213" t="n">
-        <v>6563155</v>
+        <v>6563100</v>
       </c>
       <c r="S213" t="n">
         <v>25</v>
@@ -24123,22 +24138,22 @@
       </c>
       <c r="Y213" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -24164,58 +24179,50 @@
       <c r="AY213" t="inlineStr"/>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136767144</t>
+          <t>https://artportalen.se/Sighting/136767125</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>109890506</v>
+        <v>136767144</v>
       </c>
       <c r="B214" t="n">
-        <v>99118</v>
+        <v>56866</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>220787</v>
+        <v>205998</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr"/>
       <c r="I214" t="inlineStr"/>
-      <c r="J214" t="inlineStr"/>
-      <c r="K214" t="inlineStr"/>
-      <c r="L214" t="inlineStr"/>
-      <c r="N214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Ö Norrby Mosse, Srm</t>
+          <t>Norrby torp, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>686831</v>
+        <v>686742</v>
       </c>
       <c r="R214" t="n">
-        <v>6563216</v>
+        <v>6563155</v>
       </c>
       <c r="S214" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T214" t="inlineStr">
         <is>
@@ -24239,12 +24246,22 @@
       </c>
       <c r="Y214" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="Z214" t="inlineStr">
+        <is>
+          <t>23:10</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AB214" t="inlineStr">
+        <is>
+          <t>23:10</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -24253,31 +24270,30 @@
       <c r="AE214" t="b">
         <v>0</v>
       </c>
-      <c r="AF214" t="inlineStr"/>
       <c r="AG214" t="b">
         <v>0</v>
       </c>
       <c r="AT214" t="inlineStr"/>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
       <c r="AZ214" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109890506</t>
+          <t>https://artportalen.se/Sighting/136767144</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>122781008</v>
+        <v>109890506</v>
       </c>
       <c r="B215" t="n">
         <v>99118</v>
@@ -24312,14 +24328,14 @@
       <c r="N215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Knärot, Srm</t>
+          <t>Ö Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>686833</v>
+        <v>686831</v>
       </c>
       <c r="R215" t="n">
-        <v>6563215</v>
+        <v>6563216</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -24346,17 +24362,12 @@
       </c>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC215" t="inlineStr">
-        <is>
-          <t>Knärot</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -24372,24 +24383,24 @@
       <c r="AT215" t="inlineStr"/>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122781008</t>
+          <t>https://artportalen.se/Sighting/109890506</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>126418709</v>
+        <v>122781008</v>
       </c>
       <c r="B216" t="n">
         <v>99118</v>
@@ -24417,29 +24428,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I216" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J216" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I216" t="inlineStr"/>
+      <c r="J216" t="inlineStr"/>
       <c r="K216" t="inlineStr"/>
       <c r="L216" t="inlineStr"/>
       <c r="N216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Knärot, Srm</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>686771</v>
+        <v>686833</v>
       </c>
       <c r="R216" t="n">
-        <v>6563297</v>
+        <v>6563215</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -24466,17 +24469,17 @@
       </c>
       <c r="Y216" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AC216" t="inlineStr">
         <is>
-          <t>Två av dem i knopp, ca 3 m väster om de andra.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -24492,24 +24495,24 @@
       <c r="AT216" t="inlineStr"/>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
       <c r="AZ216" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126418709</t>
+          <t>https://artportalen.se/Sighting/122781008</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>126418756</v>
+        <v>126418709</v>
       </c>
       <c r="B217" t="n">
         <v>99118</v>
@@ -24539,7 +24542,7 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
@@ -24556,10 +24559,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>686781</v>
+        <v>686771</v>
       </c>
       <c r="R217" t="n">
-        <v>6563292</v>
+        <v>6563297</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -24596,7 +24599,7 @@
       </c>
       <c r="AC217" t="inlineStr">
         <is>
-          <t>En av dem i knopp.</t>
+          <t>Två av dem i knopp, ca 3 m väster om de andra.</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -24623,13 +24626,13 @@
       <c r="AY217" t="inlineStr"/>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126418756</t>
+          <t>https://artportalen.se/Sighting/126418709</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>129564285</v>
+        <v>126418756</v>
       </c>
       <c r="B218" t="n">
         <v>99118</v>
@@ -24657,8 +24660,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I218" t="inlineStr"/>
-      <c r="J218" t="inlineStr"/>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K218" t="inlineStr"/>
       <c r="L218" t="inlineStr"/>
       <c r="N218" t="inlineStr"/>
@@ -24668,10 +24679,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>686625</v>
+        <v>686781</v>
       </c>
       <c r="R218" t="n">
-        <v>6563000</v>
+        <v>6563292</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -24698,12 +24709,17 @@
       </c>
       <c r="Y218" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC218" t="inlineStr">
+        <is>
+          <t>En av dem i knopp.</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -24730,63 +24746,55 @@
       <c r="AY218" t="inlineStr"/>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129564285</t>
+          <t>https://artportalen.se/Sighting/126418756</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>126234373</v>
+        <v>129564285</v>
       </c>
       <c r="B219" t="n">
-        <v>106244</v>
+        <v>99118</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I219" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J219" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr"/>
+      <c r="J219" t="inlineStr"/>
       <c r="K219" t="inlineStr"/>
       <c r="L219" t="inlineStr"/>
       <c r="N219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Norrby mosse SO, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>686756</v>
+        <v>686625</v>
       </c>
       <c r="R219" t="n">
-        <v>6563092</v>
+        <v>6563000</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -24813,12 +24821,12 @@
       </c>
       <c r="Y219" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -24834,27 +24842,27 @@
       <c r="AT219" t="inlineStr"/>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126234373</t>
+          <t>https://artportalen.se/Sighting/129564285</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>122929342</v>
+        <v>126234373</v>
       </c>
       <c r="B220" t="n">
-        <v>97986</v>
+        <v>106244</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -24862,41 +24870,49 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>221946</v>
+        <v>221144</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I220" t="inlineStr"/>
-      <c r="J220" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K220" t="inlineStr"/>
       <c r="L220" t="inlineStr"/>
       <c r="N220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>Norrby mosse SO, Srm</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>686569</v>
+        <v>686756</v>
       </c>
       <c r="R220" t="n">
-        <v>6562949</v>
+        <v>6563092</v>
       </c>
       <c r="S220" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T220" t="inlineStr">
         <is>
@@ -24920,22 +24936,12 @@
       </c>
       <c r="Y220" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="Z220" t="inlineStr">
-        <is>
-          <t>10:52</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="AB220" t="inlineStr">
-        <is>
-          <t>10:52</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -24944,33 +24950,34 @@
       <c r="AE220" t="b">
         <v>0</v>
       </c>
+      <c r="AF220" t="inlineStr"/>
       <c r="AG220" t="b">
         <v>0</v>
       </c>
       <c r="AT220" t="inlineStr"/>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122929342</t>
+          <t>https://artportalen.se/Sighting/126234373</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>134487656</v>
+        <v>122929342</v>
       </c>
       <c r="B221" t="n">
-        <v>99217</v>
+        <v>97986</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -24978,45 +24985,41 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>221952</v>
+        <v>221946</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
       <c r="J221" t="inlineStr"/>
-      <c r="K221" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K221" t="inlineStr"/>
       <c r="L221" t="inlineStr"/>
       <c r="N221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>686835</v>
+        <v>686569</v>
       </c>
       <c r="R221" t="n">
-        <v>6563212</v>
+        <v>6562949</v>
       </c>
       <c r="S221" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T221" t="inlineStr">
         <is>
@@ -25040,17 +25043,22 @@
       </c>
       <c r="Y221" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="Z221" t="inlineStr">
+        <is>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="AC221" t="inlineStr">
-        <is>
-          <t>2 i blom samt några plantor med endast blad.</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AB221" t="inlineStr">
+        <is>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -25059,72 +25067,76 @@
       <c r="AE221" t="b">
         <v>0</v>
       </c>
-      <c r="AF221" t="inlineStr"/>
       <c r="AG221" t="b">
         <v>0</v>
       </c>
       <c r="AT221" t="inlineStr"/>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134487656</t>
+          <t>https://artportalen.se/Sighting/122929342</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>118843519</v>
+        <v>134487656</v>
       </c>
       <c r="B222" t="n">
-        <v>91431</v>
+        <v>99217</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>6039941</v>
+        <v>221952</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Gelatinfingersvamp</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Ramaria primulina</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
       <c r="J222" t="inlineStr"/>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr"/>
       <c r="N222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Norrby Mosse, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>686668</v>
+        <v>686835</v>
       </c>
       <c r="R222" t="n">
-        <v>6563218</v>
+        <v>6563212</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -25151,17 +25163,17 @@
       </c>
       <c r="Y222" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AC222" t="inlineStr">
         <is>
-          <t>Kollekt BR55. Dublett av tidigare fynd för att rapportera resultat av sekvensering. Ursprungligt fynd rapporterat av Bodil Ravn och finns här https://www.artportalen.se/Sighting/112337794</t>
+          <t>2 i blom samt några plantor med endast blad.</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -25177,78 +25189,65 @@
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY222" t="inlineStr">
-        <is>
-          <t>Fynd med DNA-sekvens - extern</t>
-        </is>
-      </c>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY222" t="inlineStr"/>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118843519</t>
+          <t>https://artportalen.se/Sighting/134487656</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>122203249</v>
+        <v>118843519</v>
       </c>
       <c r="B223" t="n">
-        <v>96554</v>
+        <v>91431</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>210</v>
+        <v>6039941</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Gelatinfingersvamp</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Ramaria primulina</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I223" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr"/>
       <c r="J223" t="inlineStr"/>
-      <c r="K223" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
-      <c r="L223" t="inlineStr"/>
+      <c r="K223" t="inlineStr"/>
       <c r="N223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Ö Norrbytorp, Srm</t>
+          <t>Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>687968</v>
+        <v>686668</v>
       </c>
       <c r="R223" t="n">
-        <v>6562733</v>
+        <v>6563218</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -25275,17 +25274,17 @@
       </c>
       <c r="Y223" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AC223" t="inlineStr">
         <is>
-          <t>På murken granlåga i äldre skog.</t>
+          <t>Kollekt BR55. Dublett av tidigare fynd för att rapportera resultat av sekvensering. Ursprungligt fynd rapporterat av Bodil Ravn och finns här https://www.artportalen.se/Sighting/112337794</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -25301,24 +25300,28 @@
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
-        </is>
-      </c>
-      <c r="AY223" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY223" t="inlineStr">
+        <is>
+          <t>Fynd med DNA-sekvens - extern</t>
+        </is>
+      </c>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122203249</t>
+          <t>https://artportalen.se/Sighting/118843519</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>122780924</v>
+        <v>122203249</v>
       </c>
       <c r="B224" t="n">
         <v>96554</v>
@@ -25346,21 +25349,29 @@
           <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
-      <c r="I224" t="inlineStr"/>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
       <c r="J224" t="inlineStr"/>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr"/>
       <c r="N224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
-          <t>Grön sköldmossa, Srm</t>
+          <t>Ö Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>687970</v>
+        <v>687968</v>
       </c>
       <c r="R224" t="n">
-        <v>6562732</v>
+        <v>6562733</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -25387,17 +25398,17 @@
       </c>
       <c r="Y224" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="AC224" t="inlineStr">
         <is>
-          <t>Grön sköldmossa på rutten stam</t>
+          <t>På murken granlåga i äldre skog.</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -25413,27 +25424,27 @@
       <c r="AT224" t="inlineStr"/>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122780924</t>
+          <t>https://artportalen.se/Sighting/122203249</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>136777554</v>
+        <v>122780924</v>
       </c>
       <c r="B225" t="n">
-        <v>96784</v>
+        <v>96554</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -25459,19 +25470,23 @@
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
+      <c r="J225" t="inlineStr"/>
+      <c r="K225" t="inlineStr"/>
+      <c r="L225" t="inlineStr"/>
+      <c r="N225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
-          <t>Norrby torp, Tyresta, Srm</t>
+          <t>Grön sköldmossa, Srm</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>687973</v>
+        <v>687970</v>
       </c>
       <c r="R225" t="n">
-        <v>6562731</v>
+        <v>6562732</v>
       </c>
       <c r="S225" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T225" t="inlineStr">
         <is>
@@ -25495,22 +25510,17 @@
       </c>
       <c r="Y225" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="Z225" t="inlineStr">
-        <is>
-          <t>12:19</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="AB225" t="inlineStr">
-        <is>
-          <t>12:19</t>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC225" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa på rutten stam</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -25519,89 +25529,72 @@
       <c r="AE225" t="b">
         <v>0</v>
       </c>
+      <c r="AF225" t="inlineStr"/>
       <c r="AG225" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ225" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK225" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO225" t="inlineStr">
-        <is>
-          <t>Kraftigt nedbruten granlåga # Picea abies</t>
-        </is>
       </c>
       <c r="AT225" t="inlineStr"/>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136777554</t>
+          <t>https://artportalen.se/Sighting/122780924</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>129624531</v>
+        <v>136777554</v>
       </c>
       <c r="B226" t="n">
-        <v>90946</v>
+        <v>96784</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>889</v>
+        <v>210</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Vintertagging</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Plicatura pendula</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
-      <c r="J226" t="inlineStr"/>
-      <c r="K226" t="inlineStr"/>
-      <c r="N226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrby torp, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>687931</v>
+        <v>687973</v>
       </c>
       <c r="R226" t="n">
-        <v>6562811</v>
+        <v>6562731</v>
       </c>
       <c r="S226" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T226" t="inlineStr">
         <is>
@@ -25625,12 +25618,22 @@
       </c>
       <c r="Y226" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="Z226" t="inlineStr">
+        <is>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AB226" t="inlineStr">
+        <is>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -25639,31 +25642,45 @@
       <c r="AE226" t="b">
         <v>0</v>
       </c>
-      <c r="AF226" t="inlineStr"/>
       <c r="AG226" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ226" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK226" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO226" t="inlineStr">
+        <is>
+          <t>Kraftigt nedbruten granlåga # Picea abies</t>
+        </is>
       </c>
       <c r="AT226" t="inlineStr"/>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129624531</t>
+          <t>https://artportalen.se/Sighting/136777554</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>129624696</v>
+        <v>129624531</v>
       </c>
       <c r="B227" t="n">
         <v>90946</v>
@@ -25701,10 +25718,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>687973</v>
+        <v>687931</v>
       </c>
       <c r="R227" t="n">
-        <v>6562815</v>
+        <v>6562811</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25739,11 +25756,6 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC227" t="inlineStr">
-        <is>
-          <t>På död tall.</t>
-        </is>
-      </c>
       <c r="AD227" t="b">
         <v>0</v>
       </c>
@@ -25768,16 +25780,16 @@
       <c r="AY227" t="inlineStr"/>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129624696</t>
+          <t>https://artportalen.se/Sighting/129624531</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>122203275</v>
+        <v>129624696</v>
       </c>
       <c r="B228" t="n">
-        <v>91909</v>
+        <v>90946</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -25785,21 +25797,21 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>1202</v>
+        <v>889</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Plicatura pendula</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -25808,14 +25820,14 @@
       <c r="N228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
-          <t>Ö Norrbytorp, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>687981</v>
+        <v>687973</v>
       </c>
       <c r="R228" t="n">
-        <v>6562724</v>
+        <v>6562815</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25842,12 +25854,17 @@
       </c>
       <c r="Y228" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC228" t="inlineStr">
+        <is>
+          <t>På död tall.</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -25874,16 +25891,16 @@
       <c r="AY228" t="inlineStr"/>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122203275</t>
+          <t>https://artportalen.se/Sighting/129624696</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>136778798</v>
+        <v>122203275</v>
       </c>
       <c r="B229" t="n">
-        <v>92113</v>
+        <v>91909</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -25909,19 +25926,22 @@
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
+      <c r="J229" t="inlineStr"/>
+      <c r="K229" t="inlineStr"/>
+      <c r="N229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
-          <t>Norrbytorp_inventering_2026-08-30, Srm</t>
+          <t>Ö Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>687985</v>
+        <v>687981</v>
       </c>
       <c r="R229" t="n">
-        <v>6562721</v>
+        <v>6562724</v>
       </c>
       <c r="S229" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T229" t="inlineStr">
         <is>
@@ -25945,22 +25965,12 @@
       </c>
       <c r="Y229" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="Z229" t="inlineStr">
-        <is>
-          <t>12:11</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="AB229" t="inlineStr">
-        <is>
-          <t>12:11</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -25969,93 +25979,72 @@
       <c r="AE229" t="b">
         <v>0</v>
       </c>
+      <c r="AF229" t="inlineStr"/>
       <c r="AG229" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ229" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK229" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO229" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT229" t="inlineStr"/>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136778798</t>
+          <t>https://artportalen.se/Sighting/122203275</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>135358856</v>
+        <v>136778798</v>
       </c>
       <c r="B230" t="n">
-        <v>91573</v>
+        <v>92113</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>2051</v>
+        <v>1202</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I230" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J230" t="inlineStr"/>
-      <c r="K230" t="inlineStr"/>
-      <c r="N230" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr"/>
       <c r="P230" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrbytorp_inventering_2026-08-30, Srm</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>688004</v>
+        <v>687985</v>
       </c>
       <c r="R230" t="n">
-        <v>6562799</v>
+        <v>6562721</v>
       </c>
       <c r="S230" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T230" t="inlineStr">
         <is>
@@ -26079,12 +26068,22 @@
       </c>
       <c r="Y230" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="Z230" t="inlineStr">
+        <is>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AB230" t="inlineStr">
+        <is>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -26093,72 +26092,93 @@
       <c r="AE230" t="b">
         <v>0</v>
       </c>
-      <c r="AF230" t="inlineStr"/>
       <c r="AG230" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ230" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK230" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO230" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT230" t="inlineStr"/>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358856</t>
+          <t>https://artportalen.se/Sighting/136778798</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>136777555</v>
+        <v>135358856</v>
       </c>
       <c r="B231" t="n">
-        <v>96831</v>
+        <v>91573</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>2170</v>
+        <v>2051</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I231" t="inlineStr"/>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr"/>
+      <c r="K231" t="inlineStr"/>
+      <c r="N231" t="inlineStr"/>
       <c r="P231" t="inlineStr">
         <is>
-          <t>Norrby torp, Tyresta, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>687973</v>
+        <v>688004</v>
       </c>
       <c r="R231" t="n">
-        <v>6562731</v>
+        <v>6562799</v>
       </c>
       <c r="S231" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T231" t="inlineStr">
         <is>
@@ -26182,22 +26202,12 @@
       </c>
       <c r="Y231" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="Z231" t="inlineStr">
-        <is>
-          <t>12:19</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="AB231" t="inlineStr">
-        <is>
-          <t>12:19</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -26206,48 +26216,34 @@
       <c r="AE231" t="b">
         <v>0</v>
       </c>
+      <c r="AF231" t="inlineStr"/>
       <c r="AG231" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ231" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK231" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO231" t="inlineStr">
-        <is>
-          <t>Kraftigt nedbruten granlåga # Picea abies</t>
-        </is>
       </c>
       <c r="AT231" t="inlineStr"/>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136777555</t>
+          <t>https://artportalen.se/Sighting/135358856</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>136241603</v>
+        <v>136777555</v>
       </c>
       <c r="B232" t="n">
-        <v>96938</v>
+        <v>96831</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -26255,38 +26251,34 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>2180</v>
+        <v>2170</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
-      <c r="J232" t="inlineStr"/>
-      <c r="K232" t="inlineStr"/>
-      <c r="L232" t="inlineStr"/>
-      <c r="N232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
-          <t>Norrbytorp, Srm</t>
+          <t>Norrby torp, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>688059</v>
+        <v>687973</v>
       </c>
       <c r="R232" t="n">
-        <v>6562773</v>
+        <v>6562731</v>
       </c>
       <c r="S232" t="n">
         <v>5</v>
@@ -26318,7 +26310,7 @@
       </c>
       <c r="Z232" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
@@ -26328,7 +26320,7 @@
       </c>
       <c r="AB232" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -26337,34 +26329,48 @@
       <c r="AE232" t="b">
         <v>0</v>
       </c>
-      <c r="AF232" t="inlineStr"/>
       <c r="AG232" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ232" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK232" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO232" t="inlineStr">
+        <is>
+          <t>Kraftigt nedbruten granlåga # Picea abies</t>
+        </is>
       </c>
       <c r="AT232" t="inlineStr"/>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Björn Persson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>Björn Persson</t>
+          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136241603</t>
+          <t>https://artportalen.se/Sighting/136777555</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>136777551</v>
+        <v>136241603</v>
       </c>
       <c r="B233" t="n">
-        <v>96261</v>
+        <v>96938</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -26372,33 +26378,41 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>2558</v>
+        <v>2180</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Krushättemossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Ulota crispa s.lat.</t>
-        </is>
-      </c>
-      <c r="H233" t="inlineStr"/>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
       <c r="I233" t="inlineStr"/>
+      <c r="J233" t="inlineStr"/>
+      <c r="K233" t="inlineStr"/>
+      <c r="L233" t="inlineStr"/>
+      <c r="N233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
-          <t>Norrby torp, Tyresta, Srm</t>
+          <t>Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>687848</v>
+        <v>688059</v>
       </c>
       <c r="R233" t="n">
-        <v>6562771</v>
+        <v>6562773</v>
       </c>
       <c r="S233" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T233" t="inlineStr">
         <is>
@@ -26427,7 +26441,7 @@
       </c>
       <c r="Z233" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
@@ -26437,7 +26451,7 @@
       </c>
       <c r="AB233" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -26446,48 +26460,34 @@
       <c r="AE233" t="b">
         <v>0</v>
       </c>
+      <c r="AF233" t="inlineStr"/>
       <c r="AG233" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ233" t="inlineStr">
-        <is>
-          <t>hassel</t>
-        </is>
-      </c>
-      <c r="AK233" t="inlineStr">
-        <is>
-          <t>Corylus avellana</t>
-        </is>
-      </c>
-      <c r="AO233" t="inlineStr">
-        <is>
-          <t>Levande hasselgren # Corylus avellana</t>
-        </is>
       </c>
       <c r="AT233" t="inlineStr"/>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Björn Persson</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
+          <t>Björn Persson</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136777551</t>
+          <t>https://artportalen.se/Sighting/136241603</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>136231090</v>
+        <v>136777551</v>
       </c>
       <c r="B234" t="n">
-        <v>96656</v>
+        <v>96261</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -26495,37 +26495,33 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>2671</v>
+        <v>2558</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Krushättemossa</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
-        </is>
-      </c>
-      <c r="H234" t="inlineStr">
-        <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
+          <t>Ulota crispa s.lat.</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr"/>
       <c r="I234" t="inlineStr"/>
       <c r="P234" t="inlineStr">
         <is>
-          <t>Norrby torp, Norrby torp, Srm</t>
+          <t>Norrby torp, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>688046</v>
+        <v>687848</v>
       </c>
       <c r="R234" t="n">
-        <v>6562700</v>
+        <v>6562771</v>
       </c>
       <c r="S234" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T234" t="inlineStr">
         <is>
@@ -26552,11 +26548,21 @@
           <t>2026-08-30</t>
         </is>
       </c>
+      <c r="Z234" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA234" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
+      <c r="AB234" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AD234" t="b">
         <v>0</v>
       </c>
@@ -26565,31 +26571,46 @@
       </c>
       <c r="AG234" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ234" t="inlineStr">
+        <is>
+          <t>hassel</t>
+        </is>
+      </c>
+      <c r="AK234" t="inlineStr">
+        <is>
+          <t>Corylus avellana</t>
+        </is>
+      </c>
+      <c r="AO234" t="inlineStr">
+        <is>
+          <t>Levande hasselgren # Corylus avellana</t>
+        </is>
       </c>
       <c r="AT234" t="inlineStr"/>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136231090</t>
+          <t>https://artportalen.se/Sighting/136777551</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>136777556</v>
+        <v>136231090</v>
       </c>
       <c r="B235" t="n">
-        <v>96688</v>
+        <v>96656</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -26597,37 +26618,37 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>2818</v>
+        <v>2671</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
       <c r="P235" t="inlineStr">
         <is>
-          <t>Norrby torp, Tyresta, Srm</t>
+          <t>Norrby torp, Norrby torp, Srm</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>687973</v>
+        <v>688046</v>
       </c>
       <c r="R235" t="n">
-        <v>6562731</v>
+        <v>6562700</v>
       </c>
       <c r="S235" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T235" t="inlineStr">
         <is>
@@ -26654,21 +26675,11 @@
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="Z235" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
       <c r="AA235" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="AB235" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
       <c r="AD235" t="b">
         <v>0</v>
       </c>
@@ -26677,87 +26688,69 @@
       </c>
       <c r="AG235" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ235" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK235" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO235" t="inlineStr">
-        <is>
-          <t>Kraftigt nedbruten granlåga # Picea abies</t>
-        </is>
       </c>
       <c r="AT235" t="inlineStr"/>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136777556</t>
+          <t>https://artportalen.se/Sighting/136231090</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>136697134</v>
+        <v>136777556</v>
       </c>
       <c r="B236" t="n">
-        <v>93411</v>
+        <v>96688</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>4364</v>
+        <v>2818</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
-      <c r="J236" t="inlineStr"/>
-      <c r="K236" t="inlineStr"/>
-      <c r="N236" t="inlineStr"/>
       <c r="P236" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrby torp, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>688040</v>
+        <v>687973</v>
       </c>
       <c r="R236" t="n">
-        <v>6562791</v>
+        <v>6562731</v>
       </c>
       <c r="S236" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T236" t="inlineStr">
         <is>
@@ -26781,12 +26774,22 @@
       </c>
       <c r="Y236" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="Z236" t="inlineStr">
+        <is>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AB236" t="inlineStr">
+        <is>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -26795,31 +26798,45 @@
       <c r="AE236" t="b">
         <v>0</v>
       </c>
-      <c r="AF236" t="inlineStr"/>
       <c r="AG236" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ236" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK236" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO236" t="inlineStr">
+        <is>
+          <t>Kraftigt nedbruten granlåga # Picea abies</t>
+        </is>
       </c>
       <c r="AT236" t="inlineStr"/>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136697134</t>
+          <t>https://artportalen.se/Sighting/136777556</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>136778799</v>
+        <v>136697134</v>
       </c>
       <c r="B237" t="n">
         <v>93411</v>
@@ -26847,24 +26864,23 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I237" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I237" t="inlineStr"/>
+      <c r="J237" t="inlineStr"/>
+      <c r="K237" t="inlineStr"/>
+      <c r="N237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
-          <t>Norrbytorp_inventering_2026-08-30, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>688075</v>
+        <v>688040</v>
       </c>
       <c r="R237" t="n">
-        <v>6562783</v>
+        <v>6562791</v>
       </c>
       <c r="S237" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T237" t="inlineStr">
         <is>
@@ -26888,22 +26904,12 @@
       </c>
       <c r="Y237" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="Z237" t="inlineStr">
-        <is>
-          <t>13:26</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="AB237" t="inlineStr">
-        <is>
-          <t>13:26</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -26912,82 +26918,76 @@
       <c r="AE237" t="b">
         <v>0</v>
       </c>
+      <c r="AF237" t="inlineStr"/>
       <c r="AG237" t="b">
         <v>0</v>
       </c>
       <c r="AT237" t="inlineStr"/>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136778799</t>
+          <t>https://artportalen.se/Sighting/136697134</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>128314411</v>
+        <v>136778799</v>
       </c>
       <c r="B238" t="n">
-        <v>92348</v>
+        <v>93411</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>5420</v>
+        <v>4364</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J238" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K238" t="inlineStr"/>
-      <c r="N238" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P238" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrbytorp_inventering_2026-08-30, Srm</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>688088</v>
+        <v>688075</v>
       </c>
       <c r="R238" t="n">
-        <v>6562722</v>
+        <v>6562783</v>
       </c>
       <c r="S238" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T238" t="inlineStr">
         <is>
@@ -27011,12 +27011,22 @@
       </c>
       <c r="Y238" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="Z238" t="inlineStr">
+        <is>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AB238" t="inlineStr">
+        <is>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -27025,34 +27035,33 @@
       <c r="AE238" t="b">
         <v>0</v>
       </c>
-      <c r="AF238" t="inlineStr"/>
       <c r="AG238" t="b">
         <v>0</v>
       </c>
       <c r="AT238" t="inlineStr"/>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128314411</t>
+          <t>https://artportalen.se/Sighting/136778799</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>136394237</v>
+        <v>128314411</v>
       </c>
       <c r="B239" t="n">
-        <v>92524</v>
+        <v>92348</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -27077,20 +27086,31 @@
           <t>(Fr.) Pat.</t>
         </is>
       </c>
-      <c r="I239" t="inlineStr"/>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr"/>
+      <c r="N239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
-          <t>Norrbytorp, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>688093</v>
+        <v>688088</v>
       </c>
       <c r="R239" t="n">
-        <v>6562720</v>
+        <v>6562722</v>
       </c>
       <c r="S239" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T239" t="inlineStr">
         <is>
@@ -27114,22 +27134,12 @@
       </c>
       <c r="Y239" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="Z239" t="inlineStr">
-        <is>
-          <t>12:05</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="AB239" t="inlineStr">
-        <is>
-          <t>12:05</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -27138,33 +27148,34 @@
       <c r="AE239" t="b">
         <v>0</v>
       </c>
+      <c r="AF239" t="inlineStr"/>
       <c r="AG239" t="b">
         <v>0</v>
       </c>
       <c r="AT239" t="inlineStr"/>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136394237</t>
+          <t>https://artportalen.se/Sighting/128314411</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>136268106</v>
+        <v>136394237</v>
       </c>
       <c r="B240" t="n">
-        <v>92076</v>
+        <v>92524</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -27172,40 +27183,37 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>5447</v>
+        <v>5420</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
-      <c r="J240" t="inlineStr"/>
-      <c r="K240" t="inlineStr"/>
-      <c r="N240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>687910</v>
+        <v>688093</v>
       </c>
       <c r="R240" t="n">
-        <v>6562787</v>
+        <v>6562720</v>
       </c>
       <c r="S240" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T240" t="inlineStr">
         <is>
@@ -27232,14 +27240,19 @@
           <t>2026-08-30</t>
         </is>
       </c>
+      <c r="Z240" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
       <c r="AA240" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="AC240" t="inlineStr">
-        <is>
-          <t>På rätt klen, senvuxen?, lutande granlåga i ett kärr.</t>
+      <c r="AB240" t="inlineStr">
+        <is>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -27248,31 +27261,30 @@
       <c r="AE240" t="b">
         <v>0</v>
       </c>
-      <c r="AF240" t="inlineStr"/>
       <c r="AG240" t="b">
         <v>0</v>
       </c>
       <c r="AT240" t="inlineStr"/>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136268106</t>
+          <t>https://artportalen.se/Sighting/136394237</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>136697126</v>
+        <v>136268106</v>
       </c>
       <c r="B241" t="n">
         <v>92076</v>
@@ -27310,10 +27322,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>687998</v>
+        <v>687910</v>
       </c>
       <c r="R241" t="n">
-        <v>6562803</v>
+        <v>6562787</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -27340,12 +27352,17 @@
       </c>
       <c r="Y241" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="AA241" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AC241" t="inlineStr">
+        <is>
+          <t>På rätt klen, senvuxen?, lutande granlåga i ett kärr.</t>
         </is>
       </c>
       <c r="AD241" t="b">
@@ -27372,38 +27389,38 @@
       <c r="AY241" t="inlineStr"/>
       <c r="AZ241" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136697126</t>
+          <t>https://artportalen.se/Sighting/136268106</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>128314833</v>
+        <v>136697126</v>
       </c>
       <c r="B242" t="n">
-        <v>93235</v>
+        <v>92076</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -27416,10 +27433,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>688073</v>
+        <v>687998</v>
       </c>
       <c r="R242" t="n">
-        <v>6562768</v>
+        <v>6562803</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -27446,12 +27463,12 @@
       </c>
       <c r="Y242" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -27478,13 +27495,13 @@
       <c r="AY242" t="inlineStr"/>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128314833</t>
+          <t>https://artportalen.se/Sighting/136697126</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>128317789</v>
+        <v>128314833</v>
       </c>
       <c r="B243" t="n">
         <v>93235</v>
@@ -27522,10 +27539,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>688094</v>
+        <v>688073</v>
       </c>
       <c r="R243" t="n">
-        <v>6562777</v>
+        <v>6562768</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -27584,13 +27601,13 @@
       <c r="AY243" t="inlineStr"/>
       <c r="AZ243" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128317789</t>
+          <t>https://artportalen.se/Sighting/128314833</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>128526064</v>
+        <v>128317789</v>
       </c>
       <c r="B244" t="n">
         <v>93235</v>
@@ -27628,10 +27645,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>687952</v>
+        <v>688094</v>
       </c>
       <c r="R244" t="n">
-        <v>6562790</v>
+        <v>6562777</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -27658,12 +27675,12 @@
       </c>
       <c r="Y244" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -27690,13 +27707,13 @@
       <c r="AY244" t="inlineStr"/>
       <c r="AZ244" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128526064</t>
+          <t>https://artportalen.se/Sighting/128317789</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>128646583</v>
+        <v>128526064</v>
       </c>
       <c r="B245" t="n">
         <v>93235</v>
@@ -27734,10 +27751,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>688067</v>
+        <v>687952</v>
       </c>
       <c r="R245" t="n">
-        <v>6562731</v>
+        <v>6562790</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -27764,12 +27781,12 @@
       </c>
       <c r="Y245" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -27796,16 +27813,16 @@
       <c r="AY245" t="inlineStr"/>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128646583</t>
+          <t>https://artportalen.se/Sighting/128526064</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>136801045</v>
+        <v>128646583</v>
       </c>
       <c r="B246" t="n">
-        <v>93449</v>
+        <v>93235</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -27840,10 +27857,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>687990</v>
+        <v>688067</v>
       </c>
       <c r="R246" t="n">
-        <v>6562795</v>
+        <v>6562731</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -27870,12 +27887,12 @@
       </c>
       <c r="Y246" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -27902,13 +27919,13 @@
       <c r="AY246" t="inlineStr"/>
       <c r="AZ246" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136801045</t>
+          <t>https://artportalen.se/Sighting/128646583</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>136801064</v>
+        <v>136801045</v>
       </c>
       <c r="B247" t="n">
         <v>93449</v>
@@ -27946,10 +27963,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>687946</v>
+        <v>687990</v>
       </c>
       <c r="R247" t="n">
-        <v>6562790</v>
+        <v>6562795</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -28008,16 +28025,16 @@
       <c r="AY247" t="inlineStr"/>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136801064</t>
+          <t>https://artportalen.se/Sighting/136801045</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>136241765</v>
+        <v>136801064</v>
       </c>
       <c r="B248" t="n">
-        <v>80095</v>
+        <v>93449</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -28025,44 +28042,40 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
       <c r="J248" t="inlineStr"/>
-      <c r="K248" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K248" t="inlineStr"/>
       <c r="N248" t="inlineStr"/>
       <c r="P248" t="inlineStr">
         <is>
-          <t>Norrbytorp, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>688014</v>
+        <v>687946</v>
       </c>
       <c r="R248" t="n">
-        <v>6562734</v>
+        <v>6562790</v>
       </c>
       <c r="S248" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T248" t="inlineStr">
         <is>
@@ -28086,22 +28099,12 @@
       </c>
       <c r="Y248" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="Z248" t="inlineStr">
-        <is>
-          <t>12:38</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="AB248" t="inlineStr">
-        <is>
-          <t>12:38</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -28117,27 +28120,27 @@
       <c r="AT248" t="inlineStr"/>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Björn Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>Björn Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136241765</t>
+          <t>https://artportalen.se/Sighting/136801064</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>17285491</v>
+        <v>136241765</v>
       </c>
       <c r="B249" t="n">
-        <v>80432</v>
+        <v>80095</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -28145,39 +28148,44 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
       <c r="J249" t="inlineStr"/>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
-          <t>Norrby torp, 480 m Ö, Srm</t>
+          <t>Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>688111</v>
+        <v>688014</v>
       </c>
       <c r="R249" t="n">
-        <v>6562706</v>
+        <v>6562734</v>
       </c>
       <c r="S249" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T249" t="inlineStr">
         <is>
@@ -28201,17 +28209,22 @@
       </c>
       <c r="Y249" t="inlineStr">
         <is>
-          <t>2015-04-02</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="Z249" t="inlineStr">
+        <is>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA249" t="inlineStr">
         <is>
-          <t>2015-04-02</t>
-        </is>
-      </c>
-      <c r="AC249" t="inlineStr">
-        <is>
-          <t>På ek i bergskanten, ca 220 cm omkrets. Sparsamt vid 20 resp. 70 cm höjd.</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AB249" t="inlineStr">
+        <is>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -28220,35 +28233,31 @@
       <c r="AE249" t="b">
         <v>0</v>
       </c>
+      <c r="AF249" t="inlineStr"/>
       <c r="AG249" t="b">
         <v>0</v>
-      </c>
-      <c r="AI249" t="inlineStr">
-        <is>
-          <t>Yngre gallrad blandskog</t>
-        </is>
       </c>
       <c r="AT249" t="inlineStr"/>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Björn Persson</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Björn Persson</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/17285491</t>
+          <t>https://artportalen.se/Sighting/136241765</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>79273786</v>
+        <v>17285491</v>
       </c>
       <c r="B250" t="n">
         <v>80432</v>
@@ -28277,16 +28286,18 @@
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
+      <c r="J250" t="inlineStr"/>
+      <c r="K250" t="inlineStr"/>
       <c r="P250" t="inlineStr">
         <is>
-          <t>Åvadal, Srm</t>
+          <t>Norrby torp, 480 m Ö, Srm</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>688109</v>
+        <v>688111</v>
       </c>
       <c r="R250" t="n">
-        <v>6562704</v>
+        <v>6562706</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -28313,12 +28324,17 @@
       </c>
       <c r="Y250" t="inlineStr">
         <is>
-          <t>2019-08-01</t>
+          <t>2015-04-02</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
         <is>
-          <t>2019-08-01</t>
+          <t>2015-04-02</t>
+        </is>
+      </c>
+      <c r="AC250" t="inlineStr">
+        <is>
+          <t>På ek i bergskanten, ca 220 cm omkrets. Sparsamt vid 20 resp. 70 cm höjd.</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -28330,42 +28346,32 @@
       <c r="AG250" t="b">
         <v>0</v>
       </c>
-      <c r="AJ250" t="inlineStr">
-        <is>
-          <t>skogsek</t>
-        </is>
-      </c>
-      <c r="AK250" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
-      </c>
-      <c r="AO250" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
+      <c r="AI250" t="inlineStr">
+        <is>
+          <t>Yngre gallrad blandskog</t>
         </is>
       </c>
       <c r="AT250" t="inlineStr"/>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Gustav Wikström</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>Gustav Wikström</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/79273786</t>
+          <t>https://artportalen.se/Sighting/17285491</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>89840770</v>
+        <v>79273786</v>
       </c>
       <c r="B251" t="n">
         <v>80432</v>
@@ -28394,19 +28400,16 @@
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
-      <c r="J251" t="inlineStr"/>
-      <c r="K251" t="inlineStr"/>
-      <c r="N251" t="inlineStr"/>
       <c r="P251" t="inlineStr">
         <is>
-          <t>Ö Norrby Torp, Srm</t>
+          <t>Åvadal, Srm</t>
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>688146</v>
+        <v>688109</v>
       </c>
       <c r="R251" t="n">
-        <v>6562738</v>
+        <v>6562704</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -28433,17 +28436,12 @@
       </c>
       <c r="Y251" t="inlineStr">
         <is>
-          <t>2020-12-30</t>
+          <t>2019-08-01</t>
         </is>
       </c>
       <c r="AA251" t="inlineStr">
         <is>
-          <t>2020-12-30</t>
-        </is>
-      </c>
-      <c r="AC251" t="inlineStr">
-        <is>
-          <t>Tre bålar på en ek som inte längre ser ut att vara så livskraftig. Finns en annan noterad ek med lavar en bit ifrån.</t>
+          <t>2019-08-01</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -28452,31 +28450,45 @@
       <c r="AE251" t="b">
         <v>0</v>
       </c>
-      <c r="AF251" t="inlineStr"/>
       <c r="AG251" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ251" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK251" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO251" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
       </c>
       <c r="AT251" t="inlineStr"/>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Gustav Wikström</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Gustav Wikström</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89840770</t>
+          <t>https://artportalen.se/Sighting/79273786</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>112384453</v>
+        <v>89840770</v>
       </c>
       <c r="B252" t="n">
         <v>80432</v>
@@ -28510,14 +28522,14 @@
       <c r="N252" t="inlineStr"/>
       <c r="P252" t="inlineStr">
         <is>
-          <t>Norrby torp Ö om, Srm</t>
+          <t>Ö Norrby Torp, Srm</t>
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>688145</v>
+        <v>688146</v>
       </c>
       <c r="R252" t="n">
-        <v>6562737</v>
+        <v>6562738</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -28544,17 +28556,17 @@
       </c>
       <c r="Y252" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2020-12-30</t>
         </is>
       </c>
       <c r="AA252" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2020-12-30</t>
         </is>
       </c>
       <c r="AC252" t="inlineStr">
         <is>
-          <t>Återfynd. På halvdöd ek med blottad ved men några levande grenar i toppen, ca 120 cm omkrets. Två mindre blaffor i dåligt skick, hänger något löst, ca 40 resp. 130 cm höjd.</t>
+          <t>Tre bålar på en ek som inte längre ser ut att vara så livskraftig. Finns en annan noterad ek med lavar en bit ifrån.</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -28570,24 +28582,24 @@
       <c r="AT252" t="inlineStr"/>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112384453</t>
+          <t>https://artportalen.se/Sighting/89840770</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>122779297</v>
+        <v>112384453</v>
       </c>
       <c r="B253" t="n">
         <v>80432</v>
@@ -28621,14 +28633,14 @@
       <c r="N253" t="inlineStr"/>
       <c r="P253" t="inlineStr">
         <is>
-          <t>Lunglav, Srm</t>
+          <t>Norrby torp Ö om, Srm</t>
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>688116</v>
+        <v>688145</v>
       </c>
       <c r="R253" t="n">
-        <v>6562703</v>
+        <v>6562737</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -28655,17 +28667,17 @@
       </c>
       <c r="Y253" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA253" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AC253" t="inlineStr">
         <is>
-          <t>Lunglav på gammal ek</t>
+          <t>Återfynd. På halvdöd ek med blottad ved men några levande grenar i toppen, ca 120 cm omkrets. Två mindre blaffor i dåligt skick, hänger något löst, ca 40 resp. 130 cm höjd.</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -28681,81 +28693,68 @@
       <c r="AT253" t="inlineStr"/>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122779297</t>
+          <t>https://artportalen.se/Sighting/112384453</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>125923864</v>
+        <v>122779297</v>
       </c>
       <c r="B254" t="n">
-        <v>57754</v>
+        <v>80432</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>102118</v>
+        <v>6458</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I254" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr"/>
+      <c r="J254" t="inlineStr"/>
       <c r="K254" t="inlineStr"/>
-      <c r="L254" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M254" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
       <c r="N254" t="inlineStr"/>
       <c r="P254" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Lunglav, Srm</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>687916</v>
+        <v>688116</v>
       </c>
       <c r="R254" t="n">
-        <v>6562815</v>
+        <v>6562703</v>
       </c>
       <c r="S254" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T254" t="inlineStr">
         <is>
@@ -28779,17 +28778,17 @@
       </c>
       <c r="Y254" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AC254" t="inlineStr">
         <is>
-          <t>Stöttes och stannade nära, det fanns ett ägg. Än så länge?</t>
+          <t>Lunglav på gammal ek</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -28798,63 +28797,72 @@
       <c r="AE254" t="b">
         <v>0</v>
       </c>
+      <c r="AF254" t="inlineStr"/>
       <c r="AG254" t="b">
         <v>0</v>
       </c>
       <c r="AT254" t="inlineStr"/>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125923864</t>
+          <t>https://artportalen.se/Sighting/122779297</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>128317861</v>
+        <v>125923864</v>
       </c>
       <c r="B255" t="n">
-        <v>58114</v>
+        <v>57754</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>103021</v>
+        <v>102118</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I255" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K255" t="inlineStr"/>
-      <c r="L255" t="inlineStr"/>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>bo, ägg/ungar</t>
         </is>
       </c>
       <c r="N255" t="inlineStr"/>
@@ -28864,10 +28872,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>688058</v>
+        <v>687916</v>
       </c>
       <c r="R255" t="n">
-        <v>6562805</v>
+        <v>6562815</v>
       </c>
       <c r="S255" t="n">
         <v>25</v>
@@ -28894,12 +28902,17 @@
       </c>
       <c r="Y255" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="AA255" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AC255" t="inlineStr">
+        <is>
+          <t>Stöttes och stannade nära, det fanns ett ägg. Än så länge?</t>
         </is>
       </c>
       <c r="AD255" t="b">
@@ -28925,16 +28938,16 @@
       <c r="AY255" t="inlineStr"/>
       <c r="AZ255" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128317861</t>
+          <t>https://artportalen.se/Sighting/125923864</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>136138855</v>
+        <v>128317861</v>
       </c>
       <c r="B256" t="n">
-        <v>58169</v>
+        <v>58114</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -28974,13 +28987,13 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>687836</v>
+        <v>688058</v>
       </c>
       <c r="R256" t="n">
-        <v>6562786</v>
+        <v>6562805</v>
       </c>
       <c r="S256" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T256" t="inlineStr">
         <is>
@@ -29004,12 +29017,12 @@
       </c>
       <c r="Y256" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA256" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD256" t="b">
@@ -29035,13 +29048,13 @@
       <c r="AY256" t="inlineStr"/>
       <c r="AZ256" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136138855</t>
+          <t>https://artportalen.se/Sighting/128317861</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>136138971</v>
+        <v>136138855</v>
       </c>
       <c r="B257" t="n">
         <v>58169</v>
@@ -29084,13 +29097,13 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>687977</v>
+        <v>687836</v>
       </c>
       <c r="R257" t="n">
-        <v>6562735</v>
+        <v>6562786</v>
       </c>
       <c r="S257" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T257" t="inlineStr">
         <is>
@@ -29145,13 +29158,13 @@
       <c r="AY257" t="inlineStr"/>
       <c r="AZ257" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136138971</t>
+          <t>https://artportalen.se/Sighting/136138855</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>136823037</v>
+        <v>136138971</v>
       </c>
       <c r="B258" t="n">
         <v>58169</v>
@@ -29194,10 +29207,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>688141</v>
+        <v>687977</v>
       </c>
       <c r="R258" t="n">
-        <v>6562748</v>
+        <v>6562735</v>
       </c>
       <c r="S258" t="n">
         <v>25</v>
@@ -29224,12 +29237,12 @@
       </c>
       <c r="Y258" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AA258" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AD258" t="b">
@@ -29255,13 +29268,13 @@
       <c r="AY258" t="inlineStr"/>
       <c r="AZ258" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136823037</t>
+          <t>https://artportalen.se/Sighting/136138971</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>136823087</v>
+        <v>136823037</v>
       </c>
       <c r="B259" t="n">
         <v>58169</v>
@@ -29304,13 +29317,13 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>687936</v>
+        <v>688141</v>
       </c>
       <c r="R259" t="n">
-        <v>6562770</v>
+        <v>6562748</v>
       </c>
       <c r="S259" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T259" t="inlineStr">
         <is>
@@ -29365,59 +29378,62 @@
       <c r="AY259" t="inlineStr"/>
       <c r="AZ259" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136823087</t>
+          <t>https://artportalen.se/Sighting/136823037</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>136777552</v>
+        <v>136823087</v>
       </c>
       <c r="B260" t="n">
-        <v>5202</v>
+        <v>58169</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
+      <c r="K260" t="inlineStr"/>
+      <c r="L260" t="inlineStr"/>
       <c r="M260" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N260" t="inlineStr"/>
       <c r="P260" t="inlineStr">
         <is>
-          <t>Norrby torp, Tyresta, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>687944</v>
+        <v>687936</v>
       </c>
       <c r="R260" t="n">
-        <v>6562783</v>
+        <v>6562770</v>
       </c>
       <c r="S260" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T260" t="inlineStr">
         <is>
@@ -29441,22 +29457,12 @@
       </c>
       <c r="Y260" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="Z260" t="inlineStr">
-        <is>
-          <t>11:54</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA260" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="AB260" t="inlineStr">
-        <is>
-          <t>11:54</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD260" t="b">
@@ -29467,46 +29473,31 @@
       </c>
       <c r="AG260" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ260" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK260" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO260" t="inlineStr">
-        <is>
-          <t>Klen barklös granlåga # Picea abies</t>
-        </is>
       </c>
       <c r="AT260" t="inlineStr"/>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
       <c r="AZ260" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136777552</t>
+          <t>https://artportalen.se/Sighting/136823087</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>136823074</v>
+        <v>136777552</v>
       </c>
       <c r="B261" t="n">
-        <v>8463</v>
+        <v>5202</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -29514,46 +29505,42 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
-      <c r="J261" t="inlineStr"/>
-      <c r="K261" t="inlineStr"/>
-      <c r="L261" t="inlineStr"/>
       <c r="M261" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N261" t="inlineStr"/>
       <c r="P261" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrby torp, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>687940</v>
+        <v>687944</v>
       </c>
       <c r="R261" t="n">
-        <v>6562785</v>
+        <v>6562783</v>
       </c>
       <c r="S261" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T261" t="inlineStr">
         <is>
@@ -29577,12 +29564,22 @@
       </c>
       <c r="Y261" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="Z261" t="inlineStr">
+        <is>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA261" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AB261" t="inlineStr">
+        <is>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD261" t="b">
@@ -29591,34 +29588,48 @@
       <c r="AE261" t="b">
         <v>0</v>
       </c>
-      <c r="AF261" t="inlineStr"/>
       <c r="AG261" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ261" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK261" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO261" t="inlineStr">
+        <is>
+          <t>Klen barklös granlåga # Picea abies</t>
+        </is>
       </c>
       <c r="AT261" t="inlineStr"/>
       <c r="AW261" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
       <c r="AZ261" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136823074</t>
+          <t>https://artportalen.se/Sighting/136777552</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>136777549</v>
+        <v>136823074</v>
       </c>
       <c r="B262" t="n">
-        <v>8452</v>
+        <v>8463</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -29626,42 +29637,46 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
+      <c r="J262" t="inlineStr"/>
+      <c r="K262" t="inlineStr"/>
+      <c r="L262" t="inlineStr"/>
       <c r="M262" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
+      <c r="N262" t="inlineStr"/>
       <c r="P262" t="inlineStr">
         <is>
-          <t>Norrby torp, Tyresta, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>687859</v>
+        <v>687940</v>
       </c>
       <c r="R262" t="n">
-        <v>6562767</v>
+        <v>6562785</v>
       </c>
       <c r="S262" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T262" t="inlineStr">
         <is>
@@ -29685,22 +29700,12 @@
       </c>
       <c r="Y262" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="Z262" t="inlineStr">
-        <is>
-          <t>11:28</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA262" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="AB262" t="inlineStr">
-        <is>
-          <t>11:28</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD262" t="b">
@@ -29709,48 +29714,34 @@
       <c r="AE262" t="b">
         <v>0</v>
       </c>
+      <c r="AF262" t="inlineStr"/>
       <c r="AG262" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ262" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK262" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO262" t="inlineStr">
-        <is>
-          <t>Död stående björk # Betula</t>
-        </is>
       </c>
       <c r="AT262" t="inlineStr"/>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
       <c r="AZ262" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136777549</t>
+          <t>https://artportalen.se/Sighting/136823074</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>122692266</v>
+        <v>136777549</v>
       </c>
       <c r="B263" t="n">
-        <v>58826</v>
+        <v>8452</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -29758,54 +29749,42 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>208242</v>
+        <v>106554</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I263" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J263" t="inlineStr"/>
-      <c r="K263" t="inlineStr"/>
-      <c r="L263" t="inlineStr"/>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr"/>
       <c r="M263" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N263" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P263" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander, Srm</t>
+          <t>Norrby torp, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>687868</v>
+        <v>687859</v>
       </c>
       <c r="R263" t="n">
-        <v>6562755</v>
+        <v>6562767</v>
       </c>
       <c r="S263" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T263" t="inlineStr">
         <is>
@@ -29829,17 +29808,22 @@
       </c>
       <c r="Y263" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="Z263" t="inlineStr">
+        <is>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA263" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AC263" t="inlineStr">
-        <is>
-          <t>Mindre vattensalamander</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AB263" t="inlineStr">
+        <is>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD263" t="b">
@@ -29848,34 +29832,48 @@
       <c r="AE263" t="b">
         <v>0</v>
       </c>
-      <c r="AF263" t="inlineStr"/>
       <c r="AG263" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ263" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK263" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO263" t="inlineStr">
+        <is>
+          <t>Död stående björk # Betula</t>
+        </is>
       </c>
       <c r="AT263" t="inlineStr"/>
       <c r="AW263" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
       <c r="AZ263" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122692266</t>
+          <t>https://artportalen.se/Sighting/136777549</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>136241491</v>
+        <v>122692266</v>
       </c>
       <c r="B264" t="n">
-        <v>58845</v>
+        <v>58826</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -29883,16 +29881,16 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>208245</v>
+        <v>208242</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -29900,19 +29898,31 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I264" t="inlineStr"/>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J264" t="inlineStr"/>
       <c r="K264" t="inlineStr"/>
       <c r="L264" t="inlineStr"/>
-      <c r="M264" t="inlineStr"/>
-      <c r="N264" t="inlineStr"/>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P264" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Mindre vattensalamander, Srm</t>
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>687873</v>
+        <v>687868</v>
       </c>
       <c r="R264" t="n">
         <v>6562755</v>
@@ -29942,17 +29952,17 @@
       </c>
       <c r="Y264" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA264" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AC264" t="inlineStr">
         <is>
-          <t>Troligen årsunge.</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="AD264" t="b">
@@ -29968,27 +29978,27 @@
       <c r="AT264" t="inlineStr"/>
       <c r="AW264" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
       <c r="AZ264" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136241491</t>
+          <t>https://artportalen.se/Sighting/122692266</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>101544040</v>
+        <v>136241491</v>
       </c>
       <c r="B265" t="n">
-        <v>99035</v>
+        <v>58845</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -29996,41 +30006,42 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>219790</v>
+        <v>208245</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
       <c r="J265" t="inlineStr"/>
       <c r="K265" t="inlineStr"/>
       <c r="L265" t="inlineStr"/>
+      <c r="M265" t="inlineStr"/>
       <c r="N265" t="inlineStr"/>
       <c r="P265" t="inlineStr">
         <is>
-          <t>NO Norrby Torp, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>687896</v>
+        <v>687873</v>
       </c>
       <c r="R265" t="n">
-        <v>6562764</v>
+        <v>6562755</v>
       </c>
       <c r="S265" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T265" t="inlineStr">
         <is>
@@ -30054,12 +30065,17 @@
       </c>
       <c r="Y265" t="inlineStr">
         <is>
-          <t>2022-06-09</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="AA265" t="inlineStr">
         <is>
-          <t>2022-06-09</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AC265" t="inlineStr">
+        <is>
+          <t>Troligen årsunge.</t>
         </is>
       </c>
       <c r="AD265" t="b">
@@ -30086,16 +30102,16 @@
       <c r="AY265" t="inlineStr"/>
       <c r="AZ265" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101544040</t>
+          <t>https://artportalen.se/Sighting/136241491</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>136394236</v>
+        <v>101544040</v>
       </c>
       <c r="B266" t="n">
-        <v>98215</v>
+        <v>99035</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -30103,37 +30119,41 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
+      <c r="J266" t="inlineStr"/>
+      <c r="K266" t="inlineStr"/>
+      <c r="L266" t="inlineStr"/>
+      <c r="N266" t="inlineStr"/>
       <c r="P266" t="inlineStr">
         <is>
-          <t>Norrbytorp, Srm</t>
+          <t>NO Norrby Torp, Srm</t>
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>687882</v>
+        <v>687896</v>
       </c>
       <c r="R266" t="n">
-        <v>6562761</v>
+        <v>6562764</v>
       </c>
       <c r="S266" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="T266" t="inlineStr">
         <is>
@@ -30157,22 +30177,12 @@
       </c>
       <c r="Y266" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="Z266" t="inlineStr">
-        <is>
-          <t>11:26</t>
+          <t>2022-06-09</t>
         </is>
       </c>
       <c r="AA266" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="AB266" t="inlineStr">
-        <is>
-          <t>11:26</t>
+          <t>2022-06-09</t>
         </is>
       </c>
       <c r="AD266" t="b">
@@ -30181,33 +30191,34 @@
       <c r="AE266" t="b">
         <v>0</v>
       </c>
+      <c r="AF266" t="inlineStr"/>
       <c r="AG266" t="b">
         <v>0</v>
       </c>
       <c r="AT266" t="inlineStr"/>
       <c r="AW266" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX266" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
       <c r="AZ266" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136394236</t>
+          <t>https://artportalen.se/Sighting/101544040</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>122930166</v>
+        <v>136394236</v>
       </c>
       <c r="B267" t="n">
-        <v>96554</v>
+        <v>98215</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -30215,41 +30226,37 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>210</v>
+        <v>221945</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
-      <c r="J267" t="inlineStr"/>
-      <c r="K267" t="inlineStr"/>
-      <c r="L267" t="inlineStr"/>
-      <c r="N267" t="inlineStr"/>
       <c r="P267" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>686762</v>
+        <v>687882</v>
       </c>
       <c r="R267" t="n">
-        <v>6562715</v>
+        <v>6562761</v>
       </c>
       <c r="S267" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="T267" t="inlineStr">
         <is>
@@ -30273,22 +30280,22 @@
       </c>
       <c r="Y267" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="Z267" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA267" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="AB267" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD267" t="b">
@@ -30303,68 +30310,69 @@
       <c r="AT267" t="inlineStr"/>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
       <c r="AZ267" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122930166</t>
+          <t>https://artportalen.se/Sighting/136394236</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>119061006</v>
+        <v>122930166</v>
       </c>
       <c r="B268" t="n">
-        <v>91533</v>
+        <v>96554</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>2051</v>
+        <v>210</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
       <c r="J268" t="inlineStr"/>
       <c r="K268" t="inlineStr"/>
+      <c r="L268" t="inlineStr"/>
       <c r="N268" t="inlineStr"/>
       <c r="P268" t="inlineStr">
         <is>
-          <t>S Norrby mosse, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>686477</v>
+        <v>686762</v>
       </c>
       <c r="R268" t="n">
-        <v>6562857</v>
+        <v>6562715</v>
       </c>
       <c r="S268" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="T268" t="inlineStr">
         <is>
@@ -30388,17 +30396,22 @@
       </c>
       <c r="Y268" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="Z268" t="inlineStr">
+        <is>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA268" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC268" t="inlineStr">
-        <is>
-          <t>Brukad skog nära kant mot gammal.</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AB268" t="inlineStr">
+        <is>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD268" t="b">
@@ -30407,85 +30420,71 @@
       <c r="AE268" t="b">
         <v>0</v>
       </c>
-      <c r="AF268" t="inlineStr"/>
       <c r="AG268" t="b">
         <v>0</v>
       </c>
       <c r="AT268" t="inlineStr"/>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
       <c r="AZ268" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119061006</t>
+          <t>https://artportalen.se/Sighting/122930166</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>136947774</v>
+        <v>119061006</v>
       </c>
       <c r="B269" t="n">
-        <v>57195</v>
+        <v>91533</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>100138</v>
+        <v>2051</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I269" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr"/>
+      <c r="J269" t="inlineStr"/>
       <c r="K269" t="inlineStr"/>
-      <c r="L269" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M269" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N269" t="inlineStr"/>
       <c r="P269" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>S Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>686354</v>
+        <v>686477</v>
       </c>
       <c r="R269" t="n">
-        <v>6562881</v>
+        <v>6562857</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -30512,17 +30511,17 @@
       </c>
       <c r="Y269" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA269" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AC269" t="inlineStr">
         <is>
-          <t>Ruggad stjärtpenna, 33.5 cm.</t>
+          <t>Brukad skog nära kant mot gammal.</t>
         </is>
       </c>
       <c r="AD269" t="b">
@@ -30531,6 +30530,7 @@
       <c r="AE269" t="b">
         <v>0</v>
       </c>
+      <c r="AF269" t="inlineStr"/>
       <c r="AG269" t="b">
         <v>0</v>
       </c>
@@ -30548,16 +30548,16 @@
       <c r="AY269" t="inlineStr"/>
       <c r="AZ269" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136947774</t>
+          <t>https://artportalen.se/Sighting/119061006</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>122929535</v>
+        <v>136947774</v>
       </c>
       <c r="B270" t="n">
-        <v>8455</v>
+        <v>57195</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -30565,21 +30565,21 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -30587,24 +30587,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J270" t="inlineStr"/>
       <c r="K270" t="inlineStr"/>
-      <c r="L270" t="inlineStr"/>
-      <c r="M270" t="inlineStr"/>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N270" t="inlineStr"/>
       <c r="P270" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>686612</v>
+        <v>686354</v>
       </c>
       <c r="R270" t="n">
-        <v>6562882</v>
+        <v>6562881</v>
       </c>
       <c r="S270" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T270" t="inlineStr">
         <is>
@@ -30628,22 +30635,17 @@
       </c>
       <c r="Y270" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="Z270" t="inlineStr">
-        <is>
-          <t>11:01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AA270" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="AB270" t="inlineStr">
-        <is>
-          <t>11:01</t>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AC270" t="inlineStr">
+        <is>
+          <t>Ruggad stjärtpenna, 33.5 cm.</t>
         </is>
       </c>
       <c r="AD270" t="b">
@@ -30658,27 +30660,27 @@
       <c r="AT270" t="inlineStr"/>
       <c r="AW270" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
       <c r="AZ270" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122929535</t>
+          <t>https://artportalen.se/Sighting/136947774</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>122928987</v>
+        <v>122929535</v>
       </c>
       <c r="B271" t="n">
-        <v>97983</v>
+        <v>8455</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -30686,27 +30688,32 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I271" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J271" t="inlineStr"/>
       <c r="K271" t="inlineStr"/>
       <c r="L271" t="inlineStr"/>
+      <c r="M271" t="inlineStr"/>
       <c r="N271" t="inlineStr"/>
       <c r="P271" t="inlineStr">
         <is>
@@ -30714,13 +30721,13 @@
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>686389</v>
+        <v>686612</v>
       </c>
       <c r="R271" t="n">
-        <v>6562967</v>
+        <v>6562882</v>
       </c>
       <c r="S271" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T271" t="inlineStr">
         <is>
@@ -30749,7 +30756,7 @@
       </c>
       <c r="Z271" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA271" t="inlineStr">
@@ -30759,7 +30766,7 @@
       </c>
       <c r="AB271" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD271" t="b">
@@ -30785,51 +30792,55 @@
       <c r="AY271" t="inlineStr"/>
       <c r="AZ271" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122928987</t>
+          <t>https://artportalen.se/Sighting/122929535</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>126061106</v>
+        <v>122928987</v>
       </c>
       <c r="B272" t="n">
-        <v>91333</v>
+        <v>97983</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>2008</v>
+        <v>221945</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>Pers., nom.sanct.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
+      <c r="J272" t="inlineStr"/>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr"/>
+      <c r="N272" t="inlineStr"/>
       <c r="P272" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>686883</v>
+        <v>686389</v>
       </c>
       <c r="R272" t="n">
-        <v>6562742</v>
+        <v>6562967</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -30856,22 +30867,22 @@
       </c>
       <c r="Y272" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="Z272" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA272" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="AB272" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD272" t="b">
@@ -30886,49 +30897,49 @@
       <c r="AT272" t="inlineStr"/>
       <c r="AW272" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX272" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY272" t="inlineStr"/>
       <c r="AZ272" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061106</t>
+          <t>https://artportalen.se/Sighting/122928987</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>126061107</v>
+        <v>126061106</v>
       </c>
       <c r="B273" t="n">
-        <v>96458</v>
+        <v>91333</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>2818</v>
+        <v>2008</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Pers., nom.sanct.</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
@@ -30938,10 +30949,10 @@
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>686880</v>
+        <v>686883</v>
       </c>
       <c r="R273" t="n">
-        <v>6562745</v>
+        <v>6562742</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -30973,7 +30984,7 @@
       </c>
       <c r="Z273" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA273" t="inlineStr">
@@ -30983,7 +30994,7 @@
       </c>
       <c r="AB273" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD273" t="b">
@@ -31009,16 +31020,16 @@
       <c r="AY273" t="inlineStr"/>
       <c r="AZ273" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061107</t>
+          <t>https://artportalen.se/Sighting/126061106</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>129215187</v>
+        <v>126061107</v>
       </c>
       <c r="B274" t="n">
-        <v>91872</v>
+        <v>96458</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -31026,37 +31037,34 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>5447</v>
+        <v>2818</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
-      <c r="J274" t="inlineStr"/>
-      <c r="K274" t="inlineStr"/>
-      <c r="N274" t="inlineStr"/>
       <c r="P274" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>686977</v>
+        <v>686880</v>
       </c>
       <c r="R274" t="n">
-        <v>6562706</v>
+        <v>6562745</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -31083,12 +31091,22 @@
       </c>
       <c r="Y274" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z274" t="inlineStr">
+        <is>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA274" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB274" t="inlineStr">
+        <is>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD274" t="b">
@@ -31097,34 +31115,33 @@
       <c r="AE274" t="b">
         <v>0</v>
       </c>
-      <c r="AF274" t="inlineStr"/>
       <c r="AG274" t="b">
         <v>0</v>
       </c>
       <c r="AT274" t="inlineStr"/>
       <c r="AW274" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX274" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY274" t="inlineStr"/>
       <c r="AZ274" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215187</t>
+          <t>https://artportalen.se/Sighting/126061107</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>126061104</v>
+        <v>129215187</v>
       </c>
       <c r="B275" t="n">
-        <v>4775</v>
+        <v>91872</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -31132,34 +31149,37 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>100299</v>
+        <v>5447</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
+      <c r="J275" t="inlineStr"/>
+      <c r="K275" t="inlineStr"/>
+      <c r="N275" t="inlineStr"/>
       <c r="P275" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>686868</v>
+        <v>686977</v>
       </c>
       <c r="R275" t="n">
-        <v>6562739</v>
+        <v>6562706</v>
       </c>
       <c r="S275" t="n">
         <v>10</v>
@@ -31186,22 +31206,12 @@
       </c>
       <c r="Y275" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z275" t="inlineStr">
-        <is>
-          <t>13:41</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AA275" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB275" t="inlineStr">
-        <is>
-          <t>13:41</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AD275" t="b">
@@ -31210,53 +31220,34 @@
       <c r="AE275" t="b">
         <v>0</v>
       </c>
+      <c r="AF275" t="inlineStr"/>
       <c r="AG275" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ275" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK275" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL275" t="inlineStr">
-        <is>
-          <t>Stående död gran.</t>
-        </is>
-      </c>
-      <c r="AO275" t="inlineStr">
-        <is>
-          <t>Picea abies # Stående död gran.</t>
-        </is>
       </c>
       <c r="AT275" t="inlineStr"/>
       <c r="AW275" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX275" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY275" t="inlineStr"/>
       <c r="AZ275" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061104</t>
+          <t>https://artportalen.se/Sighting/129215187</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>126061116</v>
+        <v>126061104</v>
       </c>
       <c r="B276" t="n">
-        <v>44177</v>
+        <v>4775</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -31264,21 +31255,21 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>101735</v>
+        <v>100299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
@@ -31288,10 +31279,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>686928</v>
+        <v>686868</v>
       </c>
       <c r="R276" t="n">
-        <v>6562716</v>
+        <v>6562739</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -31323,7 +31314,7 @@
       </c>
       <c r="Z276" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA276" t="inlineStr">
@@ -31333,7 +31324,7 @@
       </c>
       <c r="AB276" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD276" t="b">
@@ -31347,22 +31338,22 @@
       </c>
       <c r="AJ276" t="inlineStr">
         <is>
-          <t>fnöskticka</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK276" t="inlineStr">
         <is>
-          <t>Fomes fomentarius</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL276" t="inlineStr">
         <is>
-          <t>Fnöskticka på björk.</t>
+          <t>Stående död gran.</t>
         </is>
       </c>
       <c r="AO276" t="inlineStr">
         <is>
-          <t>Fomes fomentarius # Fnöskticka på björk.</t>
+          <t>Picea abies # Stående död gran.</t>
         </is>
       </c>
       <c r="AT276" t="inlineStr"/>
@@ -31379,16 +31370,16 @@
       <c r="AY276" t="inlineStr"/>
       <c r="AZ276" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061116</t>
+          <t>https://artportalen.se/Sighting/126061104</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>125974903</v>
+        <v>126061116</v>
       </c>
       <c r="B277" t="n">
-        <v>8444</v>
+        <v>44177</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -31396,50 +31387,37 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>106554</v>
+        <v>101735</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I277" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J277" t="inlineStr"/>
-      <c r="K277" t="inlineStr"/>
-      <c r="L277" t="inlineStr"/>
-      <c r="M277" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N277" t="inlineStr"/>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr"/>
       <c r="P277" t="inlineStr">
         <is>
-          <t>söder om Tyresta, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>686838</v>
+        <v>686928</v>
       </c>
       <c r="R277" t="n">
-        <v>6562733</v>
+        <v>6562716</v>
       </c>
       <c r="S277" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T277" t="inlineStr">
         <is>
@@ -31466,14 +31444,19 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="Z277" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA277" t="inlineStr">
         <is>
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC277" t="inlineStr">
-        <is>
-          <t>gammal björklåga med spår längs hela stammen</t>
+      <c r="AB277" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD277" t="b">
@@ -31482,51 +31465,50 @@
       <c r="AE277" t="b">
         <v>0</v>
       </c>
-      <c r="AF277" t="inlineStr"/>
       <c r="AG277" t="b">
         <v>0</v>
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>vårtbjörk</t>
+          <t>fnöskticka</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
         <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
-      <c r="AM277" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
+          <t>Fomes fomentarius</t>
+        </is>
+      </c>
+      <c r="AL277" t="inlineStr">
+        <is>
+          <t>Fnöskticka på björk.</t>
         </is>
       </c>
       <c r="AO277" t="inlineStr">
         <is>
-          <t>Wood surface of dead wood # Betula pendula</t>
+          <t>Fomes fomentarius # Fnöskticka på björk.</t>
         </is>
       </c>
       <c r="AT277" t="inlineStr"/>
       <c r="AW277" t="inlineStr">
         <is>
-          <t>Nette Bygren</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX277" t="inlineStr">
         <is>
-          <t>Nette Bygren</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY277" t="inlineStr"/>
       <c r="AZ277" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125974903</t>
+          <t>https://artportalen.se/Sighting/126061116</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>126061105</v>
+        <v>125974903</v>
       </c>
       <c r="B278" t="n">
         <v>8444</v>
@@ -31554,20 +31536,33 @@
           <t>Janson, 1856</t>
         </is>
       </c>
-      <c r="I278" t="inlineStr"/>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr"/>
+      <c r="K278" t="inlineStr"/>
+      <c r="L278" t="inlineStr"/>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N278" t="inlineStr"/>
       <c r="P278" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>söder om Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>686860</v>
+        <v>686838</v>
       </c>
       <c r="R278" t="n">
-        <v>6562743</v>
+        <v>6562733</v>
       </c>
       <c r="S278" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T278" t="inlineStr">
         <is>
@@ -31594,19 +31589,14 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z278" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA278" t="inlineStr">
         <is>
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AB278" t="inlineStr">
-        <is>
-          <t>13:36</t>
+      <c r="AC278" t="inlineStr">
+        <is>
+          <t>gammal björklåga med spår längs hela stammen</t>
         </is>
       </c>
       <c r="AD278" t="b">
@@ -31615,37 +31605,170 @@
       <c r="AE278" t="b">
         <v>0</v>
       </c>
+      <c r="AF278" t="inlineStr"/>
       <c r="AG278" t="b">
         <v>0</v>
       </c>
       <c r="AJ278" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>vårtbjörk</t>
         </is>
       </c>
       <c r="AK278" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AM278" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO278" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Wood surface of dead wood # Betula pendula</t>
         </is>
       </c>
       <c r="AT278" t="inlineStr"/>
       <c r="AW278" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Nette Bygren</t>
         </is>
       </c>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Nette Bygren</t>
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
       <c r="AZ278" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125974903</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>126061105</v>
+      </c>
+      <c r="B279" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E279" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr"/>
+      <c r="P279" t="inlineStr">
+        <is>
+          <t>Ö Tyresta by, Srm</t>
+        </is>
+      </c>
+      <c r="Q279" t="n">
+        <v>686860</v>
+      </c>
+      <c r="R279" t="n">
+        <v>6562743</v>
+      </c>
+      <c r="S279" t="n">
+        <v>10</v>
+      </c>
+      <c r="T279" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U279" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V279" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W279" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y279" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z279" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA279" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB279" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AD279" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE279" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG279" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ279" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK279" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO279" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AT279" t="inlineStr"/>
+      <c r="AW279" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX279" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AY279" t="inlineStr"/>
+      <c r="AZ279" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/126061105</t>
         </is>
@@ -31930,6 +32053,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ276" r:id="rId275"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ277" r:id="rId276"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ279" r:id="rId278"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 152-2026 artfynd.xlsx
+++ b/artfynd/S 152-2026 artfynd.xlsx
@@ -1870,7 +1870,7 @@
         <v>136422855</v>
       </c>
       <c r="B13" t="n">
-        <v>90844</v>
+        <v>90846</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>136497917</v>
       </c>
       <c r="B14" t="n">
-        <v>90844</v>
+        <v>90846</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>136697240</v>
       </c>
       <c r="B15" t="n">
-        <v>90844</v>
+        <v>90846</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>136778801</v>
       </c>
       <c r="B16" t="n">
-        <v>90844</v>
+        <v>90846</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>136924639</v>
       </c>
       <c r="B17" t="n">
-        <v>90844</v>
+        <v>90846</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         <v>136697189</v>
       </c>
       <c r="B19" t="n">
-        <v>90859</v>
+        <v>90861</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>136394246</v>
       </c>
       <c r="B21" t="n">
-        <v>96938</v>
+        <v>96944</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>136777570</v>
       </c>
       <c r="B22" t="n">
-        <v>96938</v>
+        <v>96944</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>136557239</v>
       </c>
       <c r="B24" t="n">
-        <v>91889</v>
+        <v>91891</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>136697244</v>
       </c>
       <c r="B27" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>136497924</v>
       </c>
       <c r="B30" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         <v>136777559</v>
       </c>
       <c r="B31" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>136394238</v>
       </c>
       <c r="B40" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>136422890</v>
       </c>
       <c r="B41" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5044,7 +5044,7 @@
         <v>136697333</v>
       </c>
       <c r="B42" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         <v>136697388</v>
       </c>
       <c r="B43" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
         <v>136697399</v>
       </c>
       <c r="B44" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         <v>136777560</v>
       </c>
       <c r="B45" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         <v>136777566</v>
       </c>
       <c r="B46" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
         <v>136778803</v>
       </c>
       <c r="B47" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         <v>136778804</v>
       </c>
       <c r="B48" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>136778808</v>
       </c>
       <c r="B49" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>136778810</v>
       </c>
       <c r="B50" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         <v>136801360</v>
       </c>
       <c r="B51" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>136842788</v>
       </c>
       <c r="B52" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         <v>136842792</v>
       </c>
       <c r="B53" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>136842794</v>
       </c>
       <c r="B54" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         <v>136801292</v>
       </c>
       <c r="B55" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         <v>136394243</v>
       </c>
       <c r="B60" t="n">
-        <v>92134</v>
+        <v>92136</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         <v>136924655</v>
       </c>
       <c r="B67" t="n">
-        <v>93437</v>
+        <v>93439</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
         <v>136801166</v>
       </c>
       <c r="B71" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
         <v>136801323</v>
       </c>
       <c r="B72" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         <v>136801440</v>
       </c>
       <c r="B73" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8559,7 +8559,7 @@
         <v>136824502</v>
       </c>
       <c r="B74" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8665,7 +8665,7 @@
         <v>136824536</v>
       </c>
       <c r="B75" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>136824638</v>
       </c>
       <c r="B76" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>136842793</v>
       </c>
       <c r="B77" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8989,7 +8989,7 @@
         <v>136924440</v>
       </c>
       <c r="B78" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9095,7 +9095,7 @@
         <v>136801417</v>
       </c>
       <c r="B79" t="n">
-        <v>92791</v>
+        <v>92793</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -13070,7 +13070,7 @@
         <v>136777571</v>
       </c>
       <c r="B114" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>136394241</v>
       </c>
       <c r="B125" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14402,7 +14402,7 @@
         <v>136394242</v>
       </c>
       <c r="B126" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>136394244</v>
       </c>
       <c r="B127" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>136394245</v>
       </c>
       <c r="B128" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14738,7 +14738,7 @@
         <v>136778812</v>
       </c>
       <c r="B129" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -16731,7 +16731,7 @@
         <v>136329952</v>
       </c>
       <c r="B147" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>136330044</v>
       </c>
       <c r="B148" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17626,7 +17626,7 @@
         <v>136330155</v>
       </c>
       <c r="B155" t="n">
-        <v>92134</v>
+        <v>92136</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>136330904</v>
       </c>
       <c r="B156" t="n">
-        <v>92134</v>
+        <v>92136</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>136778218</v>
       </c>
       <c r="B160" t="n">
-        <v>93437</v>
+        <v>93439</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18911,7 +18911,7 @@
         <v>136737384</v>
       </c>
       <c r="B167" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19028,7 +19028,7 @@
         <v>136737387</v>
       </c>
       <c r="B168" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19140,7 +19140,7 @@
         <v>136778023</v>
       </c>
       <c r="B169" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19246,7 +19246,7 @@
         <v>136778100</v>
       </c>
       <c r="B170" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19352,7 +19352,7 @@
         <v>136778150</v>
       </c>
       <c r="B171" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19458,7 +19458,7 @@
         <v>136778261</v>
       </c>
       <c r="B172" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19564,7 +19564,7 @@
         <v>136778691</v>
       </c>
       <c r="B173" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19670,7 +19670,7 @@
         <v>136778703</v>
       </c>
       <c r="B174" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19776,7 +19776,7 @@
         <v>136778721</v>
       </c>
       <c r="B175" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19882,7 +19882,7 @@
         <v>136778733</v>
       </c>
       <c r="B176" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19988,7 +19988,7 @@
         <v>136778740</v>
       </c>
       <c r="B177" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20901,7 +20901,7 @@
         <v>136737383</v>
       </c>
       <c r="B185" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -25556,7 +25556,7 @@
         <v>136777554</v>
       </c>
       <c r="B226" t="n">
-        <v>96784</v>
+        <v>96790</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -26006,7 +26006,7 @@
         <v>136778798</v>
       </c>
       <c r="B230" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -26243,7 +26243,7 @@
         <v>136777555</v>
       </c>
       <c r="B232" t="n">
-        <v>96831</v>
+        <v>96837</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -26487,7 +26487,7 @@
         <v>136777551</v>
       </c>
       <c r="B234" t="n">
-        <v>96261</v>
+        <v>96267</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -26712,7 +26712,7 @@
         <v>136777556</v>
       </c>
       <c r="B236" t="n">
-        <v>96688</v>
+        <v>96694</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -26839,7 +26839,7 @@
         <v>136697134</v>
       </c>
       <c r="B237" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -26945,7 +26945,7 @@
         <v>136778799</v>
       </c>
       <c r="B238" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -27175,7 +27175,7 @@
         <v>136394237</v>
       </c>
       <c r="B240" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -27398,7 +27398,7 @@
         <v>136697126</v>
       </c>
       <c r="B242" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -27928,7 +27928,7 @@
         <v>136801045</v>
       </c>
       <c r="B247" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -28034,7 +28034,7 @@
         <v>136801064</v>
       </c>
       <c r="B248" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -30218,7 +30218,7 @@
         <v>136394236</v>
       </c>
       <c r="B267" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>

--- a/artfynd/S 152-2026 artfynd.xlsx
+++ b/artfynd/S 152-2026 artfynd.xlsx
@@ -1870,7 +1870,7 @@
         <v>136422855</v>
       </c>
       <c r="B13" t="n">
-        <v>90846</v>
+        <v>90848</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>136497917</v>
       </c>
       <c r="B14" t="n">
-        <v>90846</v>
+        <v>90848</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>136697240</v>
       </c>
       <c r="B15" t="n">
-        <v>90846</v>
+        <v>90848</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>136778801</v>
       </c>
       <c r="B16" t="n">
-        <v>90846</v>
+        <v>90848</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>136924639</v>
       </c>
       <c r="B17" t="n">
-        <v>90846</v>
+        <v>90848</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         <v>136697189</v>
       </c>
       <c r="B19" t="n">
-        <v>90861</v>
+        <v>90863</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>136394246</v>
       </c>
       <c r="B21" t="n">
-        <v>96944</v>
+        <v>96946</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>136777570</v>
       </c>
       <c r="B22" t="n">
-        <v>96944</v>
+        <v>96946</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
+          <t>Klas Magnusson, Jennica Andersson, Gustav Bringby, Petya Valcheva, Björn Persson, Birgitta Tulin, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3120,7 +3120,7 @@
         <v>136557239</v>
       </c>
       <c r="B24" t="n">
-        <v>91891</v>
+        <v>91893</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>136697244</v>
       </c>
       <c r="B27" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>136497924</v>
       </c>
       <c r="B30" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         <v>136777559</v>
       </c>
       <c r="B31" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
+          <t>Klas Magnusson, Jennica Andersson, Gustav Bringby, Petya Valcheva, Björn Persson, Birgitta Tulin, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4818,7 +4818,7 @@
         <v>136394238</v>
       </c>
       <c r="B40" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>136422890</v>
       </c>
       <c r="B41" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5044,7 +5044,7 @@
         <v>136697333</v>
       </c>
       <c r="B42" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         <v>136697388</v>
       </c>
       <c r="B43" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
         <v>136697399</v>
       </c>
       <c r="B44" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         <v>136777560</v>
       </c>
       <c r="B45" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
+          <t>Klas Magnusson, Jennica Andersson, Gustav Bringby, Petya Valcheva, Björn Persson, Birgitta Tulin, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5474,7 +5474,7 @@
         <v>136777566</v>
       </c>
       <c r="B46" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
+          <t>Klas Magnusson, Jennica Andersson, Gustav Bringby, Petya Valcheva, Björn Persson, Birgitta Tulin, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5586,7 +5586,7 @@
         <v>136778803</v>
       </c>
       <c r="B47" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         <v>136778804</v>
       </c>
       <c r="B48" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>136778808</v>
       </c>
       <c r="B49" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>136778810</v>
       </c>
       <c r="B50" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         <v>136801360</v>
       </c>
       <c r="B51" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>136842788</v>
       </c>
       <c r="B52" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         <v>136842792</v>
       </c>
       <c r="B53" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>136842794</v>
       </c>
       <c r="B54" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         <v>136801292</v>
       </c>
       <c r="B55" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         <v>136394243</v>
       </c>
       <c r="B60" t="n">
-        <v>92136</v>
+        <v>92138</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         <v>136924655</v>
       </c>
       <c r="B67" t="n">
-        <v>93439</v>
+        <v>93441</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
         <v>136801166</v>
       </c>
       <c r="B71" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
         <v>136801323</v>
       </c>
       <c r="B72" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         <v>136801440</v>
       </c>
       <c r="B73" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8559,7 +8559,7 @@
         <v>136824502</v>
       </c>
       <c r="B74" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8665,7 +8665,7 @@
         <v>136824536</v>
       </c>
       <c r="B75" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>136824638</v>
       </c>
       <c r="B76" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>136842793</v>
       </c>
       <c r="B77" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8989,7 +8989,7 @@
         <v>136924440</v>
       </c>
       <c r="B78" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9095,7 +9095,7 @@
         <v>136801417</v>
       </c>
       <c r="B79" t="n">
-        <v>92793</v>
+        <v>92795</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
+          <t>Klas Magnusson, Jennica Andersson, Gustav Bringby, Petya Valcheva, Björn Persson, Birgitta Tulin, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -11940,7 +11940,7 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
+          <t>Klas Magnusson, Jennica Andersson, Gustav Bringby, Petya Valcheva, Björn Persson, Birgitta Tulin, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
@@ -12384,7 +12384,7 @@
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
+          <t>Klas Magnusson, Jennica Andersson, Gustav Bringby, Petya Valcheva, Björn Persson, Birgitta Tulin, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
@@ -12613,7 +12613,7 @@
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
+          <t>Klas Magnusson, Jennica Andersson, Gustav Bringby, Petya Valcheva, Björn Persson, Birgitta Tulin, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
@@ -13070,7 +13070,7 @@
         <v>136777571</v>
       </c>
       <c r="B114" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
+          <t>Klas Magnusson, Jennica Andersson, Gustav Bringby, Petya Valcheva, Björn Persson, Birgitta Tulin, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
@@ -14290,7 +14290,7 @@
         <v>136394241</v>
       </c>
       <c r="B125" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14402,7 +14402,7 @@
         <v>136394242</v>
       </c>
       <c r="B126" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>136394244</v>
       </c>
       <c r="B127" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>136394245</v>
       </c>
       <c r="B128" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14738,7 +14738,7 @@
         <v>136778812</v>
       </c>
       <c r="B129" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -17626,7 +17626,7 @@
         <v>136330155</v>
       </c>
       <c r="B155" t="n">
-        <v>92136</v>
+        <v>92138</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>136778218</v>
       </c>
       <c r="B160" t="n">
-        <v>93439</v>
+        <v>93441</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18911,7 +18911,7 @@
         <v>136737384</v>
       </c>
       <c r="B167" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19028,7 +19028,7 @@
         <v>136737387</v>
       </c>
       <c r="B168" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19140,7 +19140,7 @@
         <v>136778023</v>
       </c>
       <c r="B169" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19246,7 +19246,7 @@
         <v>136778100</v>
       </c>
       <c r="B170" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19352,7 +19352,7 @@
         <v>136778150</v>
       </c>
       <c r="B171" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19458,7 +19458,7 @@
         <v>136778261</v>
       </c>
       <c r="B172" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19564,7 +19564,7 @@
         <v>136778691</v>
       </c>
       <c r="B173" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19670,7 +19670,7 @@
         <v>136778703</v>
       </c>
       <c r="B174" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19776,7 +19776,7 @@
         <v>136778721</v>
       </c>
       <c r="B175" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19882,7 +19882,7 @@
         <v>136778733</v>
       </c>
       <c r="B176" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19988,7 +19988,7 @@
         <v>136778740</v>
       </c>
       <c r="B177" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20901,7 +20901,7 @@
         <v>136737383</v>
       </c>
       <c r="B185" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -25556,7 +25556,7 @@
         <v>136777554</v>
       </c>
       <c r="B226" t="n">
-        <v>96790</v>
+        <v>96792</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -25668,7 +25668,7 @@
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
+          <t>Klas Magnusson, Jennica Andersson, Gustav Bringby, Petya Valcheva, Björn Persson, Birgitta Tulin, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
@@ -26006,7 +26006,7 @@
         <v>136778798</v>
       </c>
       <c r="B230" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -26243,7 +26243,7 @@
         <v>136777555</v>
       </c>
       <c r="B232" t="n">
-        <v>96837</v>
+        <v>96839</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -26355,7 +26355,7 @@
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
+          <t>Klas Magnusson, Jennica Andersson, Gustav Bringby, Petya Valcheva, Björn Persson, Birgitta Tulin, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
@@ -26487,7 +26487,7 @@
         <v>136777551</v>
       </c>
       <c r="B234" t="n">
-        <v>96267</v>
+        <v>96269</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -26595,7 +26595,7 @@
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
+          <t>Klas Magnusson, Jennica Andersson, Gustav Bringby, Petya Valcheva, Björn Persson, Birgitta Tulin, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
@@ -26712,7 +26712,7 @@
         <v>136777556</v>
       </c>
       <c r="B236" t="n">
-        <v>96694</v>
+        <v>96696</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -26824,7 +26824,7 @@
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
+          <t>Klas Magnusson, Jennica Andersson, Gustav Bringby, Petya Valcheva, Björn Persson, Birgitta Tulin, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
@@ -26839,7 +26839,7 @@
         <v>136697134</v>
       </c>
       <c r="B237" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -26945,7 +26945,7 @@
         <v>136778799</v>
       </c>
       <c r="B238" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -27175,7 +27175,7 @@
         <v>136394237</v>
       </c>
       <c r="B240" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -27398,7 +27398,7 @@
         <v>136697126</v>
       </c>
       <c r="B242" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -27928,7 +27928,7 @@
         <v>136801045</v>
       </c>
       <c r="B247" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -28034,7 +28034,7 @@
         <v>136801064</v>
       </c>
       <c r="B248" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -29614,7 +29614,7 @@
       </c>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
+          <t>Klas Magnusson, Jennica Andersson, Gustav Bringby, Petya Valcheva, Björn Persson, Birgitta Tulin, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
@@ -29858,7 +29858,7 @@
       </c>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
+          <t>Klas Magnusson, Jennica Andersson, Gustav Bringby, Petya Valcheva, Björn Persson, Birgitta Tulin, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
@@ -30218,7 +30218,7 @@
         <v>136394236</v>
       </c>
       <c r="B267" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>

--- a/artfynd/S 152-2026 artfynd.xlsx
+++ b/artfynd/S 152-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ291"/>
+  <dimension ref="A1:AZ290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32005,10 +32005,10 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>137045663</v>
+        <v>126061106</v>
       </c>
       <c r="B283" t="n">
-        <v>92118</v>
+        <v>91333</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -32016,37 +32016,34 @@
         </is>
       </c>
       <c r="E283" t="n">
-        <v>1202</v>
+        <v>2008</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pers., nom.sanct.</t>
         </is>
       </c>
       <c r="I283" t="inlineStr"/>
-      <c r="J283" t="inlineStr"/>
-      <c r="K283" t="inlineStr"/>
-      <c r="N283" t="inlineStr"/>
       <c r="P283" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>686887</v>
+        <v>686883</v>
       </c>
       <c r="R283" t="n">
-        <v>6562652</v>
+        <v>6562742</v>
       </c>
       <c r="S283" t="n">
         <v>10</v>
@@ -32073,12 +32070,22 @@
       </c>
       <c r="Y283" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z283" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA283" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB283" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD283" t="b">
@@ -32087,56 +32094,55 @@
       <c r="AE283" t="b">
         <v>0</v>
       </c>
-      <c r="AF283" t="inlineStr"/>
       <c r="AG283" t="b">
         <v>0</v>
       </c>
       <c r="AT283" t="inlineStr"/>
       <c r="AW283" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX283" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY283" t="inlineStr"/>
       <c r="AZ283" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137045663</t>
+          <t>https://artportalen.se/Sighting/126061106</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>126061106</v>
+        <v>126061107</v>
       </c>
       <c r="B284" t="n">
-        <v>91333</v>
+        <v>96458</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>2008</v>
+        <v>2818</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>Pers., nom.sanct.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I284" t="inlineStr"/>
@@ -32146,10 +32152,10 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>686883</v>
+        <v>686880</v>
       </c>
       <c r="R284" t="n">
-        <v>6562742</v>
+        <v>6562745</v>
       </c>
       <c r="S284" t="n">
         <v>10</v>
@@ -32181,7 +32187,7 @@
       </c>
       <c r="Z284" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA284" t="inlineStr">
@@ -32191,7 +32197,7 @@
       </c>
       <c r="AB284" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD284" t="b">
@@ -32217,16 +32223,16 @@
       <c r="AY284" t="inlineStr"/>
       <c r="AZ284" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061106</t>
+          <t>https://artportalen.se/Sighting/126061107</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>126061107</v>
+        <v>129215187</v>
       </c>
       <c r="B285" t="n">
-        <v>96458</v>
+        <v>91872</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -32234,34 +32240,37 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>2818</v>
+        <v>5447</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I285" t="inlineStr"/>
+      <c r="J285" t="inlineStr"/>
+      <c r="K285" t="inlineStr"/>
+      <c r="N285" t="inlineStr"/>
       <c r="P285" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>686880</v>
+        <v>686977</v>
       </c>
       <c r="R285" t="n">
-        <v>6562745</v>
+        <v>6562706</v>
       </c>
       <c r="S285" t="n">
         <v>10</v>
@@ -32288,22 +32297,12 @@
       </c>
       <c r="Y285" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z285" t="inlineStr">
-        <is>
-          <t>13:19</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AA285" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB285" t="inlineStr">
-        <is>
-          <t>13:19</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AD285" t="b">
@@ -32312,33 +32311,34 @@
       <c r="AE285" t="b">
         <v>0</v>
       </c>
+      <c r="AF285" t="inlineStr"/>
       <c r="AG285" t="b">
         <v>0</v>
       </c>
       <c r="AT285" t="inlineStr"/>
       <c r="AW285" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX285" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY285" t="inlineStr"/>
       <c r="AZ285" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061107</t>
+          <t>https://artportalen.se/Sighting/129215187</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>129215187</v>
+        <v>126061104</v>
       </c>
       <c r="B286" t="n">
-        <v>91872</v>
+        <v>4775</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -32346,37 +32346,34 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>5447</v>
+        <v>100299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I286" t="inlineStr"/>
-      <c r="J286" t="inlineStr"/>
-      <c r="K286" t="inlineStr"/>
-      <c r="N286" t="inlineStr"/>
       <c r="P286" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>686977</v>
+        <v>686868</v>
       </c>
       <c r="R286" t="n">
-        <v>6562706</v>
+        <v>6562739</v>
       </c>
       <c r="S286" t="n">
         <v>10</v>
@@ -32403,12 +32400,22 @@
       </c>
       <c r="Y286" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z286" t="inlineStr">
+        <is>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA286" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB286" t="inlineStr">
+        <is>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD286" t="b">
@@ -32417,34 +32424,53 @@
       <c r="AE286" t="b">
         <v>0</v>
       </c>
-      <c r="AF286" t="inlineStr"/>
       <c r="AG286" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ286" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK286" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL286" t="inlineStr">
+        <is>
+          <t>Stående död gran.</t>
+        </is>
+      </c>
+      <c r="AO286" t="inlineStr">
+        <is>
+          <t>Picea abies # Stående död gran.</t>
+        </is>
       </c>
       <c r="AT286" t="inlineStr"/>
       <c r="AW286" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX286" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY286" t="inlineStr"/>
       <c r="AZ286" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215187</t>
+          <t>https://artportalen.se/Sighting/126061104</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>126061104</v>
+        <v>126061116</v>
       </c>
       <c r="B287" t="n">
-        <v>4775</v>
+        <v>44177</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -32452,21 +32478,21 @@
         </is>
       </c>
       <c r="E287" t="n">
-        <v>100299</v>
+        <v>101735</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I287" t="inlineStr"/>
@@ -32476,10 +32502,10 @@
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>686868</v>
+        <v>686928</v>
       </c>
       <c r="R287" t="n">
-        <v>6562739</v>
+        <v>6562716</v>
       </c>
       <c r="S287" t="n">
         <v>10</v>
@@ -32511,7 +32537,7 @@
       </c>
       <c r="Z287" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA287" t="inlineStr">
@@ -32521,7 +32547,7 @@
       </c>
       <c r="AB287" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD287" t="b">
@@ -32535,22 +32561,22 @@
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>fnöskticka</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Fomes fomentarius</t>
         </is>
       </c>
       <c r="AL287" t="inlineStr">
         <is>
-          <t>Stående död gran.</t>
+          <t>Fnöskticka på björk.</t>
         </is>
       </c>
       <c r="AO287" t="inlineStr">
         <is>
-          <t>Picea abies # Stående död gran.</t>
+          <t>Fomes fomentarius # Fnöskticka på björk.</t>
         </is>
       </c>
       <c r="AT287" t="inlineStr"/>
@@ -32567,16 +32593,16 @@
       <c r="AY287" t="inlineStr"/>
       <c r="AZ287" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061104</t>
+          <t>https://artportalen.se/Sighting/126061116</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>126061116</v>
+        <v>125974903</v>
       </c>
       <c r="B288" t="n">
-        <v>44177</v>
+        <v>8444</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -32584,37 +32610,50 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>101735</v>
+        <v>106554</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
-        </is>
-      </c>
-      <c r="I288" t="inlineStr"/>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr"/>
+      <c r="K288" t="inlineStr"/>
+      <c r="L288" t="inlineStr"/>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N288" t="inlineStr"/>
       <c r="P288" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>söder om Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>686928</v>
+        <v>686838</v>
       </c>
       <c r="R288" t="n">
-        <v>6562716</v>
+        <v>6562733</v>
       </c>
       <c r="S288" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T288" t="inlineStr">
         <is>
@@ -32641,19 +32680,14 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z288" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AA288" t="inlineStr">
         <is>
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AB288" t="inlineStr">
-        <is>
-          <t>11:58</t>
+      <c r="AC288" t="inlineStr">
+        <is>
+          <t>gammal björklåga med spår längs hela stammen</t>
         </is>
       </c>
       <c r="AD288" t="b">
@@ -32662,50 +32696,51 @@
       <c r="AE288" t="b">
         <v>0</v>
       </c>
+      <c r="AF288" t="inlineStr"/>
       <c r="AG288" t="b">
         <v>0</v>
       </c>
       <c r="AJ288" t="inlineStr">
         <is>
-          <t>fnöskticka</t>
+          <t>vårtbjörk</t>
         </is>
       </c>
       <c r="AK288" t="inlineStr">
         <is>
-          <t>Fomes fomentarius</t>
-        </is>
-      </c>
-      <c r="AL288" t="inlineStr">
-        <is>
-          <t>Fnöskticka på björk.</t>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AM288" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO288" t="inlineStr">
         <is>
-          <t>Fomes fomentarius # Fnöskticka på björk.</t>
+          <t>Wood surface of dead wood # Betula pendula</t>
         </is>
       </c>
       <c r="AT288" t="inlineStr"/>
       <c r="AW288" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Nette Bygren</t>
         </is>
       </c>
       <c r="AX288" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Nette Bygren</t>
         </is>
       </c>
       <c r="AY288" t="inlineStr"/>
       <c r="AZ288" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061116</t>
+          <t>https://artportalen.se/Sighting/125974903</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>125974903</v>
+        <v>126061105</v>
       </c>
       <c r="B289" t="n">
         <v>8444</v>
@@ -32733,33 +32768,20 @@
           <t>Janson, 1856</t>
         </is>
       </c>
-      <c r="I289" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J289" t="inlineStr"/>
-      <c r="K289" t="inlineStr"/>
-      <c r="L289" t="inlineStr"/>
-      <c r="M289" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N289" t="inlineStr"/>
+      <c r="I289" t="inlineStr"/>
       <c r="P289" t="inlineStr">
         <is>
-          <t>söder om Tyresta, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>686838</v>
+        <v>686860</v>
       </c>
       <c r="R289" t="n">
-        <v>6562733</v>
+        <v>6562743</v>
       </c>
       <c r="S289" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T289" t="inlineStr">
         <is>
@@ -32786,14 +32808,19 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="Z289" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AA289" t="inlineStr">
         <is>
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC289" t="inlineStr">
-        <is>
-          <t>gammal björklåga med spår längs hela stammen</t>
+      <c r="AB289" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD289" t="b">
@@ -32802,54 +32829,48 @@
       <c r="AE289" t="b">
         <v>0</v>
       </c>
-      <c r="AF289" t="inlineStr"/>
       <c r="AG289" t="b">
         <v>0</v>
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>vårtbjörk</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
         <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
-      <c r="AM289" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO289" t="inlineStr">
         <is>
-          <t>Wood surface of dead wood # Betula pendula</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT289" t="inlineStr"/>
       <c r="AW289" t="inlineStr">
         <is>
-          <t>Nette Bygren</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX289" t="inlineStr">
         <is>
-          <t>Nette Bygren</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY289" t="inlineStr"/>
       <c r="AZ289" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125974903</t>
+          <t>https://artportalen.se/Sighting/126061105</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>126061105</v>
+        <v>137045669</v>
       </c>
       <c r="B290" t="n">
-        <v>8444</v>
+        <v>98227</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -32857,34 +32878,38 @@
         </is>
       </c>
       <c r="E290" t="n">
-        <v>106554</v>
+        <v>221946</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I290" t="inlineStr"/>
+      <c r="J290" t="inlineStr"/>
+      <c r="K290" t="inlineStr"/>
+      <c r="L290" t="inlineStr"/>
+      <c r="N290" t="inlineStr"/>
       <c r="P290" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q290" t="n">
-        <v>686860</v>
+        <v>686837</v>
       </c>
       <c r="R290" t="n">
-        <v>6562743</v>
+        <v>6562677</v>
       </c>
       <c r="S290" t="n">
         <v>10</v>
@@ -32911,22 +32936,12 @@
       </c>
       <c r="Y290" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z290" t="inlineStr">
-        <is>
-          <t>13:36</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AA290" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB290" t="inlineStr">
-        <is>
-          <t>13:36</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AD290" t="b">
@@ -32935,144 +32950,23 @@
       <c r="AE290" t="b">
         <v>0</v>
       </c>
+      <c r="AF290" t="inlineStr"/>
       <c r="AG290" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ290" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK290" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO290" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT290" t="inlineStr"/>
       <c r="AW290" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX290" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY290" t="inlineStr"/>
       <c r="AZ290" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/126061105</t>
-        </is>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" t="n">
-        <v>137045669</v>
-      </c>
-      <c r="B291" t="n">
-        <v>98227</v>
-      </c>
-      <c r="D291" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E291" t="n">
-        <v>221946</v>
-      </c>
-      <c r="F291" t="inlineStr">
-        <is>
-          <t>Mattlummer</t>
-        </is>
-      </c>
-      <c r="G291" t="inlineStr">
-        <is>
-          <t>Lycopodium clavatum</t>
-        </is>
-      </c>
-      <c r="H291" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I291" t="inlineStr"/>
-      <c r="J291" t="inlineStr"/>
-      <c r="K291" t="inlineStr"/>
-      <c r="L291" t="inlineStr"/>
-      <c r="N291" t="inlineStr"/>
-      <c r="P291" t="inlineStr">
-        <is>
-          <t>N Norrbytorp, Srm</t>
-        </is>
-      </c>
-      <c r="Q291" t="n">
-        <v>686837</v>
-      </c>
-      <c r="R291" t="n">
-        <v>6562677</v>
-      </c>
-      <c r="S291" t="n">
-        <v>10</v>
-      </c>
-      <c r="T291" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="U291" t="inlineStr">
-        <is>
-          <t>Haninge</t>
-        </is>
-      </c>
-      <c r="V291" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W291" t="inlineStr">
-        <is>
-          <t>Österhaninge</t>
-        </is>
-      </c>
-      <c r="Y291" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AA291" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AD291" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE291" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF291" t="inlineStr"/>
-      <c r="AG291" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT291" t="inlineStr"/>
-      <c r="AW291" t="inlineStr">
-        <is>
-          <t>Bodil Ravn</t>
-        </is>
-      </c>
-      <c r="AX291" t="inlineStr">
-        <is>
-          <t>Bodil Ravn</t>
-        </is>
-      </c>
-      <c r="AY291" t="inlineStr"/>
-      <c r="AZ291" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137045669</t>
         </is>
@@ -33369,7 +33263,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ288" r:id="rId287"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ289" r:id="rId288"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ290" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ291" r:id="rId290"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 152-2026 artfynd.xlsx
+++ b/artfynd/S 152-2026 artfynd.xlsx
@@ -3015,7 +3015,7 @@
         <v>136777570</v>
       </c>
       <c r="B23" t="n">
-        <v>96957</v>
+        <v>96959</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -13727,7 +13727,7 @@
         <v>136777571</v>
       </c>
       <c r="B120" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14402,7 +14402,7 @@
         <v>137089136</v>
       </c>
       <c r="B126" t="n">
-        <v>98240</v>
+        <v>98242</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15515,7 +15515,7 @@
         <v>136778812</v>
       </c>
       <c r="B136" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -26863,7 +26863,7 @@
         <v>136777554</v>
       </c>
       <c r="B238" t="n">
-        <v>96803</v>
+        <v>96805</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -27550,7 +27550,7 @@
         <v>136777555</v>
       </c>
       <c r="B244" t="n">
-        <v>96850</v>
+        <v>96852</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -27794,7 +27794,7 @@
         <v>136777551</v>
       </c>
       <c r="B246" t="n">
-        <v>96280</v>
+        <v>96282</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -28019,7 +28019,7 @@
         <v>136777556</v>
       </c>
       <c r="B248" t="n">
-        <v>96707</v>
+        <v>96709</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -33510,7 +33510,7 @@
         <v>137045669</v>
       </c>
       <c r="B296" t="n">
-        <v>98237</v>
+        <v>98239</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>

--- a/artfynd/S 152-2026 artfynd.xlsx
+++ b/artfynd/S 152-2026 artfynd.xlsx
@@ -2094,7 +2094,7 @@
         <v>136697240</v>
       </c>
       <c r="B15" t="n">
-        <v>90874</v>
+        <v>90876</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>136778801</v>
       </c>
       <c r="B16" t="n">
-        <v>90874</v>
+        <v>90876</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>136924639</v>
       </c>
       <c r="B17" t="n">
-        <v>90874</v>
+        <v>90876</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         <v>136697189</v>
       </c>
       <c r="B19" t="n">
-        <v>90889</v>
+        <v>90891</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>136777570</v>
       </c>
       <c r="B22" t="n">
-        <v>96974</v>
+        <v>96976</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>136697244</v>
       </c>
       <c r="B27" t="n">
-        <v>93433</v>
+        <v>93434</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         <v>136777559</v>
       </c>
       <c r="B31" t="n">
-        <v>93435</v>
+        <v>93436</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
+          <t>Klas Magnusson, Jennica Andersson, Gustav Bringby, Petya Valcheva, Björn Persson, Birgitta Tulin, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -5044,7 +5044,7 @@
         <v>136697333</v>
       </c>
       <c r="B42" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         <v>136697388</v>
       </c>
       <c r="B43" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
         <v>136697399</v>
       </c>
       <c r="B44" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         <v>136777560</v>
       </c>
       <c r="B45" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
+          <t>Klas Magnusson, Jennica Andersson, Gustav Bringby, Petya Valcheva, Björn Persson, Birgitta Tulin, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5474,7 +5474,7 @@
         <v>136777566</v>
       </c>
       <c r="B46" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
+          <t>Klas Magnusson, Petya Valcheva, Gustav Bringby, Jennica Andersson, Björn Persson, Birgitta Tulin, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5586,7 +5586,7 @@
         <v>136778803</v>
       </c>
       <c r="B47" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         <v>136778804</v>
       </c>
       <c r="B48" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>136778808</v>
       </c>
       <c r="B49" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>136778810</v>
       </c>
       <c r="B50" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         <v>136801360</v>
       </c>
       <c r="B51" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>136842788</v>
       </c>
       <c r="B52" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         <v>136842792</v>
       </c>
       <c r="B53" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>136842794</v>
       </c>
       <c r="B54" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         <v>136801292</v>
       </c>
       <c r="B55" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         <v>136924655</v>
       </c>
       <c r="B67" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
         <v>136801166</v>
       </c>
       <c r="B71" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
         <v>136801323</v>
       </c>
       <c r="B72" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         <v>136801440</v>
       </c>
       <c r="B73" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8559,7 +8559,7 @@
         <v>136824502</v>
       </c>
       <c r="B74" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8665,7 +8665,7 @@
         <v>136824536</v>
       </c>
       <c r="B75" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>136824638</v>
       </c>
       <c r="B76" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>136842793</v>
       </c>
       <c r="B77" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8989,7 +8989,7 @@
         <v>136924440</v>
       </c>
       <c r="B78" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9095,7 +9095,7 @@
         <v>137143672</v>
       </c>
       <c r="B79" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         <v>137144281</v>
       </c>
       <c r="B80" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>137220342</v>
       </c>
       <c r="B81" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         <v>136801417</v>
       </c>
       <c r="B82" t="n">
-        <v>92821</v>
+        <v>92823</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9870,7 +9870,7 @@
         <v>137106176</v>
       </c>
       <c r="B86" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9980,7 +9980,7 @@
         <v>137143649</v>
       </c>
       <c r="B87" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10328,7 +10328,7 @@
         <v>136824120</v>
       </c>
       <c r="B90" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10447,7 +10447,7 @@
         <v>136777562</v>
       </c>
       <c r="B91" t="n">
-        <v>44223</v>
+        <v>44225</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
+          <t>Klas Magnusson, Jennica Andersson, Gustav Bringby, Petya Valcheva, Björn Persson, Birgitta Tulin, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -11679,7 +11679,7 @@
         <v>136824136</v>
       </c>
       <c r="B102" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         <v>136824277</v>
       </c>
       <c r="B103" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11899,7 +11899,7 @@
         <v>136824305</v>
       </c>
       <c r="B104" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
         <v>136777563</v>
       </c>
       <c r="B108" t="n">
-        <v>8452</v>
+        <v>8453</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12478,7 +12478,7 @@
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
+          <t>Klas Magnusson, Jennica Andersson, Gustav Bringby, Petya Valcheva, Björn Persson, Birgitta Tulin, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -12493,7 +12493,7 @@
         <v>136767154</v>
       </c>
       <c r="B109" t="n">
-        <v>56900</v>
+        <v>56902</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>136767150</v>
       </c>
       <c r="B110" t="n">
-        <v>56879</v>
+        <v>56881</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12713,7 +12713,7 @@
         <v>136767156</v>
       </c>
       <c r="B111" t="n">
-        <v>56902</v>
+        <v>56904</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         <v>136777561</v>
       </c>
       <c r="B112" t="n">
-        <v>58858</v>
+        <v>58860</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12922,7 +12922,7 @@
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
+          <t>Klas Magnusson, Jennica Andersson, Gustav Bringby, Petya Valcheva, Björn Persson, Birgitta Tulin, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
@@ -12937,7 +12937,7 @@
         <v>136778811</v>
       </c>
       <c r="B113" t="n">
-        <v>58858</v>
+        <v>58860</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13054,7 +13054,7 @@
         <v>136777569</v>
       </c>
       <c r="B114" t="n">
-        <v>58885</v>
+        <v>58887</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>136777571</v>
       </c>
       <c r="B119" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13705,7 +13705,7 @@
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
+          <t>Klas Magnusson, Jennica Andersson, Gustav Bringby, Petya Valcheva, Björn Persson, Birgitta Tulin, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
@@ -14283,7 +14283,7 @@
         <v>137089136</v>
       </c>
       <c r="B125" t="n">
-        <v>98257</v>
+        <v>98259</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15396,7 +15396,7 @@
         <v>136778812</v>
       </c>
       <c r="B135" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15961,7 +15961,7 @@
         <v>137045897</v>
       </c>
       <c r="B140" t="n">
-        <v>92534</v>
+        <v>92536</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -18390,7 +18390,7 @@
         <v>136330155</v>
       </c>
       <c r="B162" t="n">
-        <v>92164</v>
+        <v>92166</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18933,7 +18933,7 @@
         <v>136778218</v>
       </c>
       <c r="B167" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>136737384</v>
       </c>
       <c r="B174" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19792,7 +19792,7 @@
         <v>136737387</v>
       </c>
       <c r="B175" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19904,7 +19904,7 @@
         <v>136778023</v>
       </c>
       <c r="B176" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20010,7 +20010,7 @@
         <v>136778100</v>
       </c>
       <c r="B177" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20116,7 +20116,7 @@
         <v>136778150</v>
       </c>
       <c r="B178" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20222,7 +20222,7 @@
         <v>136778261</v>
       </c>
       <c r="B179" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20328,7 +20328,7 @@
         <v>136778691</v>
       </c>
       <c r="B180" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20434,7 +20434,7 @@
         <v>136778703</v>
       </c>
       <c r="B181" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20540,7 +20540,7 @@
         <v>136778721</v>
       </c>
       <c r="B182" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20646,7 +20646,7 @@
         <v>136778733</v>
       </c>
       <c r="B183" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20752,7 +20752,7 @@
         <v>136778740</v>
       </c>
       <c r="B184" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20858,7 +20858,7 @@
         <v>137088961</v>
       </c>
       <c r="B185" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20964,7 +20964,7 @@
         <v>137089019</v>
       </c>
       <c r="B186" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21070,7 +21070,7 @@
         <v>137090631</v>
       </c>
       <c r="B187" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21176,7 +21176,7 @@
         <v>137090646</v>
       </c>
       <c r="B188" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -22089,7 +22089,7 @@
         <v>136737383</v>
       </c>
       <c r="B196" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22670,7 +22670,7 @@
         <v>136767143</v>
       </c>
       <c r="B201" t="n">
-        <v>56895</v>
+        <v>56897</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -22782,7 +22782,7 @@
         <v>136767141</v>
       </c>
       <c r="B202" t="n">
-        <v>56898</v>
+        <v>56900</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -22894,7 +22894,7 @@
         <v>136778200</v>
       </c>
       <c r="B203" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -23013,7 +23013,7 @@
         <v>136972809</v>
       </c>
       <c r="B204" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -24043,7 +24043,7 @@
         <v>136631248</v>
       </c>
       <c r="B213" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -24153,7 +24153,7 @@
         <v>136947615</v>
       </c>
       <c r="B214" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -24927,7 +24927,7 @@
         <v>136767139</v>
       </c>
       <c r="B221" t="n">
-        <v>56888</v>
+        <v>56890</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -25039,7 +25039,7 @@
         <v>136767130</v>
       </c>
       <c r="B222" t="n">
-        <v>56900</v>
+        <v>56902</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -25151,7 +25151,7 @@
         <v>136767147</v>
       </c>
       <c r="B223" t="n">
-        <v>56900</v>
+        <v>56902</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -25263,7 +25263,7 @@
         <v>136767125</v>
       </c>
       <c r="B224" t="n">
-        <v>56879</v>
+        <v>56881</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -25376,7 +25376,7 @@
         <v>136767144</v>
       </c>
       <c r="B225" t="n">
-        <v>56879</v>
+        <v>56881</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26744,7 +26744,7 @@
         <v>136777554</v>
       </c>
       <c r="B237" t="n">
-        <v>96820</v>
+        <v>96822</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -26856,7 +26856,7 @@
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
+          <t>Klas Magnusson, Jennica Andersson, Gustav Bringby, Petya Valcheva, Björn Persson, Birgitta Tulin, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
@@ -27194,7 +27194,7 @@
         <v>136778798</v>
       </c>
       <c r="B241" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -27431,7 +27431,7 @@
         <v>136777555</v>
       </c>
       <c r="B243" t="n">
-        <v>96867</v>
+        <v>96869</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -27543,7 +27543,7 @@
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
+          <t>Klas Magnusson, Jennica Andersson, Gustav Bringby, Petya Valcheva, Björn Persson, Birgitta Tulin, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
@@ -27675,7 +27675,7 @@
         <v>136777551</v>
       </c>
       <c r="B245" t="n">
-        <v>96297</v>
+        <v>96299</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -27783,7 +27783,7 @@
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
+          <t>Klas Magnusson, Jennica Andersson, Gustav Bringby, Petya Valcheva, Björn Persson, Birgitta Tulin, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
@@ -27900,7 +27900,7 @@
         <v>136777556</v>
       </c>
       <c r="B247" t="n">
-        <v>96724</v>
+        <v>96726</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -28012,7 +28012,7 @@
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
+          <t>Klas Magnusson, Jennica Andersson, Gustav Bringby, Petya Valcheva, Björn Persson, Birgitta Tulin, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
@@ -28027,7 +28027,7 @@
         <v>136697134</v>
       </c>
       <c r="B248" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -28133,7 +28133,7 @@
         <v>136778799</v>
       </c>
       <c r="B249" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -28586,7 +28586,7 @@
         <v>136697126</v>
       </c>
       <c r="B253" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>136801045</v>
       </c>
       <c r="B258" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -29222,7 +29222,7 @@
         <v>136801064</v>
       </c>
       <c r="B259" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -29328,7 +29328,7 @@
         <v>137143298</v>
       </c>
       <c r="B260" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -29434,7 +29434,7 @@
         <v>137143509</v>
       </c>
       <c r="B261" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -29540,7 +29540,7 @@
         <v>137143542</v>
       </c>
       <c r="B262" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -30783,7 +30783,7 @@
         <v>136823037</v>
       </c>
       <c r="B273" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -30893,7 +30893,7 @@
         <v>136823087</v>
       </c>
       <c r="B274" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -31120,7 +31120,7 @@
       </c>
       <c r="AX275" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
+          <t>Klas Magnusson, Jennica Andersson, Gustav Bringby, Petya Valcheva, Björn Persson, Birgitta Tulin, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY275" t="inlineStr"/>
@@ -31135,7 +31135,7 @@
         <v>136823074</v>
       </c>
       <c r="B276" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -31247,7 +31247,7 @@
         <v>136777549</v>
       </c>
       <c r="B277" t="n">
-        <v>8452</v>
+        <v>8453</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -31364,7 +31364,7 @@
       </c>
       <c r="AX277" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
+          <t>Klas Magnusson, Jennica Andersson, Gustav Bringby, Petya Valcheva, Björn Persson, Birgitta Tulin, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY277" t="inlineStr"/>
@@ -32063,7 +32063,7 @@
         <v>137090662</v>
       </c>
       <c r="B284" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -32169,7 +32169,7 @@
         <v>136947774</v>
       </c>
       <c r="B285" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>

--- a/artfynd/S 152-2026 artfynd.xlsx
+++ b/artfynd/S 152-2026 artfynd.xlsx
@@ -2094,7 +2094,7 @@
         <v>136697240</v>
       </c>
       <c r="B15" t="n">
-        <v>90876</v>
+        <v>90879</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>136778801</v>
       </c>
       <c r="B16" t="n">
-        <v>90876</v>
+        <v>90879</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>136924639</v>
       </c>
       <c r="B17" t="n">
-        <v>90876</v>
+        <v>90879</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         <v>136697189</v>
       </c>
       <c r="B19" t="n">
-        <v>90891</v>
+        <v>90894</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>137045898</v>
       </c>
       <c r="B20" t="n">
-        <v>93458</v>
+        <v>93461</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>136777570</v>
       </c>
       <c r="B23" t="n">
-        <v>96976</v>
+        <v>96979</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         <v>136697244</v>
       </c>
       <c r="B28" t="n">
-        <v>93434</v>
+        <v>93437</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>136777559</v>
       </c>
       <c r="B32" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4078,7 +4078,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Jennica Andersson, Gustav Bringby, Petya Valcheva, Björn Persson, Birgitta Tulin, Bodil Ravn</t>
+          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -5163,7 +5163,7 @@
         <v>136697333</v>
       </c>
       <c r="B43" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>136697388</v>
       </c>
       <c r="B44" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>136697399</v>
       </c>
       <c r="B45" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5481,7 +5481,7 @@
         <v>136777560</v>
       </c>
       <c r="B46" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Jennica Andersson, Gustav Bringby, Petya Valcheva, Björn Persson, Birgitta Tulin, Bodil Ravn</t>
+          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5593,7 +5593,7 @@
         <v>136777566</v>
       </c>
       <c r="B47" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Petya Valcheva, Gustav Bringby, Jennica Andersson, Björn Persson, Birgitta Tulin, Bodil Ravn</t>
+          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5705,7 +5705,7 @@
         <v>136778803</v>
       </c>
       <c r="B48" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
         <v>136778804</v>
       </c>
       <c r="B49" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>136778808</v>
       </c>
       <c r="B50" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6053,7 +6053,7 @@
         <v>136778810</v>
       </c>
       <c r="B51" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         <v>136801360</v>
       </c>
       <c r="B52" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6275,7 +6275,7 @@
         <v>136842788</v>
       </c>
       <c r="B53" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
         <v>136842792</v>
       </c>
       <c r="B54" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>136842794</v>
       </c>
       <c r="B55" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         <v>136801292</v>
       </c>
       <c r="B56" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7913,7 +7913,7 @@
         <v>136924655</v>
       </c>
       <c r="B68" t="n">
-        <v>93468</v>
+        <v>93471</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>136801166</v>
       </c>
       <c r="B72" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>136801323</v>
       </c>
       <c r="B73" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         <v>136801440</v>
       </c>
       <c r="B74" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>136824502</v>
       </c>
       <c r="B75" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
         <v>136824536</v>
       </c>
       <c r="B76" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>136824638</v>
       </c>
       <c r="B77" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>136842793</v>
       </c>
       <c r="B78" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>136924440</v>
       </c>
       <c r="B79" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>137045947</v>
       </c>
       <c r="B80" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>137143672</v>
       </c>
       <c r="B81" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>137144281</v>
       </c>
       <c r="B82" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         <v>137220342</v>
       </c>
       <c r="B83" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9638,7 +9638,7 @@
         <v>136801417</v>
       </c>
       <c r="B84" t="n">
-        <v>92823</v>
+        <v>92826</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Jennica Andersson, Gustav Bringby, Petya Valcheva, Björn Persson, Birgitta Tulin, Bodil Ravn</t>
+          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
@@ -12679,7 +12679,7 @@
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Jennica Andersson, Gustav Bringby, Petya Valcheva, Björn Persson, Birgitta Tulin, Bodil Ravn</t>
+          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
@@ -13123,7 +13123,7 @@
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Jennica Andersson, Gustav Bringby, Petya Valcheva, Björn Persson, Birgitta Tulin, Bodil Ravn</t>
+          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
@@ -13809,7 +13809,7 @@
         <v>136777571</v>
       </c>
       <c r="B121" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13906,7 +13906,7 @@
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Jennica Andersson, Gustav Bringby, Petya Valcheva, Björn Persson, Birgitta Tulin, Bodil Ravn</t>
+          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
@@ -14484,7 +14484,7 @@
         <v>137089136</v>
       </c>
       <c r="B127" t="n">
-        <v>98259</v>
+        <v>98262</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15597,7 +15597,7 @@
         <v>136778812</v>
       </c>
       <c r="B137" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16162,7 +16162,7 @@
         <v>137045897</v>
       </c>
       <c r="B142" t="n">
-        <v>92536</v>
+        <v>92539</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -18591,7 +18591,7 @@
         <v>136330155</v>
       </c>
       <c r="B164" t="n">
-        <v>92166</v>
+        <v>92169</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19134,7 +19134,7 @@
         <v>136778218</v>
       </c>
       <c r="B169" t="n">
-        <v>93468</v>
+        <v>93471</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19876,7 +19876,7 @@
         <v>136737384</v>
       </c>
       <c r="B176" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19993,7 +19993,7 @@
         <v>136737387</v>
       </c>
       <c r="B177" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20105,7 +20105,7 @@
         <v>136778023</v>
       </c>
       <c r="B178" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>136778100</v>
       </c>
       <c r="B179" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20317,7 +20317,7 @@
         <v>136778150</v>
       </c>
       <c r="B180" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20423,7 +20423,7 @@
         <v>136778261</v>
       </c>
       <c r="B181" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20529,7 +20529,7 @@
         <v>136778691</v>
       </c>
       <c r="B182" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20635,7 +20635,7 @@
         <v>136778703</v>
       </c>
       <c r="B183" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20741,7 +20741,7 @@
         <v>136778721</v>
       </c>
       <c r="B184" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20847,7 +20847,7 @@
         <v>136778733</v>
       </c>
       <c r="B185" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20953,7 +20953,7 @@
         <v>136778740</v>
       </c>
       <c r="B186" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21059,7 +21059,7 @@
         <v>137088961</v>
       </c>
       <c r="B187" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         <v>137089019</v>
       </c>
       <c r="B188" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>137090631</v>
       </c>
       <c r="B189" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -21377,7 +21377,7 @@
         <v>137090646</v>
       </c>
       <c r="B190" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -26929,7 +26929,7 @@
         <v>136777554</v>
       </c>
       <c r="B239" t="n">
-        <v>96822</v>
+        <v>96825</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -27041,7 +27041,7 @@
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Jennica Andersson, Gustav Bringby, Petya Valcheva, Björn Persson, Birgitta Tulin, Bodil Ravn</t>
+          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
@@ -27379,7 +27379,7 @@
         <v>136778798</v>
       </c>
       <c r="B243" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -27616,7 +27616,7 @@
         <v>136777555</v>
       </c>
       <c r="B245" t="n">
-        <v>96869</v>
+        <v>96872</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -27728,7 +27728,7 @@
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Jennica Andersson, Gustav Bringby, Petya Valcheva, Björn Persson, Birgitta Tulin, Bodil Ravn</t>
+          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
@@ -27860,7 +27860,7 @@
         <v>136777551</v>
       </c>
       <c r="B247" t="n">
-        <v>96299</v>
+        <v>96302</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -27968,7 +27968,7 @@
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Jennica Andersson, Gustav Bringby, Petya Valcheva, Björn Persson, Birgitta Tulin, Bodil Ravn</t>
+          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
@@ -28085,7 +28085,7 @@
         <v>136777556</v>
       </c>
       <c r="B249" t="n">
-        <v>96726</v>
+        <v>96729</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -28197,7 +28197,7 @@
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Jennica Andersson, Gustav Bringby, Petya Valcheva, Björn Persson, Birgitta Tulin, Bodil Ravn</t>
+          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
@@ -28212,7 +28212,7 @@
         <v>136697134</v>
       </c>
       <c r="B250" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -28318,7 +28318,7 @@
         <v>136778799</v>
       </c>
       <c r="B251" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -28771,7 +28771,7 @@
         <v>136697126</v>
       </c>
       <c r="B255" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -29301,7 +29301,7 @@
         <v>136801045</v>
       </c>
       <c r="B260" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -29407,7 +29407,7 @@
         <v>136801064</v>
       </c>
       <c r="B261" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -29513,7 +29513,7 @@
         <v>137143298</v>
       </c>
       <c r="B262" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -29619,7 +29619,7 @@
         <v>137143509</v>
       </c>
       <c r="B263" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -29725,7 +29725,7 @@
         <v>137143542</v>
       </c>
       <c r="B264" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -31293,7 +31293,7 @@
       </c>
       <c r="AX277" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Jennica Andersson, Gustav Bringby, Petya Valcheva, Björn Persson, Birgitta Tulin, Bodil Ravn</t>
+          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY277" t="inlineStr"/>
@@ -31529,7 +31529,7 @@
       </c>
       <c r="AX279" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Jennica Andersson, Gustav Bringby, Petya Valcheva, Björn Persson, Birgitta Tulin, Bodil Ravn</t>
+          <t>Klas Magnusson, Bodil Ravn, Birgitta Tulin, Björn Persson, Petya Valcheva, Gustav Bringby, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY279" t="inlineStr"/>
@@ -32228,7 +32228,7 @@
         <v>137090662</v>
       </c>
       <c r="B286" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -33548,7 +33548,7 @@
         <v>137045669</v>
       </c>
       <c r="B297" t="n">
-        <v>98256</v>
+        <v>98259</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>

--- a/artfynd/S 152-2026 artfynd.xlsx
+++ b/artfynd/S 152-2026 artfynd.xlsx
@@ -2208,7 +2208,7 @@
         <v>136778801</v>
       </c>
       <c r="B16" t="n">
-        <v>90879</v>
+        <v>90889</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>136924639</v>
       </c>
       <c r="B17" t="n">
-        <v>90879</v>
+        <v>90889</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>137045898</v>
       </c>
       <c r="B20" t="n">
-        <v>93461</v>
+        <v>93471</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>136777570</v>
       </c>
       <c r="B23" t="n">
-        <v>96979</v>
+        <v>96989</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>136777559</v>
       </c>
       <c r="B32" t="n">
-        <v>93439</v>
+        <v>93449</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5481,7 +5481,7 @@
         <v>136777560</v>
       </c>
       <c r="B46" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>136777566</v>
       </c>
       <c r="B47" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>136778803</v>
       </c>
       <c r="B48" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
         <v>136778804</v>
       </c>
       <c r="B49" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>136778808</v>
       </c>
       <c r="B50" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6053,7 +6053,7 @@
         <v>136778810</v>
       </c>
       <c r="B51" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         <v>136801360</v>
       </c>
       <c r="B52" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6275,7 +6275,7 @@
         <v>136842788</v>
       </c>
       <c r="B53" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
         <v>136842792</v>
       </c>
       <c r="B54" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>136842794</v>
       </c>
       <c r="B55" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         <v>136801292</v>
       </c>
       <c r="B56" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7913,7 +7913,7 @@
         <v>136924655</v>
       </c>
       <c r="B68" t="n">
-        <v>93471</v>
+        <v>93481</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>136801166</v>
       </c>
       <c r="B72" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>136801323</v>
       </c>
       <c r="B73" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         <v>136801440</v>
       </c>
       <c r="B74" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>136824502</v>
       </c>
       <c r="B75" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
         <v>136824536</v>
       </c>
       <c r="B76" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>136824638</v>
       </c>
       <c r="B77" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>136842793</v>
       </c>
       <c r="B78" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>136924440</v>
       </c>
       <c r="B79" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>137045947</v>
       </c>
       <c r="B80" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>137143672</v>
       </c>
       <c r="B81" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>137144281</v>
       </c>
       <c r="B82" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         <v>137220342</v>
       </c>
       <c r="B83" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9638,7 +9638,7 @@
         <v>136801417</v>
       </c>
       <c r="B84" t="n">
-        <v>92826</v>
+        <v>92836</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10095,7 +10095,7 @@
         <v>137106176</v>
       </c>
       <c r="B88" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10205,7 +10205,7 @@
         <v>137143649</v>
       </c>
       <c r="B89" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10553,7 +10553,7 @@
         <v>136824120</v>
       </c>
       <c r="B92" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
         <v>136777562</v>
       </c>
       <c r="B93" t="n">
-        <v>44225</v>
+        <v>44235</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11896,7 +11896,7 @@
         <v>136824136</v>
       </c>
       <c r="B104" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12002,7 +12002,7 @@
         <v>136824277</v>
       </c>
       <c r="B105" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12108,7 +12108,7 @@
         <v>136824305</v>
       </c>
       <c r="B106" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>136777563</v>
       </c>
       <c r="B110" t="n">
-        <v>8453</v>
+        <v>8459</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12694,7 +12694,7 @@
         <v>136767154</v>
       </c>
       <c r="B111" t="n">
-        <v>56902</v>
+        <v>56912</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12806,7 +12806,7 @@
         <v>136767150</v>
       </c>
       <c r="B112" t="n">
-        <v>56881</v>
+        <v>56891</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>136767156</v>
       </c>
       <c r="B113" t="n">
-        <v>56904</v>
+        <v>56914</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13026,7 +13026,7 @@
         <v>136777561</v>
       </c>
       <c r="B114" t="n">
-        <v>58860</v>
+        <v>58870</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
         <v>136778811</v>
       </c>
       <c r="B115" t="n">
-        <v>58860</v>
+        <v>58870</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13255,7 +13255,7 @@
         <v>136777569</v>
       </c>
       <c r="B116" t="n">
-        <v>58887</v>
+        <v>58897</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13809,7 +13809,7 @@
         <v>136777571</v>
       </c>
       <c r="B121" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14484,7 +14484,7 @@
         <v>137089136</v>
       </c>
       <c r="B127" t="n">
-        <v>98262</v>
+        <v>98272</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15597,7 +15597,7 @@
         <v>136778812</v>
       </c>
       <c r="B137" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16162,7 +16162,7 @@
         <v>137045897</v>
       </c>
       <c r="B142" t="n">
-        <v>92539</v>
+        <v>92549</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -18591,7 +18591,7 @@
         <v>136330155</v>
       </c>
       <c r="B164" t="n">
-        <v>92169</v>
+        <v>92179</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19134,7 +19134,7 @@
         <v>136778218</v>
       </c>
       <c r="B169" t="n">
-        <v>93471</v>
+        <v>93481</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19876,7 +19876,7 @@
         <v>136737384</v>
       </c>
       <c r="B176" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19993,7 +19993,7 @@
         <v>136737387</v>
       </c>
       <c r="B177" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20105,7 +20105,7 @@
         <v>136778023</v>
       </c>
       <c r="B178" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>136778100</v>
       </c>
       <c r="B179" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20317,7 +20317,7 @@
         <v>136778150</v>
       </c>
       <c r="B180" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20423,7 +20423,7 @@
         <v>136778261</v>
       </c>
       <c r="B181" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20529,7 +20529,7 @@
         <v>136778691</v>
       </c>
       <c r="B182" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20635,7 +20635,7 @@
         <v>136778703</v>
       </c>
       <c r="B183" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20741,7 +20741,7 @@
         <v>136778721</v>
       </c>
       <c r="B184" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20847,7 +20847,7 @@
         <v>136778733</v>
       </c>
       <c r="B185" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20953,7 +20953,7 @@
         <v>136778740</v>
       </c>
       <c r="B186" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21059,7 +21059,7 @@
         <v>137088961</v>
       </c>
       <c r="B187" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         <v>137089019</v>
       </c>
       <c r="B188" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>137090631</v>
       </c>
       <c r="B189" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -21377,7 +21377,7 @@
         <v>137090646</v>
       </c>
       <c r="B190" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -22290,7 +22290,7 @@
         <v>136737383</v>
       </c>
       <c r="B198" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -22871,7 +22871,7 @@
         <v>136767143</v>
       </c>
       <c r="B203" t="n">
-        <v>56897</v>
+        <v>56907</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -22983,7 +22983,7 @@
         <v>136767141</v>
       </c>
       <c r="B204" t="n">
-        <v>56900</v>
+        <v>56910</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -23095,7 +23095,7 @@
         <v>136778200</v>
       </c>
       <c r="B205" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -23210,7 +23210,7 @@
         <v>136972809</v>
       </c>
       <c r="B206" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24342,7 +24342,7 @@
         <v>136947615</v>
       </c>
       <c r="B216" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -25112,7 +25112,7 @@
         <v>136767139</v>
       </c>
       <c r="B223" t="n">
-        <v>56890</v>
+        <v>56900</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -25224,7 +25224,7 @@
         <v>136767130</v>
       </c>
       <c r="B224" t="n">
-        <v>56902</v>
+        <v>56912</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -25336,7 +25336,7 @@
         <v>136767147</v>
       </c>
       <c r="B225" t="n">
-        <v>56902</v>
+        <v>56912</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -25448,7 +25448,7 @@
         <v>136767125</v>
       </c>
       <c r="B226" t="n">
-        <v>56881</v>
+        <v>56891</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -25561,7 +25561,7 @@
         <v>136767144</v>
       </c>
       <c r="B227" t="n">
-        <v>56881</v>
+        <v>56891</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -26929,7 +26929,7 @@
         <v>136777554</v>
       </c>
       <c r="B239" t="n">
-        <v>96825</v>
+        <v>96835</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -27379,7 +27379,7 @@
         <v>136778798</v>
       </c>
       <c r="B243" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -27616,7 +27616,7 @@
         <v>136777555</v>
       </c>
       <c r="B245" t="n">
-        <v>96872</v>
+        <v>96882</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -27860,7 +27860,7 @@
         <v>136777551</v>
       </c>
       <c r="B247" t="n">
-        <v>96302</v>
+        <v>96312</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -28085,7 +28085,7 @@
         <v>136777556</v>
       </c>
       <c r="B249" t="n">
-        <v>96729</v>
+        <v>96739</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -28318,7 +28318,7 @@
         <v>136778799</v>
       </c>
       <c r="B251" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29301,7 +29301,7 @@
         <v>136801045</v>
       </c>
       <c r="B260" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -29407,7 +29407,7 @@
         <v>136801064</v>
       </c>
       <c r="B261" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -29513,7 +29513,7 @@
         <v>137143298</v>
       </c>
       <c r="B262" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -29619,7 +29619,7 @@
         <v>137143509</v>
       </c>
       <c r="B263" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -29725,7 +29725,7 @@
         <v>137143542</v>
       </c>
       <c r="B264" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -30968,7 +30968,7 @@
         <v>136823037</v>
       </c>
       <c r="B275" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -31074,7 +31074,7 @@
         <v>136823087</v>
       </c>
       <c r="B276" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -31180,7 +31180,7 @@
         <v>136777552</v>
       </c>
       <c r="B277" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -31308,7 +31308,7 @@
         <v>136823074</v>
       </c>
       <c r="B278" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -31416,7 +31416,7 @@
         <v>136777549</v>
       </c>
       <c r="B279" t="n">
-        <v>8453</v>
+        <v>8459</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -32228,7 +32228,7 @@
         <v>137090662</v>
       </c>
       <c r="B286" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -32334,7 +32334,7 @@
         <v>136947774</v>
       </c>
       <c r="B287" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -33548,7 +33548,7 @@
         <v>137045669</v>
       </c>
       <c r="B297" t="n">
-        <v>98259</v>
+        <v>98269</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>

--- a/artfynd/S 152-2026 artfynd.xlsx
+++ b/artfynd/S 152-2026 artfynd.xlsx
@@ -2208,7 +2208,7 @@
         <v>136778801</v>
       </c>
       <c r="B16" t="n">
-        <v>90889</v>
+        <v>90890</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>136924639</v>
       </c>
       <c r="B17" t="n">
-        <v>90889</v>
+        <v>90890</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>137045898</v>
       </c>
       <c r="B20" t="n">
-        <v>93471</v>
+        <v>93472</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>136777570</v>
       </c>
       <c r="B23" t="n">
-        <v>96989</v>
+        <v>96990</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>136777559</v>
       </c>
       <c r="B32" t="n">
-        <v>93449</v>
+        <v>93450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5481,7 +5481,7 @@
         <v>136777560</v>
       </c>
       <c r="B46" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>136777566</v>
       </c>
       <c r="B47" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>136778803</v>
       </c>
       <c r="B48" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
         <v>136778804</v>
       </c>
       <c r="B49" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>136778808</v>
       </c>
       <c r="B50" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6053,7 +6053,7 @@
         <v>136778810</v>
       </c>
       <c r="B51" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         <v>136801360</v>
       </c>
       <c r="B52" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6275,7 +6275,7 @@
         <v>136842788</v>
       </c>
       <c r="B53" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
         <v>136842792</v>
       </c>
       <c r="B54" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>136842794</v>
       </c>
       <c r="B55" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         <v>136801292</v>
       </c>
       <c r="B56" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7913,7 +7913,7 @@
         <v>136924655</v>
       </c>
       <c r="B68" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>136801166</v>
       </c>
       <c r="B72" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>136801323</v>
       </c>
       <c r="B73" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         <v>136801440</v>
       </c>
       <c r="B74" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>136824502</v>
       </c>
       <c r="B75" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
         <v>136824536</v>
       </c>
       <c r="B76" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>136824638</v>
       </c>
       <c r="B77" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>136842793</v>
       </c>
       <c r="B78" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>136924440</v>
       </c>
       <c r="B79" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>137045947</v>
       </c>
       <c r="B80" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>137143672</v>
       </c>
       <c r="B81" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>137144281</v>
       </c>
       <c r="B82" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         <v>137220342</v>
       </c>
       <c r="B83" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9638,7 +9638,7 @@
         <v>136801417</v>
       </c>
       <c r="B84" t="n">
-        <v>92836</v>
+        <v>92837</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -13809,7 +13809,7 @@
         <v>136777571</v>
       </c>
       <c r="B121" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14484,7 +14484,7 @@
         <v>137089136</v>
       </c>
       <c r="B127" t="n">
-        <v>98272</v>
+        <v>98273</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15597,7 +15597,7 @@
         <v>136778812</v>
       </c>
       <c r="B137" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16162,7 +16162,7 @@
         <v>137045897</v>
       </c>
       <c r="B142" t="n">
-        <v>92549</v>
+        <v>92550</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -18591,7 +18591,7 @@
         <v>136330155</v>
       </c>
       <c r="B164" t="n">
-        <v>92179</v>
+        <v>92180</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19134,7 +19134,7 @@
         <v>136778218</v>
       </c>
       <c r="B169" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19876,7 +19876,7 @@
         <v>136737384</v>
       </c>
       <c r="B176" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19993,7 +19993,7 @@
         <v>136737387</v>
       </c>
       <c r="B177" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20105,7 +20105,7 @@
         <v>136778023</v>
       </c>
       <c r="B178" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>136778100</v>
       </c>
       <c r="B179" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20317,7 +20317,7 @@
         <v>136778150</v>
       </c>
       <c r="B180" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20423,7 +20423,7 @@
         <v>136778261</v>
       </c>
       <c r="B181" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20529,7 +20529,7 @@
         <v>136778691</v>
       </c>
       <c r="B182" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20635,7 +20635,7 @@
         <v>136778703</v>
       </c>
       <c r="B183" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20741,7 +20741,7 @@
         <v>136778721</v>
       </c>
       <c r="B184" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20847,7 +20847,7 @@
         <v>136778733</v>
       </c>
       <c r="B185" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20953,7 +20953,7 @@
         <v>136778740</v>
       </c>
       <c r="B186" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21059,7 +21059,7 @@
         <v>137088961</v>
       </c>
       <c r="B187" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         <v>137089019</v>
       </c>
       <c r="B188" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>137090631</v>
       </c>
       <c r="B189" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -21377,7 +21377,7 @@
         <v>137090646</v>
       </c>
       <c r="B190" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -26929,7 +26929,7 @@
         <v>136777554</v>
       </c>
       <c r="B239" t="n">
-        <v>96835</v>
+        <v>96836</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -27379,7 +27379,7 @@
         <v>136778798</v>
       </c>
       <c r="B243" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -27616,7 +27616,7 @@
         <v>136777555</v>
       </c>
       <c r="B245" t="n">
-        <v>96882</v>
+        <v>96883</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -27860,7 +27860,7 @@
         <v>136777551</v>
       </c>
       <c r="B247" t="n">
-        <v>96312</v>
+        <v>96313</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -28085,7 +28085,7 @@
         <v>136777556</v>
       </c>
       <c r="B249" t="n">
-        <v>96739</v>
+        <v>96740</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -28318,7 +28318,7 @@
         <v>136778799</v>
       </c>
       <c r="B251" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29301,7 +29301,7 @@
         <v>136801045</v>
       </c>
       <c r="B260" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -29407,7 +29407,7 @@
         <v>136801064</v>
       </c>
       <c r="B261" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -29513,7 +29513,7 @@
         <v>137143298</v>
       </c>
       <c r="B262" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -29619,7 +29619,7 @@
         <v>137143509</v>
       </c>
       <c r="B263" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -29725,7 +29725,7 @@
         <v>137143542</v>
       </c>
       <c r="B264" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -32228,7 +32228,7 @@
         <v>137090662</v>
       </c>
       <c r="B286" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -33548,7 +33548,7 @@
         <v>137045669</v>
       </c>
       <c r="B297" t="n">
-        <v>98269</v>
+        <v>98270</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>

--- a/artfynd/S 152-2026 artfynd.xlsx
+++ b/artfynd/S 152-2026 artfynd.xlsx
@@ -2208,7 +2208,7 @@
         <v>136778801</v>
       </c>
       <c r="B16" t="n">
-        <v>90890</v>
+        <v>90893</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>136924639</v>
       </c>
       <c r="B17" t="n">
-        <v>90890</v>
+        <v>90893</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>137045898</v>
       </c>
       <c r="B20" t="n">
-        <v>93472</v>
+        <v>93477</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>136777570</v>
       </c>
       <c r="B23" t="n">
-        <v>96990</v>
+        <v>96995</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>136777559</v>
       </c>
       <c r="B32" t="n">
-        <v>93450</v>
+        <v>93455</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5481,7 +5481,7 @@
         <v>136777560</v>
       </c>
       <c r="B46" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>136777566</v>
       </c>
       <c r="B47" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>136778803</v>
       </c>
       <c r="B48" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
         <v>136778804</v>
       </c>
       <c r="B49" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>136778808</v>
       </c>
       <c r="B50" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6053,7 +6053,7 @@
         <v>136778810</v>
       </c>
       <c r="B51" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         <v>136801360</v>
       </c>
       <c r="B52" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6275,7 +6275,7 @@
         <v>136842788</v>
       </c>
       <c r="B53" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
         <v>136842792</v>
       </c>
       <c r="B54" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>136842794</v>
       </c>
       <c r="B55" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         <v>136801292</v>
       </c>
       <c r="B56" t="n">
-        <v>93468</v>
+        <v>93473</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7913,7 +7913,7 @@
         <v>136924655</v>
       </c>
       <c r="B68" t="n">
-        <v>93482</v>
+        <v>93487</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>136801166</v>
       </c>
       <c r="B72" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>136801323</v>
       </c>
       <c r="B73" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         <v>136801440</v>
       </c>
       <c r="B74" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>136824502</v>
       </c>
       <c r="B75" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
         <v>136824536</v>
       </c>
       <c r="B76" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>136824638</v>
       </c>
       <c r="B77" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>136842793</v>
       </c>
       <c r="B78" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>136924440</v>
       </c>
       <c r="B79" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>137045947</v>
       </c>
       <c r="B80" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>137143672</v>
       </c>
       <c r="B81" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>137144281</v>
       </c>
       <c r="B82" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         <v>137220342</v>
       </c>
       <c r="B83" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9638,7 +9638,7 @@
         <v>136801417</v>
       </c>
       <c r="B84" t="n">
-        <v>92837</v>
+        <v>92840</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10095,7 +10095,7 @@
         <v>137106176</v>
       </c>
       <c r="B88" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10205,7 +10205,7 @@
         <v>137143649</v>
       </c>
       <c r="B89" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10553,7 +10553,7 @@
         <v>136824120</v>
       </c>
       <c r="B92" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
         <v>136777562</v>
       </c>
       <c r="B93" t="n">
-        <v>44235</v>
+        <v>44236</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11896,7 +11896,7 @@
         <v>136824136</v>
       </c>
       <c r="B104" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12002,7 +12002,7 @@
         <v>136824277</v>
       </c>
       <c r="B105" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12108,7 +12108,7 @@
         <v>136824305</v>
       </c>
       <c r="B106" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12694,7 +12694,7 @@
         <v>136767154</v>
       </c>
       <c r="B111" t="n">
-        <v>56912</v>
+        <v>56913</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12806,7 +12806,7 @@
         <v>136767150</v>
       </c>
       <c r="B112" t="n">
-        <v>56891</v>
+        <v>56892</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>136767156</v>
       </c>
       <c r="B113" t="n">
-        <v>56914</v>
+        <v>56915</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13026,7 +13026,7 @@
         <v>136777561</v>
       </c>
       <c r="B114" t="n">
-        <v>58870</v>
+        <v>58872</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
         <v>136778811</v>
       </c>
       <c r="B115" t="n">
-        <v>58870</v>
+        <v>58872</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13255,7 +13255,7 @@
         <v>136777569</v>
       </c>
       <c r="B116" t="n">
-        <v>58897</v>
+        <v>58899</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13809,7 +13809,7 @@
         <v>136777571</v>
       </c>
       <c r="B121" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14484,7 +14484,7 @@
         <v>137089136</v>
       </c>
       <c r="B127" t="n">
-        <v>98273</v>
+        <v>98278</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15597,7 +15597,7 @@
         <v>136778812</v>
       </c>
       <c r="B137" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16162,7 +16162,7 @@
         <v>137045897</v>
       </c>
       <c r="B142" t="n">
-        <v>92550</v>
+        <v>92553</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -18591,7 +18591,7 @@
         <v>136330155</v>
       </c>
       <c r="B164" t="n">
-        <v>92180</v>
+        <v>92183</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19134,7 +19134,7 @@
         <v>136778218</v>
       </c>
       <c r="B169" t="n">
-        <v>93482</v>
+        <v>93487</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20105,7 +20105,7 @@
         <v>136778023</v>
       </c>
       <c r="B178" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>136778100</v>
       </c>
       <c r="B179" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20317,7 +20317,7 @@
         <v>136778150</v>
       </c>
       <c r="B180" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20423,7 +20423,7 @@
         <v>136778261</v>
       </c>
       <c r="B181" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20529,7 +20529,7 @@
         <v>136778691</v>
       </c>
       <c r="B182" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20635,7 +20635,7 @@
         <v>136778703</v>
       </c>
       <c r="B183" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20741,7 +20741,7 @@
         <v>136778721</v>
       </c>
       <c r="B184" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20847,7 +20847,7 @@
         <v>136778733</v>
       </c>
       <c r="B185" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20953,7 +20953,7 @@
         <v>136778740</v>
       </c>
       <c r="B186" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21059,7 +21059,7 @@
         <v>137088961</v>
       </c>
       <c r="B187" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         <v>137089019</v>
       </c>
       <c r="B188" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>137090631</v>
       </c>
       <c r="B189" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -21377,7 +21377,7 @@
         <v>137090646</v>
       </c>
       <c r="B190" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -22871,7 +22871,7 @@
         <v>136767143</v>
       </c>
       <c r="B203" t="n">
-        <v>56907</v>
+        <v>56908</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -22983,7 +22983,7 @@
         <v>136767141</v>
       </c>
       <c r="B204" t="n">
-        <v>56910</v>
+        <v>56911</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -23095,7 +23095,7 @@
         <v>136778200</v>
       </c>
       <c r="B205" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -23210,7 +23210,7 @@
         <v>136972809</v>
       </c>
       <c r="B206" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24342,7 +24342,7 @@
         <v>136947615</v>
       </c>
       <c r="B216" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -25112,7 +25112,7 @@
         <v>136767139</v>
       </c>
       <c r="B223" t="n">
-        <v>56900</v>
+        <v>56901</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -25224,7 +25224,7 @@
         <v>136767130</v>
       </c>
       <c r="B224" t="n">
-        <v>56912</v>
+        <v>56913</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -25336,7 +25336,7 @@
         <v>136767147</v>
       </c>
       <c r="B225" t="n">
-        <v>56912</v>
+        <v>56913</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -25448,7 +25448,7 @@
         <v>136767125</v>
       </c>
       <c r="B226" t="n">
-        <v>56891</v>
+        <v>56892</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -25561,7 +25561,7 @@
         <v>136767144</v>
       </c>
       <c r="B227" t="n">
-        <v>56891</v>
+        <v>56892</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -26929,7 +26929,7 @@
         <v>136777554</v>
       </c>
       <c r="B239" t="n">
-        <v>96836</v>
+        <v>96841</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -27379,7 +27379,7 @@
         <v>136778798</v>
       </c>
       <c r="B243" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -27616,7 +27616,7 @@
         <v>136777555</v>
       </c>
       <c r="B245" t="n">
-        <v>96883</v>
+        <v>96888</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -27860,7 +27860,7 @@
         <v>136777551</v>
       </c>
       <c r="B247" t="n">
-        <v>96313</v>
+        <v>96318</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -28085,7 +28085,7 @@
         <v>136777556</v>
       </c>
       <c r="B249" t="n">
-        <v>96740</v>
+        <v>96745</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -28318,7 +28318,7 @@
         <v>136778799</v>
       </c>
       <c r="B251" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29301,7 +29301,7 @@
         <v>136801045</v>
       </c>
       <c r="B260" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -29407,7 +29407,7 @@
         <v>136801064</v>
       </c>
       <c r="B261" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -29513,7 +29513,7 @@
         <v>137143298</v>
       </c>
       <c r="B262" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -29619,7 +29619,7 @@
         <v>137143509</v>
       </c>
       <c r="B263" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -29725,7 +29725,7 @@
         <v>137143542</v>
       </c>
       <c r="B264" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -30968,7 +30968,7 @@
         <v>136823037</v>
       </c>
       <c r="B275" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -31074,7 +31074,7 @@
         <v>136823087</v>
       </c>
       <c r="B276" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -32228,7 +32228,7 @@
         <v>137090662</v>
       </c>
       <c r="B286" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -32334,7 +32334,7 @@
         <v>136947774</v>
       </c>
       <c r="B287" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -33548,7 +33548,7 @@
         <v>137045669</v>
       </c>
       <c r="B297" t="n">
-        <v>98270</v>
+        <v>98275</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>

--- a/artfynd/S 152-2026 artfynd.xlsx
+++ b/artfynd/S 152-2026 artfynd.xlsx
@@ -2663,7 +2663,7 @@
         <v>137045898</v>
       </c>
       <c r="B20" t="n">
-        <v>93477</v>
+        <v>93479</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>136777570</v>
       </c>
       <c r="B23" t="n">
-        <v>96995</v>
+        <v>96997</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>136777559</v>
       </c>
       <c r="B32" t="n">
-        <v>93455</v>
+        <v>93457</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5481,7 +5481,7 @@
         <v>136777560</v>
       </c>
       <c r="B46" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>136777566</v>
       </c>
       <c r="B47" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>136778803</v>
       </c>
       <c r="B48" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
         <v>136778804</v>
       </c>
       <c r="B49" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>136778808</v>
       </c>
       <c r="B50" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6053,7 +6053,7 @@
         <v>136778810</v>
       </c>
       <c r="B51" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         <v>136801360</v>
       </c>
       <c r="B52" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6275,7 +6275,7 @@
         <v>136842788</v>
       </c>
       <c r="B53" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
         <v>136842792</v>
       </c>
       <c r="B54" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>136842794</v>
       </c>
       <c r="B55" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         <v>136801292</v>
       </c>
       <c r="B56" t="n">
-        <v>93473</v>
+        <v>93475</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7913,7 +7913,7 @@
         <v>136924655</v>
       </c>
       <c r="B68" t="n">
-        <v>93487</v>
+        <v>93489</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>136801166</v>
       </c>
       <c r="B72" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>136801323</v>
       </c>
       <c r="B73" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         <v>136801440</v>
       </c>
       <c r="B74" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>136824502</v>
       </c>
       <c r="B75" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
         <v>136824536</v>
       </c>
       <c r="B76" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>136824638</v>
       </c>
       <c r="B77" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>136842793</v>
       </c>
       <c r="B78" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>136924440</v>
       </c>
       <c r="B79" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>137045947</v>
       </c>
       <c r="B80" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>137143672</v>
       </c>
       <c r="B81" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>137144281</v>
       </c>
       <c r="B82" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         <v>137220342</v>
       </c>
       <c r="B83" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9638,7 +9638,7 @@
         <v>136801417</v>
       </c>
       <c r="B84" t="n">
-        <v>92840</v>
+        <v>92842</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -13809,7 +13809,7 @@
         <v>136777571</v>
       </c>
       <c r="B121" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14484,7 +14484,7 @@
         <v>137089136</v>
       </c>
       <c r="B127" t="n">
-        <v>98278</v>
+        <v>98280</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15597,7 +15597,7 @@
         <v>136778812</v>
       </c>
       <c r="B137" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16162,7 +16162,7 @@
         <v>137045897</v>
       </c>
       <c r="B142" t="n">
-        <v>92553</v>
+        <v>92555</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -18591,7 +18591,7 @@
         <v>136330155</v>
       </c>
       <c r="B164" t="n">
-        <v>92183</v>
+        <v>92185</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19134,7 +19134,7 @@
         <v>136778218</v>
       </c>
       <c r="B169" t="n">
-        <v>93487</v>
+        <v>93489</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20105,7 +20105,7 @@
         <v>136778023</v>
       </c>
       <c r="B178" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>136778100</v>
       </c>
       <c r="B179" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20317,7 +20317,7 @@
         <v>136778150</v>
       </c>
       <c r="B180" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20423,7 +20423,7 @@
         <v>136778261</v>
       </c>
       <c r="B181" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20529,7 +20529,7 @@
         <v>136778691</v>
       </c>
       <c r="B182" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20635,7 +20635,7 @@
         <v>136778703</v>
       </c>
       <c r="B183" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20741,7 +20741,7 @@
         <v>136778721</v>
       </c>
       <c r="B184" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20847,7 +20847,7 @@
         <v>136778733</v>
       </c>
       <c r="B185" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20953,7 +20953,7 @@
         <v>136778740</v>
       </c>
       <c r="B186" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21059,7 +21059,7 @@
         <v>137088961</v>
       </c>
       <c r="B187" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         <v>137089019</v>
       </c>
       <c r="B188" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>137090631</v>
       </c>
       <c r="B189" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -21377,7 +21377,7 @@
         <v>137090646</v>
       </c>
       <c r="B190" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -26929,7 +26929,7 @@
         <v>136777554</v>
       </c>
       <c r="B239" t="n">
-        <v>96841</v>
+        <v>96843</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -27379,7 +27379,7 @@
         <v>136778798</v>
       </c>
       <c r="B243" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -27616,7 +27616,7 @@
         <v>136777555</v>
       </c>
       <c r="B245" t="n">
-        <v>96888</v>
+        <v>96890</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -27860,7 +27860,7 @@
         <v>136777551</v>
       </c>
       <c r="B247" t="n">
-        <v>96318</v>
+        <v>96320</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -28085,7 +28085,7 @@
         <v>136777556</v>
       </c>
       <c r="B249" t="n">
-        <v>96745</v>
+        <v>96747</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -28318,7 +28318,7 @@
         <v>136778799</v>
       </c>
       <c r="B251" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29301,7 +29301,7 @@
         <v>136801045</v>
       </c>
       <c r="B260" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -29407,7 +29407,7 @@
         <v>136801064</v>
       </c>
       <c r="B261" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -29513,7 +29513,7 @@
         <v>137143298</v>
       </c>
       <c r="B262" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -29619,7 +29619,7 @@
         <v>137143509</v>
       </c>
       <c r="B263" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -29725,7 +29725,7 @@
         <v>137143542</v>
       </c>
       <c r="B264" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -32228,7 +32228,7 @@
         <v>137090662</v>
       </c>
       <c r="B286" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -33548,7 +33548,7 @@
         <v>137045669</v>
       </c>
       <c r="B297" t="n">
-        <v>98275</v>
+        <v>98277</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>

--- a/artfynd/S 152-2026 artfynd.xlsx
+++ b/artfynd/S 152-2026 artfynd.xlsx
@@ -2324,7 +2324,7 @@
         <v>136924639</v>
       </c>
       <c r="B17" t="n">
-        <v>90893</v>
+        <v>90898</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>137045898</v>
       </c>
       <c r="B20" t="n">
-        <v>93479</v>
+        <v>93485</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         <v>136801360</v>
       </c>
       <c r="B52" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6275,7 +6275,7 @@
         <v>136842788</v>
       </c>
       <c r="B53" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
         <v>136842792</v>
       </c>
       <c r="B54" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>136842794</v>
       </c>
       <c r="B55" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         <v>136801292</v>
       </c>
       <c r="B56" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7913,7 +7913,7 @@
         <v>136924655</v>
       </c>
       <c r="B68" t="n">
-        <v>93489</v>
+        <v>93495</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>136801166</v>
       </c>
       <c r="B72" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>136801323</v>
       </c>
       <c r="B73" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         <v>136801440</v>
       </c>
       <c r="B74" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>136824502</v>
       </c>
       <c r="B75" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
         <v>136824536</v>
       </c>
       <c r="B76" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>136824638</v>
       </c>
       <c r="B77" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>136842793</v>
       </c>
       <c r="B78" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>136924440</v>
       </c>
       <c r="B79" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>137045947</v>
       </c>
       <c r="B80" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>137143672</v>
       </c>
       <c r="B81" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>137144281</v>
       </c>
       <c r="B82" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         <v>137220342</v>
       </c>
       <c r="B83" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9638,7 +9638,7 @@
         <v>136801417</v>
       </c>
       <c r="B84" t="n">
-        <v>92842</v>
+        <v>92847</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10095,7 +10095,7 @@
         <v>137106176</v>
       </c>
       <c r="B88" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10205,7 +10205,7 @@
         <v>137143649</v>
       </c>
       <c r="B89" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11896,7 +11896,7 @@
         <v>136824136</v>
       </c>
       <c r="B104" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12002,7 +12002,7 @@
         <v>136824277</v>
       </c>
       <c r="B105" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12108,7 +12108,7 @@
         <v>136824305</v>
       </c>
       <c r="B106" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -14484,7 +14484,7 @@
         <v>137089136</v>
       </c>
       <c r="B127" t="n">
-        <v>98280</v>
+        <v>98286</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -16162,7 +16162,7 @@
         <v>137045897</v>
       </c>
       <c r="B142" t="n">
-        <v>92555</v>
+        <v>92560</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -18591,7 +18591,7 @@
         <v>136330155</v>
       </c>
       <c r="B164" t="n">
-        <v>92185</v>
+        <v>92190</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -21059,7 +21059,7 @@
         <v>137088961</v>
       </c>
       <c r="B187" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         <v>137089019</v>
       </c>
       <c r="B188" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>137090631</v>
       </c>
       <c r="B189" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -21377,7 +21377,7 @@
         <v>137090646</v>
       </c>
       <c r="B190" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -24342,7 +24342,7 @@
         <v>136947615</v>
       </c>
       <c r="B216" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -29301,7 +29301,7 @@
         <v>136801045</v>
       </c>
       <c r="B260" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -29407,7 +29407,7 @@
         <v>136801064</v>
       </c>
       <c r="B261" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -29513,7 +29513,7 @@
         <v>137143298</v>
       </c>
       <c r="B262" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -29619,7 +29619,7 @@
         <v>137143509</v>
       </c>
       <c r="B263" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -29725,7 +29725,7 @@
         <v>137143542</v>
       </c>
       <c r="B264" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -30968,7 +30968,7 @@
         <v>136823037</v>
       </c>
       <c r="B275" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -31074,7 +31074,7 @@
         <v>136823087</v>
       </c>
       <c r="B276" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -32228,7 +32228,7 @@
         <v>137090662</v>
       </c>
       <c r="B286" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -33548,7 +33548,7 @@
         <v>137045669</v>
       </c>
       <c r="B297" t="n">
-        <v>98277</v>
+        <v>98283</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>

--- a/artfynd/S 152-2026 artfynd.xlsx
+++ b/artfynd/S 152-2026 artfynd.xlsx
@@ -2324,7 +2324,7 @@
         <v>136924639</v>
       </c>
       <c r="B17" t="n">
-        <v>90898</v>
+        <v>90909</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>137045898</v>
       </c>
       <c r="B20" t="n">
-        <v>93485</v>
+        <v>93497</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -6275,7 +6275,7 @@
         <v>136842788</v>
       </c>
       <c r="B53" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
         <v>136842792</v>
       </c>
       <c r="B54" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>136842794</v>
       </c>
       <c r="B55" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7913,7 +7913,7 @@
         <v>136924655</v>
       </c>
       <c r="B68" t="n">
-        <v>93495</v>
+        <v>93507</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>136842793</v>
       </c>
       <c r="B78" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>136924440</v>
       </c>
       <c r="B79" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>137045947</v>
       </c>
       <c r="B80" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>137143672</v>
       </c>
       <c r="B81" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>137144281</v>
       </c>
       <c r="B82" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         <v>137220342</v>
       </c>
       <c r="B83" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -14484,7 +14484,7 @@
         <v>137089136</v>
       </c>
       <c r="B127" t="n">
-        <v>98286</v>
+        <v>98298</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -16162,7 +16162,7 @@
         <v>137045897</v>
       </c>
       <c r="B142" t="n">
-        <v>92560</v>
+        <v>92572</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16268,7 +16268,7 @@
         <v>128952262</v>
       </c>
       <c r="B143" t="n">
-        <v>93490</v>
+        <v>93502</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -18697,7 +18697,7 @@
         <v>136330155</v>
       </c>
       <c r="B165" t="n">
-        <v>92190</v>
+        <v>92202</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         <v>137088961</v>
       </c>
       <c r="B188" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>137089019</v>
       </c>
       <c r="B189" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -21377,7 +21377,7 @@
         <v>137090631</v>
       </c>
       <c r="B190" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -21483,7 +21483,7 @@
         <v>137090646</v>
       </c>
       <c r="B191" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -29619,7 +29619,7 @@
         <v>137143298</v>
       </c>
       <c r="B263" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -29725,7 +29725,7 @@
         <v>137143509</v>
       </c>
       <c r="B264" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -29831,7 +29831,7 @@
         <v>137143542</v>
       </c>
       <c r="B265" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -32334,7 +32334,7 @@
         <v>137090662</v>
       </c>
       <c r="B287" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -33654,7 +33654,7 @@
         <v>137045669</v>
       </c>
       <c r="B298" t="n">
-        <v>98283</v>
+        <v>98295</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>

--- a/artfynd/S 152-2026 artfynd.xlsx
+++ b/artfynd/S 152-2026 artfynd.xlsx
@@ -2324,7 +2324,7 @@
         <v>136924639</v>
       </c>
       <c r="B17" t="n">
-        <v>90909</v>
+        <v>90910</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>137045898</v>
       </c>
       <c r="B20" t="n">
-        <v>93497</v>
+        <v>93498</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -7913,7 +7913,7 @@
         <v>136924655</v>
       </c>
       <c r="B68" t="n">
-        <v>93507</v>
+        <v>93508</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>136924440</v>
       </c>
       <c r="B79" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>137045947</v>
       </c>
       <c r="B80" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>137143672</v>
       </c>
       <c r="B81" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>137144281</v>
       </c>
       <c r="B82" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         <v>137220342</v>
       </c>
       <c r="B83" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -14484,7 +14484,7 @@
         <v>137089136</v>
       </c>
       <c r="B127" t="n">
-        <v>98298</v>
+        <v>98299</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -16162,7 +16162,7 @@
         <v>137045897</v>
       </c>
       <c r="B142" t="n">
-        <v>92572</v>
+        <v>92573</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16268,7 +16268,7 @@
         <v>128952262</v>
       </c>
       <c r="B143" t="n">
-        <v>93502</v>
+        <v>93503</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         <v>137088961</v>
       </c>
       <c r="B188" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>137089019</v>
       </c>
       <c r="B189" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -21377,7 +21377,7 @@
         <v>137090631</v>
       </c>
       <c r="B190" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -21483,7 +21483,7 @@
         <v>137090646</v>
       </c>
       <c r="B191" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -29619,7 +29619,7 @@
         <v>137143298</v>
       </c>
       <c r="B263" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -29725,7 +29725,7 @@
         <v>137143509</v>
       </c>
       <c r="B264" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -29831,7 +29831,7 @@
         <v>137143542</v>
       </c>
       <c r="B265" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -32334,7 +32334,7 @@
         <v>137090662</v>
       </c>
       <c r="B287" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -33654,7 +33654,7 @@
         <v>137045669</v>
       </c>
       <c r="B298" t="n">
-        <v>98295</v>
+        <v>98296</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>

--- a/artfynd/S 152-2026 artfynd.xlsx
+++ b/artfynd/S 152-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ298"/>
+  <dimension ref="A1:AZ303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2324,7 +2324,7 @@
         <v>136924639</v>
       </c>
       <c r="B17" t="n">
-        <v>90910</v>
+        <v>90913</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>137045898</v>
       </c>
       <c r="B20" t="n">
-        <v>93498</v>
+        <v>93501</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -7913,7 +7913,7 @@
         <v>136924655</v>
       </c>
       <c r="B68" t="n">
-        <v>93508</v>
+        <v>93511</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>136924440</v>
       </c>
       <c r="B79" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>137045947</v>
       </c>
       <c r="B80" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>137143672</v>
       </c>
       <c r="B81" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>137144281</v>
       </c>
       <c r="B82" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         <v>137220342</v>
       </c>
       <c r="B83" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -14484,7 +14484,7 @@
         <v>137089136</v>
       </c>
       <c r="B127" t="n">
-        <v>98299</v>
+        <v>98302</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -16162,7 +16162,7 @@
         <v>137045897</v>
       </c>
       <c r="B142" t="n">
-        <v>92573</v>
+        <v>92576</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16268,7 +16268,7 @@
         <v>128952262</v>
       </c>
       <c r="B143" t="n">
-        <v>93503</v>
+        <v>93506</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         <v>137088961</v>
       </c>
       <c r="B188" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>137089019</v>
       </c>
       <c r="B189" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -21377,7 +21377,7 @@
         <v>137090631</v>
       </c>
       <c r="B190" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -21483,7 +21483,7 @@
         <v>137090646</v>
       </c>
       <c r="B191" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -29619,7 +29619,7 @@
         <v>137143298</v>
       </c>
       <c r="B263" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -29725,7 +29725,7 @@
         <v>137143509</v>
       </c>
       <c r="B264" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -29831,7 +29831,7 @@
         <v>137143542</v>
       </c>
       <c r="B265" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -32220,48 +32220,53 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>119061006</v>
+        <v>137477223</v>
       </c>
       <c r="B286" t="n">
-        <v>91533</v>
+        <v>96865</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E286" t="n">
-        <v>2051</v>
+        <v>210</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I286" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J286" t="inlineStr"/>
       <c r="K286" t="inlineStr"/>
+      <c r="L286" t="inlineStr"/>
       <c r="N286" t="inlineStr"/>
       <c r="P286" t="inlineStr">
         <is>
-          <t>S Norrby mosse, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>686477</v>
+        <v>686323</v>
       </c>
       <c r="R286" t="n">
-        <v>6562857</v>
+        <v>6562942</v>
       </c>
       <c r="S286" t="n">
         <v>10</v>
@@ -32288,17 +32293,17 @@
       </c>
       <c r="Y286" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="AA286" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="AC286" t="inlineStr">
         <is>
-          <t>Brukad skog nära kant mot gammal.</t>
+          <t>Två uppspruckna samt fyra nya kapslar.</t>
         </is>
       </c>
       <c r="AD286" t="b">
@@ -32325,43 +32330,48 @@
       <c r="AY286" t="inlineStr"/>
       <c r="AZ286" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119061006</t>
+          <t>https://artportalen.se/Sighting/137477223</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>137090662</v>
+        <v>137478093</v>
       </c>
       <c r="B287" t="n">
-        <v>93520</v>
+        <v>96865</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E287" t="n">
-        <v>5966</v>
+        <v>210</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I287" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J287" t="inlineStr"/>
       <c r="K287" t="inlineStr"/>
+      <c r="L287" t="inlineStr"/>
       <c r="N287" t="inlineStr"/>
       <c r="P287" t="inlineStr">
         <is>
@@ -32369,10 +32379,10 @@
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>686314</v>
+        <v>686351</v>
       </c>
       <c r="R287" t="n">
-        <v>6562873</v>
+        <v>6562954</v>
       </c>
       <c r="S287" t="n">
         <v>10</v>
@@ -32399,12 +32409,17 @@
       </c>
       <c r="Y287" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="AA287" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="AC287" t="inlineStr">
+        <is>
+          <t>Nya kapslar på tallåga. Tidigare röjt och nyligen gallrat intill. (Rätt nära diket, antingen visade koordinaterna fel trots dubbel test eller så är diket inte rätt utritat.)</t>
         </is>
       </c>
       <c r="AD287" t="b">
@@ -32431,16 +32446,16 @@
       <c r="AY287" t="inlineStr"/>
       <c r="AZ287" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137090662</t>
+          <t>https://artportalen.se/Sighting/137478093</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>136947774</v>
+        <v>137478534</v>
       </c>
       <c r="B288" t="n">
-        <v>57221</v>
+        <v>96865</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -32448,31 +32463,31 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>100138</v>
+        <v>210</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr"/>
       <c r="K288" t="inlineStr"/>
       <c r="L288" t="inlineStr"/>
-      <c r="M288" t="inlineStr"/>
       <c r="N288" t="inlineStr"/>
       <c r="P288" t="inlineStr">
         <is>
@@ -32480,10 +32495,10 @@
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>686354</v>
+        <v>686608</v>
       </c>
       <c r="R288" t="n">
-        <v>6562881</v>
+        <v>6562885</v>
       </c>
       <c r="S288" t="n">
         <v>10</v>
@@ -32510,17 +32525,17 @@
       </c>
       <c r="Y288" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="AA288" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="AC288" t="inlineStr">
         <is>
-          <t>Ruggad stjärtpenna, 33.5 cm.</t>
+          <t>Nya kapslar.</t>
         </is>
       </c>
       <c r="AD288" t="b">
@@ -32529,6 +32544,7 @@
       <c r="AE288" t="b">
         <v>0</v>
       </c>
+      <c r="AF288" t="inlineStr"/>
       <c r="AG288" t="b">
         <v>0</v>
       </c>
@@ -32546,16 +32562,16 @@
       <c r="AY288" t="inlineStr"/>
       <c r="AZ288" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136947774</t>
+          <t>https://artportalen.se/Sighting/137478534</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>122929535</v>
+        <v>137478552</v>
       </c>
       <c r="B289" t="n">
-        <v>8455</v>
+        <v>96865</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -32563,46 +32579,45 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>106545</v>
+        <v>210</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J289" t="inlineStr"/>
       <c r="K289" t="inlineStr"/>
       <c r="L289" t="inlineStr"/>
-      <c r="M289" t="inlineStr"/>
       <c r="N289" t="inlineStr"/>
       <c r="P289" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>686612</v>
+        <v>686632</v>
       </c>
       <c r="R289" t="n">
-        <v>6562882</v>
+        <v>6562869</v>
       </c>
       <c r="S289" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T289" t="inlineStr">
         <is>
@@ -32626,22 +32641,17 @@
       </c>
       <c r="Y289" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="Z289" t="inlineStr">
-        <is>
-          <t>11:01</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="AA289" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="AB289" t="inlineStr">
-        <is>
-          <t>11:01</t>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="AC289" t="inlineStr">
+        <is>
+          <t>Nya kapslar.</t>
         </is>
       </c>
       <c r="AD289" t="b">
@@ -32650,72 +32660,72 @@
       <c r="AE289" t="b">
         <v>0</v>
       </c>
+      <c r="AF289" t="inlineStr"/>
       <c r="AG289" t="b">
         <v>0</v>
       </c>
       <c r="AT289" t="inlineStr"/>
       <c r="AW289" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX289" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY289" t="inlineStr"/>
       <c r="AZ289" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122929535</t>
+          <t>https://artportalen.se/Sighting/137478552</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>122928987</v>
+        <v>119061006</v>
       </c>
       <c r="B290" t="n">
-        <v>97983</v>
+        <v>91533</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E290" t="n">
-        <v>221945</v>
+        <v>2051</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I290" t="inlineStr"/>
       <c r="J290" t="inlineStr"/>
       <c r="K290" t="inlineStr"/>
-      <c r="L290" t="inlineStr"/>
       <c r="N290" t="inlineStr"/>
       <c r="P290" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>S Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q290" t="n">
-        <v>686389</v>
+        <v>686477</v>
       </c>
       <c r="R290" t="n">
-        <v>6562967</v>
+        <v>6562857</v>
       </c>
       <c r="S290" t="n">
         <v>10</v>
@@ -32742,22 +32752,17 @@
       </c>
       <c r="Y290" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="Z290" t="inlineStr">
-        <is>
-          <t>10:36</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA290" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="AB290" t="inlineStr">
-        <is>
-          <t>10:36</t>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC290" t="inlineStr">
+        <is>
+          <t>Brukad skog nära kant mot gammal.</t>
         </is>
       </c>
       <c r="AD290" t="b">
@@ -32766,33 +32771,34 @@
       <c r="AE290" t="b">
         <v>0</v>
       </c>
+      <c r="AF290" t="inlineStr"/>
       <c r="AG290" t="b">
         <v>0</v>
       </c>
       <c r="AT290" t="inlineStr"/>
       <c r="AW290" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX290" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY290" t="inlineStr"/>
       <c r="AZ290" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122928987</t>
+          <t>https://artportalen.se/Sighting/119061006</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>126061106</v>
+        <v>137090662</v>
       </c>
       <c r="B291" t="n">
-        <v>91333</v>
+        <v>93523</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -32800,34 +32806,37 @@
         </is>
       </c>
       <c r="E291" t="n">
-        <v>2008</v>
+        <v>5966</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>Pers., nom.sanct.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I291" t="inlineStr"/>
+      <c r="J291" t="inlineStr"/>
+      <c r="K291" t="inlineStr"/>
+      <c r="N291" t="inlineStr"/>
       <c r="P291" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q291" t="n">
-        <v>686883</v>
+        <v>686314</v>
       </c>
       <c r="R291" t="n">
-        <v>6562742</v>
+        <v>6562873</v>
       </c>
       <c r="S291" t="n">
         <v>10</v>
@@ -32854,22 +32863,12 @@
       </c>
       <c r="Y291" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z291" t="inlineStr">
-        <is>
-          <t>13:23</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="AA291" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB291" t="inlineStr">
-        <is>
-          <t>13:23</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="AD291" t="b">
@@ -32878,33 +32877,34 @@
       <c r="AE291" t="b">
         <v>0</v>
       </c>
+      <c r="AF291" t="inlineStr"/>
       <c r="AG291" t="b">
         <v>0</v>
       </c>
       <c r="AT291" t="inlineStr"/>
       <c r="AW291" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX291" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY291" t="inlineStr"/>
       <c r="AZ291" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061106</t>
+          <t>https://artportalen.se/Sighting/137090662</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>126061107</v>
+        <v>136947774</v>
       </c>
       <c r="B292" t="n">
-        <v>96458</v>
+        <v>57221</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -32912,34 +32912,42 @@
         </is>
       </c>
       <c r="E292" t="n">
-        <v>2818</v>
+        <v>100138</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I292" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr"/>
+      <c r="L292" t="inlineStr"/>
+      <c r="M292" t="inlineStr"/>
+      <c r="N292" t="inlineStr"/>
       <c r="P292" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q292" t="n">
-        <v>686880</v>
+        <v>686354</v>
       </c>
       <c r="R292" t="n">
-        <v>6562745</v>
+        <v>6562881</v>
       </c>
       <c r="S292" t="n">
         <v>10</v>
@@ -32966,22 +32974,17 @@
       </c>
       <c r="Y292" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z292" t="inlineStr">
-        <is>
-          <t>13:19</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AA292" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB292" t="inlineStr">
-        <is>
-          <t>13:19</t>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AC292" t="inlineStr">
+        <is>
+          <t>Ruggad stjärtpenna, 33.5 cm.</t>
         </is>
       </c>
       <c r="AD292" t="b">
@@ -32996,54 +32999,55 @@
       <c r="AT292" t="inlineStr"/>
       <c r="AW292" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX292" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY292" t="inlineStr"/>
       <c r="AZ292" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061107</t>
+          <t>https://artportalen.se/Sighting/136947774</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>129215187</v>
+        <v>137478542</v>
       </c>
       <c r="B293" t="n">
-        <v>91872</v>
+        <v>58196</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E293" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I293" t="inlineStr"/>
-      <c r="J293" t="inlineStr"/>
       <c r="K293" t="inlineStr"/>
+      <c r="L293" t="inlineStr"/>
+      <c r="M293" t="inlineStr"/>
       <c r="N293" t="inlineStr"/>
       <c r="P293" t="inlineStr">
         <is>
@@ -33051,10 +33055,10 @@
         </is>
       </c>
       <c r="Q293" t="n">
-        <v>686977</v>
+        <v>686626</v>
       </c>
       <c r="R293" t="n">
-        <v>6562706</v>
+        <v>6562878</v>
       </c>
       <c r="S293" t="n">
         <v>10</v>
@@ -33081,12 +33085,12 @@
       </c>
       <c r="Y293" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="AA293" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="AD293" t="b">
@@ -33095,7 +33099,6 @@
       <c r="AE293" t="b">
         <v>0</v>
       </c>
-      <c r="AF293" t="inlineStr"/>
       <c r="AG293" t="b">
         <v>0</v>
       </c>
@@ -33113,16 +33116,16 @@
       <c r="AY293" t="inlineStr"/>
       <c r="AZ293" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215187</t>
+          <t>https://artportalen.se/Sighting/137478542</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>126061104</v>
+        <v>122929535</v>
       </c>
       <c r="B294" t="n">
-        <v>4775</v>
+        <v>8455</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -33130,37 +33133,46 @@
         </is>
       </c>
       <c r="E294" t="n">
-        <v>100299</v>
+        <v>106545</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I294" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr"/>
+      <c r="K294" t="inlineStr"/>
+      <c r="L294" t="inlineStr"/>
+      <c r="M294" t="inlineStr"/>
+      <c r="N294" t="inlineStr"/>
       <c r="P294" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q294" t="n">
-        <v>686868</v>
+        <v>686612</v>
       </c>
       <c r="R294" t="n">
-        <v>6562739</v>
+        <v>6562882</v>
       </c>
       <c r="S294" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T294" t="inlineStr">
         <is>
@@ -33184,22 +33196,22 @@
       </c>
       <c r="Y294" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="Z294" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA294" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="AB294" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD294" t="b">
@@ -33210,51 +33222,31 @@
       </c>
       <c r="AG294" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ294" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK294" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL294" t="inlineStr">
-        <is>
-          <t>Stående död gran.</t>
-        </is>
-      </c>
-      <c r="AO294" t="inlineStr">
-        <is>
-          <t>Picea abies # Stående död gran.</t>
-        </is>
       </c>
       <c r="AT294" t="inlineStr"/>
       <c r="AW294" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX294" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY294" t="inlineStr"/>
       <c r="AZ294" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061104</t>
+          <t>https://artportalen.se/Sighting/122929535</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>126061116</v>
+        <v>122928987</v>
       </c>
       <c r="B295" t="n">
-        <v>44177</v>
+        <v>97983</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -33262,34 +33254,38 @@
         </is>
       </c>
       <c r="E295" t="n">
-        <v>101735</v>
+        <v>221945</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I295" t="inlineStr"/>
+      <c r="J295" t="inlineStr"/>
+      <c r="K295" t="inlineStr"/>
+      <c r="L295" t="inlineStr"/>
+      <c r="N295" t="inlineStr"/>
       <c r="P295" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q295" t="n">
-        <v>686928</v>
+        <v>686389</v>
       </c>
       <c r="R295" t="n">
-        <v>6562716</v>
+        <v>6562967</v>
       </c>
       <c r="S295" t="n">
         <v>10</v>
@@ -33316,22 +33312,22 @@
       </c>
       <c r="Y295" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="Z295" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA295" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="AB295" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD295" t="b">
@@ -33342,102 +33338,69 @@
       </c>
       <c r="AG295" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ295" t="inlineStr">
-        <is>
-          <t>fnöskticka</t>
-        </is>
-      </c>
-      <c r="AK295" t="inlineStr">
-        <is>
-          <t>Fomes fomentarius</t>
-        </is>
-      </c>
-      <c r="AL295" t="inlineStr">
-        <is>
-          <t>Fnöskticka på björk.</t>
-        </is>
-      </c>
-      <c r="AO295" t="inlineStr">
-        <is>
-          <t>Fomes fomentarius # Fnöskticka på björk.</t>
-        </is>
       </c>
       <c r="AT295" t="inlineStr"/>
       <c r="AW295" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX295" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY295" t="inlineStr"/>
       <c r="AZ295" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061116</t>
+          <t>https://artportalen.se/Sighting/122928987</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>125974903</v>
+        <v>126061106</v>
       </c>
       <c r="B296" t="n">
-        <v>8444</v>
+        <v>91333</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E296" t="n">
-        <v>106554</v>
+        <v>2008</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I296" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J296" t="inlineStr"/>
-      <c r="K296" t="inlineStr"/>
-      <c r="L296" t="inlineStr"/>
-      <c r="M296" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N296" t="inlineStr"/>
+          <t>Pers., nom.sanct.</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr"/>
       <c r="P296" t="inlineStr">
         <is>
-          <t>söder om Tyresta, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q296" t="n">
-        <v>686838</v>
+        <v>686883</v>
       </c>
       <c r="R296" t="n">
-        <v>6562733</v>
+        <v>6562742</v>
       </c>
       <c r="S296" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T296" t="inlineStr">
         <is>
@@ -33464,14 +33427,19 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="Z296" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AA296" t="inlineStr">
         <is>
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC296" t="inlineStr">
-        <is>
-          <t>gammal björklåga med spår längs hela stammen</t>
+      <c r="AB296" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD296" t="b">
@@ -33480,54 +33448,33 @@
       <c r="AE296" t="b">
         <v>0</v>
       </c>
-      <c r="AF296" t="inlineStr"/>
       <c r="AG296" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ296" t="inlineStr">
-        <is>
-          <t>vårtbjörk</t>
-        </is>
-      </c>
-      <c r="AK296" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
-      <c r="AM296" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO296" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Betula pendula</t>
-        </is>
       </c>
       <c r="AT296" t="inlineStr"/>
       <c r="AW296" t="inlineStr">
         <is>
-          <t>Nette Bygren</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX296" t="inlineStr">
         <is>
-          <t>Nette Bygren</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY296" t="inlineStr"/>
       <c r="AZ296" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125974903</t>
+          <t>https://artportalen.se/Sighting/126061106</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>126061105</v>
+        <v>126061107</v>
       </c>
       <c r="B297" t="n">
-        <v>8444</v>
+        <v>96458</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -33535,21 +33482,21 @@
         </is>
       </c>
       <c r="E297" t="n">
-        <v>106554</v>
+        <v>2818</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I297" t="inlineStr"/>
@@ -33559,10 +33506,10 @@
         </is>
       </c>
       <c r="Q297" t="n">
-        <v>686860</v>
+        <v>686880</v>
       </c>
       <c r="R297" t="n">
-        <v>6562743</v>
+        <v>6562745</v>
       </c>
       <c r="S297" t="n">
         <v>10</v>
@@ -33594,7 +33541,7 @@
       </c>
       <c r="Z297" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA297" t="inlineStr">
@@ -33604,7 +33551,7 @@
       </c>
       <c r="AB297" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD297" t="b">
@@ -33615,21 +33562,6 @@
       </c>
       <c r="AG297" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ297" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK297" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO297" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT297" t="inlineStr"/>
       <c r="AW297" t="inlineStr">
@@ -33645,16 +33577,16 @@
       <c r="AY297" t="inlineStr"/>
       <c r="AZ297" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061105</t>
+          <t>https://artportalen.se/Sighting/126061107</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>137045669</v>
+        <v>129215187</v>
       </c>
       <c r="B298" t="n">
-        <v>98296</v>
+        <v>91872</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -33662,27 +33594,26 @@
         </is>
       </c>
       <c r="E298" t="n">
-        <v>221946</v>
+        <v>5447</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I298" t="inlineStr"/>
       <c r="J298" t="inlineStr"/>
       <c r="K298" t="inlineStr"/>
-      <c r="L298" t="inlineStr"/>
       <c r="N298" t="inlineStr"/>
       <c r="P298" t="inlineStr">
         <is>
@@ -33690,10 +33621,10 @@
         </is>
       </c>
       <c r="Q298" t="n">
-        <v>686837</v>
+        <v>686977</v>
       </c>
       <c r="R298" t="n">
-        <v>6562677</v>
+        <v>6562706</v>
       </c>
       <c r="S298" t="n">
         <v>10</v>
@@ -33720,12 +33651,12 @@
       </c>
       <c r="Y298" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AA298" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AD298" t="b">
@@ -33751,6 +33682,645 @@
       </c>
       <c r="AY298" t="inlineStr"/>
       <c r="AZ298" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215187</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>126061104</v>
+      </c>
+      <c r="B299" t="n">
+        <v>4775</v>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E299" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr"/>
+      <c r="P299" t="inlineStr">
+        <is>
+          <t>Ö Tyresta by, Srm</t>
+        </is>
+      </c>
+      <c r="Q299" t="n">
+        <v>686868</v>
+      </c>
+      <c r="R299" t="n">
+        <v>6562739</v>
+      </c>
+      <c r="S299" t="n">
+        <v>10</v>
+      </c>
+      <c r="T299" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U299" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V299" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W299" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y299" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z299" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AA299" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB299" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AD299" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE299" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG299" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ299" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK299" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL299" t="inlineStr">
+        <is>
+          <t>Stående död gran.</t>
+        </is>
+      </c>
+      <c r="AO299" t="inlineStr">
+        <is>
+          <t>Picea abies # Stående död gran.</t>
+        </is>
+      </c>
+      <c r="AT299" t="inlineStr"/>
+      <c r="AW299" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX299" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AY299" t="inlineStr"/>
+      <c r="AZ299" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061104</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>126061116</v>
+      </c>
+      <c r="B300" t="n">
+        <v>44177</v>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E300" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr"/>
+      <c r="P300" t="inlineStr">
+        <is>
+          <t>Ö Tyresta by, Srm</t>
+        </is>
+      </c>
+      <c r="Q300" t="n">
+        <v>686928</v>
+      </c>
+      <c r="R300" t="n">
+        <v>6562716</v>
+      </c>
+      <c r="S300" t="n">
+        <v>10</v>
+      </c>
+      <c r="T300" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U300" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V300" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W300" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y300" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z300" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA300" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB300" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AD300" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE300" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG300" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ300" t="inlineStr">
+        <is>
+          <t>fnöskticka</t>
+        </is>
+      </c>
+      <c r="AK300" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
+      </c>
+      <c r="AL300" t="inlineStr">
+        <is>
+          <t>Fnöskticka på björk.</t>
+        </is>
+      </c>
+      <c r="AO300" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius # Fnöskticka på björk.</t>
+        </is>
+      </c>
+      <c r="AT300" t="inlineStr"/>
+      <c r="AW300" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX300" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AY300" t="inlineStr"/>
+      <c r="AZ300" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061116</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>125974903</v>
+      </c>
+      <c r="B301" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E301" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr"/>
+      <c r="K301" t="inlineStr"/>
+      <c r="L301" t="inlineStr"/>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N301" t="inlineStr"/>
+      <c r="P301" t="inlineStr">
+        <is>
+          <t>söder om Tyresta, Srm</t>
+        </is>
+      </c>
+      <c r="Q301" t="n">
+        <v>686838</v>
+      </c>
+      <c r="R301" t="n">
+        <v>6562733</v>
+      </c>
+      <c r="S301" t="n">
+        <v>5</v>
+      </c>
+      <c r="T301" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U301" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V301" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W301" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y301" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA301" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC301" t="inlineStr">
+        <is>
+          <t>gammal björklåga med spår längs hela stammen</t>
+        </is>
+      </c>
+      <c r="AD301" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE301" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF301" t="inlineStr"/>
+      <c r="AG301" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ301" t="inlineStr">
+        <is>
+          <t>vårtbjörk</t>
+        </is>
+      </c>
+      <c r="AK301" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AM301" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO301" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Betula pendula</t>
+        </is>
+      </c>
+      <c r="AT301" t="inlineStr"/>
+      <c r="AW301" t="inlineStr">
+        <is>
+          <t>Nette Bygren</t>
+        </is>
+      </c>
+      <c r="AX301" t="inlineStr">
+        <is>
+          <t>Nette Bygren</t>
+        </is>
+      </c>
+      <c r="AY301" t="inlineStr"/>
+      <c r="AZ301" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125974903</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>126061105</v>
+      </c>
+      <c r="B302" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E302" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr"/>
+      <c r="P302" t="inlineStr">
+        <is>
+          <t>Ö Tyresta by, Srm</t>
+        </is>
+      </c>
+      <c r="Q302" t="n">
+        <v>686860</v>
+      </c>
+      <c r="R302" t="n">
+        <v>6562743</v>
+      </c>
+      <c r="S302" t="n">
+        <v>10</v>
+      </c>
+      <c r="T302" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U302" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V302" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W302" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y302" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z302" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA302" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB302" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AD302" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE302" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG302" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ302" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK302" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO302" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AT302" t="inlineStr"/>
+      <c r="AW302" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX302" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AY302" t="inlineStr"/>
+      <c r="AZ302" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061105</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>137045669</v>
+      </c>
+      <c r="B303" t="n">
+        <v>98299</v>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E303" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr"/>
+      <c r="J303" t="inlineStr"/>
+      <c r="K303" t="inlineStr"/>
+      <c r="L303" t="inlineStr"/>
+      <c r="N303" t="inlineStr"/>
+      <c r="P303" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q303" t="n">
+        <v>686837</v>
+      </c>
+      <c r="R303" t="n">
+        <v>6562677</v>
+      </c>
+      <c r="S303" t="n">
+        <v>10</v>
+      </c>
+      <c r="T303" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U303" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V303" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W303" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y303" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AA303" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AD303" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE303" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF303" t="inlineStr"/>
+      <c r="AG303" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT303" t="inlineStr"/>
+      <c r="AW303" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX303" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY303" t="inlineStr"/>
+      <c r="AZ303" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137045669</t>
         </is>
@@ -34055,6 +34625,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ296" r:id="rId295"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ297" r:id="rId296"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ298" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ299" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ300" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ301" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ302" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ303" r:id="rId302"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 152-2026 artfynd.xlsx
+++ b/artfynd/S 152-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ303"/>
+  <dimension ref="A1:AZ304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32452,7 +32452,7 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>137478534</v>
+        <v>137478379</v>
       </c>
       <c r="B288" t="n">
         <v>96865</v>
@@ -32482,7 +32482,7 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J288" t="inlineStr"/>
@@ -32495,10 +32495,10 @@
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>686608</v>
+        <v>686508</v>
       </c>
       <c r="R288" t="n">
-        <v>6562885</v>
+        <v>6562904</v>
       </c>
       <c r="S288" t="n">
         <v>10</v>
@@ -32535,7 +32535,7 @@
       </c>
       <c r="AC288" t="inlineStr">
         <is>
-          <t>Nya kapslar.</t>
+          <t>Två uppspruckna kapslar.</t>
         </is>
       </c>
       <c r="AD288" t="b">
@@ -32562,13 +32562,13 @@
       <c r="AY288" t="inlineStr"/>
       <c r="AZ288" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137478534</t>
+          <t>https://artportalen.se/Sighting/137478379</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>137478552</v>
+        <v>137478534</v>
       </c>
       <c r="B289" t="n">
         <v>96865</v>
@@ -32598,7 +32598,7 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J289" t="inlineStr"/>
@@ -32611,10 +32611,10 @@
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>686632</v>
+        <v>686608</v>
       </c>
       <c r="R289" t="n">
-        <v>6562869</v>
+        <v>6562885</v>
       </c>
       <c r="S289" t="n">
         <v>10</v>
@@ -32678,54 +32678,59 @@
       <c r="AY289" t="inlineStr"/>
       <c r="AZ289" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137478552</t>
+          <t>https://artportalen.se/Sighting/137478534</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>119061006</v>
+        <v>137478552</v>
       </c>
       <c r="B290" t="n">
-        <v>91533</v>
+        <v>96865</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E290" t="n">
-        <v>2051</v>
+        <v>210</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I290" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J290" t="inlineStr"/>
       <c r="K290" t="inlineStr"/>
+      <c r="L290" t="inlineStr"/>
       <c r="N290" t="inlineStr"/>
       <c r="P290" t="inlineStr">
         <is>
-          <t>S Norrby mosse, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q290" t="n">
-        <v>686477</v>
+        <v>686632</v>
       </c>
       <c r="R290" t="n">
-        <v>6562857</v>
+        <v>6562869</v>
       </c>
       <c r="S290" t="n">
         <v>10</v>
@@ -32752,17 +32757,17 @@
       </c>
       <c r="Y290" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="AA290" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="AC290" t="inlineStr">
         <is>
-          <t>Brukad skog nära kant mot gammal.</t>
+          <t>Nya kapslar.</t>
         </is>
       </c>
       <c r="AD290" t="b">
@@ -32789,38 +32794,38 @@
       <c r="AY290" t="inlineStr"/>
       <c r="AZ290" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119061006</t>
+          <t>https://artportalen.se/Sighting/137478552</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>137090662</v>
+        <v>119061006</v>
       </c>
       <c r="B291" t="n">
-        <v>93523</v>
+        <v>91533</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E291" t="n">
-        <v>5966</v>
+        <v>2051</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I291" t="inlineStr"/>
@@ -32829,14 +32834,14 @@
       <c r="N291" t="inlineStr"/>
       <c r="P291" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>S Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q291" t="n">
-        <v>686314</v>
+        <v>686477</v>
       </c>
       <c r="R291" t="n">
-        <v>6562873</v>
+        <v>6562857</v>
       </c>
       <c r="S291" t="n">
         <v>10</v>
@@ -32863,12 +32868,17 @@
       </c>
       <c r="Y291" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA291" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC291" t="inlineStr">
+        <is>
+          <t>Brukad skog nära kant mot gammal.</t>
         </is>
       </c>
       <c r="AD291" t="b">
@@ -32895,48 +32905,43 @@
       <c r="AY291" t="inlineStr"/>
       <c r="AZ291" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137090662</t>
+          <t>https://artportalen.se/Sighting/119061006</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>136947774</v>
+        <v>137090662</v>
       </c>
       <c r="B292" t="n">
-        <v>57221</v>
+        <v>93523</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E292" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I292" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr"/>
+      <c r="J292" t="inlineStr"/>
       <c r="K292" t="inlineStr"/>
-      <c r="L292" t="inlineStr"/>
-      <c r="M292" t="inlineStr"/>
       <c r="N292" t="inlineStr"/>
       <c r="P292" t="inlineStr">
         <is>
@@ -32944,10 +32949,10 @@
         </is>
       </c>
       <c r="Q292" t="n">
-        <v>686354</v>
+        <v>686314</v>
       </c>
       <c r="R292" t="n">
-        <v>6562881</v>
+        <v>6562873</v>
       </c>
       <c r="S292" t="n">
         <v>10</v>
@@ -32974,17 +32979,12 @@
       </c>
       <c r="Y292" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="AA292" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="AC292" t="inlineStr">
-        <is>
-          <t>Ruggad stjärtpenna, 33.5 cm.</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="AD292" t="b">
@@ -32993,6 +32993,7 @@
       <c r="AE292" t="b">
         <v>0</v>
       </c>
+      <c r="AF292" t="inlineStr"/>
       <c r="AG292" t="b">
         <v>0</v>
       </c>
@@ -33010,41 +33011,45 @@
       <c r="AY292" t="inlineStr"/>
       <c r="AZ292" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136947774</t>
+          <t>https://artportalen.se/Sighting/137090662</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>137478542</v>
+        <v>136947774</v>
       </c>
       <c r="B293" t="n">
-        <v>58196</v>
+        <v>57221</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E293" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I293" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K293" t="inlineStr"/>
       <c r="L293" t="inlineStr"/>
       <c r="M293" t="inlineStr"/>
@@ -33055,10 +33060,10 @@
         </is>
       </c>
       <c r="Q293" t="n">
-        <v>686626</v>
+        <v>686354</v>
       </c>
       <c r="R293" t="n">
-        <v>6562878</v>
+        <v>6562881</v>
       </c>
       <c r="S293" t="n">
         <v>10</v>
@@ -33085,12 +33090,17 @@
       </c>
       <c r="Y293" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AA293" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AC293" t="inlineStr">
+        <is>
+          <t>Ruggad stjärtpenna, 33.5 cm.</t>
         </is>
       </c>
       <c r="AD293" t="b">
@@ -33116,63 +33126,58 @@
       <c r="AY293" t="inlineStr"/>
       <c r="AZ293" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137478542</t>
+          <t>https://artportalen.se/Sighting/136947774</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>122929535</v>
+        <v>137478542</v>
       </c>
       <c r="B294" t="n">
-        <v>8455</v>
+        <v>58196</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E294" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I294" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J294" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr"/>
       <c r="K294" t="inlineStr"/>
       <c r="L294" t="inlineStr"/>
       <c r="M294" t="inlineStr"/>
       <c r="N294" t="inlineStr"/>
       <c r="P294" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q294" t="n">
-        <v>686612</v>
+        <v>686626</v>
       </c>
       <c r="R294" t="n">
-        <v>6562882</v>
+        <v>6562878</v>
       </c>
       <c r="S294" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T294" t="inlineStr">
         <is>
@@ -33196,22 +33201,12 @@
       </c>
       <c r="Y294" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="Z294" t="inlineStr">
-        <is>
-          <t>11:01</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="AA294" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="AB294" t="inlineStr">
-        <is>
-          <t>11:01</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="AD294" t="b">
@@ -33226,27 +33221,27 @@
       <c r="AT294" t="inlineStr"/>
       <c r="AW294" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX294" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY294" t="inlineStr"/>
       <c r="AZ294" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122929535</t>
+          <t>https://artportalen.se/Sighting/137478542</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>122928987</v>
+        <v>122929535</v>
       </c>
       <c r="B295" t="n">
-        <v>97983</v>
+        <v>8455</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -33254,27 +33249,32 @@
         </is>
       </c>
       <c r="E295" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I295" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J295" t="inlineStr"/>
       <c r="K295" t="inlineStr"/>
       <c r="L295" t="inlineStr"/>
+      <c r="M295" t="inlineStr"/>
       <c r="N295" t="inlineStr"/>
       <c r="P295" t="inlineStr">
         <is>
@@ -33282,13 +33282,13 @@
         </is>
       </c>
       <c r="Q295" t="n">
-        <v>686389</v>
+        <v>686612</v>
       </c>
       <c r="R295" t="n">
-        <v>6562967</v>
+        <v>6562882</v>
       </c>
       <c r="S295" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T295" t="inlineStr">
         <is>
@@ -33317,7 +33317,7 @@
       </c>
       <c r="Z295" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA295" t="inlineStr">
@@ -33327,7 +33327,7 @@
       </c>
       <c r="AB295" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD295" t="b">
@@ -33353,51 +33353,55 @@
       <c r="AY295" t="inlineStr"/>
       <c r="AZ295" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122928987</t>
+          <t>https://artportalen.se/Sighting/122929535</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>126061106</v>
+        <v>122928987</v>
       </c>
       <c r="B296" t="n">
-        <v>91333</v>
+        <v>97983</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E296" t="n">
-        <v>2008</v>
+        <v>221945</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>Pers., nom.sanct.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I296" t="inlineStr"/>
+      <c r="J296" t="inlineStr"/>
+      <c r="K296" t="inlineStr"/>
+      <c r="L296" t="inlineStr"/>
+      <c r="N296" t="inlineStr"/>
       <c r="P296" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q296" t="n">
-        <v>686883</v>
+        <v>686389</v>
       </c>
       <c r="R296" t="n">
-        <v>6562742</v>
+        <v>6562967</v>
       </c>
       <c r="S296" t="n">
         <v>10</v>
@@ -33424,22 +33428,22 @@
       </c>
       <c r="Y296" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="Z296" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA296" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="AB296" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD296" t="b">
@@ -33454,49 +33458,49 @@
       <c r="AT296" t="inlineStr"/>
       <c r="AW296" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX296" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY296" t="inlineStr"/>
       <c r="AZ296" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061106</t>
+          <t>https://artportalen.se/Sighting/122928987</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>126061107</v>
+        <v>126061106</v>
       </c>
       <c r="B297" t="n">
-        <v>96458</v>
+        <v>91333</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E297" t="n">
-        <v>2818</v>
+        <v>2008</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Pers., nom.sanct.</t>
         </is>
       </c>
       <c r="I297" t="inlineStr"/>
@@ -33506,10 +33510,10 @@
         </is>
       </c>
       <c r="Q297" t="n">
-        <v>686880</v>
+        <v>686883</v>
       </c>
       <c r="R297" t="n">
-        <v>6562745</v>
+        <v>6562742</v>
       </c>
       <c r="S297" t="n">
         <v>10</v>
@@ -33541,7 +33545,7 @@
       </c>
       <c r="Z297" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA297" t="inlineStr">
@@ -33551,7 +33555,7 @@
       </c>
       <c r="AB297" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD297" t="b">
@@ -33577,16 +33581,16 @@
       <c r="AY297" t="inlineStr"/>
       <c r="AZ297" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061107</t>
+          <t>https://artportalen.se/Sighting/126061106</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>129215187</v>
+        <v>126061107</v>
       </c>
       <c r="B298" t="n">
-        <v>91872</v>
+        <v>96458</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -33594,37 +33598,34 @@
         </is>
       </c>
       <c r="E298" t="n">
-        <v>5447</v>
+        <v>2818</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I298" t="inlineStr"/>
-      <c r="J298" t="inlineStr"/>
-      <c r="K298" t="inlineStr"/>
-      <c r="N298" t="inlineStr"/>
       <c r="P298" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q298" t="n">
-        <v>686977</v>
+        <v>686880</v>
       </c>
       <c r="R298" t="n">
-        <v>6562706</v>
+        <v>6562745</v>
       </c>
       <c r="S298" t="n">
         <v>10</v>
@@ -33651,12 +33652,22 @@
       </c>
       <c r="Y298" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z298" t="inlineStr">
+        <is>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA298" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB298" t="inlineStr">
+        <is>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD298" t="b">
@@ -33665,34 +33676,33 @@
       <c r="AE298" t="b">
         <v>0</v>
       </c>
-      <c r="AF298" t="inlineStr"/>
       <c r="AG298" t="b">
         <v>0</v>
       </c>
       <c r="AT298" t="inlineStr"/>
       <c r="AW298" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX298" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY298" t="inlineStr"/>
       <c r="AZ298" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215187</t>
+          <t>https://artportalen.se/Sighting/126061107</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>126061104</v>
+        <v>129215187</v>
       </c>
       <c r="B299" t="n">
-        <v>4775</v>
+        <v>91872</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -33700,34 +33710,37 @@
         </is>
       </c>
       <c r="E299" t="n">
-        <v>100299</v>
+        <v>5447</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I299" t="inlineStr"/>
+      <c r="J299" t="inlineStr"/>
+      <c r="K299" t="inlineStr"/>
+      <c r="N299" t="inlineStr"/>
       <c r="P299" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q299" t="n">
-        <v>686868</v>
+        <v>686977</v>
       </c>
       <c r="R299" t="n">
-        <v>6562739</v>
+        <v>6562706</v>
       </c>
       <c r="S299" t="n">
         <v>10</v>
@@ -33754,22 +33767,12 @@
       </c>
       <c r="Y299" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z299" t="inlineStr">
-        <is>
-          <t>13:41</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AA299" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB299" t="inlineStr">
-        <is>
-          <t>13:41</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AD299" t="b">
@@ -33778,53 +33781,34 @@
       <c r="AE299" t="b">
         <v>0</v>
       </c>
+      <c r="AF299" t="inlineStr"/>
       <c r="AG299" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ299" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK299" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL299" t="inlineStr">
-        <is>
-          <t>Stående död gran.</t>
-        </is>
-      </c>
-      <c r="AO299" t="inlineStr">
-        <is>
-          <t>Picea abies # Stående död gran.</t>
-        </is>
       </c>
       <c r="AT299" t="inlineStr"/>
       <c r="AW299" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX299" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY299" t="inlineStr"/>
       <c r="AZ299" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061104</t>
+          <t>https://artportalen.se/Sighting/129215187</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>126061116</v>
+        <v>126061104</v>
       </c>
       <c r="B300" t="n">
-        <v>44177</v>
+        <v>4775</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -33832,21 +33816,21 @@
         </is>
       </c>
       <c r="E300" t="n">
-        <v>101735</v>
+        <v>100299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I300" t="inlineStr"/>
@@ -33856,10 +33840,10 @@
         </is>
       </c>
       <c r="Q300" t="n">
-        <v>686928</v>
+        <v>686868</v>
       </c>
       <c r="R300" t="n">
-        <v>6562716</v>
+        <v>6562739</v>
       </c>
       <c r="S300" t="n">
         <v>10</v>
@@ -33891,7 +33875,7 @@
       </c>
       <c r="Z300" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA300" t="inlineStr">
@@ -33901,7 +33885,7 @@
       </c>
       <c r="AB300" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD300" t="b">
@@ -33915,22 +33899,22 @@
       </c>
       <c r="AJ300" t="inlineStr">
         <is>
-          <t>fnöskticka</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK300" t="inlineStr">
         <is>
-          <t>Fomes fomentarius</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL300" t="inlineStr">
         <is>
-          <t>Fnöskticka på björk.</t>
+          <t>Stående död gran.</t>
         </is>
       </c>
       <c r="AO300" t="inlineStr">
         <is>
-          <t>Fomes fomentarius # Fnöskticka på björk.</t>
+          <t>Picea abies # Stående död gran.</t>
         </is>
       </c>
       <c r="AT300" t="inlineStr"/>
@@ -33947,16 +33931,16 @@
       <c r="AY300" t="inlineStr"/>
       <c r="AZ300" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061116</t>
+          <t>https://artportalen.se/Sighting/126061104</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>125974903</v>
+        <v>126061116</v>
       </c>
       <c r="B301" t="n">
-        <v>8444</v>
+        <v>44177</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -33964,50 +33948,37 @@
         </is>
       </c>
       <c r="E301" t="n">
-        <v>106554</v>
+        <v>101735</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I301" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J301" t="inlineStr"/>
-      <c r="K301" t="inlineStr"/>
-      <c r="L301" t="inlineStr"/>
-      <c r="M301" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N301" t="inlineStr"/>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr"/>
       <c r="P301" t="inlineStr">
         <is>
-          <t>söder om Tyresta, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>686838</v>
+        <v>686928</v>
       </c>
       <c r="R301" t="n">
-        <v>6562733</v>
+        <v>6562716</v>
       </c>
       <c r="S301" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T301" t="inlineStr">
         <is>
@@ -34034,14 +34005,19 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="Z301" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA301" t="inlineStr">
         <is>
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC301" t="inlineStr">
-        <is>
-          <t>gammal björklåga med spår längs hela stammen</t>
+      <c r="AB301" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD301" t="b">
@@ -34050,51 +34026,50 @@
       <c r="AE301" t="b">
         <v>0</v>
       </c>
-      <c r="AF301" t="inlineStr"/>
       <c r="AG301" t="b">
         <v>0</v>
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>vårtbjörk</t>
+          <t>fnöskticka</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
         <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
-      <c r="AM301" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
+          <t>Fomes fomentarius</t>
+        </is>
+      </c>
+      <c r="AL301" t="inlineStr">
+        <is>
+          <t>Fnöskticka på björk.</t>
         </is>
       </c>
       <c r="AO301" t="inlineStr">
         <is>
-          <t>Wood surface of dead wood # Betula pendula</t>
+          <t>Fomes fomentarius # Fnöskticka på björk.</t>
         </is>
       </c>
       <c r="AT301" t="inlineStr"/>
       <c r="AW301" t="inlineStr">
         <is>
-          <t>Nette Bygren</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX301" t="inlineStr">
         <is>
-          <t>Nette Bygren</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY301" t="inlineStr"/>
       <c r="AZ301" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125974903</t>
+          <t>https://artportalen.se/Sighting/126061116</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>126061105</v>
+        <v>125974903</v>
       </c>
       <c r="B302" t="n">
         <v>8444</v>
@@ -34122,20 +34097,33 @@
           <t>Janson, 1856</t>
         </is>
       </c>
-      <c r="I302" t="inlineStr"/>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr"/>
+      <c r="K302" t="inlineStr"/>
+      <c r="L302" t="inlineStr"/>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N302" t="inlineStr"/>
       <c r="P302" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>söder om Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q302" t="n">
-        <v>686860</v>
+        <v>686838</v>
       </c>
       <c r="R302" t="n">
-        <v>6562743</v>
+        <v>6562733</v>
       </c>
       <c r="S302" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T302" t="inlineStr">
         <is>
@@ -34162,19 +34150,14 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z302" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA302" t="inlineStr">
         <is>
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AB302" t="inlineStr">
-        <is>
-          <t>13:36</t>
+      <c r="AC302" t="inlineStr">
+        <is>
+          <t>gammal björklåga med spår längs hela stammen</t>
         </is>
       </c>
       <c r="AD302" t="b">
@@ -34183,48 +34166,54 @@
       <c r="AE302" t="b">
         <v>0</v>
       </c>
+      <c r="AF302" t="inlineStr"/>
       <c r="AG302" t="b">
         <v>0</v>
       </c>
       <c r="AJ302" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>vårtbjörk</t>
         </is>
       </c>
       <c r="AK302" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AM302" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO302" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Wood surface of dead wood # Betula pendula</t>
         </is>
       </c>
       <c r="AT302" t="inlineStr"/>
       <c r="AW302" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Nette Bygren</t>
         </is>
       </c>
       <c r="AX302" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Nette Bygren</t>
         </is>
       </c>
       <c r="AY302" t="inlineStr"/>
       <c r="AZ302" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061105</t>
+          <t>https://artportalen.se/Sighting/125974903</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>137045669</v>
+        <v>126061105</v>
       </c>
       <c r="B303" t="n">
-        <v>98299</v>
+        <v>8444</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -34232,38 +34221,34 @@
         </is>
       </c>
       <c r="E303" t="n">
-        <v>221946</v>
+        <v>106554</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I303" t="inlineStr"/>
-      <c r="J303" t="inlineStr"/>
-      <c r="K303" t="inlineStr"/>
-      <c r="L303" t="inlineStr"/>
-      <c r="N303" t="inlineStr"/>
       <c r="P303" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q303" t="n">
-        <v>686837</v>
+        <v>686860</v>
       </c>
       <c r="R303" t="n">
-        <v>6562677</v>
+        <v>6562743</v>
       </c>
       <c r="S303" t="n">
         <v>10</v>
@@ -34290,12 +34275,22 @@
       </c>
       <c r="Y303" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z303" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA303" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB303" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD303" t="b">
@@ -34304,23 +34299,144 @@
       <c r="AE303" t="b">
         <v>0</v>
       </c>
-      <c r="AF303" t="inlineStr"/>
       <c r="AG303" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ303" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK303" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO303" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT303" t="inlineStr"/>
       <c r="AW303" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX303" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY303" t="inlineStr"/>
       <c r="AZ303" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061105</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>137045669</v>
+      </c>
+      <c r="B304" t="n">
+        <v>98299</v>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E304" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr"/>
+      <c r="J304" t="inlineStr"/>
+      <c r="K304" t="inlineStr"/>
+      <c r="L304" t="inlineStr"/>
+      <c r="N304" t="inlineStr"/>
+      <c r="P304" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q304" t="n">
+        <v>686837</v>
+      </c>
+      <c r="R304" t="n">
+        <v>6562677</v>
+      </c>
+      <c r="S304" t="n">
+        <v>10</v>
+      </c>
+      <c r="T304" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U304" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V304" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W304" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y304" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AA304" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AD304" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE304" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF304" t="inlineStr"/>
+      <c r="AG304" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT304" t="inlineStr"/>
+      <c r="AW304" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX304" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY304" t="inlineStr"/>
+      <c r="AZ304" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137045669</t>
         </is>
@@ -34630,6 +34746,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ301" r:id="rId300"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ302" r:id="rId301"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ303" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ304" r:id="rId303"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 152-2026 artfynd.xlsx
+++ b/artfynd/S 152-2026 artfynd.xlsx
@@ -2663,7 +2663,7 @@
         <v>137045898</v>
       </c>
       <c r="B20" t="n">
-        <v>93501</v>
+        <v>93505</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>137045947</v>
       </c>
       <c r="B80" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>137143672</v>
       </c>
       <c r="B81" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>137144281</v>
       </c>
       <c r="B82" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         <v>137220342</v>
       </c>
       <c r="B83" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10095,7 +10095,7 @@
         <v>137106176</v>
       </c>
       <c r="B88" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10205,7 +10205,7 @@
         <v>137143649</v>
       </c>
       <c r="B89" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -14484,7 +14484,7 @@
         <v>137089136</v>
       </c>
       <c r="B127" t="n">
-        <v>98302</v>
+        <v>98306</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -16162,7 +16162,7 @@
         <v>137045897</v>
       </c>
       <c r="B142" t="n">
-        <v>92576</v>
+        <v>92580</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16268,7 +16268,7 @@
         <v>128952262</v>
       </c>
       <c r="B143" t="n">
-        <v>93506</v>
+        <v>93510</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         <v>137088961</v>
       </c>
       <c r="B188" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>137089019</v>
       </c>
       <c r="B189" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -21377,7 +21377,7 @@
         <v>137090631</v>
       </c>
       <c r="B190" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -21483,7 +21483,7 @@
         <v>137090646</v>
       </c>
       <c r="B191" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -23316,7 +23316,7 @@
         <v>136972809</v>
       </c>
       <c r="B207" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24448,7 +24448,7 @@
         <v>136947615</v>
       </c>
       <c r="B217" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -29619,7 +29619,7 @@
         <v>137143298</v>
       </c>
       <c r="B263" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -29725,7 +29725,7 @@
         <v>137143509</v>
       </c>
       <c r="B264" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -29831,7 +29831,7 @@
         <v>137143542</v>
       </c>
       <c r="B265" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -32223,7 +32223,7 @@
         <v>137477223</v>
       </c>
       <c r="B286" t="n">
-        <v>96865</v>
+        <v>96869</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -32339,7 +32339,7 @@
         <v>137478093</v>
       </c>
       <c r="B287" t="n">
-        <v>96865</v>
+        <v>96869</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -32455,7 +32455,7 @@
         <v>137478379</v>
       </c>
       <c r="B288" t="n">
-        <v>96865</v>
+        <v>96869</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -32571,7 +32571,7 @@
         <v>137478534</v>
       </c>
       <c r="B289" t="n">
-        <v>96865</v>
+        <v>96869</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -32687,7 +32687,7 @@
         <v>137478552</v>
       </c>
       <c r="B290" t="n">
-        <v>96865</v>
+        <v>96869</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -32914,7 +32914,7 @@
         <v>137090662</v>
       </c>
       <c r="B292" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -33020,7 +33020,7 @@
         <v>136947774</v>
       </c>
       <c r="B293" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -33135,7 +33135,7 @@
         <v>137478542</v>
       </c>
       <c r="B294" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -34340,7 +34340,7 @@
         <v>137045669</v>
       </c>
       <c r="B304" t="n">
-        <v>98299</v>
+        <v>98303</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
